--- a/Output/Eknath Shinde/extracted_links_Eknath Shinde_failed_links.xlsx
+++ b/Output/Eknath Shinde/extracted_links_Eknath Shinde_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A454"/>
+  <dimension ref="A1:A498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,3171 +438,3479 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/eknath-shinde-speaks-to-stranded-maharashtra-tourists-in-nepal-assures-help-for-safe-return-23593455</t>
+          <t>https://www.ptinews.com/story/national/shiv-sena-protests-against-sanjay-raut-of-sena-ubt-for-%E2%80%98insulting%E2%80%99-eknath-shinde%E2%80%99s-mentor/2934437</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/govt-won-t-do-injustice-to-marathas-over-quota-but-won-t-let-down-other-communities-either-shinde/ar-AA1LtI68</t>
+          <t>https://www.indiatvnews.com/maharashtra/eknath-shinde-maharashtra-deputy-cm-x-account-hacked-hackers-post-pakistan-turkey-flags-hacking-sparks-uproar-2025-09-21-1009219</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/decision-to-relocate-dahisar-toll-booth-by-2-km-finalised-by-dy-cm-eknath-shinde/articleshow/123791057.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/when-i-go-to-villages-i-feel-fresh-my-opponents-get-depressed-says-dy-cm-eknath-shinde-at-launch-of-gram-samruddhi-yojana/articleshow/123964878.cms</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.news18.com/videos/breaking-news/nepal-protests-news-eknath-shinde-talks-to-over-300-maharashtra-tourists-stuck-in-nepal-news18-9564261.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ahead-of-bmc-elections-eknath-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena-23594416</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/videos/times-now/india/rahul-gandhi-skips-vice-president-oath-bjp-and-eknath-shinde-call-it-anti-democracy-english-news-video-152787678</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-dy-cm-eknath-shinde-meets-with-newly-elected-vice-president-cp-radhakrishnan20250912162242/</t>
+          <t>https://www.tribuneindia.com/news/india/maharashtra-deputy-cm-eknath-shindes-x-account-hacked/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vp-election-mp-shrikant-shinde-named-ndas-authorised-representative-says-shiv-sena-3717960</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-dy-cm-eknath-shindes-x-account-hacked/2934860</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/other/shinde-loses-shine/ar-AA1GdsEp?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/maharashtra-deputy-cm-eknath-shinde-takes-action-against-builders-of-65-illegal-buildings-in-kalyan-dombivli/articleshow/124011193.cms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbais-elphinstone-bridge-to-shut-for-demolition-as-dcm-eknath-shinde-approves-in-situ-rehab-for-83-affected-local-residents/articleshow/123835022.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/gr-row-eknath-shinde-assures-obcs-won-t-suffer-loss-over-maratha-quota/ar-AA1M7R61</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-images-of-pakistan-turkey-flags-posted/articleshow/124024337.cms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/rahul-gandhi-skips-vice-president-oath-bjp-and-eknath-shinde-call-it-anti-democracy-english-news/vi-AA1Mpu03?ocid=hpmsn</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-dy-cm-eknath-shindes-x-account-hacked-9315607/amp/1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-eknath-shinde-speaks-to-tourists-from-maharashtra-stuck-in-nepal-amid-unrest-107305</t>
+          <t>https://www.tribuneindia.com/news/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/in-shindes-presence-former-sc-judge-oka-slams-deterioration-of-living-conditions-in-thane/ar-AA1KdHgt?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.hindustantimes.com/india-news/paint-thrown-at-bust-of-uddhav-thackerays-late-mother-sena-workers-angry-probe-on-101758106562970.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/how-can-blood-cricket-flow-together-uddhav-thackeray-opposes-india-pak-match-slams-pm-narendra-modi-govt/ar-AA1MuVCW</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/gst-rate-cut-will-boost-economy-shield-india-from-us-tariff-hikes-says-maharashtras-deputy-chief-minister-eknath-shinde/articleshow/124002613.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mumbai-s-elphinstone-bridge-shuts-today-eknath-shinde-okays-paps-in-situ-rehab/ar-AA1MorfV</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633937-crackdown-on-unauthorized-buildings-in-thane-eknath-shinde-leads-investigation?amp</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/eknath-shinde-unlikely-to-get-home-ministry-ajit-pawar-to-take-finance-ministry-big-scoop-on-maharashtra-cabinet-portfolios/ar-AA1vmwGF?ocid=BingNewsVerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.devdiscourse.com/article/politics/3630294-eknath-shinde-criticizes-congress-amid-controversy-over-ai-video</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-ubt-gets-shivaji-park-for-dussehra-rally/articleshow/123811882.cms</t>
+          <t>https://www.msn.com/en-in/health/health-news/maharashtra-govt-formation-bjp-cm-s-name-still-under-wraps-all-eyes-on-unwell-shinde-s-big-decision/ar-AA1v3aC9?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/defection-of-7-ex-mayors-from-ubt-strengthens-sena-in-sambhajinagar/articleshow/123793431.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/most-uddhav-sena-mlas-mps-in-touch-with-shinde-camp-claims-tumane/articleshow/123793545.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-gifts-modi-394-namo-udyans-101758050819661.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/photo/in-photos-maharashtra-deputy-cm-eknath-shinde-addresses-shiv-sena-mlas-in-chhatrapati-sambhajinagar-107258/2</t>
+          <t>https://www.ndtvprofit.com/amp/nation/thane-metro-4a-trial-run-on-monday-check-station-list-and-other-key-details</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/no-injustice-to-anybody-weve-only-simplified-the-process-of-issuing-kunbi-certificates-dcm-shinde/articleshow/123772724.cms</t>
+          <t>https://www.ptinews.com/detail/states/Ahead-of-BMC-polls-Shinde-asks-ex-corporators-to-tell-people-about-work-done-by-Shiv-Sena/2921488</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-shiv-sena-leader-seeks-carter-road-be-named-after-rajesh-khanna-23593222</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/find-the-masterminds-behind-the-kdmc-illegal-buildings-scam-shinde-101758309996962.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/shrikant-shinde-appointed-ndas-authorised-representative-for-vice-presidential-poll-23593020</t>
+          <t>https://aninews.in/news/national/politics/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother20250916212035/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-eknath-shinde-approves-relocation-of-dahisar-toll-naka-to-be-shifted-2-km-ahead-before-diwali-23593159</t>
+          <t>https://zeenews.india.com/india/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked-hackers-post-pakistan-turkey-flags-2962608.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/en/politics/maharashtra-politics-shinde-sena-announces-21-member-panel-as-preparations-intensify-for-bmc-elections-89940</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-charges-baseless-says-ekanth-shinde-23594783</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/uddhav-thackeray-lacks-moral-right-to-oppose-india-pak-match-shiv-sena/articleshow/123869366.cms</t>
+          <t>https://www.ptinews.com/editor-detail/Dy-CM-Shinde-s-X-account-hacked;-Cong-leader-questions-cyber-security/2935531</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shiv-sena-sets-up-21-member-panel-under-shinde-for-bmc-elections/2903156</t>
+          <t>https://www.aninews.in/news/national/general-news/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi20250917174418?amp=1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/dahisar-toll-naka-to-be-shifted-relief-for-mirabhayandar-101757444943587.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bombay-hc-can-plea-against-shinde-order-be-a-pil/articleshow/124022877.cms</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Uddhav-lacks-moral-right-to-oppose-India-Pak-match-Shiv-Sena/2911625</t>
+          <t>https://kashmirlife.net/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-406229/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Shiv-Sena-sets-up-21-member-panel-under-Shinde-for-BMC-elections/2903156</t>
+          <t>https://www.hindustantimes.com/india-news/maharashtra-dy-cm-eknath-shindes-x-account-hacked-pakistan-turkey-flags-posted-101758428709090-amp.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/hc-rejects-sena-ubt-leaders-poll-plea-against-victory-of-rival-faction-mp-in-2024-ls-polls/2898806</t>
+          <t>https://www.newsband.in/article_detail/awhad-slams-the-states-selective-compassion-over-demolition-notices</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Vision-Document-2047-will-be-guiding-framework-for-key-policies-Fadnavis/2895888</t>
+          <t>https://www.indiatvnews.com/video/news/pm-modi-adopts-nation-first-policy-eknath-shinde-slams-congress-over-remarks-on-pm-s-mother-2025-09-17-1008597</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-acharya-devvrat-to-be-sworn-in-as-maharashtra-governor-on-monday-23593997</t>
+          <t>https://www.ptinews.com/story/national/women-office-bearers-workers-of-sena-ubt-from-palghar-join-shinde-led-sena-ahead-of-local-polls/2927880</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/637267.html</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/most-of-rs-46000cr-projects-for-marathwada-announced-by-shinde-led-cabinet-in-2023-still-on-paper/articleshow/123907066.cms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/shiv-sena-forms-21-member-panel-headed-by-maharashtra-deputy-cm-shinde-for-bmc-poll-strategy-23593356</t>
+          <t>https://realty.economictimes.indiatimes.com/news/industry/strict-action-ordered-against-65-illegal-buildings-in-kalyan-dombivli-by-deputy-chief-minister-eknath-shinde/124008652</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/news/west/politics-mah-shinde-radhakrishnan/3572001.html</t>
+          <t>https://www.ptinews.com/story/national/bjp-gave-up-claim-for-mumbai-mayor-s-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/2921301</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/gr-row-no-new-decision-was-taken-on-maratha-quota-obcs-won-t-suffer-any-loss-says-shinde/2896558</t>
+          <t>https://www.msn.com/en-in/news/India/shiv-sena-workers-protest-in-thane-over-sanjay-raut-s-remarks-on-anand-dighe/ar-AA1MOXSd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/gujarat-governor-devvrat-now-holds-maharashtra-post-temporarily-23593972</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-23595086?button=next</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-elphinstone-bridge-to-finally-be-shut-from-midnight-today-23593601</t>
+          <t>https://www.ptinews.com/detail/national/Shiv-Sena-publishes-full-page-ads-in-dailies-on-PM-s-birthday-Shinde-hails-his-New-India-push/2923561</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/entertainment/bollywood/atul-parchure-death-maharashtra-cm-eknath-shinde-says-his-loss-not-recoverable/ar-AA1sfNuN?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/india/not-an-mla-but-get-rs-20-cr-in-funds-sena-leader-sarvankar-boasts-later-clarifies/articleshow/124028510.cms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6601532</t>
+          <t>https://www.ptinews.com/story/national/ncp-sp-cong-welcome-sc-order-on-maharashtra-local-bodies-polls-mahayuti-will-win-says-shinde/2920944</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6612911</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3633705-infrastructure-revamp-a-new-dawn-for-navi-mumbais-villages</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/maharashtra-deputy-cm-eknath-shinde-hails-radhakrishnans-election-as-vp-calls-it-a-matter-of-pride/</t>
+          <t>https://www.ptinews.com/story/national/pms-birthday-a-black-day-for-democracy-says-congress-mp-praniti-shinde-bjp-hits-back/2920762</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/14/mumbai-cm-fadnavis-welcomes-maharashtra-governor-gallery/</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3630397-maharashtra-launches-namo-parks-to-celebrate-modis-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/high-court/plea-shiv-sena-shinde-mp-naresh-election/</t>
+          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/cong-urges-maharashtra-council-chairman-to-take-swift-decision-on-vacant-lop-post-10060663</t>
+          <t>https://www.ptinews.com/story/national/take-action-against-those-involved-in-constructing-65-illegal-buildings-in-kalyan-dombivali-shinde/2931430</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/dcm-shinde-calls-stranded-maharashtrian-tourists-assures-hundred-plus-visitors-over-phone-working-with-indian-embassy-135893014.html</t>
+          <t>https://www.ptinews.com/detail/national/On-eve-of-PM-s-birthday-Shinde-announces-scheme-to-develop-Namo-Parks-in-Maharashtra/2921302</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6622494</t>
+          <t>https://www.ptinews.com/editor-detail/prioritise-development-in-14-villages-added-to-navi-mumbai-civic-limits--dy-cm-shinde/2930925</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-govt-transfers-%E2%82%B91892-crore-to-over-91-lakh-farmers-under-namo-shetkari-scheme/</t>
+          <t>https://www.aninews.in/news/national/general-news/mmrda-temporarily-suspends-monorail-services-in-mumbai20250920092952</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/gr-row-no-new-decision-was-taken-on-maratha-quota-obcs-wont-suffer-any-loss-says-shinde-10061663</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-shiv-sena-leaders-speech-adds-fuel-to-accusations-of-biased-allocation-of-funds-23595109?covid-19-breakingnews</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-shiv-sena-ministers-important-meeting-in-dada-bhuse-janjira-bungalow-near-mantralaya-bmc-election-2025/articleshow/123885610.cms</t>
+          <t>https://www.lokmattimes.com/maharashtra/maharashtra-dy-cm-eknath-shindes-x-account-hacked-amid-india-pakistan-asia-cup-pakistani-and-turkish-flags-posted-a525/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/other-cities/dcm-eknath-shinde-is-upset/</t>
+          <t>https://www.newsx.com/india/eknath-shinde-account-hacked-during-india-pakistan-asia-cup-cybercrime-cybersecurity-national-flags-of-turkey-and-pakistan-restored-in-45-minutes-75975/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-how-mva-mps-did-cross-voting-in-vice-president-election-devendra-fadnavis-eknath-shinde-played-big-role-9604766.html</t>
+          <t>https://www.newsdrum.in/national/ahead-of-bmc-polls-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena-10471368</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/mumbai-municipal-corporation-elections-21-member-committee-headed-eknath-shinde-see-who-is-included-in-the-list-b507/</t>
+          <t>https://www.socialnews.xyz/2025/09/15/mumbai-acharya-devvrat-sworn-in-as-maharashtra-governor-gallery/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-bmc-election-15-ex-counsellors-likely-to-return-in-uddhav-thackeray-fraction-from-eknath-shinde-shiv-sena-as-ghar-wapsi/articleshow/123880813.cms</t>
+          <t>https://www.bhaskarenglish.in/national/news/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-pakistan-flag-135976151.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/sanjay-raut-statement-anti-national-eknath-shinde-shiv-sena-ex-mp-sanjay-nirupam-filed-police-complaint/articleshow/123833024.cms</t>
+          <t>https://thehindustangazette.com/election/eknath-shinde-x-account-hacked-pak-turkey-flags-39959</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-reshuffles-shiv-sena-for-bmc-elections-appoints-separate-chief-for-each-assembly-constituency/articleshow/123791339.cms</t>
+          <t>https://x.com/i/broadcasts/1dRKZavRjoVxB</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/maharashtra/nagpur/eknath-shinde-mla-krupal-tumane-claim-uddhav-thackeray-leaders-may-quit-shiv-sena-before-maharashtra-nikay-chunav/articleshow/123779263.cms</t>
+          <t>https://thecsrjournal.in/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hindi/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%A0-%E0%A4%A3%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%B8%E0%A4%A6-%E0%A4%95-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%B0%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%B9-%E0%A4%AC%E0%A4%82%E0%A4%AC%E0%A4%88-hc-%E0%A4%A8%E0%A5%87-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%97-%E0%A4%AA%E0%A4%B0-%E0%A4%B8%E0%A5%81%E0%A4%A8-%E0%A4%AF-%E0%A4%AF%E0%A4%B9-%E0%A4%AB%E0%A5%88%E0%A4%B8%E0%A4%B2/ar-AA1MeANM</t>
+          <t>https://www.indiatv.in/maharashtra/sanjay-raut-said-eknath-shinde-mentality-is-very-low-level-there-is-nothing-left-to-talk-about-2025-09-20-1163910</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8-%E0%A4%AF-%E0%A4%B8-%E0%A4%B9%E0%A4%B2%E0%A4%9A%E0%A4%B2-%E0%A4%A1-%E0%A4%AA%E0%A5%8D%E0%A4%9F-cm-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A5%81%E0%A4%88-%E0%A4%AC-%E0%A4%A4/ar-AA1CYrvY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flags-9649355.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%A8%E0%A5%87-bjp-%E0%A4%95%E0%A5%87-%E0%A4%A6%E0%A5%81%E0%A4%B6%E0%A5%8D%E0%A4%AE%E0%A4%A8-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF-%E0%A4%B9-%E0%A4%A5-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%97-%E0%A4%A4%E0%A4%A8-%E0%A4%B5/ar-AA1M5VN9</t>
+          <t>https://www.msn.com/hi-in/news/other/eknath-shinde-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B2%E0%A4%AF-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%AE%E0%A4%A8%E0%A5%87-%E0%A4%9C%E0%A4%82%E0%A4%9C-%E0%A4%B0-%E0%A4%AC%E0%A4%82%E0%A4%97%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A4%82%E0%A4%97-%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AE-%E0%A4%9C%E0%A5%82%E0%A4%A6-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%95%E0%A5%81%E0%A4%9B-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%B9-%E0%A4%B0%E0%A4%B9-%E0%A4%B9%E0%A5%88/ar-AA1Mx0NI</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-shiv-sena-dussehra-rally-in-mumbai-shivaji-park-eknath-shinde-fail/articleshow/123819576.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/deputy-cm-eknath-shinde-x-account-hacked-hackers-posted-images-of-pakistan-and-turkey-flags/articleshow/124025137.cms</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/vice-president-election-2025-eknath-shinde-shiv-sena-leader-sanjay-nirupam-claims-uddhav-thackeray-five-mp-done-cross-voting-know-all/articleshow/123810931.cms</t>
+          <t>https://www.facebook.com/DNHindi/photos/%E0%A4%B8%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8%E0%A4%BE%E0%A4%A5-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A4%BE-x-%E0%A4%85%E0%A4%95%E0%A4%BE%E0%A4%89%E0%A4%82%E0%A4%9F-%E0%A4%B9%E0%A5%88%E0%A4%95-%E0%A4%B9%E0%A5%88%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B2%E0%A4%97%E0%A4%BE%E0%A4%88-%E0%A4%AA%E0%A4%BE%E0%A4%95%E0%A4%BF%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A4%BE%E0%A4%A8-%E0%A4%A4%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9D%E0%A4%82%E0%A4%A1%E0%A5%87eknathsi/1251272843711787/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-dahisar-toll-naka-dcm-eknath-shinde-approves-relocation-of-before-diwali-to-versova-bridge-know-all/amp_articleshow/123815025.cms</t>
+          <t>https://x.com/i/broadcasts/1ypKdqyAVPpGW</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.gnttv.com/shows/fact-check/video/did-shahrukh-khan-and-salman-khan-visit-bappa-with-eknath-shinde-see-the-truth-of-the-viral-video-1274564-2025-09-08</t>
+          <t>https://www.indiatv.in/maharashtra/maharashtra-deputy-cm-eknath-shinde-x-handle-hacked-hackers-shared-posts-with-pakistan-and-turkey-flags-2025-09-21-1164034</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/eknath-shinde-%E0%A4%98%E0%A4%A1-%E0%A4%AE-%E0%A4%A1-%E0%A4%82%E0%A4%A8-%E0%A4%B5%E0%A5%87%E0%A4%97-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%A6-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%95-%E0%A4%AF/ar-AA1Mc9Cn?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-on-eknath-shinde-maharashtra-ahmedabad-bullet-train-anand-dighe-3015725</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/no-new-decision-has-been-taken-regarding-maratha-reservation-obcs-will-not-suffer-shinde/865983/</t>
+          <t>https://x.com/i/broadcasts/1gqGvrPmZvgGB</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B9%E0%A4%A3-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%B6-%E0%A4%AE-%E0%A4%B2-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%9C-%E0%A4%AC-%E0%A4%B0-%E0%A4%AC-%E0%A4%B0/ar-AA1MqkPU</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/ganesh-naik-vs-eknath-shinde-in-navi-mumbai-tussle-over-janata-darbar-petition-filed-in-high-court/articleshow/123996455.cms</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-on-eknath-shinde-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%85%E0%A4%B8%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%A5%E0%A5%87%E0%A4%9F-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A%E0%A4%82-%E0%A4%A8-%E0%A4%B5-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2%E0%A4%82/ar-AA1MsMVj</t>
+          <t>https://www.livehindustan.com/national/sanjay-raut-comments-about-eknath-shinde-mentor-anand-dighe-sparked-an-uproar-201758252385682.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-%E0%A4%86%E0%A4%9C%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B6%E0%A4%AA%E0%A4%A5%E0%A4%B5-%E0%A4%A7-%E0%A4%B2-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%86%E0%A4%B2%E0%A5%87-%E0%A4%A8-%E0%A4%B9-%E0%A4%A4-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%95/ar-AA1MoUh3</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%97%E0%A4%A3%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%A5%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%B8%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%AA%E0%A4%B0-%E0%A4%85%E0%A4%9A-%E0%A4%A8%E0%A4%95-%E0%A4%B0-%E0%A4%95-%E0%A4%95-%E0%A4%AB-%E0%A4%B2-%E0%A4%AB-%E0%A4%B0/ar-AA1xTf0a?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%86%E0%A4%A3-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%95-%E0%A4%A3%E0%A4%A4-%E0%A4%B9-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%A8-%E0%A4%B9-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/vi-AA1MtMSJ</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-claims-mahayuti-saffron-flag-will-fly-in-bmc-and-all-maharashtra-local-body-elections/articleshow/124032659.cms</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/explainer-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%86%E0%A4%A3-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A4%E0%A4%A3-%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AD-%E0%A4%88-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%B5-%E0%A4%9A-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%9A-%E0%A4%B2%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%A4%E0%A4%B0-%E0%A4%95-%E0%A4%AF/ar-AA1MsMR7</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B9%E0%A4%A3-%E0%A4%B8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%AC-%E0%A4%97%E0%A4%A1%E0%A4%BC-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A4%AC-%E0%A4%AF%E0%A4%A4-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95%E0%A5%87-%E0%A4%85%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%A4-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD%E0%A4%B0%E0%A5%8D%E0%A4%A4/ar-AA1vb0Jf?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/other-cities/9-votes-including-5-mps-of-shiv-sena-ubatha-were-split/</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AA-%E0%A4%8F%E0%A4%AE-%E0%A4%AE-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%95-%E0%A4%A4-%E0%A4%B9%E0%A4%AB-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AC%E0%A4%A8-%E0%A4%8F-%E0%A4%9C-%E0%A4%8F%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%A8%E0%A4%AE-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%95/ar-AA1MFYqT</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-cm-fadnavis-big-orders-appoint-only-ias-officers-as-commissioners-in-municipal-body-after-mira-bhayandar-vasai-virar-corruption-row/articleshow/123844784.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-uddhav-thackeray-puts-bold-conditions-for-rebels-nagar-sevak-for-ghar-wapsi-for-shinde-shiv-sena-ahead-of-bmc-polls-know-all/articleshow/123978190.cms</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/bmc-election-eknath-shindes-shiv-sena-announced-chief-executive-committee-94009</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%AE-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%9B-%E0%A4%AA-22-%E0%A4%AC-%E0%A4%B0-%E0%A4%9F%E0%A5%87%E0%A4%82%E0%A4%A1%E0%A4%B0-%E0%A4%94%E0%A4%B0-25-%E0%A4%95%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A4%AE%E0%A4%B0-%E0%A4%85%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%8F%E0%A4%AB%E0%A4%86%E0%A4%88%E0%A4%86%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF/ar-AA1IUiYB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%86%E0%A4%A3-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%95-%E0%A4%A3%E0%A4%A4-%E0%A4%B9-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%A8-%E0%A4%B9-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/vi-AA1MtMSJ?ocid=hpmsn</t>
+          <t>https://hindi.webdunia.com/maharashtra/eknath-shinde-x-account-hacked-pakistani-flags-posted-125092100012_1.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178312/</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/as-soon-as-operation-tiger-was-reported-eknath-shinde-action-mode-urgent-meeting-bmc-election-1479960.html</t>
+          <t>https://x.com/i/broadcasts/1YqKDNmQVkNJV</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%85-%E0%A5%85%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%AE-%E0%A4%A1%E0%A4%B5%E0%A4%B0-bmc-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%81%E0%A4%95-%E0%A4%86%E0%A4%A7-%E0%A4%AE-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A4%B0%E0%A4%AA%E0%A5%8D%E0%A4%B2%E0%A5%85%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AD-%E0%A4%B0-%E0%A4%AA%E0%A4%A1%E0%A4%A3-%E0%A4%B0/ar-AA1Mh7og</t>
+          <t>https://www.dainiktribuneonline.com/news/nation/shindes-x-account-hacked-maharashtras-cyber-security-in-question-uproar-over-eknath-shindes-x-account-being-hacked/amp</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!politics/voter-search-app-to-be-used-in-local-elections-dcm-eknath-shinde-informs-workers-at-rally-in-chhatrapati-sambhajinagar-mhs25090806298</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/eknath-shinde-takes-action-against-kalyan-dombivli-illegal-buildings-builders/articleshow/124011899.cms</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/shiv-sena-shinde-faction-announces-committee-of-21-leaders-for-mumbai-municipal-corporation-election-9252001</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B5-%E0%A4%9A%E0%A5%88%E0%A4%AA%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%85%E0%A4%AC-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%97%E0%A4%AF-%E0%A4%B9%E0%A5%88-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%9C-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A4%B0-%E0%A4%B8%E0%A5%81%E0%A4%A8-%E0%A4%B2-%E0%A4%A4%E0%A4%9F%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%90%E0%A4%B8-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%AC-%E0%A4%B2-%E0%A4%97%E0%A4%8F/ar-AA1v8byj?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178001/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A4%B2-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A4%9F-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%82%E0%A4%97-%E0%A4%B0-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%89%E0%A4%A0-%E0%A4%8F-%E0%A4%9C-%E0%A4%8F%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A4%A6%E0%A4%AE/ar-AA1Dro6h?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/topics/eknath-shinde/</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-deputy-cm-eknath-shinde-s-twitter-account-hacked-raises-cybersecurity-concerns-201758454098732.html</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-in-faced-trouble-in-mumbai-bastion-of-uddhav-thackeray-shiv-sena-ubt-1477662.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%A8%E0%A4%96%E0%A4%B0-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%AA-%E0%A4%9B%E0%A5%87-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%95-%E0%A4%AE%E0%A4%B9-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%B8%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A5%87%E0%A4%82%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%89%E0%A4%A4/ar-AA1vbFc0?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/topics/eknath-shinde/page/1415/</t>
+          <t>https://www.amarujala.com/video/india-news/pm-modi-birthday-congress-declares-pm-modi-s-birthday-as-black-day-enraged-eknath-shinde-issues-warning-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/eknath-shinde-and-bjp-mla-kisan-kathore-assures-safe-return-of-stranded-in-nepal/videoshow/123823498.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-namo-park-scheme-for-pm-narendra-modi-75th-birthday-deputy-cm-eknath-shinde-announcement-3014117</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/bjp-outmaneuver-eknath-shinde-and-ajit-pawar-even-before-graduate-constituency-election-announcement-maharashtra-news-mhs25090802195</t>
+          <t>https://www.abplive.com/states/maharashtra/pratap-sarnaik-comments-on-uddhav-thackeray-sanjay-raut-praises-eknath-shinde-respect-senior-leaders-3016095/amp</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/vice-presidential-election-cross-voting-by-india-alliance-mps-who-broke-uddhav-thackeray-faction-shiv-sena-maharashtra-201757568495022.amp.html</t>
+          <t>https://www.aajtak.in/india/maharashtra/video/pm-modi-75th-birthday-piyush-goyal-eknath-shinde-wishes-ytvd-2335022-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ganesh-naik-vs-eknath-shinde-news-%E0%A4%A0-%E0%A4%A3%E0%A5%87%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%A8%E0%A5%87%E0%A4%AA-%E0%A4%B3%E0%A4%9A-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%82%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A4-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%82%E0%A4%98%E0%A4%B0%E0%A5%8D%E0%A4%B7-%E0%A4%9A-%E0%A4%A8-%E0%A4%82%E0%A4%A6/vi-AA1Mi6qH</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-deputy-chief-minister-ekanth-shinde-says-rahul-gandhi-s-vote-theft-charges-baseless-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/politics/eknath-shinde-upset-on-devendra-fadnavis-maharashtra-politics-local-body-elections/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9D%E0%A4%9F%E0%A4%95-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95-%E0%A4%AE%E0%A4%97-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A4%88-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%AE-%E0%A4%B2/ar-AA1wEXx9?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/eknath-shinde-once-again-strongly-criticized-uddhav-thackeray-2-1492401.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6%E0%A4%AA%E0%A4%A5%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6-%E0%A4%96-%E0%A4%B2-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AA%E0%A4%B2%E0%A4%9F%E0%A4%B5-%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%B8%E0%A5%82%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%97%E0%A4%A1%E0%A4%BC%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%95-%E0%A4%A6-%E0%A4%B5-%E0%A4%97%E0%A4%B2%E0%A4%A4/ar-AA1MRMC6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-announced-21-leaders-committee-for-mumbai-mahapalika-election-1477124.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/chartered-officers-in-d-class-municipalities-deputy-chief-minister-eknath-shinde-is-upset-with-this-decision-of-the-chief-minister-devendra-fadnavis/921168/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%AC-%E0%A4%A8%E0%A5%87%E0%A4%9F-%E0%A4%AC%E0%A4%82%E0%A4%9F%E0%A4%B5-%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A5%82%E0%A4%B2-%E0%A4%A4%E0%A4%AF-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95-%E0%A4%95-%E0%A4%A4%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6/ar-AA1vHycG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ekanath-shinde-on-nepal-eknath-shinde-gave-comfort-while-interacting-with-tourists-from-maharashtra-stranded-in-nepal/920332/</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/thane-metro-trial-run-on-september-22-thane-residents-dream-to-come-true/articleshow/124004146.cms</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%A6-%E0%A4%B5-%E0%A4%B3-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%AE-%E0%A4%A0-%E0%A4%AD%E0%A5%82%E0%A4%95%E0%A4%82%E0%A4%AA-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8%E0%A4%B9-%E0%A4%A6%E0%A5%81%E0%A4%9C-%E0%A4%B0/ar-AA1McaIA?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.navodayatimes.in/news/national/maharashtra-deputy-cm-eknath-shinde-ex-handle-hacked/276116/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/relief-for-residents-of-affected-buildings-in-elphinstone-bridge-area-eknath-shinde-big-announcement-9260666</t>
+          <t>https://marathi.ndtv.com/cities/eknath-shinde-treated-australian-guests-to-a-feast-of-vada-pav-9289261</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-news-thane-%E0%A4%AF%E0%A5%87%E0%A4%A5%E0%A5%87-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A4%B5-%E0%A4%B8-%E0%A4%A0-thackeray-bjp-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%9B%E0%A5%81%E0%A4%AA-%E0%A4%AF%E0%A5%81%E0%A4%A4/vi-AA1Mtw78</t>
+          <t>https://www.jansatta.com/jansatta-special/jansatta-rajpaat-abhay-chautala-haryana-shinde-message-congress-du-election-bihar-seat-dispute-rld-up/4151302/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-on-ajit-pawar-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A5%E0%A5%87%E0%A4%9F%E0%A4%9A-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2%E0%A4%82-maharashtra-politics/vi-AA1MqUjw?ocid=hpmsn</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A4%B0-%E0%A4%85%E0%A4%A8%E0%A4%AC%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%B2%E0%A4%97-%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%95-%E0%A4%AF%E0%A4%A4/ar-AA1G5LqL?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-on-ajit-pawar-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A4-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2%E0%A4%82-maharashtra-politics/vi-AA1Mp1S3</t>
+          <t>https://inshorts.com/hi/amp_news/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6--%E0%A4%A6--%E0%A4%95--x-%E0%A4%85%E0%A4%95-%E0%A4%89-%E0%A4%9F-%E0%A4%B9-%E0%A4%95--%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%B8-%E0%A4%A8--%E0%A4%AA-%E0%A4%B8-%E0%A4%9F-%E0%A4%95-%E0%A4%8F-%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%A4-%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%95--%E0%A4%95--%E0%A4%9D-%E0%A4%A1---1758441470089</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/shiv-sena-leader-jitendra-janawale-express-displeasure-after-not-appointed-as-vibhag-pramukh/articleshow/123765593.cms</t>
+          <t>https://zeenews.india.com/marathi/short-videos/congress-mp-praniti-shinde-criticizes-eknath-shinde/939828</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/dcm-eknath-shinde-praises-rss-chief-mohan-bhagwat-on-his-birthday/videoshow/123842071.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%9A-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B0-%E0%A4%AC%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8-%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%9C-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B0-%E0%A4%B2-%E0%A4%97%E0%A4%A3-%E0%A4%B0%E0%A4%82-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0/ar-AA1MOxAB</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/dcm-eknath-shinde-statement-on-nepal-anarchy-alert-and-snajay-raut-remark/920876/</t>
+          <t>https://www.msn.com/mr-in/news/other/high-court-on-eknath-shinde-%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A4%9A%E0%A5%87-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%9A%E0%A5%87-%E0%A4%A4-%E0%A4%B6%E0%A5%87%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%95-%E0%A4%AF/ar-AA1MNNcC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-camp-vijay-chaugule-answer-ganesh-naik-over-his-criticism-1477274.html</t>
+          <t>https://mahasamvad.in/178497/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/there-is-no-animosity-between-eknath-shinde-and-devendra-fadnavis-ajit-pawar/939011</t>
+          <t>https://marathi.ndtv.com/maharashtra/thane-ghodbunder-news-good-news-for-thane-kalyan-badlapur-commuters-as-eknath-shinde-orders-restriction-of-heavy-vehicles-untill-midnight-9291074</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B8-%E0%A4%82%E0%A4%A6%E0%A5%82%E0%A4%B0-%E0%A4%89%E0%A4%A1-%E0%A4%B2%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%A6%E0%A4%97%E0%A4%A1-%E0%A4%A8%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B0%E0%A4%A6-%E0%A4%B0-%E0%A4%B9%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AC-%E0%A4%B2/ar-AA1Mwrue</t>
+          <t>https://www.instagram.com/policenamaa/p/DO3KXfUDC5_/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/vice-president-election-shiv-sena-ubt-mps-might-vote-for-nda-candidate-as-eknath-shinde-works-on-operation-tiger/articleshow/123785590.cms</t>
+          <t>https://mahasamvad.in/178645/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-faced-inner-struggle-before-bmc-elections-red-alert-for-eknath-shinde-1477478.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%B5-%E0%A4%9A-%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%A8%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B9-%E0%A4%A4-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%82%E0%A4%9A-%E0%A4%96%E0%A5%81%E0%A4%B2-%E0%A4%B8-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%8D%E0%A4%B5%E0%A4%A4-%E0%A4%B9%E0%A5%82%E0%A4%A8-%E0%A4%86%E0%A4%A8%E0%A4%82%E0%A4%A6-%E0%A4%A6-%E0%A4%98%E0%A5%87%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5-%E0%A4%A0%E0%A5%87%E0%A4%B5%E0%A4%B2-%E0%A4%95/ar-AA1MSjEL</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/eknath-shinde-orders-immediate-survey-and-relief-for-rain-affected-areas-in-sambhajinagar-sai29</t>
+          <t>https://thefocusindia.com/maharashtra-news/on-what-authority-did-you-give-the-stay-eknath-shinde-was-asked-in-the-supreme-court-284502/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/shahaji-bapu-patil-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%93%E0%A4%8F%E0%A4%B8%E0%A4%A1-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%AE%E0%A4%A6-%E0%A4%B0%E0%A4%95-%E0%A4%B8-%E0%A4%A0-%E0%A4%B6%E0%A4%B9-%E0%A4%9C-%E0%A4%AC-%E0%A4%AA%E0%A5%82-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%9A-%E0%A4%B2-%E0%A4%AC-%E0%A4%82%E0%A4%97-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%B2-%E0%A4%A6-%E0%A4%B2-%E0%A4%AE-%E0%A4%A0-%E0%A4%91%E0%A4%AB%E0%A4%B0/ar-AA1M5QWH</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%95-%E0%A4%A3-%E0%A4%9A-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B0-%E0%A4%AC%E0%A4%B8%E0%A4%A3-%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A5%E0%A5%87%E0%A4%9F-%E0%A4%A8-%E0%A4%B5-%E0%A4%98%E0%A5%87%E0%A4%A4-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1MHE1a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-eyes-on-vice-president-election-on-prove-his-political-power-vice-president-election-1476089.html</t>
+          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-%E0%A4%AC-%E0%A4%B3-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%82%E0%A4%9A-%E0%A4%A8-%E0%A4%B7%E0%A5%8D%E0%A4%A0-%E0%A4%B5%E0%A4%82%E0%A4%A4-%E0%A4%B8%E0%A5%87%E0%A4%B5%E0%A4%95-%E0%A4%9A%E0%A4%82%E0%A4%AA-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%A5-%E0%A4%AA-%E0%A4%9A-%E0%A4%B6%E0%A4%AA%E0%A4%A5%E0%A4%B5-%E0%A4%A7-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%AE-%E0%A4%A0-%E0%A4%AD%E0%A5%82%E0%A4%AE-%E0%A4%95-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8/ar-AA1vjijr?cvid=5C9E8D07D85E4F0FAB3B201F129171F9&amp;ocid=TIYLnav&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/ajit-pawar-cleared-devendra-fadnavis-and-eknath-shinde-clash/</t>
+          <t>https://marathi.abplive.com/news/mumbai/under-what-authority-were-the-municipal-corporation-notice-to-demolish-buildings-stopped-high-court-ask-on-eknath-shinde-whether-the-dcm-has-the-authority-to-make-that-decision-1384909</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/thane-news-murbad-nagar-panchayat-parivartan-panel-8-corporators-have-joined-eknath-shinde-shiv-sena-1476476.html</t>
+          <t>https://mahasamvad.in/179440/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/internal-displeasure-within-shiv-sena-shinde-faction-over-the-selection-of-office-bearers-some-even-reached-out-to-meet-shinde-thackeray-faction-also-balked-1383155</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticized-eknath-shinde-for-washing-rajan-vichares-feet-and-taking-a-pilgrimage/923077/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/even-before-the-mumbai-municipal-corporation-elections-internal-discontent-within-eknath-shindes-shiv-sena-has-been-aroused-mumbai-maharashtra-news-mhs25091203856</t>
+          <t>https://mahasamvad.in/178790/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/displeasure-in-shinde-led-shiv-sena-after-appointment-of-32-vidhan-pramukh-ahead-of-bmc-election/articleshow/123762650.cms</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-decision-mandatory-to-construct-administrative-buildings-of-municipal-councils-according-to-the-model-plan-1482062.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/shiv-sena-ministers-important-meeting-at-dada-bhuse-janjira-bungalow-near-mantralaya/articleshow/123884105.cms</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/video/delhi-eknath-shinde-statement-nepal-anarchy-alert-sanjay-raut-remark-135900281.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A0-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4%E0%A4%B9-%E0%A4%AE-%E0%A4%B8%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%AE-%E0%A4%B3%E0%A4%B5%E0%A5%82%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%8A-%E0%A4%B6%E0%A4%95%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%9A%E0%A5%85%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9C-%E0%A4%A6-%E0%A4%B2%E0%A5%87/ar-AA1MFBoy</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ganesh-naik-vs-eknath-shinde-%E0%A4%A8-%E0%A4%88%E0%A4%95-%E0%A4%82%E0%A4%9A-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%A8-%E0%A4%B5-%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4-%E0%A4%9F-%E0%A4%95-shrikant-shinde-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/vi-AA1MeFJN</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shindes-ex-account-hacked-96111</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/shinde-sena-prepares-for-dussehra-rally-battle-for-azad-maidan-shinde-group-dussehra-melava-1489299.html</t>
+          <t>https://marathi.abplive.com/news/politics/the-high-court-has-questioned-eknath-shinde-over-the-suspension-of-action-against-illegal-construction-in-navi-mumbai-1384988</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-mahayuti-rift-devendra-fadnavis-eknath-shinde-ajit-dada-lead-stable-maharashtra-alliance-amidst-discontent-rumors-unanimous-decisions-1383659</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%98-%E0%A4%A1%E0%A4%AC%E0%A4%82%E0%A4%A6%E0%A4%B0-%E0%A4%B0-%E0%A4%A1%E0%A4%B5%E0%A4%B0-%E0%A4%B2-%E0%A4%B5-%E0%A4%B9%E0%A4%A4%E0%A5%82%E0%A4%95-%E0%A4%95-%E0%A4%82%E0%A4%A1-%E0%A4%95%E0%A4%AE-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%89%E0%A4%AA%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A6-%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1MJRsS</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!politics/lack-of-coordination-within-the-mahayuti-government-over-maratha-reservation-gr-eknath-shinde-radhakrishna-vikhe-patil-chhagan-bhujbal-pankaja-munde-reactions-mhs25091004171</t>
+          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%AD%E0%A4%B0-%E0%A4%A4-%E0%A5%A7%E0%A5%AB-%E0%A4%9C%E0%A5%81%E0%A4%B2%E0%A5%88%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A3-%E0%A4%B8-%E0%A4%A0%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95%E0%A4%B0/ar-AA1DqU7p?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ganesh-naik-indirectly-critisize-to-eknath-shinde-dcm-and-shiv-sena-leader-in-thane-before-tmc-elections-1477463.html</t>
+          <t>https://www.mymahanagar.com/mahamumbai/deputy-chief-minister-eknath-shinde-insistently-served-the-australian-guests-vadapav-a-signature-food-of-mumbai/922213/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/uddhav-thackerays-big-plan-against-bjp-in-pune-and-eknath-shinde-in-mumbai-maharashtra-politics/939026/amp</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-many-office-bearers-of-uddhav-thackeray-group-join-shiv-sena-95696</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/mumbai/ekanath-shinde-so-the-ravana-of-navi-mumbai-will-be-burnt-on-dussehra-shinde-group-responds-to-ganesh-naik/920396/</t>
+          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%A8%E0%A5%87%E0%A4%B9-%E0%A4%91%E0%A4%AB%E0%A4%B0-%E0%A4%A6-%E0%A4%B2%E0%A5%87%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%90%E0%A4%95%E0%A4%A4-%E0%A4%9A-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A-%E0%A4%B2%E0%A4%97%E0%A4%AC%E0%A4%97-%E0%A4%98-%E0%A4%88%E0%A4%A8%E0%A5%87-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B6-%E0%A4%B2%E0%A5%87%E0%A4%A6-%E0%A4%B0-%E0%A4%B2-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B2-%E0%A4%A8%E0%A5%87%E0%A4%B2%E0%A4%82-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%95%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2/ar-AA1yRGld?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/uddhav-thackeray-operation-tiger-15-former-corporators-who-joined-shinde-sena-1479313.html</t>
+          <t>https://x.com/i/broadcasts/1PlJQOgqMRDKE</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-slams-opportunistic-patriots-questioning-soldiers-bravery-cites-pakistan-flag-and-bomb-blast-accused-1384028</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/shiv-sena-corporaters-news-eknath-shinde-on-uddhav-thackeray-mumbai-bmc-election-2025/921652/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/178222/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-district-administration-should-remain-alert-in-wake-of-heavy-rains-eknath-shinde-instructs-94887</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/shiv-sena-mla-krupal-tumane-said-most-of-ubt-mlas-in-contact-of-dcm-eknath-shinde/articleshow/123788206.cms</t>
+          <t>https://marathi.ndtv.com/cities/cm-fadnavis-change-eknath-shindes-decision-to-ban-heavy-vehicles-from-morning-6-to-12-night-to-solve-traffic-congestion-9316039</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shinde-faction-ministers-mlas-mps-meet-deputy-cm-eknath-shinde-guides-on-local-body-and-mumbai-municipal-corporation-elections-strategy-1384091/amp</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-review-maharashtra-and-mumbai-rain-updates-orders-airlift-beed-ashti-villagers-1480338.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/former-mla-from-gangapur-in-chhatrapati-sambhajinagar-and-ajit-pawars-ncp-leader-kailas-patil-joins-eknath-shindes-shiv-sena/920102/</t>
+          <t>https://mahasamvad.in/179392/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-news-maratha-reservation-bmc-election-committee-high-court-slams-jail-admin-nagpur-robbery-pune-mcoca-and-political-debates-1383152</t>
+          <t>https://mahasamvad.in/178828/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/jitendra-awhad-demands-eknath-shinde-regarding-illegal-buildings-in-diva-daighar-dombivli-areas/videoshow/123864439.cms</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/vice-president-election-bjp-elects-shiv-sena-mp-shrikant-shinde-as-official-representative-of-nda-c-p-radhakrishnan/articleshow/123778520.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/ganesh-naik-vs-eknath-shinde-%E0%A4%A0-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A-%E0%A4%B8%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%86%E0%A4%A3-%E0%A4%AF%E0%A4%9A-%E0%A4%85%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%A4%E0%A4%B0-%E0%A4%B0-%E0%A4%B5%E0%A4%A3-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%B9%E0%A4%82%E0%A4%95-%E0%A4%B0-%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A4%B9%E0%A4%A8-%E0%A4%95%E0%A4%B0-%E0%A4%B5%E0%A5%87-%E0%A4%B2-%E0%A4%97%E0%A5%87%E0%A4%B2/ar-AA1Mh41w?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-fund-row-eknath-shinde-ministers-chhagan-bhujbal-complain-of-fund-shortage-praniti-shinde-alleges-racket-in-solapur-rain-compensation-1383593</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html?utm_source=District%20Widget&amp;utm_medium=Mobile&amp;utm_campaign=marathi</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ajit-pawar-denies-rift-between-eknath-shinde-and-devendra-fadnavis-blames-opposition-for-rumors-asserts-government-stability-1383806/amp</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-municipal-elections-eknath-shinde-puts-shiv-sena-in-action-mode-with-direct-orders-to-corporators-sharad-pawar-also-eyes-victory-in-corporations-1384728</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-ias-appointments-deputy-cm-eknath-shinde-reportedly-unhappy-over-d-class-municipal-corporation-ias-appointments-fadnavis-clarifies-1383710</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-get-set-back-bmc-scraps-12-crore-project-mumbai-1485014.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-holds-separate-meeting-with-mumbai-mlas-for-bmc-election-strategy-after-joint-session-with-ministers-and-mps-issues-key-instructions-1384127/amp</t>
+          <t>https://marathi.ndtv.com/cities/now-there-is-only-one-type-plan-for-the-administrative-buildings-of-the-municipal-council-and-municipal-panchayats-eknath-shinde-9294836</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maratha-reservation-chhagan-bhujbal-challenges-leaders-on-ews-separate-quota-eknath-shinde-ashok-chavan-clarify-stance-1383556</t>
+          <t>https://www.mumbaitak.in/political-news/story/eknath-shinde-x-account-hack-turkey-and-pakistani-flag-show-cyber-crime-3203184-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/ganesh-naik-vs-eknath-shinde-naik-s-criticism-of-eknath-shinde-without-naming-him-what-did-shrikant-shinde-say-1074019.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-big-announces-on-pm-modi-birthday-say-all-municipal-councils-will-be-established-namo-udyan-in-maharashtra-95314</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ind-vs-pak-asia-cup-2025-if-you-have-the-courage-go-to-dubai-and-uproot-pitch-jyoti-waghmare-challenge-eknath-shinde-uddhav-thackeray-1383946</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-rain-heavy-rainfall-in-beed-40-villagers-should-be-airlifted-dcm-eknath-shinde-ordered-9279677</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/ratnagiri/political-earthquake-in-konkan-shivsena-uddhav-thackeray-may-face-a-major-setback-young-leader-likely-to-join-bjp-or-eknath-shinde-party/articleshow/123798972.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/mumbai-high-court-questioned-eknath-shinde-on-new-mumbai-illegal-construction-case/922756/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/tv-show/special-report/thane-political-rivalry-ganesh-naik-s-ravana-s-ego-remark-sparks-mahayuti-tension-challenges-eknath-shinde-in-thane-municipal-corporation-elections-1383115</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-stated-that-the-change-in-gst-rates-will-lead-to-the-establishment-of-a-superpower-in-the-country-from-tomorrow/923694/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/editorial/agralekha/thackaray-political-convenience-and-thackerays-arrow/920323/amp/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-s-x-account-hacked-turkish-and-pakistani-videos-posted-account-recovered-after-team-x-complaint-1385633</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/amp/mr/politics/deputy-chief-minister-eknath-shinde-consoled-the-tourists-stranded-in-nepal-89939</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shinde-fadnavis-cold-war-high-court-questions-maharashtra-government-s-legitimacy-amid-brand-battle-corruption-allegations-and-best-depot-controversy-1384960</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/clashes-between-devendra-fadnavis-amd-eknath-shinde-on-regarding-the-appointment-of-chartered-officers-in-municipalities/</t>
+          <t>https://www.mymahanagar.com/maharashtra/local-elections-mahayuti-will-win-in-the-local-self-government-elections-eknath-shinde-is-confident/922171/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/thane-road-crumble-within-liability-period-mns-alleges-fund-misuse-by-civic-officials-vsd-99-5361399/lite/</t>
+          <t>https://www.mymahanagar.com/maharashtra/deputy-cm-eknath-shinde-on-heavy-rains-and-alert-to-district-administration/921681/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-fadnavis-shinde-rift-maharashtra-political-tensions-over-d-class-municipal-corporation-officer-appointments-clarification-issued-1383683</t>
+          <t>https://www.saamana.com/wadigodri-crime-news-fake-cid-officers-stole-the-golden-ring/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maratha-quota-chhagan-bhujbal-challenges-maratha-leaders-on-10-reservation-ewc-cm-shinde-assures-legal-framework-no-harm-to-obcs-1383536</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-for-suspending-demolition-of-societies-with-unauthorized-construction-in-vashi-area/922729/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/dcm-eknath-shinde-revert-chhagan-bhujbal-on-maratha-reservation-gr/937947</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-working-on-plan-b-for-bmc-election-likely-shock-to-uddhav-thackeray-and-bjp-also-1484790.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/short-videos/eknath-shinde-reaction-on-vice-president-marathi-news/938103</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-says-anand-dighe-never-sold-shiv-sena/923100/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.prabhasakshi.com/national/shinde-shiv-sena-accused-sanjay-raut-of-destabilizing-the-country-demanded-immediate-action</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/mns-leader-avinash-jadhav-slams-eknath-shinde-over-thane-traffic-issue/articleshow/123926772.cms</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/tension-in-the-government-over-desired-posting-cms-order-shinde-faction-unhappy/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-ghodbandar-road-eknath-shinde-ghodbandar-residents-will-be-free-from-traffic-congestion/922259/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/shinde-group-again-committed-a-scam-of-rs-22-crores-cm-fadnavis-ordered-an-investigation/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-today-21st-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-ahmedabad-bullet-train-mega-block-sunday/amp_liveblog/124023319.cms</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/raavans-ego-will-have-to-be-burnt-in-thane-ganesh-naik-indirectly-targeted-shinde/</t>
+          <t>https://news18marathi.com/news/navi-mumbai-munciple-corporation-news-dcm-eknath-shinde-directed-the-commissioner-to-give-immediate-priority-to-water-supply-roads-health-facilities-and-schools-in-14-villages-local18-1483762.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://lalluram.com/vice-presidential-election-13-mps-of-india-alliance-did-cross-voting-voted-for-nda-candidate-cp-radhakrishnan/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-solve-bmtc-employee-problem-gave-10-lakh-for-compensation-1484524.html</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/shinde-group-claims-uddhav-has-only-two-mlas-left-125090900020_1.html</t>
+          <t>https://www.tv9marathi.com/videos/mumbai-sees-banners-from-eknath-shinde-shiv-sena-celebrating-pm-modi-birthday-spark-discussion-1493541.html</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/shindes-shiv-sena-faces-backlash-over-new-department-head-appointments-4255432</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/eknath-shinde-vs-uddhav-thackeray-shinde-himself-got-caught-in-the-maze-that-surrounded-thackeray-speed-up-the-movement-behind-the-scenes/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-eknath-shinde-s-shiv-sena-in-action-mode-confident-of-mahayuti-victory-in-mumbai-civic-polls-directs-corporators-to-start-work-1384673</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/eknaths-militant-statement-to-create-chaos-like-nepal-in-the-country/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-announced-strict-action-will-be-taken-against-those-who-cheated-residents-of-65-buildings-in-kalyan-dombivali-1483839.html</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/tourists-from-maharashtra-stranded-in-nepal-eknath-shinde-interacted-directly-over-the-phone/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/withdrew-the-rs-2-5-crore-fund-given-for-sewage-plant-and-drainage-because-former-corporator-deepmala-badhe-belonged-to-the-thackeray-group/922264/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/eknath-shindes-team-of-21-leaders-in-the-wake-of-the-bmc-elections/</t>
+          <t>https://www.lokmat.com/thane/bjp-mns-uddhav-sena-alliance-formed-to-target-eknath-shinde-sena-in-shatayushi-sporting-club-elections-thane-a-a629/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/mumbai-bmc-election-2025-eknath-shinde-shivsena-executive-committee-announced-maharashtra-politics-036915.html</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-former-mla-claim-on-20-crore-make-political-stir-in-maharashtra-1484863.html</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/residents-of-two-affected-buildings-in-elphinstone-bridge-area-will-be-rehabilitated-proposal-approved-by-eknath-shinde-05-696621</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/bjp-leader-nitin-paygude-and-mns-leader-ranji-dhage-join-shiv-sena-shinde-group/articleshow/123998704.cms</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-more-than-150-tourists-from-maharashtra-stranded-in-nepal-efforts-are-on-to-bring-them-back/</t>
+          <t>https://marathi.indiatimes.com/india-news/bihar-assembly-election-amit-shah-meets-bjp-workers-gives-60-days-plan-ahead-of-poll/articleshow/123995857.cms</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/dcm-eknath-shinde-paid-a-goodwill-visit-to-vice-president-c-p-radhakrishnan/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-politics-deputy-cm-eknath-shinde-refutes-evm-allegations-confident-of-mahayuti-victory-in-mumbai-civic-polls-on-development-work-1385031/amp</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/15-corporators-of-shinde-sena-will-return-home-shivsenaubt/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-20-september-2025-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/deputy-chief-minister-ajit-pawars-absence-from-the-vice-presidents-swearing-in-ceremony-shinde-explained-the-reason-saying/</t>
+          <t>https://www.lokmat.com/maharashtra/women-from-shinde-sena-demand-minister-of-state-yogesh-kadam-to-make-deepak-kesarkar-a-minister-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/brother-upset-by-cm-fadnavis-order-it-sparked-discussions-what-exactly-happened/</t>
+          <t>https://www.saamana.com/thane-news-ganesh-naik-eknath-shinde-janta-darbar-mumbai-high-court/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/will-15-former-corporators-from-shinde-group-return-to-uddhav-thackeray-group/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/dispute-between-both-shiv-sena-parties-over-printing-anand-dighe-photo-next-to-balasaheb/940602/amp</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/7-instalments-of-the-namo-shetkari-yojana-distributed-by-the-cm-fadanvis/</t>
+          <t>https://www.saamana.com/eknath-shinde-x-account-hack/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/mumbai/pratap-sarnaik-said-dahisar-toll-naka-will-be-shifted-near-the-nursery/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-mumbai-rains-deputy-cm-eknath-shinde-reviews-flood-situation-40-50-people-trapped-in-asti-kateri-being-airlifted-from-nashik-ahilyanagar-1384293</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/all-the-passengers-from-dhasai-murbad-areas-stranded-in-nepal-have-arrived-in-india/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-thane-news-sanjay-raut-s-controversial-statements-ignite-political-war-between-shiv-sena-factions-ahead-of-municipal-elections-threats-exchanged-1385570/amp</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/what-did-eknath-shinde-say-at-the-meeting-of-developed-maharashtra-vision-document-2047-fulfilling-the-expectations-of-the-people/131638/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-namo-gardens-project-eknath-shinde-announces-394-crore-funding-for-394-municipal-councils-on-pm-modi-s-birthday-includes-garden-competition-1384925</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/ajit-pawar-absent-from-vice-presidents-swearing-in-ceremony-eknath-shindes-big-explanation/132075/</t>
+          <t>https://lalluram.com/eknath-shinde-x-account-hack-hacker-puts-pakistan-and-turkey-flags-on-home-page/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/thackeray-and-shinde-factions-face-off-over-the-beautification-of-prabhadevi-circle/132095/</t>
+          <t>https://grandnews.in/2025/09/21/big-breaking-deputy-chief-minister-eknat/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5%E0%A5%80%E0%A4%B8%E0%A4%BE%E0%A4%82%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D/116953/</t>
+          <t>https://jantaserishta.com/local/maharashtra/eknath-shindes-x-account-hacked-on-the-day-of-the-india-pakistan-match-4277868</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%A0%E0%A4%BE%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%9F%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%B8%E0%A5%81%E0%A4%A8%E0%A5%80%E0%A4%B2-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%B6%E0%A4%BF/116357/</t>
+          <t>https://khabarchalisa.com/maharashtra-deputy-cm-eknath-shindes-x-accou/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%89%E0%A4%AA%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%80-%E0%A4%A8/117016/</t>
+          <t>https://peoplesupdate.com/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-pakistan-turkey-flags-095613</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A4%BE%E0%A4%A4-%E0%A4%A8%E0%A5%87%E0%A4%AA%E0%A4%BE%E0%A4%B3%E0%A4%B8%E0%A4%BE%E0%A4%B0%E0%A4%96%E0%A5%87-%E0%A4%85%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%95/116864/</t>
+          <t>https://www.prabhasakshi.com/national/eknath-shinde-says-rahul-gandhi-vote-stealing-allegations-are-completely-baseless</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/raj-thackeray-seems-to-have-upper-hand-in-alliance-moves-with-uddhav-claim-political-analysts/articleshow/123881278.cms</t>
+          <t>https://www.thejbt.com/india/maharashtra-deputy-cm-eknath-shinde-s-x-account-hacked-hackers-posted-flags-of-pakistan-and-t%C3%BCrkiye-news-295659</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AF%E0%A4%B9-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A5-%E0%A4%9B-%E0%A4%A1%E0%A4%BC-bjp-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%AE-%E0%A4%B2-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%95%E0%A4%88-%E0%A4%AD%E0%A4%B0-%E0%A4%B8%E0%A5%87%E0%A4%AE%E0%A4%82%E0%A4%A6-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AF%E0%A4%B9-%E0%A4%B9%E0%A5%88-%E0%A4%B6-%E0%A4%95-%E0%A4%AF%E0%A4%A4/ar-AA1KLAFy?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://aninews.in/news/national/politics/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother20250916212035/?amp=1</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-dy-cm-eknath-shinde-meets-with-newly-elected-vice-president-cp-radhakrishnan20250912162242</t>
+          <t>https://www.aninews.in/news/national/acharya-devvrat-sworn-in-as-governor-of-maharashtra-reads-oath-in-sanskrit20250915150141?amp=1</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A8-%E0%A4%95-%E0%A4%AF-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%B8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%95%E0%A5%87-2-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%82-%E0%A4%95-%E0%A4%9B-%E0%A4%A1%E0%A4%BC%E0%A4%95%E0%A4%B0-%E0%A4%B8%E0%A4%AC-%E0%A4%9B-%E0%A4%A1%E0%A4%BC%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95-%E0%A4%A6-%E0%A4%B5/ar-AA1MaAzx</t>
+          <t>https://thenewsmill.com/2025/09/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/maratha-quota-controversy-eknath-shinde-clarifies-no-new-decision-taken-obc-interests-safe-23593019</t>
+          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/eknath-shinde-shiv-sena-announce-committee-over-bmc-election/articleshow/123811398.cms</t>
+          <t>https://www.dainiktribuneonline.com/news/nation/shindes-x-account-hacked-maharashtras-cyber-security-in-question-uproar-over-eknath-shindes-x-account-being-hacked/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AC-%E0%A4%8F%E0%A4%AE%E0%A4%B8-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82-21-%E0%A4%B8%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%B8%E0%A4%AE-%E0%A4%A4-%E0%A4%95-%E0%A4%97%E0%A4%A0%E0%A4%A8/ar-AA1MhjC4</t>
+          <t>https://www.msn.com/hi-in/news/other/eknath-shinde-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A4%B2-%E0%A4%A6%E0%A5%87-%E0%A4%B8%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AA%E0%A4%A6-%E0%A4%B8%E0%A5%87-%E0%A4%87%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%AB-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%B8%E0%A5%87-%E0%A4%86%E0%A4%88-%E0%A4%96%E0%A4%AC%E0%A4%B0/ar-AA1uIeu8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/eknath-shinde-jalna-news-balasaheb-thackeray-thoughts-are-his-wealth-we-will-not-claim-anything-says-eknath-shinde-1382619</t>
+          <t>https://www.ptinews.com/story/national/shiv-sena-protests-against-sanjay-raut-of-sena-ubt-for-insulting-eknath-shindes-mentor/2934437</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AA%E0%A4%A6-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%81%E0%A4%95-%E0%A4%B5%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%AE%E0%A4%A4%E0%A4%AE-%E0%A4%9C%E0%A4%A3-%E0%A4%86%E0%A4%A7-%E0%A4%9A-%E0%A4%A8-%E0%A4%95-%E0%A4%B2-%E0%A4%B8-%E0%A4%82%E0%A4%97%E0%A5%82%E0%A4%A8-%E0%A4%9F-%E0%A4%95%E0%A4%B2-n18s/vi-AA1MaBrj</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A6-%E0%A4%AC-%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AC%E0%A4%A8%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-cm-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%97-%E0%A4%A8-%E0%A4%88%E0%A4%82-5-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%B5%E0%A4%9C%E0%A4%B9%E0%A5%87%E0%A4%82/ar-AA1uIG8l?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AC-%E0%A4%B3-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B5-%E0%A4%9A-%E0%A4%B0-%E0%A4%B9-%E0%A4%9A-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%86%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%95%E0%A4%B6-%E0%A4%B5%E0%A4%B0%E0%A4%B9-%E0%A4%95%E0%A5%8D%E0%A4%B2%E0%A5%87%E0%A4%AE-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%9C-%E0%A4%B2%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B8%E0%A5%8D%E0%A4%B5-%E0%A4%97%E0%A4%A4/ar-AA1M85Ol</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-assembly-election-result-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A4-%E0%A4%9C-%E0%A4%A4-%E0%A4%97%E0%A4%88-%E0%A4%AE%E0%A4%97%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%9F-%E0%A4%95-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A5%81%E0%A4%86/ar-AA1uBWUK?cvid=165226EF5620437992660C8F5EC7383E&amp;ocid=TIYLnav&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/photo/in-photos-maharashtra-deputy-cm-eknath-shinde-addresses-shiv-sena-mlas-in-chhatrapati-sambhajinagar-107258/6</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A4-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%9C-%E0%A4%A4%E0%A4%A4%E0%A5%87-100-%E0%A4%B8-%E0%A4%9F%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%95-%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5/ar-AA1v4Uzx?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ganesh-naik-vs-eknath-shinde-%E0%A4%A8-%E0%A4%88%E0%A4%95-%E0%A4%82%E0%A4%9A-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%A8-%E0%A4%B5-%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4-%E0%A4%9F-%E0%A4%95-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-shiv-sena-vs-bjp/vi-AA1M9Jp3</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-congress-leader-questions-cyber-security/amp_articleshow/124026185.cms</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/aaditya-thackeray-attacks-maharashtra-government-over-potholes-on-mumbai-pune-expressway-11550</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-cm-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2-%E0%A4%AA%E0%A4%B8%E0%A4%82%E0%A4%A6-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9D%E0%A4%9F%E0%A4%95-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A-%E0%A4%9A-%E0%A4%B8%E0%A5%87-%E0%A4%AD-%E0%A4%AA-%E0%A4%9B%E0%A4%A1%E0%A4%BC%E0%A5%87/ar-AA1uxBrL?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AC-%E0%A4%B3-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B5-%E0%A4%9A-%E0%A4%B0-%E0%A4%B9-%E0%A4%9A-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%86%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%95%E0%A4%B6-%E0%A4%B5%E0%A4%B0%E0%A4%B9-%E0%A4%95%E0%A5%8D%E0%A4%B2%E0%A5%87%E0%A4%AE-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%9C-%E0%A4%B2%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%82%E0%A4%B9-%E0%A4%B2%E0%A4%97-%E0%A4%B5%E0%A4%B2-%E0%A4%9F-%E0%A4%B2/ar-AA1M8ppg</t>
+          <t>https://www.msn.com/hi-in/news/other/raj-thackeray-%E0%A4%B2-%E0%A4%B2-%E0%A4%AA-%E0%A4%AA-%E0%A4%B2-%E0%A4%97%E0%A5%87%E0%A4%B2%E0%A5%81-%E0%A4%AA%E0%A4%B0-%E0%A4%B2%E0%A5%9C%E0%A4%95-%E0%A4%95-%E0%A4%A1-%E0%A4%82%E0%A4%B8-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A5%9C%E0%A4%95%E0%A5%87-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AA%E0%A5%82%E0%A4%9B-%E0%A4%AF%E0%A4%B9-%E0%A4%B9%E0%A5%88-%E0%A4%B2-%E0%A4%A1%E0%A4%B2-%E0%A4%AC%E0%A4%B9%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8/ar-AA1tuyLy?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ganesh-naik-vs-eknath-shinde-%E0%A4%A8-%E0%A4%88%E0%A4%95-%E0%A4%82%E0%A4%9A-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%A8-%E0%A4%B5-%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4-%E0%A4%9F-%E0%A4%95-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-shiv-sena-vs-bjp/vi-AA1Mebzs</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-response-after-sanjay-raut-objected-to-placing-anand-dighes-photo-next-to-balasaheb-thackeray/922799/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ganesh-naik-vs-eknath-shinde-%E0%A4%A0-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A-%E0%A4%B8%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%86%E0%A4%A3-%E0%A4%AF%E0%A4%9A-%E0%A4%85%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%A4%E0%A4%B0-%E0%A4%B0-%E0%A4%B5%E0%A4%A3-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%B9%E0%A4%82%E0%A4%95-%E0%A4%B0-%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A4%B9%E0%A4%A8-%E0%A4%95%E0%A4%B0-%E0%A4%B5%E0%A5%87-%E0%A4%B2-%E0%A4%97%E0%A5%87%E0%A4%B2/ar-AA1Mh41w</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AD%E0%A5%87%E0%A4%9C-%E0%A4%A6-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%AC-%E0%A4%B9%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%A8-%E0%A4%AE-%E0%A4%AB-%E0%A4%87%E0%A4%A8%E0%A4%B2-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B0-%E0%A4%AE%E0%A4%A6-%E0%A4%B8-%E0%A4%85%E0%A4%A0-%E0%A4%B5%E0%A4%B2%E0%A5%87/ar-AA1uMd6x?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shinde-sena-corporators-reaffirm-support-to-eknath-shinde-after-sachin-ahir-s-claim-vow-to-win-upcoming-mumbai-elections-1384125/amp</t>
+          <t>https://inshorts.com/hi/news/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6--%E0%A4%A6--%E0%A4%95--x-%E0%A4%85%E0%A4%95-%E0%A4%89-%E0%A4%9F-%E0%A4%B9-%E0%A4%95--%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%B8-%E0%A4%A8--%E0%A4%AA-%E0%A4%B8-%E0%A4%9F-%E0%A4%95-%E0%A4%8F-%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%A4-%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%95--%E0%A4%95--%E0%A4%9D-%E0%A4%A1---1758441470089</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/uddhav-thackeray-big-knock-to-eknath-shinde/939014</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/eknath-shinde-mla-aamshya-padvi-tribal-reservation-opposition-abuses-protest-dhangar-banjara-controversy-gs97</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/shiv-sena-crisis-eknath-shinde-faction-leader-krupal-tumane-claims-uddhav-thackeray-group-all-mlas-are-in-touch-maharashtra-politics-marathi-news-1382665</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%89%E0%A4%AA%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-eknath-shinde-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A5%E0%A5%87%E0%A4%9F-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B9-%E0%A4%AF%E0%A5%87%E0%A4%A4%E0%A4%9A-%E0%A4%85%E0%A4%B8%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A4%9C%E0%A5%87/ar-AA1BAyul?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/mumbai-politics-15-corporators-return-uddhav-thackeray-shiv-sena-tv9d-1491525.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/dcm-eknath-shinde-on-bmc-election-with-mahayuti-alliance/videoshow/124025029.cms</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-fund-row-praniti-shinde-alleges-racket-in-fund-allocation-questions-discrimination-after-heavy-rains-in-solapur-1383545</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/sanjay-raut-attacks-eknath-shinde-shrikant-shiv-sena-rahul-modi-presser-135957579.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/09/11/eknath-shinde-shivsena-upset-bjp-and-joined-hands-with-the-family-of-infamous-pappu-kalani-for-ulhasnagar-elections/eknath-shinde-shivsena-upset-bjp-and-joined-hands-with-the-family-of-infamous-pappu-kalani-for-ulhasnagar-elections/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pm-modi-birthday-eknath-shinde-s-leader-of-the-world-tribute-article-in-loksatta-saamana-omits-ad-1384700</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-dahisar-toll-naka-dcm-eknath-shinde-approves-relocation-of-before-diwali-to-versova-bridge-know-all/articleshow/123815025.cms</t>
+          <t>https://www.saamana.com/eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flag-saamana-online-news/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%A8%E0%A5%87-bmc-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%95-%E0%A4%A4%E0%A5%87%E0%A4%9C-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-21-%E0%A4%B8%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%95%E0%A4%AE%E0%A5%87%E0%A4%9F-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%97%E0%A4%A0%E0%A4%A8/ar-AA1Mh0gE?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://news18marathi.com/maharashtra/mns-avinash-jadhav-on-vasai-child-dies-due-to-traffic-jam-criticize-eknath-shinde-pratap-sarnaik-1484355.html</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/maharashtra/nagpur-news/news-maharashtra-eknath-shinde-faction-claims---all-are-in-touch-with-uddhav-thackeray-except-two-mlas-news-hindi-1-751187-KKN.html</t>
+          <t>https://zeenews.india.com/marathi/video/thackeray-brothers-meeting-in-thane-thackeray-brothers-election-strategy/940600</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-said-bjp-does-not-have-majority-vice-presidential-election-2025-eknath-shinde-shivsena-shrikant-shinde-reaction-3009259</t>
+          <t>https://www.abplive.com/states/maharashtra/deputy-cm-eknath-shinde-x-account-hack-pakistan-turkey-flag-shown-3016093/amp</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-slams-opportunistic-patriots-questioning-soldiers-bravery-cites-pakistan-flag-and-bomb-blast-accused-1384028/amp</t>
+          <t>https://www.ndtv.com/india-news/eknath-shindes-x-account-briefly-hacked-hackers-post-pics-of-pak-turkey-flags-9315607</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ajit-pawar-denies-rift-between-eknath-shinde-and-devendra-fadnavis-blames-opposition-for-rumors-asserts-government-stability-1383806</t>
+          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-on-eknath-shinde-maharashtra-ahmedabad-bullet-train-anand-dighe-3015725/amp</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maratha-reservation-chhagan-bhujbal-challenges-leaders-on-ews-separate-quota-eknath-shinde-ashok-chavan-clarify-stance-1383556/amp</t>
+          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-strict-against-builders-involved-in-kalyan-dombivali-illegal-buildings-constructing-3015585/amp</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/dasara-melava-shiv-sena-latest-news-uddhav-thackeray-or-eknath-shinde-who-will-get-shivaji-park-for-dasara-melava-1475407.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%AC%E0%A4%97-%E0%A4%B5%E0%A4%A4-%E0%A4%95%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%97%E0%A5%81%E0%A4%B5-%E0%A4%B9-%E0%A4%9F-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%AD-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%95-%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A6%E0%A5%87%E0%A4%96%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B2-%E0%A4%B8%E0%A5%8D%E0%A4%9F/ar-AA1sOwtY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/news/in-the-upcoming-ichalkaranji-municipal-elections-the-eknath-shinde-ajit-pawar-faction-is-united-but-the-bjp-is-taking-a-different-stance-1478882.html</t>
+          <t>https://www.aajtak.in/amp/india/maharashtra/story/eknath-shinde-x-account-hacked-pakistan-turkey-flag-posted-ntc-rptc-2338322-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/maharashtra-dy-cm-eknath-shinde-meets-with-newly-elected-vice-president-cp-radhakrishnan/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%B8%E0%A4%AD-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%A4%E0%A5%87-%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AB-%E0%A4%B0-%E0%A4%AC%E0%A4%A8%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-cm-%E0%A4%AF%E0%A5%87-%E0%A4%AC-%E0%A4%A4%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A5%8D%E0%A4%B9%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%A4-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%96-%E0%A4%B8/ar-AA1s9G9J?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/11092025/ladki-bahin-yojana/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/find-the-masterminds-behind-the-kdmc-illegal-buildings-scam-shinde-101758309996962-amp.html</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ganesh-naik-vs-eknath-shinde-news-%E0%A4%A0-%E0%A4%A3%E0%A5%87-%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%A8%E0%A5%87%E0%A4%AA-%E0%A4%B3%E0%A4%9A-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%82%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A4-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%82%E0%A4%98%E0%A4%B0%E0%A5%8D%E0%A4%B7-%E0%A4%9A-%E0%A4%A8-%E0%A4%82%E0%A4%A6/vi-AA1Mi6qH?ocid=hpmsn</t>
+          <t>https://www.ptinews.com/stories-detail/national/maharashtra-dy-cm-eknath-shindes-x-account-hacked/2934860/0</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/big-responsibility-on-6-leaders-of-eknath-shindes-shiv-sena-very-important-planning-in-connection-with-the-mumbai-municipal-corporation-elections/938808/amp</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-charges-baseless-says-ekanth-shinde-23594783</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/vp-election-mp-shrikant-shinde-named-ndas-authorised-representative-says-shiv-sena-10062852</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633937-crackdown-on-unauthorized-buildings-in-thane-eknath-shinde-leads-investigation</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%B8%E0%A5%87-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%A6-%E0%A4%B2%E0%A4%9A%E0%A4%B8%E0%A5%8D%E0%A4%AA-%E0%A4%B9%E0%A5%88-mmr-%E0%A4%95-%E0%A4%B2%E0%A5%9C-%E0%A4%88-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%AE%E0%A4%A8%E0%A5%87-%E0%A4%9A%E0%A4%AE%E0%A4%A4%E0%A5%8D%E0%A4%95-%E0%A4%B0-%E0%A4%95%E0%A4%B0-%E0%A4%AA-%E0%A4%8F%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%97%E0%A4%A3%E0%A5%87%E0%A4%B6-%E0%A4%A8-%E0%A4%88%E0%A4%95-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A4%B2-%E0%A4%B0%E0%A4%B9-%E0%A4%B9%E0%A5%88/ar-AA1L2oY4?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-18-september-2025-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/smart-scam-in-thane-smart-city-cracks-in-the-walls-of-the-amphitheatre-the-historic-cannon-stand-also-collapsed/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-mumbai-rains-deputy-cm-eknath-shinde-reviews-flood-situation-40-50-people-trapped-in-asti-kateri-being-airlifted-from-nashik-ahilyanagar-1384293/amp</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.hindusthanpost.com/special/nepal-protest-safe-return-of-all-the-people-of-dhasai-and-murbad-area-of-maharashtra-stranded-in-nepal/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-illegal-construction-high-court-questions-deputy-cm-s-authority-to-stay-navi-mumbai-demolition-notices-for-naivedya-and-albela-buildings-1384927/amp</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/thane/kalyan-dombivli-municipal-election-2025-new-political-equation-in-new-ward-system/132120/</t>
+          <t>https://marathi.abplive.com/news/politics/sada-saravankar-statement-of-mla-fund-mahim-thackeray-group-mahesh-sawant-counterattack-mla-gets-rs-2-crore-but-i-get-rs-20-crore-when-i-am-not-an-mla-1385728/amp</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/who-parrikar-asks-ajit-pawar-lands-in-another-controversy-3727446</t>
+          <t>https://www.saamana.com/sanjay-raut-criticized-eknath-shinde-and-pratap-sarnaik-over-anand-dighe/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3622862-bjp-gears-up-for-modis-manipur-visit-amidst-boycott-threat?amp</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-images-of-pakistan-turkey-flags-posted/amp_articleshow/124024337.cms</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/shiv-sena-leaders-meet-mumbai-top-cop-seek-action-against-raut-for-threatening-nepal-like-anarchy-10453138</t>
+          <t>https://www.msn.com/en-in/news/other/maharashtra-election-results-bjps-best-congresss-worst-ever-show-in-state-traitors-shinde-and-pawar-prove-theyre-true-heirs/ar-AA1uDEAR?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/vice-president-election-bjp-another-strategy-to-keep-partners-happy-also-worked/4135808/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/thane-shiv-sena-workers-protest-against-sanjay-raut-s-remark-about-anand-dighe-23594679</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B2-%E0%A4%B8-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%89%E0%A4%AC-%E0%A4%A0-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%95-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%AF-%E0%A4%9A-%E0%A4%95-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%96-%E0%A4%B0-%E0%A4%9C-%E0%A4%95/ar-AA1Mc6jR</t>
+          <t>https://realty.economictimes.indiatimes.com/amp/news/industry/strict-action-ordered-against-65-illegal-buildings-in-kalyan-dombivli-by-deputy-chief-minister-eknath-shinde/124008652</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/shiv-sena-demands-action-against-sena-ubt-mp-sanjay-raut-for-provocative-remarks-b628/</t>
+          <t>https://www.devdiscourse.com/article/politics/3629545-uddhav-thackeray-criticizes-indias-cricket-match-with-pakistan-questions-bjps-patriotism?utm_campaign=Bundle&amp;utm_medium=referral&amp;utm_source=Bundle</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/congress-leaders-meet-cm-speaker-over-vacant-lop-posts-in-assembly-and-council-2025-09-09</t>
+          <t>https://www.newsband.in/article_detail/acharyadevvrattakes-oath-as-maharashtras-22nd-governor</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%B8-%E0%A4%AE%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%A8%E0%A4%AF-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%B8-%E0%A4%82%E0%A4%B8%E0%A4%A6-%E0%A4%82-%E0%A4%95-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95/ar-AA1M43aA</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-deputy-cm-eknath-shinde-s-twitter-account-hacked-raises-cybersecurity-concerns-201758454098732.amp.html</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.hindusthanpost.com/politics-news-hindi/vice-presidential-election-nda-candidate-radhakrishnans-victory-is-certain-then-why-is-shiv-senas-uddhav-thackeray-uneasy/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-polls-an-acid-test-for-shiv-sena-ubt-says-thackeray-101758222779307.html</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.rprealtyplus.com/news-views/hudco-signs-rs-11300-cr-mou-in-nagpur-welcomes-govt-director-121646.html</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-planning-for-tourism-development-in-the-kandalvan-area/922599/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/naveen-nagpur-coming-up-as-indias-next-global-financial-hub-mou-signed-3718512</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/shiv-sena-ubt-mns-bjp-raj-thackeray-uddhav-thackeray-devendra-fadnavis-unite-against-shiv-sena-eknath-shinde-for-thane-sporting-committee-election/articleshow/123938834.cms</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/amp/news/railways/maharashtra-renames-ahmednagar-railway-station-to-ahilyanagar/123862509</t>
+          <t>https://www.hindisaamana.com/the-conflict-between-naik-and-shinde-reaches-its-peak-shinde-faction-files-suit-against-naik-in-the-high-court-over-the-janata-darbar/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3622863-john-rotluangliana-a-political-veteran-eyes-dampas-by-election?amp</t>
+          <t>https://www.hindisaamana.com/the-conflict-between-the-bjp-and-shinde-factions-escalates-in-thane-district/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3622782-turmoil-in-nepal-leaves-pilgrims-stranded-amid-safety-concerns?amp</t>
+          <t>https://www.msn.com/en-in/news/India/mumbai-shiv-sena-leader-seeks-carter-road-be-named-after-rajesh-khanna/ar-AA1Megvm?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3622819-nationwide-voter-list-overhaul-to-ensure-integrity?amp</t>
+          <t>https://www.hindustantimes.com/india-news/statue-of-uddhav-thackeray-s-mother-defaced-in-mumbai-shiv-sena-ubt-protests-101758095171594.html</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/rahul-gandhi-skips-vp-s-oath-ceremony-bjp-mocks-samvidhan-savior-no-protocol-big-enough-for-lop/vi-AA1MpioO?ocid=hpmsn</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/maharashtra-makes-governance-smarter-using-artificial-intelligence-992313</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3631323-celebrating-leadership-modis-vision-for-a-new-india-on-his-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/raj-thackeray-held-a-meeting-with-the-core-team-of-his-party-mns-on-thursday-after-a-two-and-a-half-hour-discussion-with-uddhav-thackeray/amp_articleshow/123844364.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/meenatai-thackeray-statue-smeared-with-red-paint-1-held-101758136336233-amp.html</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-ahmednagar-railway-station-renamed-as-ahilyanagar-station-home-ministry-issued-notification-know-all/articleshow/123853954.cms</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3631328-statue-defacement-stirs-political-emotions-in-mumbai?amp</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/top-headlines-today-12-sept-2025-9-am-maratha-gr-maharashtra-politics-thackeray-vs-shinde/vi-AA1MorU9</t>
+          <t>https://www.devdiscourse.com/article/politics/3630398-bjps-enduring-commitment-fadnavis-recollects-2017-political-maneuverings-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B2-%E0%A4%B9%E0%A5%87-21-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%87-%E0%A4%98%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A4%AE-%E0%A4%A4-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MgSQM</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%95-%E0%A4%B5-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%B0-%E0%A4%95-%E0%A4%82%E0%A4%AA-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%A8-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%B2-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AE-%E0%A4%95/ar-AA1vTcYH?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/shiv-sena-shinde-faction-forms-chief-executive-committee-of-21-leaders-for-mumbai-municipal-corporation-elections-2025/920261/</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-election-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%AA%E0%A5%81%E0%A4%B2-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A8-%E0%A4%9F-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%AD%E0%A4%B0-%E0%A4%97-%E0%A4%A1%E0%A4%BC-%E0%A4%AA%E0%A4%95%E0%A4%A1%E0%A4%BC-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%89%E0%A4%A4-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5/ar-AA1sGJQE?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-politics-thackeray-raj-meet-sparks-alliance-buzz-india-pakistan-match-protest-maratha-obc-reservation-row-ajit-pawar-returns-1383196</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/kedar-dighes-sharp-attack-on-shinde-faction-anand-dighe-remembered-as-elections-approach/articleshow/124004160.cms</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/vice-presidential-election-live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv/920094/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-ubt-%E0%A4%A8%E0%A5%87-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B5-%E0%A4%B0-%E0%A4%A7-%E0%A4%97%E0%A4%A4-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%A4-%E0%A4%A8-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%95-%E0%A4%A8-%E0%A4%95-%E0%A4%B2/ar-AA1z6zj4?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%86%E0%A4%A3-%E0%A4%93%E0%A4%AC-%E0%A4%B8-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%B5-%E0%A4%A6-%E0%A4%B5%E0%A4%B0-%E0%A4%AE%E0%A4%A8%E0%A4%B8%E0%A5%87%E0%A4%9A-%E0%A4%AD%E0%A5%82%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B8%E0%A4%AE-%E0%A4%B0/ar-AA1MpBSC</t>
+          <t>https://www.amarujala.com/india-news/maharastra-paint-thrown-on-statue-of-meenatai-thackeray-at-mumbai-shivaji-park-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/india-pakistan-cricket-match-uddhav-thackeray-shivsena-special-campaign-on-september-14-vs-modi-government/articleshow/123822604.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A8%E0%A5%87-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%AE%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A5%87%E0%A4%B6-%E0%A4%95-%E0%A4%AF-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%A6-%E0%A4%B5-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B9%E0%A4%AE-%E0%A4%B8-%E0%A4%A5-%E0%A4%AE-%E0%A4%B2%E0%A4%95%E0%A4%B0-%E0%A4%95-%E0%A4%AE-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87/ar-AA1vfwwh?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/%E0%A4%96%E0%A5%87%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B2-%E0%A4%B5-%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A5%82-%E0%A4%AD%E0%A4%97%E0%A4%A4-%E0%A4%B2-%E0%A4%82%E0%A4%AC%E0%A4%82-%E0%A4%95%E0%A4%A6%E0%A4%AE-%E0%A4%82%E0%A4%9A-%E0%A4%AD-%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A4%B0-%E0%A4%9C-%E0%A4%A7%E0%A4%B5-%E0%A4%82%E0%A4%AC%E0%A4%A6%E0%A5%8D%E0%A4%A6%E0%A4%B2-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%AF%E0%A4%B8%E0%A5%8D%E0%A4%AB-%E0%A4%9F/ar-AA1Hsx7J?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%A6%E0%A4%AC-%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B2%E0%A5%87%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%AF%E0%A5%82%E0%A4%AC-%E0%A4%9F-%E0%A4%A8%E0%A5%87%E0%A4%A4/ar-AA1uTckb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/deputy-cm-ajit-pawar-reacted-to-the-india-pakistan-cricket-match-asia-cup-2025-maharashtra-news-mhs25091310265</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B5-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%89%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%AA%E0%A5%81%E0%A4%B2-%E0%A4%B8-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%87%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87%E0%A4%AE-%E0%A4%B2-%E0%A4%95%E0%A4%B0-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%89%E0%A4%A4/ar-AA1t7BTt?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ladki-bahin-yojana-august-installment-women-and-child-development-department/articleshow/123811716.cms</t>
+          <t>https://www.amarujala.com/india-news/uddhav-targets-bjp-over-india-pakistan-cricket-match-in-asia-cup-maharashtra-debt-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/minister-of-state-for-home-affairs-yogesh-kadam-criticized-raj-thackeray-and-uddhav-thackeray/</t>
+          <t>https://www.lokmatnews.in/blog/india/bjp-shivsena-ncp-congress-local-body-elections-your-bow-and-arrow-but-target-is-ours-drawing-dividing-line-blog-amitabh-srivastava-b507/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/maharashtra/radhakrishnan-was-preferred-in-the-vice-presidential-election/</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%B6-%E0%A4%AE%E0%A4%A4%E0%A4%AD%E0%A5%87%E0%A4%A6-%E0%A4%A8-%E0%A4%B9-%E0%A4%A4-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6%E0%A4%B9-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A5%87%E0%A4%9F-%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1K3Mqc?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/10/?m=0</t>
+          <t>https://www.aninews.in/news/world/asia/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621?amp=1</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/4/?m=0</t>
+          <t>https://www.devdiscourse.com/article/politics/3635247-modis-nation-address-anticipation-on-eve-of-navratri?amp</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/hingoli-news-heavy-rain-floodwater-enters-vasmat-villages-berola-cut-off-rds84</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/dharashiv-tuljapur-tuljabhavani-manchaki-nidra-begins-before-sharadiya-navratri-festival-2025-saree-colors-latest-marathi-news-aak2003</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/video/uddhav-thackeray-slams-pm-modi-asia-cup-2025-india-pakistan-match-pahalgam-attack-patriotism-business-hindutva-trade-questions-rajnath-amit-shah-om0906</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/articleshow/123993653.cms</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/mumbai-pune/pune-mhada-lottery-2025-affordable-homes-starting-at-695-lakh-cheapest-homes-bdk97</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/bhandara-crime-news-33-year-old-man-lured-14-year-old-girl-and-physical-assault-in-lodge-bdk97</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/business/gold-rate-today-24-carat-prices-drop-good-news-for-buyers-check-gold-price-sh04</t>
+          <t>https://www.msn.com/hi-in/news/other/nawab-malik-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-23-%E0%A4%A8%E0%A4%B5%E0%A4%82%E0%A4%AC%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A6-%E0%A4%95%E0%A5%81%E0%A4%9B-%E0%A4%AD-%E0%A4%B9-%E0%A4%B8%E0%A4%95%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%A8%E0%A4%B5-%E0%A4%AC-%E0%A4%AE%E0%A4%B2-%E0%A4%95-%E0%A4%95-%E0%A4%B8%E0%A4%A8%E0%A4%B8%E0%A4%A8-%E0%A4%96%E0%A5%87%E0%A4%9C-%E0%A4%A6-%E0%A4%B5/ar-AA1ttOeX?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/tet-exam-mandatory-for-all-teachers-otherwise-you-will-lose-job-dismissal-retirement-decision-sh04</t>
+          <t>https://24city.news/ncp-chintan-camp-ajit-pawar-reveals-people-ask-why-i-leave-sharad-pawars-support/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/major-accident-on-nagarsambhajinagar-highway-container-rams-9-cars-bdk97</t>
+          <t>https://www.hindisaamana.com/gossip-the-grand-alliances-fun-banter-janta-darbar-vs-petition-darbar/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/chhatrapati-sambhajinagar-20-year-old-woman-dies-of-heart-attack-during-gym-workout-bdk97</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ajit-pawars-absence-at-key-guv-events-raises-eyebrows/articleshow/124030467.cms</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/dhule-nims-engineering-student-end-his-life-hostel-atharva-rajpurohit-found-hanging-death-reason-unknown-latest-marathi-news-yps99</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/pm-modi-turns-75-highlights-of-initiatives-launched-by-bjp-events-held-in-several-states/articleshow/123949298.cms</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/akola-man-summons-rescue-team-after-phone-falls-into-well-vvg94</t>
+          <t>https://infra.economictimes.indiatimes.com/amp/news/railways/indias-bullet-train-project-tunnelling-to-begin-january-2026-as-tbm-arrives/124025478</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/maval-news-filmy-style-15km-chase-notorious-thief-caught-6-5-lakh-valuables-recovered-rds84</t>
+          <t>https://jantaserishta.com/amp/world/australian-mps-met-maharashtras-eknath-shinde-discussed-business-cooperation--4269467</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/beed-news-obc-reservation-man-end-life-incident-rds84</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/rajuddhav-tie-up-won-t-have-impact-on-bmc-polls-101758222840140.html</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/sports/womens-hockey-asia-cup-2025-india-storms-into-final-against-china-indian-womens-hockey-team-reaches-asia-cup-2025-final-bbj88</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/mumbai-pune/99th-akhil-bharatiya-marathi-sahitya-sammelan-to-be-presided-over-by-vishwas-patil-latest-news-pvm91</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/politics-loses-civility-in-maharashtra-101758482600190.html</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/crime-news/jalna-talathi-officer-caught-drunk-demands-beer-bar-bill-pay-to-sign-indira-gandhi-national-disability-pension-form-latest-marathi-news-aak2003</t>
+          <t>https://www.msn.com/mr-in/news/other/sanjay-raut-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%97-%E0%A4%82%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%98%E0%A5%87%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%B5%E0%A5%87%E0%A4%B3-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B0-%E0%A4%96%E0%A4%A0-%E0%A4%95-%E0%A4%AE%E0%A4%A4/ar-AA1Bwm7B?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/lifestyle/do-this-remedy-on-sunday-with-the-grace-of-the-sun-god-problems-in-life-will-go-away-sjk95</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-told-party-workers-bmc-elections-are-a-litmus-test-for-us/articleshow/123989198.cms</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/crime-news/gym-therapist-harassment-assault-drinks-poison-after-molestation-case-shocking-details-kanpur-latest-marathi-news-yps99</t>
+          <t>https://www.msn.com/mr-in/news/other/raj-thackeray-%E0%A4%AE-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A4-%E0%A4%85%E0%A4%B8%E0%A4%A4-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%97%E0%A4%B0%E0%A4%9C%E0%A4%9A-%E0%A4%95-%E0%A4%AF-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%82-%E0%A4%AE%E0%A4%A8%E0%A4%B8%E0%A5%87%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A5%81%E0%A4%96-%E0%A4%82%E0%A4%A8-%E0%A4%A1-%E0%A4%B5%E0%A4%9A%E0%A4%B2%E0%A4%82/ar-AA1vtzAn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/crime-news/minor-argument-turns-deadly-in-mahad-shivthar-bridge-tushar-yenpure-pushes-friend-tulsiram-gaikwad-into-river-latest-marathi-news-aak2003</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-sanjay-raut-supports-rahul-gandhi-saying-that-90-of-the-mahayuti-mlas-in-maharashtra-won-through-vote-theft/articleshow/124015667.cms</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/crime-news/chhattisgarh-raipur-after-illegal-panacea-party-scandal-raipur-obeisance-advertisement-on-instagram-social-media-sparks-outrage-and-police-action-latest-marathi-news-aak2003</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A4%B9-%E0%A4%B2%E0%A4%82-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%95-%E0%A4%81%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A4%9A-%E0%A4%89%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%87%E0%A4%96-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1yazrQ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/crime-news/crime-24-year-old-woman-doctor-suspicious-death-temple-marriage-abortion-junior-doctor-arrested-latest-marathi-news-yps99</t>
+          <t>https://www.msn.com/mr-in/news/other/amit-thackeray-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%AD%E0%A4%B5%E0%A4%A8-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%82%E0%A4%97%E0%A4%A3-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%88%E0%A4%A6-%E0%A4%A8-%E0%A4%A4-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%9F-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A4%A3-%E0%A4%AE-%E0%A4%A4-%E0%A4%B6%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A5%81%E0%A4%9A%E0%A4%95%E0%A4%B3%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1sKTT5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/national-international/government-official-navjot-singh-killed-in-speeding-car-crash-vvg94</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA-%E0%A4%A4%E0%A5%83%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%A4-%E0%A4%9A-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%B2-%E0%A4%AC%E0%A4%B8%E0%A4%A3-%E0%A4%B0-%E0%A4%AE-%E0%A4%A0-%E0%A4%B9-%E0%A4%A6%E0%A4%B0-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%82-%E0%A4%96%E0%A4%B3%E0%A4%AC%E0%A4%B3/ar-AA1MUzvh</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/entertainment/jannat-zubair-and-elvish-yadav-poster-romantic-pictures-goes-viral-on-social-media-svk01</t>
+          <t>https://www.msn.com/mr-in/news/other/amit-thackeray-%E0%A4%A6%E0%A4%A3%E0%A4%A6%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A4%B5-%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B9-%E0%A4%95-%E0%A4%B2-%E0%A4%AE%E0%A4%B2-%E0%A4%B9%E0%A5%87%E0%A4%9A-%E0%A4%B6-%E0%A4%95%E0%A4%B5%E0%A4%A4-%E0%A4%AF-%E0%A4%95/ar-AA1uCiYN?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/national-international/assam-earthquake-5-9-magnitude-tremors-felt-in-guwahati-udalguri-residents-panic-no-casualties-om0906</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/national-international/husband-and-his-friend-uses-momos-to-drug-wife-physical-abused-and-womens-leaves-her-unconscious-on-highway-in-chhatarpur-madhya-pradesh-crime-news-dss02</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-3/921531/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/entertainment/bigg-boss-19-update-third-week-elimination-nagma-mirajkar-natalia-janoszek-evict-and-farah-khan-hosting-weekend-ka-vaar-sm2000</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-21-september-2025-india-vs-pakistan-%E2%80%93-asia-cup-maharashtra-politics-national-international-live-update-in-marathi-940858</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/entertainment/bigg-boss-19-farah-khan-takes-over-weekend-ka-vaar-she-criticise-nehal-chudasama-baseer-ali-kuncikaa-sadanand-svk01</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/entertainment/urvashi-rautela-honoured-with-fans-favourite-star-actress-award-in-dubai-gama-awards-watch-video-sm2000</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-17-september-2025-pm-narendra-modi-75th-birthday-zp-presidentship-reservation-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/entertainment/bigg-boss-19-contestant-awez-darbar-cheated-actress-shubhi-joshi-double-dating-relationship-with-nagma-mirajkar-sm2000</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/horoscope/monday-horoscope-in-marathi-astrology-prediction-dainik-rashifal-somwarche-rashi-bhavishya-15-septeber-2025-vvg94</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-17-political-news-in-marathi-939849</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/horoscope/shani-dev-always-blesses-these-zodiac-signs-people-get-success-in-every-field-sjk95</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/breaking-news-today-18-september-monsoon-maratha-reservation-obc-bmc-election-mumbai-local-train-weather-political-doctors-strike-tajya-batmya-in-marathi-940110/amp</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://panchjanya.com/2025/09/11/434839/bharat/maharashtra/nepal-me-phanse-maharashtra-ke-150-paryatak/</t>
+          <t>https://politicalmaharashtra.in/is-the-alliance-between-the-thackeray-brothers-certain-uddhav-thackerays-hint-97844/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>http://www.raftaar.in/news/national/opposition-gets-a-jolt-from-maharashtra-in-the-vice-presidential-election-claims-of-cross-voting-shinde-faction-says-5-mps-were-in-touch</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/videos/lets-burn-ravanas-ego-ganesh-naiks-warning-to-shinde-ganesh-naik-eknath-shinde/132015/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%82%E0%A4%B8-%E0%A4%AC%E0%A4%A4-%E0%A4%B0-%E0%A4%B9-%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%89%E0%A4%AC-%E0%A4%A0-%E0%A4%B2-%E0%A4%9C-%E0%A4%A8-%E0%A4%9A-%E0%A4%86%E0%A4%A0%E0%A4%B5%E0%A4%A3-%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%AB-%E0%A4%B5-%E0%A4%A7%E0%A5%87%E0%A4%AF%E0%A4%95-%E0%A4%B5%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A1-%E0%A4%B5%E0%A4%9A%E0%A4%B2%E0%A4%82/ar-AA1CdNPz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/deeply-insensitive-political-tempers-rise-boycott-calls-grow-over-india-pakistan-asia-cup-face-off-101757810362813.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/ahmednagar-railway-station-renamed-maharashtra-government-issues-notification-what-is-new-name/articleshow/123852284.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6-%E0%A4%98%E0%A5%87-%E0%A4%B6%E0%A5%87%E0%A4%B5%E0%A4%9F%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%9C-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A5%81%E0%A4%96-%E0%A4%B9-%E0%A4%A4%E0%A5%87-%E0%A4%86%E0%A4%A3-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AB-%E0%A4%9F-%E0%A4%AC-%E0%A4%B3-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC-%E0%A4%9C%E0%A5%82%E0%A4%B2-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%9A%E0%A4%82%E0%A4%A1-%E0%A4%9A-%E0%A4%A1%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%A8%E0%A5%8D/ar-AA1MOF6O</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3622882-controversy-over-modis-relief-aid-to-flood-hit-punjab?amp</t>
+          <t>http://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%A8%E0%A4%B8%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%B5-%E0%A4%A8-%E0%A4%B6-%E0%A4%9C-%E0%A4%A7%E0%A4%B5-%E0%A4%82%E0%A4%9A-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95-%E0%A4%A5%E0%A5%87%E0%A4%9F-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%89%E0%A4%A4%E0%A4%B0%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%87%E0%A4%B6-%E0%A4%B0-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%95-%E0%A4%A2%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1MFEAF?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/9/start-giving-kunbi-certificates-to-marathas-before-17th-jarange.html</t>
+          <t>https://www.tv9marathi.com/videos/sanjay-raut-slams-eknath-shinde-modi-advertisement-and-reply-also-cm-fadnavis-over-thackeray-brand-1495206.html</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-government-to-regularise-25000-mumbai-buildings-without-occupation-certificates-says-state-minister-ashish-shelar-23593553</t>
+          <t>https://www.mymahanagar.com/maharashtra/kishori-pednekar-on-two-legs-but-see-what-happens-when-you-go-kishori-pednekars-warning-to-the-shinde-group/923218/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.etnownews.com/about/government-schemes/ladki-bahin-yojana/amp</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/?noamp=mobile</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3621066-maharashtras-namo-shetkari-mahasamman-nidhi-yojana-empowers-farmers-with-rs-189261-crore-boost?amp</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/dadar-shivaji-park-meenatai-thackeray-statue-red-color-thrown-mumbai-crime/articleshow/123936431.cms</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/maharashtra-signs-mou-with-iowa-to-boost-agriculture-technology/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%96%E0%A5%87%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B2-%E0%A4%B5-%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A5%82-%E0%A4%AD%E0%A4%97%E0%A4%A4-%E0%A4%B2-%E0%A4%82%E0%A4%AC%E0%A4%82-%E0%A4%95%E0%A4%A6%E0%A4%AE-%E0%A4%82%E0%A4%9A-%E0%A4%AD-%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A4%B0-%E0%A4%9C-%E0%A4%A7%E0%A4%B5-%E0%A4%82%E0%A4%AC%E0%A4%A6%E0%A5%8D%E0%A4%A6%E0%A4%B2-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%AF%E0%A4%B8%E0%A5%8D%E0%A4%AB-%E0%A4%9F/ar-AA1Hsx7J?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/deva-bhau-maharashtras-relentless-political-chess-master.html</t>
+          <t>https://www.navarashtra.com/maharashtra/top-marathi-news-today-breaking-news-political-news-live-update-crime-news-994890.html</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/cm-vishnu-deo-sai-steps-in-to-ensure-safe-return-of-chhattisgarh-tourists-stranded-in-nepal/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/bmc-election-raj-thackeray-will-hand-over-mumbais-subha-to-uddhav-thackeray/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/13092025/pune-weather/</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-tejashwi-yadav-calls-cm-nitish-a-cheat-minister-makes-these-big-promises-to-the-public-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/14092025/pune-weather/</t>
+          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-16-17-september-live-updates-tejashwi-yadav-bihar-adhikar-yatra-election-pm-modi-rahul-gandi-supreme-court-sahastradhara-flood-waqf/4143389/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/maharashtra-cm-distributes-seventh-instalment-of-namo-shetkari-mahasamman-kisan-yojana/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%90%E0%A4%A8-%E0%A4%A6-%E0%A4%B5-%E0%A4%B3-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%B5-%E0%A4%86%E0%A4%A3-%E0%A4%B6%E0%A4%B9%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%A4%E0%A5%81%E0%A4%9F%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AD-%E0%A4%A4-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%9A-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%87%E0%A4%B6-%E0%A4%B0/ar-AA1MTtxO</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://aboutinsider.com/vinod-shobha-narayan-patil-vsnp-defending-maratha-rights-constitutional-reform/</t>
+          <t>https://www.mymahanagar.com/maharashtra/navi-mumbai-city-petition-filed-in-janata-darbar-against-minister-ganesh-naik-by-kishore-patkar/922934/amp/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/other-cities/wadettiwar-upset-over-jaranga/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/navratri-2025-mumbai-police-will-have-strict-security-for-nine-days/amp_articleshow/124024081.cms</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/india-news/maharashtra-stuck-in-the-vortex-of-reservation-obc-organizations-are-angry-id-471400</t>
+          <t>https://yashbharat.co.in/maharashtra-deputy-cm-eknath-shindes-ex-handle-hacked-posts-with-pakistan-and-turkey-flags-spark-uproar/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bihar-news-today-in-hindi-14-september-2025-bihar-election-latest-update-nitish-kumar-1385111.html?ref_source=OI-HI&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
+          <t>https://jantaserishta.com/local/maharashtra/shinde-group-rauts-ties-with-pawar-led-to-thackeray-groups-losses-4276178</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/other-cities/15-thousand-police-recruitment-soon/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/thane-city-challenge-to-eknath-shinde-in-the-fort-itself-bjp-leader-ganesh-naiks-janata-darbar-for-the-third-consecutive-time/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/other-cities/hearing-on-maratha-reservation-begins-in-high-court/</t>
+          <t>https://www.theindiadaily.com/india/eknath-shinde-x-account-hacked-cyber-security-pakistan-t%C3%BCrkiye-flags-social-media-security-digital-platforms-cyber-crime-maharashtra-deputy-chief-minister-asia-cup-2025-news-94725</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/developed-maharashtra-by-2047-chief-minister-fadnavis-vision/articleshow/123771706.cms</t>
+          <t>https://bharatexpress.com/uttar-pradesh/bjp-mla-rajeshwar-singh-sarojini-nagar-yogi-praise-clean-image-569853</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/other-cities/now-a-youth-from-banjara-community-gave-up-his-life-for-reservation/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%9F-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-100-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%82%E0%A4%9A-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%96%E0%A4%9C-%E0%A4%A8-%E0%A4%93%E0%A4%A4%E0%A4%A3-%E0%A4%B0-167-%E0%A4%97%E0%A5%81%E0%A4%82%E0%A4%A0%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%89%E0%A4%AD%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%AD%E0%A5%82%E0%A4%A4-%E0%A4%A8-%E0%A4%AD%E0%A4%B5-%E0%A4%B7%E0%A5%8D%E0%A4%AF%E0%A4%A4-%E0%A4%85%E0%A4%B6-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%9F/ar-AA1rj5km?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.hindustantimes.com/india-news/maharashtra-dy-cm-eknath-shindes-x-account-hacked-pakistan-turkey-flags-posted-101758428709090.html</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/namo-shetkari-samman-nidhi-yojana-seventh-installment-distribute-today-check-your-account-93564</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633943-allahabad-high-court-stays-fir-proceedings-against-sambhal-cleric?amp</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/mumbai-suburban/andheri-east/mumbai-vice-chief-minister-interacts-with-tourists-15377421</t>
+          <t>https://www.hindustantimes.com/india-news/manipur-shuts-schools-in-5-districts-after-heavy-rainfall-70-yr-old-man-goes-missing-101757952408864.html</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-nepal-protests-pm-kp-sharma-oli-resigns-amid-violent-unrest-parliament-torched-looting-other-news-pune-koyta-gang-delhi-thar-accident-gold-price-hike-1383070</t>
+          <t>https://thenewsmill.com/2025/09/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maratha-reservation-government-decision-on-caste-certificates-declared-illegal-manoj-jarange-patil-issues-ultimatum-for-marathwada-issuance-1382610</t>
+          <t>https://kantoor-amersfoort.nl/sport/matteo-franzoso-non-ce-lha-fatta-morto-lo-sciatore-25enne-caduto-in-allenamento_4njEheZ5JWnJoqYkgr0rTv</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ganeshotsav-2025-one-lakh-94-thousand-ganesh-idols-were-immersed-in-mumbai/articleshow/123763432.cms</t>
+          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sickle-cell-disease-needs-serious-attention-air-ambulances-will-be-considered-in-very-remote-areas-health-minister-prakash-abitkar-maharashtra-news-mhs25091204509</t>
+          <t>https://www.punekarnews.in/national-restaurant-association-of-india-urges-maharashtra-government-to-boost-ease-of-doing-business-for-hospitality-sector-in-pune-city/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maratha-kunbi-certificate-controversy-2-5-lakh-certificates-issued-under-september-2-2025-gr-intensifying-obc-maratha-conflict-and-job-concerns-1383568</t>
+          <t>https://www.patrika.com/mumbai-news/government-will-bear-cost-of-expensive-treatment-maharashtra-took-big-decision-19948817</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/uddhav-thackeray-slams-pm-modi-over-india-pakistan-cricket-match-thackeray-sena-my-sindoor-my-nation-protest-bjp-counter-reaction-asia-cup-2025-om0906</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-date-extended-supreme-court-give-new-deadline-31st-january-2026-know-all/articleshow/123920003.cms</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/indian-tourists-stranded-in-nepal-gen-z-protest-violence/articleshow/123821831.cms</t>
+          <t>https://www.patrika.com/national-news/no-cap-on-prices-of-cars-for-guv-cm-and-judges-in-maharashtra-vehicle-policy-19954354</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/naukri-jobs-news/sbi-recruitment-2025-without-exam-government-job-get-payment-upto-1-5-lakh-sh04</t>
+          <t>https://www.amarujala.com/amp/india-news/maharashtra-deputy-chief-minister-eknath-shinde-s-x-account-hacked-news-in-hindi-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/mahayuti-is-not-building-a-metro-but-is-creating-a-debt-trap-going-to-take-a-loan-of-billions-for-thane-pune-and-nagpur-metro/</t>
+          <t>https://mandalnews.com/amravati/government-should-take-decision-with-a-common-perspective-regarding-tet-for-teachers/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/maharashtra-namo-shetkari-mahasamman-seventh-installment-devendra-fadnavis-farmers-1892-61-crores</t>
+          <t>https://www.amarujala.com/india-news/modi-govt-gave-rs-21-000-cr-for-marathwada-rail-lines-rs-450-crore-came-during-upa-time-fadnavis-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/krushi/maharashtra-cabinet-decision-four-big-decisions-in-maharashtra-state-cabinet-meeting/</t>
+          <t>https://www.amarujala.com/india-news/vhp-s-hindu-only-diktat-for-garba-open-invitation-for-violence-ramdas-athawale-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bihar-news-today-in-hindi-14-september-2025-bihar-election-latest-update-nitish-kumar-1385111.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/desh/vice-president-election-2025-cp-radhakrishnan-victory-cross-voting-nda-india-aghadi-jap93</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/breaking-news-today-live-updates-20-sept-maharashtra-political-news-rain-updates-shinde-thackeray-ajit-pawar-sharad-pawar-mumbai-pm-modi-940635/amp</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/even-if-the-thackeray-brothers-come-together-they-will-not-get-votes-yogesh-kadam/</t>
+          <t>https://www.hindisaamana.com/hau-dada-and-shinde-bankrupted-the-state-took-a-loan-of-24-thousand-crores-in-90-days/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/why-is-only-devendra-fadnavis-targeted-among-the-12-maratha-chief-ministers-of-maharashtra-questions-on-the-minds-of-maharashtra-on-the-banner-of-vaijapur-284041/</t>
+          <t>https://jantaserishta.com/world/australian-mps-met-maharashtras-eknath-shinde-discussed-business-cooperation--4269467</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/mill-workers-threaten-to-protest-again-for-hosuing-issue/articleshow/123776984.cms</t>
+          <t>https://thebharatnow.in/national/ahmednagar-railway-station-renamed-now-it-will-be-known-as-ahilyanagar/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mumbai-cooper-hospital-administration-has-started-cleaning-work-after-two-patients-were-bitten-by-rats/articleshow/123764041.cms</t>
+          <t>https://bharatexpress.com/india/update-maharashtra-deputy-cm-eknath-shindes-ex-account-hacked-photos-with-pakistan-and-turkey-flags-posted-569771/amp</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/nandurbar-news-girls-hostel-midnight-intruder-security-concerns-rds84</t>
+          <t>https://www.theindiadaily.com/india/eknath-shinde-x-account-hacked-cyber-security-pakistan-t%C3%BCrkiye-flags-social-media-security-digital-platforms-cyber-crime-maharashtra-deputy-chief-minister-asia-cup-2025-news-94725/amp</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/crime-news/western-railway-virar-dadar-mumbai-local-train-man-abuses-creates-ruckus-ladies-coach-viral-video-latest-marathi-news-aak2003</t>
+          <t>https://www.kisantak.in/amp/politics/story/akola-spinning-mill-gets-36-crore-package-relief-for-cotton-farmers-1279315-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/politics-boils-over-india-vs-pakistan-asia-cup-2025-cricket-match-demand-for-boycott-news-295086</t>
+          <t>https://bharatexpress.com/education/bpsc-71st-cce-2025-answer-key-objection-filing-final-result-1298-posts-569804/amp</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/world/demarcation-of-koliwadas-in-dp-a-pre-election-outreach-to-fishing-community-say-experts/ar-AA1MuAh8</t>
+          <t>https://mahabharti.in/pashusavardhan-vibhag-bharti-2025/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bengaluru/will-karnatakas-largest-dam-becomelarger-cabinet-to-decide-on-sept-16/articleshow/123837428.cms</t>
+          <t>https://www.amarujala.com/india-news/cpwd-floats-tender-to-install-bulletproof-glass-in-chambers-of-eam-foreign-secy-at-jn-bhawan-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/industry/mumbais-25000-buildings-to-get-occupation-certificates-under-new-policy/123842401</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-today-21st-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-ahmedabad-bullet-train-mega-block-sunday/liveblog/124023319.cms</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.dsij.in/dsijarticledetail/rs-11300-crore-infrastructure-projects-president-of-india-backed-financial-institution-signs-mou-with-nagpur-metropolitan-region-development-authority-nmrda-id001-52321</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-september-2025-marathi-live-updates-mumbai-rains-news-flood-situation-political-updates/liveblog/123988202.cms</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/hudco-shares-in-focus-after-rs-11-300-crore-mou-with-nagpur-metro/ar-AA1M9EOs</t>
+          <t>https://www.marathi.hindusthanpost.com/social/11-eligible-workers-were-given-cheques-by-eknath-shinde/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-smart-city-waterfront-project-under-scrutiny-after-structural-damages-and-misuse-allegations/articleshow/123870505.cms</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/18-of-city-s-real-estate-opened-up-by-govt-for-development-101757531718177.html</t>
+          <t>https://dainikekmat.com/%E0%A4%8F%E0%A4%95%E0%A4%A8%E0%A4%BE%E0%A4%A5-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B5%E0%A5%80%E0%A4%9F%E0%A4%B0-%E0%A4%96%E0%A4%BE/118128/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rs-10cr-rtgs-stalled-as-nmc-struggles-with-empty-coffers/articleshow/123816257.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-police-restrict-heavy-truck-movement-for-eighteen-hours-daily-to-ease-traffic-congestion/articleshow/123927129.cms</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/177909/</t>
+          <t>https://www.devdiscourse.com/article/politics/3635522-canada-recognizes-the-state-of-palestine-a-new-chapter-in-international-relations?amp</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/raj-thackeray-seems-to-have-upper-hand-in-alliance-moves-with-uddhav-claim-political-analysts/amp_articleshow/123881278.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-municipal-election-2025-mns-district-chief-raju-dindorle-will-join-bjp-mm76-rg93</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/reservation-issue-becomes-wider-in-maharashtra-even-as-govt-grapples-with-maratha-vs-obc-quota-problem-3723032</t>
+          <t>https://news18marathi.com/maharashtra/thane/thane-traffic-update-heavy-vehicles-entering-city-banned-from-6-am-to-12-midnight-ws-b-1482548.html</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.sarkaritel.com/vision-maharashtra-document-2047-is-our-guiding-principle-cm-fadnavis/</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-govt-fadnavis-cabinet-approves-8-major-decisions-including-expressway-and-new-policies-nck90</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-will-enforces-no-puc-no-fuel-policy-to-curb-vehicular-pollution-minister-pratap-sarnaik-big-announcement-know-all/articleshow/123827727.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178107/</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-1384548</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3625558-eu-tightens-grip-new-sanctions-target-shadow-fleet-and-banks?amp</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/control-over-bangladeshi-infiltrators-important-decision-of-the-state-government.html</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/ladki-behna-august-month-installment-update-maharashtra-mukhyamantri-meri-ladli-behen-scheme-19935227</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%96%E0%A4%9F-%E0%A4%96%E0%A4%9F-3000-%E0%A4%B0%E0%A5%81%E0%A4%AA%E0%A4%AF%E0%A5%87-%E0%A4%9C%E0%A4%AE-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%B2%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A4%9A-%E0%A4%98-%E0%A4%B7%E0%A4%A3-%E0%A4%B9-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A4%A4/ar-AA1LNbUF?cvid=68b8b6e3cd4941a99ed797d972e6c857&amp;ocid=U452DHP&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/land-approved-for-bhandara-judges-residence-revenue-minister-chandrashekhar-bawankules-initiative.html</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ladki-bahin-when-will-the-installment-of-ladki-bahin-yojana-for-the-month-of-august-be-available-what-did-aditi-tatkare-say/920537/</t>
+          <t>https://www.msn.com/en-in/entertainment/tv/ok-tata-bye-bye-paytm-ceo-vijay-shekhar-sharma-deleted-his-post-on-ratan-tata-s-passing-after-facing-backlash/ar-AA1s2Nt7?ocid=hpdhp17&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/ladki-bahin-yojana-august-2025-installment-maharashtra-beneficiaries-update-2751664.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/technical-panel-approves-2-stps-along-indrayani-cm/articleshow/124005440.cms</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/eknath-shinde-speaks-to-stranded-maharashtra-tourists-in-nepal-assures-help-for-safe-return-23593455</t>
+          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/sambhajinagar-hoarding-questions-why-only-fadnavis-targeted-over-maratha-quota/articleshow/123874467.cms</t>
+          <t>https://www.loksatta.com/maharashtra/garware-youth-development-centre-satara-skill-training-helps-13-rural-youths-get-jobs-rds-00-5385521/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/railways/maharashtra-renames-ahmednagar-railway-station-to-ahilyanagar/123862509?utm_source=newslisting&amp;utm_medium=latestNews</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/25000-farmers-to-attend-cms-kisan-mela-in-ramtek-today/amp_articleshow/123836580.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-gifts-namo-gardens-to-394-towns-on-pm-modis-75th-birthday-rs-394-crore-sanctioned/articleshow/123964170.cms</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-traffic-to-ease-soon-dahisar-toll-plaza-to-be-shifted-near-versova-bridge-before-diwali-article-152742117</t>
+          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/?p=457335</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/hc-to-shinde-by-what-authority-did-you-stay-navi-mumbai-civic-bodys-notice-to-raze-illegal-buildings/articleshow/123952725.cms</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/pune/pune-new-it-park-in-purandar-due-to-heavy-traffic-in-hinjewadi-vijay-shivtare-latest-news-1475517.html</t>
+          <t>https://www.devdiscourse.com/article/Newsalert/3630442-like-you-i-am-also-fully-committed-to-taking-india-us-partnership-to-new-heights-pm-modi-to-trump?amp</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/desh/karnataka-siddaramaiah-government-shivaji-maharaj-metro-station-renamed-st-mary-fadnavis-criticism-dk88</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6-%E0%A4%A6-%E0%A4%A4-%E0%A4%9C-%E0%A4%B0-%E0%A4%AD%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AD-%E0%A4%88-%E0%A4%B8%E0%A4%A2%E0%A4%B3-%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%96%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC%E0%A4%9C%E0%A5%87%E0%A4%9F%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%95%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%AE%E0%A4%A7%E0%A5%82%E0%A4%A8-%E0%A4%87%E0%A4%82%E0%A4%9F%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%82%E0%A4%97-%E0%A4%86%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%B0/ar-AA1wtpDt?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ahmednagar-railway-station-renamed-as-ahilyanagar-railway-station-home-ministry-issued-notification-asj-82-5367632/lite/</t>
+          <t>https://www.thehindu.com/news/national/andhra-pradesh/bjp-highlights-indias-economic-transformation-under-pm-modi-welcomes-gst-reforms/article70051830.ece</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/big-news-spark-of-discontent-between-chief-minister-fadnavis-and-eknath-shinde/</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/amp_articleshow/123993653.cms</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://policenama.com/maharashtra-political-except-two-thackeray-mlas-all-mlas-are-in-touch-with-shiv-sena-this-big-leaders-claim-creates-a-stir-in-politics/</t>
+          <t>https://m.economictimes.com/news/india/hardik-pandya-reveals-his-daily-fitness-routine-and-diet-secrets/the-importance-of-recovery/slideshow/123994093.cms</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-distributes-seventh-instalment-of-namo-shetkari-mahasamman-kisan-yojana20250909155017</t>
+          <t>https://m.economictimes.com/news/new-updates/navratri-2025-5-garba-looks-that-will-make-you-the-star-of-every-dandiya-night/sustainable-and-minimalist-look/slideshow/124026182.cms</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/cm-vishnu-deo-sai-steps-in-to-ensure-safe-return-of-chhattisgarh-tourists-stranded-in-nepal20250911052136-64846/</t>
+          <t>https://m.economictimes.com/news/india/h3n2-flu-outbreak-in-delhi-ncr-all-about-symptoms-treatment-and-prevention-tips/staying-safe-from-h3n2/slideshow/123977652.cms</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/in-review-meeting-of-developed-maharashtra-vision-2047-cm-fadnavis-said-we-are-moving-towards-making-maharashtra-developed-state/articleshow/123776908.cms</t>
+          <t>https://m.economictimes.com/news/new-updates/asia-cup-2025-india-vs-pakistan-t20-super-four-dubai-international-stadium-pitch-report-of-tody-match-ind-vs-pak-t20-dubai-weather-forecast-updates-today-match/amp_articleshow/124026458.cms</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/gujarat-governor-acharya-devvrat-given-additional-charge-of-maharashtra-traveled-by-train-from-ahmedabad-to-m-2025-09-14?src=story-related-links</t>
+          <t>https://m.economictimes.com/news/mumbai-news/mmrda-temporarily-suspends-monorail-services-in-mumbai/amp_articleshow/124009977.cms</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharshtra-co-guardian-ministers-gets-power-cm-fadnavis-said-said-they-also-solve-problems-know-all/articleshow/123869141.cms</t>
+          <t>https://m.economictimes.com/news/india/7-breathtaking-indian-sites-join-unesco-tentative-list-from-kerala-to-meghalaya/deccan-traps-at-panchgani-amp-mahabaleshwar-maharashtra/slideshow/124000073.cms</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-ganeshostav-2025-anant-chaturthi-2025-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shinde-deputy-cm-3/919321/</t>
+          <t>https://economictimes.indiatimes.com/news/politics-and-nation/bmc-polls-50-50-seats-for-sena-ubt-mns-in-mumbai-strongholds-60-40-in-others-say-party-leaders/articleshow/124027839.cms</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-ganeshostav-2025-anant-chaturthi-2025-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shinde-deputy-cm-4/919718/</t>
+          <t>https://economictimes.indiatimes.com/news/politics-and-nation/caste-census-communities-make-efforts-to-see-their-dominance-reflected-in-survey-outcome/articleshow/124027718.cms</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-12-september-2025-nepal-protest-cp-radhakrishnan-manoj-jarange-maratha-reservation-obc-chhagan-bhujbal-maharashtra-politics-devendra-fadnavis-eknath-shinde-maharashtra-weather-1383360</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-prakash-ambedkar-criticizes-modi-foreign-policy-us-tariff-russia-manipur-statement-135925944.html</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/live-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-maratha-reservation-obc-reservation-nepal-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shinde-deputy-c/921106/</t>
+          <t>https://www.devdiscourse.com/article/technology/3629546-nato-boosts-eastern-european-defense-with-eastern-sentry?amp</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/ahmednagar-railway-station-renamed-successfully-now-known-as-ahilyanagar/articleshow/123851201.cms</t>
+          <t>https://www.nationalheraldindia.com/amp/story/politics/maharashtra-govt-flips-again-ladki-bahin-payouts-to-resume-for-most-women</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://panchjanya.com/2025/09/11/434839/bharat/nepal-me-phanse-maharashtra-ke-150-paryatak/</t>
+          <t>https://www.lokmattimes.com/maharashtra/ladki-bahin-yojana-beneficiaries-have-not-decreased-says-minister-aditi-tatkare-a517/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/now-there-is-a-conflict-between-maratha-and-obc-cm-fadnavis-own-people-have-increased-his-tension/</t>
+          <t>https://www.lokmattimes.com/maharashtra/maharashtra-orders-aadhaar-e-kyc-for-womens-welfare-scheme-beneficiaries-a525/</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/25000-farmers-to-attend-cms-kisan-mela-in-ramtek-today/articleshow/123836580.cms</t>
+          <t>https://marathi.abplive.com/business/mukhyamantri-ladki-bahin-yojana-ekyc-compulsory-for-all-check-how-complete-this-process-1385224</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-to-host-farmers-fair-focused-on-sustainable-agriculture/articleshow/123793282.cms</t>
+          <t>https://zeenews.india.com/marathi/photos/ladki-bahin-yojana-ekyc-kashi-karaychi-rule-change-by-maharashtra-government-documents-application-process-deadline-ifnormation-every-details-you-need-to-know/940522</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/elphinstone-bridge-to-be-closed-for-traffic-from-midnight-101757618198130.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ladki-bahin-scheme-important-information-from-minister-aditi-tatkare-how-to-complete-the-e-kyc-process/articleshow/124024396.cms</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/12/moradabad-tricycles-distributed-to-differently-abled-gallery/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=moradabad-tricycles-distributed-to-differently-abled-gallery</t>
+          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/maharashtra-signs-mou-with-iowa-to-boost-agriculture-technology20250912161419-66621/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-aditi-tatkare-important-explanation-about-ladki-bahin-yojana/articleshow/123977249.cms</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/12/dr-bhagwat-turns-75.html</t>
+          <t>https://www.aninews.in/news/national/general-news/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde20250922072527</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/as-many-people-so-</t>
+          <t>https://www.uttamhindu.com/maharashtra-in-turmoil-cm-eknath-shindes-x-account-hacked/</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-hindu-erode-9WW6/20250913/281861534649383</t>
+          <t>https://politicalmaharashtra.in/deepak-kesarkar-a-leader-from-konkan-who-is-in-the-news-for-not-getting-a-place-in-the-state-cabinet-this-year-is-likely-to-get-a-big-responsibility-soon-97814/</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/bhagwat-turns-75-bjp-leaders-led-by-pm-modi-heap-praise-on-his-leadership-of-rss-10418236</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/how-the-bjp-alliance-won-maharashtra-101757921779535.html</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/deputy-chief-minister-ajit-pawars-big-statemetnt-pune-citizen-jan-samvad/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/hc-seeks-govt-s-stand-on-illegal-stay-on-demolition-by-dy-cm-101758137116362.html</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/deputy-chief-minister-eknath-shinde-visited-chhatrapati-sambhaji-nagar-125090900002_1.html</t>
+          <t>https://www.thehindu.com/news/national/uttarakhand/uttarakhand-govt-to-buy-produce-from-apple-growers-in-disaster-hit-dharali/article70076273.ece</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3621474-udhayanidhi-stalin-champions-dravidian-model-of-progress-in-tamil-nadu?amp</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/amid-india-pakistan-match-boycott-controversy-shiv-sena-leader-sanjay-raut-calls-deputy-cm-ajit-pawar-half-pakistani-b628/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/blog/india/cm-devendra-fadnavis-uddhav-thackeray-raj-thackeray-deva-bhau-does-what-says-definitely-does-doesnt-say-2-brothers-get-entangled-affairs-1-bhau-blog-amitabh-srivastava-b507/</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/maharashtra-government-vehicle-policy-revised-2025-ntc-rptc-2336368-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-2/920740/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9F%E0%A4%B5%E0%A4%9F%E0%A4%B5-%E0%A4%A4-%E0%A4%B6%E0%A5%87%E0%A4%A4-%E0%A4%9A%E0%A5%87-%E0%A4%B0%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%A8%E0%A4%82-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2%E0%A4%82-%E0%A4%95%E0%A4%82%E0%A4%9F-%E0%A4%B3-%E0%A4%86%E0%A4%B2-%E0%A4%95-%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%87%E0%A4%B2-%E0%A4%95-%E0%A4%AA%E0%A5%8D%E0%A4%9F%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%B6%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%B0/ar-AA1MRcAj</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/mumbai-pune/political-earthquake-in-pune-maval-bapu-bhegde-quits-ncp-ahead-of-civic-polls-joins-bjp-with-hundreds-of-workers-nck90</t>
+          <t>https://www.lokmatnews.in/business/mukhyamantri-mazi-ladki-bahin-yojana-no-e-kyc-no-rs-1500-all-beneficiaries-can-avail-facility-visiting-web-portal-b507/amp/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.swarajdigital.in/nation/cp-radhakrishnan-vice-president-oath</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%B2-%E0%A4%AC%E0%A4%A6%E0%A4%B2%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A4%B0-%E0%A4%A6-%E0%A4%B6-%E0%A4%A4-%E0%A4%9A/ar-AA1vkDcb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/uddhav-lacks-moral-right-to-oppose-india-pak-match-shiv-sena-101757765668199.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/msrtc-employees-gives-big-warning-to-maharashtra-government/amp_articleshow/123997908.cms</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://nagalandpost.com/leaders-of-oppn-parties-target-govt-bcci-for-india-pak-match/</t>
+          <t>https://www.navarashtra.com/maharashtra/top-marathi-news-today-live-breaking-news-live-updates-maharashtra-politics-live-news-latest-news-993761.html</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/india/cm-siddaramaiah-announces-420-crore-caste-survey-in-karnatak-to-cover-7-crore-people-during-dusshera</t>
+          <t>https://m.economictimes.com/nri/latest-updates/h1b-100k-h-1b-fee-sparks-rush-in-us-flight-bookings-makemytrip/amp_articleshow/124024106.cms</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://www.navakal.in/rajkiya/devendra-fadnavis-a-capable-chief-minister-mp-sanjay-raut-marathi-news/</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/maharashtra-deputy-cm-eknath-shinde-takes-action-against-builders-of-65-illegal-buildings-in-kalyan-dombivli/amp_articleshow/124011193.cms</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/sanjay-raut-chaggan-bhujbal/</t>
+          <t>https://www.indiatvnews.com/amp/maharashtra/eknath-shinde-maharashtra-deputy-cm-x-account-hacked-hackers-post-pakistan-turkey-flags-hacking-sparks-uproar-2025-09-21-1009219</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/ajit-pawar-launches-state-wide-jansamvad-from-hadapsar-4-000-complaints-registered-on-day-one-101757789360861.html</t>
+          <t>https://www.newsx.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-71735/</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/hudco-shares-in-focus-after-rs-11300-crore-mou-with-nagpur-metro/articleshow/123777233.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%95%E0%A5%87%E0%A4%B2-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0/ar-AA1sjqmA?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-cabinet-extends-power-tariff-concession-for-lift-irrigation-schemes-until-march-2027</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-update-monsoon-2025-rain-update-maharashtra-rain-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shinde-9/923517/</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278571243/maharashtra-signs-mou-with-iowa-to-boost-agriculture-technology</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-and-ncp-allege-biased-ward-formation-in-navi-mumbai-and-demand-revision/articleshow/123793239.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/pil-questions-ganesh-naik-s-right-to-hold-janata-darbars-in-navi-mumbai-101758223019260-amp.html</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/only-ias-officers-to-head-municipal-corporations-mandates-cm-101757530879984.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/navi-mumbai-city-petition-filed-in-janata-darbar-against-minister-ganesh-naik-by-kishore-patkar/922934/</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bhujbal-fadnavis-and-the-obcs-101757877151905.html</t>
+          <t>https://www.hindustantimes.com/india-news/didnt-do-so-for-power-but-ajit-pawar-on-why-he-split-with-sharad-pawar-101758292291397-amp.html</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/over-25-000-buildings-without-oc-in-mumbai-to-be-regularised-under-new-policy-minister-2025-09-11</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/opposition-ruling-parties-spar-over-rahuls-fresh-vote-chori-charges-seek-fadnavis-resignation/article70068451.ece</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A4%B0-%E0%A4%95%E0%A5%9C%E0%A4%95-%E0%A4%95%E0%A5%88%E0%A4%AA%E0%A5%8D%E0%A4%9F%E0%A4%A8-%E0%A4%AC%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A4%97%E0%A4%B0-%E0%A4%A8-%E0%A4%97%E0%A4%AE-%E0%A4%82-%E0%A4%95-%E0%A4%85%E0%A4%AC-%E0%A4%B8-%E0%A4%B0%E0%A5%8D%E0%A4%AB-ias-%E0%A4%B9-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%9C-%E0%A4%A8-%E0%A4%B2-%E0%A4%9C-%E0%A4%8F-%E0%A4%B5%E0%A4%9C%E0%A4%B9/ar-AA1MoZu8</t>
+          <t>https://www.thehindu.com/news/national/kerala/kerala-minister-v-sivankutty-taken-to-hospital-after-experiencing-dizziness-in-assembly/article70068758.ece</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://www.psuconnect.in/hi/memorandum-of-understanding/hudco-sign-mou-with-nagpur-metropolitan-region-development-authority-to-provide-funds-</t>
+          <t>https://www.msn.com/en-in/news/India/bjp-led-mahayuti-alliance-to-sweep-maharashtra-predicts-axis-my-india-exit-poll/ar-AA1uvbog?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178120/</t>
+          <t>https://www.aninews.in/news/national/acharya-devvrat-sworn-in-as-governor-of-maharashtra-reads-oath-in-sanskrit20250915150141</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178444/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/the-ed-governments-vehicle-is-running-fast-only-on-paper-issued-14590-gr-in-9-months-the-matter-is-in-a-mess-on-the-ground/</t>
+          <t>https://www.latestly.com/google-trends/18092025/swachhata-hi-seva/</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://khabarindia.in/%E0%A4%8F%E0%A4%A8%E0%A4%AC%E0%A5%80%E0%A4%B8%E0%A5%80%E0%A4%B8%E0%A5%80-%E0%A4%AC%E0%A4%A8%E0%A4%BE%E0%A4%8F%E0%A4%97%E0%A4%BE-%E0%A4%AD%E0%A4%B5%E0%A4%BF%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%95/</t>
+          <t>https://thenewsmill.com/2025/09/maharashtra-mmrda-to-suspend-monorail-services-on-september-20-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/mumbai/ashish-shelar-assured-on-the-policy-of-issuing-ocs-to-more-than-25000-buildings/</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-assembly-election-2025-cm-nitish-eyes-the-lost-seats-of-paswan-and-kushwaha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/~/acharya-devvrat-arrives-in-mumbai-will-be-sworn-in-as-maha-guv-on-monday/States/news/3576851.html</t>
+          <t>https://www.lokmatnews.in/business/mukhyamantri-mazi-ladki-bahin-yojana-no-e-kyc-no-rs-1500-all-beneficiaries-can-avail-facility-visiting-web-portal-b507/</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/no-shortage-of-resources-for-tribal-development-cm-vishnu-dev-sai20250911031606-64765/</t>
+          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/vp-election-cp-radhakrishnan-demits-office-gujarat-governor-acharya-devvrat-gets-additional-charge-of-maharashtra/articleshow/123828786.cms</t>
+          <t>https://www.amarujala.com/video/india-news/tejashwi-yadav-bihar-adhikar-yatra-tejashwi-yadav-afraid-of-rahul-gandhi-bihar-election-2025-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3621476-radhakrishnan-triumphs-a-victory-beyond-party-lines?amp</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-rahul-gandhi-and-tejashwi-yadav-lalu-yadav-decide-on-seat-sharing-within-mahagathbandhan-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3621481-congress-gears-up-for-bihar-assembly-elections-strategic-talks-and-alliances?amp</t>
+          <t>https://www.amarujala.com/video/india-news/chief-minister-bhagwant-mann-launched-mission-chadti-kala-for-flood-victims-in-punjab-made-this-appeal-to-t-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/vision-maharashtra-document-2047-our-guiding-principle-cm-fadnavis-449925</t>
+          <t>https://www.msn.com/mr-in/news/other/raigad-guardian-minister-%E0%A4%A8-%E0%A4%97-%E0%A4%97-%E0%A4%B5%E0%A4%B2%E0%A5%87-%E0%A4%A8-%E0%A4%A4%E0%A4%9F%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%B0-%E0%A4%AF%E0%A4%97%E0%A4%A1%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%B5%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%97%E0%A5%81%E0%A4%97%E0%A4%B2-%E0%A4%9C%E0%A4%AC-%E0%A4%AC%E0%A4%A6-%E0%A4%B0-%E0%A4%A5%E0%A5%87%E0%A4%9F/ar-AA1yaaoP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/other/assistance-of-rs-5-lakhs-announced-for-hospitalised-cricketer-kambli-shiv-sena-assures-all-possible-help/ar-AA1wspSW?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%AF%E0%A5%82%E0%A4%AA-%E0%A4%AA%E0%A5%85%E0%A4%9F%E0%A4%B0%E0%A5%8D%E0%A4%A8%E0%A4%B2-%E0%A4%AB-%E0%A4%9F-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A5%85%E0%A4%9F%E0%A4%B0%E0%A5%8D%E0%A4%A8%E0%A4%B5%E0%A4%B0-%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%A4-cm-%E0%A4%AA%E0%A4%A6-%E0%A4%B8-%E0%A4%A0-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A5%8D%E0%A4%AF%E0%A5%81%E0%A4%B2/ar-AA1yKFrb?cvid=14C0E25EB3514BFF8311922AA83DAF4A&amp;ocid=nyl&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/sports/cricket/how-can-blood-cricket-flow-together-uddhav-thackeray-opposes-india-pak-match-protests-to-target-pm-modi/ar-AA1MuVCW</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/acharya-devvrat-is-the-new-governor-of-maharashtra-took-oath-in-the-presence-of-the-chief-minister.amp.html</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/mumbai-activists-of-rival-shiv-sena-factions-clash-over-beautification-work-at-prabhadevi-10452372</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/amp_articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AA%E0%A5%83%E0%A4%A5%E0%A5%8D%E0%A4%B5-%E0%A4%B0-%E0%A4%9C-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%B8%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4/ar-AA1uFHkz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mahayuti-election-strategy-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9D%E0%A5%87%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%B2-%E0%A4%9A-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%81%E0%A4%95-%E0%A4%89%E0%A4%A6%E0%A4%AF-%E0%A4%B8-%E0%A4%AE%E0%A4%82%E0%A4%A4/ar-AA1MsnDU</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/?amp</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sanjay-raut-%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%9C%E0%A4%B0-%E0%A4%B9-%E0%A4%82%E0%A4%A6%E0%A5%82-%E0%A4%85%E0%A4%B8-%E0%A4%B2-%E0%A4%A4%E0%A4%B0-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%82%E0%A4%9A-%E0%A4%A4-%E0%A4%AB-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%A7%E0%A4%A1-%E0%A4%A1%E0%A4%B2/ar-AA1MsxoR</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/editorial/agralekha/thackaray-political-convenience-and-thackerays-arrow/920323/</t>
+          <t>https://www.primetvindia.com/eknath-shindes-x-account-has-been-hacked-posts-of-pakistani-and-turkish-flags-have-sparked-concern/</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/sharad-pawar-will-enter-the-fray-rohit-pawar-is-preparing-hard/</t>
+          <t>https://indiagroundreport.com/mumbai-acharya-devvrat-took-additional-charge-as-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34520/</t>
+          <t>https://dainikekmat.com/ministerial-status-to-the-chairman-of-parashuram-corporation/117448/</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/pune-city-party-melava-neelam-gorhe-guidance/</t>
+          <t>https://www.ptinews.com/story/national/bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/2921301</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/demarcation-of-koliwadas-in-dp-a-pre-election-outreach-to-fishing-community-say-experts/articleshow/123872340.cms</t>
+          <t>https://www.thehindu.com/news/national/karnataka/bk-singh-to-head-sit-formed-to-probe-aland-voter-fraud-case/article70074360.ece</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/i-am-an-uncompromising-nationalist-says-vice-president-elect-cp-radhakrishnan-3721393</t>
+          <t>https://www.thehindu.com/news/national/congress-doing-negative-politics-over-great-nicobar-project-environment-minister/article70067325.ece</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://www.apnnews.com/nbcc-to-build-future-ready-naveen-nagpur-as-the-international-business-finance-center-ibfc/</t>
+          <t>https://www.bhaskarenglish.in/amp/national/news/bhaskar-evening-wrap-21-09-25-pm-modi-gst-white-house-trump-mithun-manhas-135977196.html</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/mumbai-dahisar-toll-plaza-relocation-near-versova-bridge-before-diwali-hindi/</t>
+          <t>https://mahasamvad.in/178810/</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178029/</t>
+          <t>https://www.mymahanagar.com/maharashtra/dcm-eknath-shinde-criticized-rahul-gandhi-evm-vote-chori-case/922837/</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178213/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A4-%E0%A4%96%E0%A4%B0%E0%A5%87%E0%A4%A6-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A4%A4%E0%A5%87%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0%E0%A4%9A-%E0%A4%A7%E0%A4%A8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%A1%E0%A5%87-%E0%A4%A6-%E0%A4%96%E0%A4%B2-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%85%E0%A4%82%E0%A4%9C%E0%A4%B2-%E0%A4%A6%E0%A4%AE-%E0%A4%A8-%E0%A4%AF-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%85%E0%A4%AC%E0%A5%8D%E0%A4%B0%E0%A5%81-%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A4%B8-%E0%A4%A8-%E0%A4%9A-%E0%A4%A6-%E0%A4%B5/ar-AA1yofLg?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/nagpur/important-mous-with-companies-for-the-development-of-new-nagpur-93565</t>
+          <t>https://www.aninews.in/news/national/general-news/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi20250917174418</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%BE%E0%A4%9A%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A4%A8%E0%A4%BF%E0%A4%AF%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%A4/117060/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%AE-%E0%A4%B3-%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0%E0%A4%B9-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%A1%E0%A4%9A%E0%A4%A3-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%B9-%E0%A4%A4-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%B5-%E0%A4%A2%E0%A4%B5%E0%A4%B2%E0%A4%82-%E0%A4%9F%E0%A5%87%E0%A4%A8%E0%A5%8D%E0%A4%B6%E0%A4%A8/ar-AA1vHvrk?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://m.daijiworld.com/news/newsDisplay?newsID=1292051</t>
+          <t>https://vishwanewsmarathi.com/action-should-be-taken-against-deputy-chief-minister-shinde-sanjay-raut-lashed-out/</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/girl-falls-into-open-manhole-escapes-unhurt-in-hyderabad/articleshow/123837508.cms</t>
+          <t>https://vishwanewsmarathi.com/we-will-get-success-like-the-assembly-chief-minister-shinde/</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/ludhiana/crumbling-jagraon-bridge-gets-facelift/articleshow/123837098.cms</t>
+          <t>https://www.dainikprabhat.com/rs-20-crores-of-funds-were-received-without-any-mla-shinde-faction-leaders-statement-increases-mahayutis-problems/</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1291660</t>
+          <t>https://marathi.timesnownews.com/maharashtra/explainer-a-test-of-mahayuti-in-bmc-elections-shiv-sena-bjp-tug-of-war-over-91-seats-article-152842707</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.indianewsstream.com/jarange-patil-gives-quota-ultimatum-to-maha-govt-demands-kunbi-certificates-by-sep-17/</t>
+          <t>https://www.marathi.hindusthanpost.com/social/get-20-crores-even-though-i-am-not-an-mla-sada-saravankar/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-chhagan-bhujbal-urges-cm-devendra-fadnavis-to-withdraw-gr-on-kunbi-certificates-for-marathas</t>
+          <t>https://www.timemaharashtra.com/politics/the-way-sanjay-rauts-tongue-is-slipping-every-day-ubatya-will-soon-have-to-celebrate-a-slip-up-festival-jyoti-waghmare/133177/amp/</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/bmc-election-shiv-sena-in-action-mode-in-the-backdrop-of-municipal-elections-chief-executive-committee-announced/</t>
+          <t>https://dainikekmat.com/attorney-general-birendra-saraf-resigns/117476/</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/vp-elect-c-p-radhakrishnan-demits-office-as-maharashtra-governor-rashtrapati-bhavan-3722935</t>
+          <t>https://www.tribuneindia.com/news/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education/amp/?utm=relatedarticles</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/vp-polls-nda-has-numbers-stacked-in-its-favour-3717659</t>
+          <t>https://www.freepressjournal.in/mumbai/pm-narendra-modi-a-strong-national-leader-maha-cm-devendra-fadnavis-wishes-pm-modi-on-his-75th-bday-hails-his-vision-to-reshape-indias-fortune</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/12/qatars-prime-minister-will-meet-top-u-s-officials-in-washington-d-c-video/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=qatars-prime-minister-will-meet-top-u-s-officials-in-washington-d-c-video</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/raigarh/alibag/raigad-sheetal-gogawal-appointed-as-state-secretary-of-shiv-udyog-sena-15378981</t>
+          <t>https://mahasamvad.in/178444/</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/vice-president-election-cross-voting-jolts-india-bloc-bjp-gives-clear-message-to-maha-vikas-aghadi/articleshow/123805413.cms</t>
+          <t>https://www.tarunmitra.in/state/maharashtra/maharashtra-governments-unique-initiative-plan-to-build-namo-park-on/article-105368</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/national-marathi-news/voting-for-vice-presidential-election-today-125090900005_1.html</t>
+          <t>https://jantaserishta.com/local/maharashtra/the-mahayutis-saffron-flag-will-fly-in-other-municipalities-including-the-mumbai-municipal-corporation--4278128</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/mumbai-s-elphinstone-bridge-to-close-on-friday-traffic-police-announces-diversions-full-details-here-23593582</t>
+          <t>https://www.marathiebatmya.com/political/mou-signed-between-mahagenco-and-nmrda-in-the-presence-of-the-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/final-safety-check-of-mumbai-metro-line-2b-phase-1-to-start-tomorrow-10240149/</t>
+          <t>https://www.msn.com/en-in/news/india/pm-s-birthday-a-black-day-for-democracy-says-congress-mp-praniti-shinde-bjp-hits-back/ar-AA1MFgP7</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/maratha-reservation-demand-of-jarange-accepted-governments-big-decision-when-will-the-cases-against-maratha-protesters-be-withdrawn/920282/</t>
+          <t>https://www.devdiscourse.com/article/politics/3631054-maharashtra-leaders-hail-pm-modis-visionary-leadership-on-75th-birthday?amp</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%AF-%E0%A4%B2%E0%A5%87%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%A6-%E0%A4%A1%E0%A4%BC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%9F-%E0%A4%AE-%E0%A4%AC%E0%A4%A8-%E0%A4%95%E0%A4%B0-%E0%A4%95-%E0%A4%AE-%E0%A4%95%E0%A4%B0-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82%E0%A4%B8-%E0%A4%B0%E0%A5%8D%E0%A4%AB-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%B5-%E0%A4%B2%E0%A5%87-%E0%A4%B5-%E0%A4%9C%E0%A5%8D%E0%A4%9E-%E0%A4%AA%E0%A4%A8-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87/ar-AA1M1Yno</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-deputy-chief-minister-eknath-shinde-launches-the-seva-fortnight-chief-minister-samruddhi-panchayat-raj-abhiyan-in-thane-district/922593/</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-cm-devendra-fadnavis-talk-on-obc-reservation/articleshow/123889715.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/shiv-sena-portfolio-list-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%A8%E0%A5%87-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%97%E0%A5%83%E0%A4%B9-%E0%A4%96-%E0%A4%A4%E0%A4%82-%E0%A4%A6-%E0%A4%B2%E0%A4%82%E0%A4%9A-%E0%A4%A8-%E0%A4%B9-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%B2-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%95-%E0%A4%AF-%E0%A4%AE-%E0%A4%B3-%E0%A4%B2%E0%A4%82/ar-AA1whDCo?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/rohit-pawar-attacks-devendra-fadnavis-over-farmer-suicide-125090800034_1.html</t>
+          <t>https://thefocusindia.com/maharashtra-news/bhujbal-retorts-pawar-did-not-attend-all-party-meeting-reservation-284529/</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/dahisar-toll-naka-to-be-relocated-before-diwali</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/how-can-blood-cricket-flow-together-uddhav-thackeray-opposes-india-pak-match-protests-to-target-pm-modi/articleshow/123878115.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/politics/3632371-trumps-crackdown-on-antifa-following-kirk-assassination?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/dusu-elections-today-all-about-key-candidates-voting-guidelines-traffic-advisory-101758167381891.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>https://www.newsonair.gov.in/union-minister-piyush-goyal-launches-swasth-nari-sashakt-parivar-campaign-in-mumbai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/politics/3630214-chalo-jeete-hain-bjp-launches-film-tour-across-bihar?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>https://www.newsx.com/india/i-call-on-youth-to-root-out-addiction-from-societysukanta-majumdar-joins-namo-yuva-run-in-kolkata20250921104533-75973/amp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nashik/kumbh-mela-committee-accommodates-representatives-of-bjps-mahayuti-allies-ncp-shiv-sena/articleshow/124020480.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-workers-burn-effigy-of-shiv-sena-ubt-mp-sanjay-raut-for-his-remark-about-anand-dighe/articleshow/123981706.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/full-page-newspaper-ads-and-slew-of-initiatives-shiv-sena-goes-all-out-to-celebrate-pm-s-birthday/2925344</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/opposition-targets-shiv-sena-over-mumbais-gb-hway-traffic-ahead-of-civic-polls/articleshow/124020437.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/politics/3630229-supreme-courts-deadline-sparks-political-reactions-in-maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-23595086</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/national/shiv-sena-workers-protest-against-rauts-remark-about-dighe-10476846</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/national/paint-thrown-on-statue-of-meenatai-thackeray-at-mumbais-shivaji-park-10472418</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%B8%E0%A4%AE%E0%A4%82%E0%A4%A6%E0%A4%B0-%E0%A4%B9%E0%A5%82%E0%A4%82-%E0%A4%B2-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%B5-%E0%A4%AA%E0%A4%B8-%E0%A4%86%E0%A4%8A%E0%A4%82%E0%A4%97-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AC%E0%A4%A8%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AE%E0%A4%97%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%A1-%E0%A4%AA%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%8F%E0%A4%AE/ar-AA1uBRUD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/mumba-devi-vidhan-sabha-chunav-result-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%B8-%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%A8-%E0%A4%AE-%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%AC-%E0%A4%9C-%E0%A4%AF%E0%A4%B9-%E0%A4%82-%E0%A4%AA%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%A4-%E0%A4%9C-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C%E0%A5%81%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A4%B0-%E0%A4%85%E0%A4%AA%E0%A4%A1%E0%A5%87%E0%A4%9F/ar-AA1uBcsK?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-148-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-103-%E0%A4%B8-%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A5%87%E0%A4%97-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%95%E0%A5%81%E0%A4%9B-%E0%A4%B8-%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%B8%E0%A5%8D%E0%A4%A5-%E0%A4%A4-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%A8%E0%A4%B9-%E0%A4%82/ar-AA1tbokT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%9A-%E0%A4%B0-%E0%A4%9A-%E0%A4%B6%E0%A4%82%E0%A4%96-%E0%A4%AB%E0%A5%81%E0%A4%82%E0%A4%95%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%9A-%E0%A4%B0-%E0%A4%B8-%E0%A4%A0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%86%E0%A4%98-%E0%A4%A1-%E0%A4%B8%E0%A4%AD%E0%A5%87%E0%A4%9A-%E0%A4%A4-%E0%A4%B0-%E0%A4%96-%E0%A4%86%E0%A4%A3-%E0%A4%B5%E0%A5%87%E0%A4%B3%E0%A4%B9-%E0%A4%A0%E0%A4%B0%E0%A4%B2/ar-AA1toilT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/sushma-andhare-%E0%A4%A1%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%9F-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%96%E0%A4%B0%E0%A5%87-%E0%A4%B0%E0%A5%81%E0%A4%AA-%E0%A4%86%E0%A4%9C-%E0%A4%AC-%E0%A4%B9%E0%A5%87%E0%A4%B0-%E0%A4%86%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A5%81%E0%A4%B7%E0%A4%AE-%E0%A4%85%E0%A4%82%E0%A4%A7-%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%98%E0%A4%A3-%E0%A4%98-%E0%A4%A4/ar-AA1HY5L7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/sanjay-raut-%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%9C%E0%A4%B0-%E0%A4%B9-%E0%A4%82%E0%A4%A6%E0%A5%82-%E0%A4%85%E0%A4%B8-%E0%A4%B2-%E0%A4%A4%E0%A4%B0-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%82%E0%A4%9A-%E0%A4%A4-%E0%A4%AB-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%A7%E0%A4%A1-%E0%A4%A1%E0%A4%B2/ar-AA1MsxoR?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/mahayuti-election-strategy-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9D%E0%A5%87%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%B2-%E0%A4%9A-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%81%E0%A4%95-%E0%A4%89%E0%A4%A6%E0%A4%AF-%E0%A4%B8-%E0%A4%AE%E0%A4%82%E0%A4%A4/ar-AA1MsnDU?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%AA-%E0%A4%A0-%E0%A4%82%E0%A4%AC-%E0%A4%95-%E0%A4%A6-%E0%A4%B2-%E0%A4%A8-%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%8F%E0%A4%95-%E0%A4%B5-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B8-%E0%A4%82%E0%A4%97%E0%A5%82%E0%A4%A8-%E0%A4%9F-%E0%A4%95%E0%A4%B2%E0%A5%87/ar-AA1u7Jyx?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/business/3629575-thane-takes-traffic-control-measures-midnight-movement-for-heavy-vehicles</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/national/fadnavis-leads-maharashtra-in-greeting-pm-modi-on-birthday-calls-him-global-statesman-inspiration-10472727</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-polls-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%B5-%E0%A4%A8%E0%A4%96%E0%A5%87%E0%A4%A1%E0%A4%BC%E0%A5%87-%E0%A4%AB-%E0%A4%B0-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%82-mumbai-%E0%A4%95-%E0%A4%87%E0%A4%B8-%E0%A4%B8-%E0%A4%9F-%E0%A4%B8%E0%A5%87-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%85%E0%A4%9F%E0%A4%95%E0%A4%B2%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%9F-%E0%A4%95%E0%A4%9F/ar-AA1spTNA?cvid=BC85FE97FDE740EB8B309A7E01FCE3DD&amp;ocid=hpmsn&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/iti-students-will-run-cleanliness-campaign-in-750-villages-special-campaign-by-minister-mangal-prabhat-lodha-on-pm-modis-birthday/articleshow/123915570.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>https://tamil.getlokalapp.com/amp/maharashtra-news/the-chairman-of-this-corporation-got-ministerial-status-15423436</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>https://deshbandhump.com/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%AA%E0%A4%BE%E0%A4%B2%E0%A4%BF%E0%A4%95%E0%A4%BE-%E0%A4%B8%E0%A4%B9%E0%A4%BF%E0%A4%A4-%E0%A4%85%E0%A4%A8%E0%A5%8D/</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>https://www.hindisaamana.com/the-state-has-a-debt-of-rs-9-lakh-crores-development-of-the-state-is-stalled-deva-bhau-is-busy-in-advertising/</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>https://bharatexpress.com/india/bihar-news-nitish-governments-big-decision-vikas-mitras-to-get-tablets-education-workers-to-get-help-with-smartphones-569758/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>https://indiagroundreport.com/mumbai-acharya-devvrat-took-additional-charge-as-governor-of-maharashtra/?amp=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/politics/bjps-criticism-of-sanjay-raut/</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>https://lokmanthan.com/arrangements-should-be-made-to-issue-all-relevant-permits-for-industries-in-a-single-application-chief-minister-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-23595086</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/jarange-plans-national-maratha-convention-in-delhi-hake-warns-of-obc-march-to-mumbai/articleshow/123952548.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/eps-calls-on-amit-shah-in-delhi-meets-vpradhakrishnan-101758052028562.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/acharya-devvrat-oath-maharashtra-governor-10250775/</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/international/us/charlie-kirk-memorial-in-arizona-set-to-draw-nearly-100000-people-a-look-at-americas-largest-funerals/amp_articleshow/124025590.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>http://www.uniindia.com/gujarat-governor-acharya-devvrat-sworn-in-as-maharashtra-governor/west/news/3577613.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/transporters-cite-increased-costs-supply-disruptions-want-new-traffic-curbs-lifted/articleshow/124005110.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/modi-likely-to-inaugurate-navi-mumbai-airport-101758050399819.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/ashwini-vaishnaw-conducts-breakthrough-of-bullet-train-tunnel-says-first-phase-to-start-in-2027/article70073192.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/trial-runs-on-metro-4s-cadbury-junction-gaimukh-stretch-to-commence-monday-mumbai-metropolitan-region-development-authority-officials-say-corridor-on-track-for-year-end-operations/articleshow/124001171.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/amp/story/maharashtra/maharashtra-govt-fadnavis-cabinet-approves-8-major-decisions-including-expressway-and-new-policies-nck90</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/mumbai/sanjay-raut-statement-on-anand-dighe-thane-balasaheb-thackeray-photo-advertise-shivsena-maharashtra-marathi-news-1385015</t>
         </is>
       </c>
     </row>

--- a/Output/Eknath Shinde/extracted_links_Eknath Shinde_failed_links.xlsx
+++ b/Output/Eknath Shinde/extracted_links_Eknath Shinde_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A498"/>
+  <dimension ref="A1:A468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,2359 +438,2359 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shiv-sena-protests-against-sanjay-raut-of-sena-ubt-for-%E2%80%98insulting%E2%80%99-eknath-shinde%E2%80%99s-mentor/2934437</t>
+          <t>https://www.ndtv.com/india-news/eknath-shindes-x-account-briefly-hacked-hackers-post-pics-of-pak-turkey-flags-9315607</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/eknath-shinde-maharashtra-deputy-cm-x-account-hacked-hackers-post-pakistan-turkey-flags-hacking-sparks-uproar-2025-09-21-1009219</t>
+          <t>https://www.tribuneindia.com/news/india/maharashtra-deputy-cm-eknath-shindes-x-account-hacked/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/when-i-go-to-villages-i-feel-fresh-my-opponents-get-depressed-says-dy-cm-eknath-shinde-at-launch-of-gram-samruddhi-yojana/articleshow/123964878.cms</t>
+          <t>https://www.msn.com/en-in/news/india/not-in-race-to-claim-credit-eknath-shinde-on-ads-featuring-only-d-fadnavis/ar-AA1M0Xg8?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ahead-of-bmc-elections-eknath-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena-23594416</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/when-i-go-to-villages-i-feel-fresh-my-opponents-get-depressed-says-dy-cm-eknath-shinde-at-launch-of-gram-samruddhi-yojana/articleshow/123964878.cms</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ahead-of-bmc-elections-eknath-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena-23594416</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/maharashtra-deputy-cm-eknath-shindes-x-account-hacked/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-dy-cm-eknath-shindes-x-account-hacked/2934860</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/maharashtra-deputy-cm-eknath-shinde-takes-action-against-builders-of-65-illegal-buildings-in-kalyan-dombivli/articleshow/124011193.cms</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-dy-cm-eknath-shindes-x-account-hacked/ar-AA1MZ0l6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/maharashtra-deputy-cm-eknath-shinde-takes-action-against-builders-of-65-illegal-buildings-in-kalyan-dombivli/articleshow/124011193.cms</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-images-of-pakistan-turkey-flags-posted/articleshow/124024337.cms</t>
+          <t>https://www.msn.com/en-in/autos/general/maharashtra-dy-cm-eknath-shinde-attends-autofest-2025-in-thane/ar-BB1rljGt?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-dy-cm-eknath-shindes-x-account-hacked-9315607/amp/1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-images-of-pakistan-turkey-flags-posted/articleshow/124024337.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education/</t>
+          <t>https://www.ptinews.com/stories-detail/national/maharashtra-dy-cm-eknath-shindes-x-account-hacked/2934860/0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/paint-thrown-at-bust-of-uddhav-thackerays-late-mother-sena-workers-angry-probe-on-101758106562970.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/gst-rate-cut-will-boost-economy-shield-india-from-us-tariff-hikes-says-maharashtras-deputy-chief-minister-eknath-shinde/articleshow/124002613.cms</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/gst-rate-cut-will-boost-economy-shield-india-from-us-tariff-hikes-says-maharashtras-deputy-chief-minister-eknath-shinde/articleshow/124002613.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-cong-leader-questions-cyber-security-23595093</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633937-crackdown-on-unauthorized-buildings-in-thane-eknath-shinde-leads-investigation?amp</t>
+          <t>https://zeenews.india.com/india/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked-hackers-post-pakistan-turkey-flags-2962608.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3630294-eknath-shinde-criticizes-congress-amid-controversy-over-ai-video</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-gifts-modi-394-namo-udyans-101758050819661.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/health/health-news/maharashtra-govt-formation-bjp-cm-s-name-still-under-wraps-all-eyes-on-unwell-shinde-s-big-decision/ar-AA1v3aC9?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
+          <t>https://www.aninews.in/news/national/politics/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother20250916212035</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-gifts-modi-394-namo-udyans-101758050819661.html</t>
+          <t>https://www.newsband.in/article_detail/allies-in-conflict-bjp-shinde-sena-lock-horns-on-dahisar-toll-shift</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.ndtvprofit.com/amp/nation/thane-metro-4a-trial-run-on-monday-check-station-list-and-other-key-details</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde-23595190</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/states/Ahead-of-BMC-polls-Shinde-asks-ex-corporators-to-tell-people-about-work-done-by-Shiv-Sena/2921488</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-charges-baseless-says-ekanth-shinde-23594783</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/find-the-masterminds-behind-the-kdmc-illegal-buildings-scam-shinde-101758309996962.html</t>
+          <t>https://www.hindustantimes.com/india-news/acharya-devvrat-takes-oath-as-maharashtra-governor-101757915941969.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/politics/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother20250916212035/</t>
+          <t>https://kashmirlife.net/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-406229/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked-hackers-post-pakistan-turkey-flags-2962608.html</t>
+          <t>https://www.indiatvnews.com/video/news/pm-modi-adopts-nation-first-policy-eknath-shinde-slams-congress-over-remarks-on-pm-s-mother-2025-09-17-1008597</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-charges-baseless-says-ekanth-shinde-23594783</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-cm-fadnavis-eknath-shinde-take-metro-ride-during-line-4-and-4a-trial-run-107480</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Dy-CM-Shinde-s-X-account-hacked;-Cong-leader-questions-cyber-security/2935531</t>
+          <t>https://realty.economictimes.indiatimes.com/news/industry/strict-action-ordered-against-65-illegal-buildings-in-kalyan-dombivli-by-deputy-chief-minister-eknath-shinde/124008652</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi20250917174418?amp=1</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-23595086?button=next</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bombay-hc-can-plea-against-shinde-order-be-a-pil/articleshow/124022877.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-cm-fadnavis-eknath-shinde-take-metro-ride-during-line-4-and-4a-trial-run-107480/6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://kashmirlife.net/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-406229/</t>
+          <t>https://timesofindia.indiatimes.com/india/not-an-mla-but-get-rs-20-cr-in-funds-sena-leader-sarvankar-boasts-later-clarifies/articleshow/124028510.cms</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-dy-cm-eknath-shindes-x-account-hacked-pakistan-turkey-flags-posted-101758428709090-amp.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/awhad-slams-the-states-selective-compassion-over-demolition-notices</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/namo-gardens-to-be-developed-in-394-municipal-councils-and-nagar-panchayats-in-maharashtra-23594437</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/video/news/pm-modi-adopts-nation-first-policy-eknath-shinde-slams-congress-over-remarks-on-pm-s-mother-2025-09-17-1008597</t>
+          <t>https://www.bignewsnetwork.com/news/278582902/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/women-office-bearers-workers-of-sena-ubt-from-palghar-join-shinde-led-sena-ahead-of-local-polls/2927880</t>
+          <t>https://menafn.com/1110089200/Maharashtra-Deputy-CM-Eknath-Shindes-X-Account-Hacked-Pakistan-And-Turkey-Flags-Live-Streamed-Report</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/most-of-rs-46000cr-projects-for-marathwada-announced-by-shinde-led-cabinet-in-2023-still-on-paper/articleshow/123907066.cms</t>
+          <t>https://english.newsnationtv.com/national/politics/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother20250916212035</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/industry/strict-action-ordered-against-65-illegal-buildings-in-kalyan-dombivli-by-deputy-chief-minister-eknath-shinde/124008652</t>
+          <t>https://thenewsmill.com/2025/09/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/bjp-gave-up-claim-for-mumbai-mayor-s-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/2921301</t>
+          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/shiv-sena-workers-protest-in-thane-over-sanjay-raut-s-remarks-on-anand-dighe/ar-AA1MOXSd</t>
+          <t>https://www.bhaskarenglish.in/national/news/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-pakistan-flag-135976151.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-23595086?button=next</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-slams-incapable-ministers-after-ajit-pawar-for-ignoring-party-expansion-and-administrative-work/articleshow/124050348.cms</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Shiv-Sena-publishes-full-page-ads-in-dailies-on-PM-s-birthday-Shinde-hails-his-New-India-push/2923561</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flags-9649355.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/not-an-mla-but-get-rs-20-cr-in-funds-sena-leader-sarvankar-boasts-later-clarifies/articleshow/124028510.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-strict-against-builders-involved-in-kalyan-dombivali-illegal-buildings-constructing-3015585</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ncp-sp-cong-welcome-sc-order-on-maharashtra-local-bodies-polls-mahayuti-will-win-says-shinde/2920944</t>
+          <t>https://www.livehindustan.com/national/sanjay-raut-comments-about-eknath-shinde-mentor-anand-dighe-sparked-an-uproar-201758252385682.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3633705-infrastructure-revamp-a-new-dawn-for-navi-mumbais-villages</t>
+          <t>https://www.facebook.com/DNHindi/photos/%E0%A4%B8%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8%E0%A4%BE%E0%A4%A5-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A4%BE-x-%E0%A4%85%E0%A4%95%E0%A4%BE%E0%A4%89%E0%A4%82%E0%A4%9F-%E0%A4%B9%E0%A5%88%E0%A4%95-%E0%A4%B9%E0%A5%88%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B2%E0%A4%97%E0%A4%BE%E0%A4%88-%E0%A4%AA%E0%A4%BE%E0%A4%95%E0%A4%BF%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A4%BE%E0%A4%A8-%E0%A4%A4%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9D%E0%A4%82%E0%A4%A1%E0%A5%87eknathsi/1251272843711787/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/pms-birthday-a-black-day-for-democracy-says-congress-mp-praniti-shinde-bjp-hits-back/2920762</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/eknath-shinde-x-account-hacked-pakistan-turkey-flag-posted-ntc-rptc-2338322-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3630397-maharashtra-launches-namo-parks-to-celebrate-modis-75th-birthday</t>
+          <t>https://www.etvbharat.com/hi/!bharat/eknath-shinde-party-shiv-sena-will-merge-with-bjp-claims-sanjay-raut-hindi-news-hin25092002104</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/deputy-cm-eknath-shinde-x-account-hacked-hackers-posted-images-of-pakistan-and-turkey-flags/articleshow/124025137.cms</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/take-action-against-those-involved-in-constructing-65-illegal-buildings-in-kalyan-dombivali-shinde/2931430</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/ganesh-naik-vs-eknath-shinde-in-navi-mumbai-tussle-over-janata-darbar-petition-filed-in-high-court/articleshow/123996455.cms</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/On-eve-of-PM-s-birthday-Shinde-announces-scheme-to-develop-Namo-Parks-in-Maharashtra/2921302</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-claims-mahayuti-saffron-flag-will-fly-in-bmc-and-all-maharashtra-local-body-elections/articleshow/124032659.cms</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/prioritise-development-in-14-villages-added-to-navi-mumbai-civic-limits--dy-cm-shinde/2930925</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-assembly-election-result-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A4-%E0%A4%9C-%E0%A4%A4-%E0%A4%97%E0%A4%88-%E0%A4%AE%E0%A4%97%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%9F-%E0%A4%95-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A5%81%E0%A4%86/ar-AA1uBWUK?cvid=165226EF5620437992660C8F5EC7383E&amp;ocid=TIYLnav&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/mmrda-temporarily-suspends-monorail-services-in-mumbai20250920092952</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A0-%E0%A4%A3%E0%A5%87-%E0%A4%95-%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%B6-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%9F-%E0%A4%AA%E0%A5%8D%E0%A4%AA%E0%A4%A3-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A6-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%A1-%E0%A4%AF%E0%A4%A8-%E0%A4%95%E0%A5%81%E0%A4%A3-%E0%A4%B2-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B9/ar-AA1BxxlJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-shiv-sena-leaders-speech-adds-fuel-to-accusations-of-biased-allocation-of-funds-23595109?covid-19-breakingnews</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-bmc-election-eknath-shinde-group-plan-b-revealed-challenge-to-devendra-fadnavis-bjp-9653396.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/maharashtra-dy-cm-eknath-shindes-x-account-hacked-amid-india-pakistan-asia-cup-pakistani-and-turkish-flags-posted-a525/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%B8%E0%A4%AD-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%A4%E0%A5%87-%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AB-%E0%A4%B0-%E0%A4%AC%E0%A4%A8%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-cm-%E0%A4%AF%E0%A5%87-%E0%A4%AC-%E0%A4%A4%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A5%8D%E0%A4%B9%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%A4-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%96-%E0%A4%B8/ar-AA1s9G9J?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/eknath-shinde-account-hacked-during-india-pakistan-asia-cup-cybercrime-cybersecurity-national-flags-of-turkey-and-pakistan-restored-in-45-minutes-75975/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%95-%E0%A4%AE%E0%A4%B9-%E0%A4%AE-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%AB-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%B2%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B9-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%A1-%E0%A4%AA%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87/ar-AA1B8Gxe?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/ahead-of-bmc-polls-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena-10471368</t>
+          <t>https://hindi.webdunia.com/maharashtra/eknath-shinde-x-account-hacked-pakistani-flags-posted-125092100012_1.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/mumbai-acharya-devvrat-sworn-in-as-maharashtra-governor-gallery/</t>
+          <t>https://www.msn.com/hi-in/news/other/eknath-shinde-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A5-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95%E0%A4%B9-%E0%A4%B5%E0%A4%B9-%E0%A4%97%E0%A4%A0%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%AC%E0%A4%A8-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9%E0%A4%A4%E0%A5%87-%E0%A4%A5%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95-%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A5%9C-%E0%A4%B0%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%AE/ar-AA1Bakv5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-pakistan-flag-135976151.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B5-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%A8%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%97%E0%A5%81%E0%A4%AE%E0%A4%B0-%E0%A4%B9-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AE-%E0%A4%A6-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AD%E0%A5%87%E0%A4%A6%E0%A4%AD-%E0%A4%B5/ar-AA1BUMn4?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://thehindustangazette.com/election/eknath-shinde-x-account-hacked-pak-turkey-flags-39959</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-uddhav-thackeray-puts-bold-conditions-for-rebels-nagar-sevak-for-ghar-wapsi-for-shinde-shiv-sena-ahead-of-bmc-polls-know-all/articleshow/123978190.cms</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://x.com/i/broadcasts/1dRKZavRjoVxB</t>
+          <t>https://www.msn.com/hi-in/news/other/raj-thackeray-%E0%A4%B2-%E0%A4%B2-%E0%A4%AA-%E0%A4%AA-%E0%A4%B2-%E0%A4%97%E0%A5%87%E0%A4%B2%E0%A5%81-%E0%A4%AA%E0%A4%B0-%E0%A4%B2%E0%A5%9C%E0%A4%95-%E0%A4%95-%E0%A4%A1-%E0%A4%82%E0%A4%B8-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A5%9C%E0%A4%95%E0%A5%87-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AA%E0%A5%82%E0%A4%9B-%E0%A4%AF%E0%A4%B9-%E0%A4%B9%E0%A5%88-%E0%A4%B2-%E0%A4%A1%E0%A4%B2-%E0%A4%AC%E0%A4%B9%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8/ar-AA1tuyLy?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hindi/</t>
+          <t>https://www.republicbharat.com/india/maharashtra-dy-cm-eknath-shinde-x-account-hacked-posting-images-of-pakistan-and-turkey-flag</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/sanjay-raut-said-eknath-shinde-mentality-is-very-low-level-there-is-nothing-left-to-talk-about-2025-09-20-1163910</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%A6-%E0%A4%96-%E0%A4%88-%E0%A4%94%E0%A4%B0-%E0%A4%87%E0%A4%A8-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%B8-%E0%A4%AF-%E0%A4%B8%E0%A4%A4-%E0%A4%95-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%AF-%E0%A4%9C%E0%A4%B5-%E0%A4%AC/ar-AA1yYRmy?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flags-9649355.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/eknath-shinde-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B2%E0%A4%AF-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%AE%E0%A4%A8%E0%A5%87-%E0%A4%9C%E0%A4%82%E0%A4%9C-%E0%A4%B0-%E0%A4%AC%E0%A4%82%E0%A4%97%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A4%82%E0%A4%97-%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AE-%E0%A4%9C%E0%A5%82%E0%A4%A6-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%95%E0%A5%81%E0%A4%9B-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%B9-%E0%A4%B0%E0%A4%B9-%E0%A4%B9%E0%A5%88/ar-AA1Mx0NI</t>
+          <t>https://www.abplive.com/states/maharashtra/shiv-sena-mla-sada-sarvankar-met-maharashtra-navnirman-sena-president-raj-thackeray-3016893</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/deputy-cm-eknath-shinde-x-account-hacked-hackers-posted-images-of-pakistan-and-turkey-flags/articleshow/124025137.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%A7-%E0%A4%B0%E0%A5%87-%E0%A4%A7-%E0%A4%B0%E0%A5%87-bjp-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%B2-%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%B8%E0%A4%A6-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%89%E0%A4%A4-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1MX3h5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/DNHindi/photos/%E0%A4%B8%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8%E0%A4%BE%E0%A4%A5-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A4%BE-x-%E0%A4%85%E0%A4%95%E0%A4%BE%E0%A4%89%E0%A4%82%E0%A4%9F-%E0%A4%B9%E0%A5%88%E0%A4%95-%E0%A4%B9%E0%A5%88%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B2%E0%A4%97%E0%A4%BE%E0%A4%88-%E0%A4%AA%E0%A4%BE%E0%A4%95%E0%A4%BF%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A4%BE%E0%A4%A8-%E0%A4%A4%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9D%E0%A4%82%E0%A4%A1%E0%A5%87eknathsi/1251272843711787/</t>
+          <t>https://zeenews.india.com/hindi/india/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-pakistan-turkiye-flag-shown-on-handle/2930969</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://x.com/i/broadcasts/1ypKdqyAVPpGW</t>
+          <t>https://www.msn.com/hi-in/news/other/mva-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%B0-%E0%A4%A8-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%97-%E0%A4%B0%E0%A4%AB%E0%A5%8D%E0%A4%A4-%E0%A4%B0-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%A5-sit-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%9C-%E0%A4%82%E0%A4%9A/ar-AA1ybCn1?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-deputy-cm-eknath-shinde-x-handle-hacked-hackers-shared-posts-with-pakistan-and-turkey-flags-2025-09-21-1164034</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-deputy-cm-eknath-shinde-s-twitter-account-hacked-raises-cybersecurity-concerns-201758454098732.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-on-eknath-shinde-maharashtra-ahmedabad-bullet-train-anand-dighe-3015725</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B0%E0%A5%87-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%95-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%B0%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-ubt-%E0%A4%95-%E0%A4%AA%E0%A4%B2%E0%A4%9F%E0%A4%B5-%E0%A4%B0-%E0%A4%B0-%E0%A4%89%E0%A4%A4-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%A4-%E0%A4%A4-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5/ar-AA1H4TcY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://x.com/i/broadcasts/1gqGvrPmZvgGB</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%89%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%82-%E0%A4%9F%E0%A5%82%E0%A4%9F-%E0%A4%82-%E0%A4%B0-%E0%A4%9C-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%95-%E0%A4%B5-%E0%A4%9C%E0%A4%AF-%E0%A4%B0%E0%A5%88%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1I1z7a?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/ganesh-naik-vs-eknath-shinde-in-navi-mumbai-tussle-over-janata-darbar-petition-filed-in-high-court/articleshow/123996455.cms</t>
+          <t>https://www.amarujala.com/video/india-news/pm-modi-birthday-congress-declares-pm-modi-s-birthday-as-black-day-enraged-eknath-shinde-issues-warning-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/sanjay-raut-comments-about-eknath-shinde-mentor-anand-dighe-sparked-an-uproar-201758252385682.html</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/deputy-cm-eknath-shinde-x-account-hack-pakistan-turkey-flag-shown-investigation-going-on-hindi-news-1390995.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%97%E0%A4%A3%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%B0%E0%A4%B9%E0%A5%87-%E0%A4%A5%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%B8%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%AA%E0%A4%B0-%E0%A4%85%E0%A4%9A-%E0%A4%A8%E0%A4%95-%E0%A4%B0-%E0%A4%95-%E0%A4%95-%E0%A4%AB-%E0%A4%B2-%E0%A4%AB-%E0%A4%B0/ar-AA1xTf0a?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/eknath-shinde-takes-action-against-kalyan-dombivli-illegal-buildings-builders/articleshow/124011899.cms</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-claims-mahayuti-saffron-flag-will-fly-in-bmc-and-all-maharashtra-local-body-elections/articleshow/124032659.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-namo-park-scheme-for-pm-narendra-modi-75th-birthday-deputy-cm-eknath-shinde-announcement-3014117</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6%E0%A4%AA%E0%A4%A5-%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B9%E0%A4%A3-%E0%A4%B8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%AC-%E0%A4%97%E0%A4%A1%E0%A4%BC-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A4%AC-%E0%A4%AF%E0%A4%A4-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%95%E0%A5%87-%E0%A4%85%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%A4-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD%E0%A4%B0%E0%A5%8D%E0%A4%A4/ar-AA1vb0Jf?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-deputy-chief-minister-ekanth-shinde-says-rahul-gandhi-s-vote-theft-charges-baseless-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AA-%E0%A4%8F%E0%A4%AE-%E0%A4%AE-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%95-%E0%A4%A4-%E0%A4%B9%E0%A4%AB-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AC%E0%A4%A8-%E0%A4%8F-%E0%A4%9C-%E0%A4%8F%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%A8%E0%A4%AE-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%95/ar-AA1MFYqT</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/cm-fadnavis-and-deputy-cm-shinde-flagged-off-trial-run-of-thane-metro-line-4-from-gaimukh-to-cadbury-11720</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-uddhav-thackeray-puts-bold-conditions-for-rebels-nagar-sevak-for-ghar-wapsi-for-shinde-shiv-sena-ahead-of-bmc-polls-know-all/articleshow/123978190.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B8-%E0%A4%85%E0%A4%95-%E0%A4%89%E0%A4%82%E0%A4%9F-%E0%A4%B9%E0%A5%88%E0%A4%95-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%87%E0%A4%AC%E0%A4%B0-%E0%A4%B8%E0%A5%81%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A4%B0-%E0%A4%89%E0%A4%A0-%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8/ar-AA1MZNrX</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%AE-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%9B-%E0%A4%AA-22-%E0%A4%AC-%E0%A4%B0-%E0%A4%9F%E0%A5%87%E0%A4%82%E0%A4%A1%E0%A4%B0-%E0%A4%94%E0%A4%B0-25-%E0%A4%95%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A4%AE%E0%A4%B0-%E0%A4%85%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%8F%E0%A4%AB%E0%A4%86%E0%A4%88%E0%A4%86%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF/ar-AA1IUiYB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.aajtak.in/india/maharashtra/video/pm-modi-75th-birthday-piyush-goyal-eknath-shinde-wishes-ytvd-2335022-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/maharashtra/eknath-shinde-x-account-hacked-pakistani-flags-posted-125092100012_1.html</t>
+          <t>https://inshorts.com/hi/news/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6--%E0%A4%A6--%E0%A4%95--x-%E0%A4%85%E0%A4%95-%E0%A4%89-%E0%A4%9F-%E0%A4%B9-%E0%A4%95--%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%B8-%E0%A4%A8--%E0%A4%AA-%E0%A4%B8-%E0%A4%9F-%E0%A4%95-%E0%A4%8F-%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%A4-%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%95--%E0%A4%95--%E0%A4%9D-%E0%A4%A1---1758441470089</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%B8%E0%A4%AD-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%A8%E0%A5%87-45-%E0%A4%89%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%A8-%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%90%E0%A4%B2-%E0%A4%A8-cm-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%87%E0%A4%B8-%E0%A4%B8-%E0%A4%9F-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5/ar-AA1sJkOe?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://x.com/i/broadcasts/1YqKDNmQVkNJV</t>
+          <t>https://www.abplive.com/states/maharashtra/pratap-sarnaik-comments-on-uddhav-thackeray-sanjay-raut-praises-eknath-shinde-respect-senior-leaders-3016095</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/nation/shindes-x-account-hacked-maharashtras-cyber-security-in-question-uproar-over-eknath-shindes-x-account-being-hacked/amp</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/kedar-dighes-sharp-attack-on-shinde-faction-anand-dighe-remembered-as-elections-approach/articleshow/124004160.cms</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/eknath-shinde-takes-action-against-kalyan-dombivli-illegal-buildings-builders/articleshow/124011899.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B5-%E0%A4%9A%E0%A5%88%E0%A4%AA%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%85%E0%A4%AC-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%97%E0%A4%AF-%E0%A4%B9%E0%A5%88-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%9C-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A4%B0-%E0%A4%B8%E0%A5%81%E0%A4%A8-%E0%A4%B2-%E0%A4%A4%E0%A4%9F%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%90%E0%A4%B8-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%AC-%E0%A4%B2-%E0%A4%97%E0%A4%8F/ar-AA1v8byj?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://x.com/i/status/1970055402231419183?ref_src=twsrc%5Egoogle%7Ctwcamp%5Eserp%7Ctwgr%5Etweet</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A4%B2-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A4%9F-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%82%E0%A4%97-%E0%A4%B0-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%89%E0%A4%A0-%E0%A4%8F-%E0%A4%9C-%E0%A4%8F%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A4%A6%E0%A4%AE/ar-AA1Dro6h?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/thane-metro-trial-run-on-september-22-thane-residents-dream-to-come-true/articleshow/124004146.cms</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-deputy-cm-eknath-shinde-s-twitter-account-hacked-raises-cybersecurity-concerns-201758454098732.html</t>
+          <t>https://www.navodayatimes.in/news/national/maharashtra-deputy-cm-eknath-shinde-ex-handle-hacked/276116/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%A8%E0%A4%96%E0%A4%B0-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%AA-%E0%A4%9B%E0%A5%87-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%95-%E0%A4%AE%E0%A4%B9-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%B8%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A5%87%E0%A4%82%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%89%E0%A4%A4/ar-AA1vbFc0?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.ndtv.com/cities/eknath-shinde-treated-australian-guests-to-a-feast-of-vada-pav-9289261</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/pm-modi-birthday-congress-declares-pm-modi-s-birthday-as-black-day-enraged-eknath-shinde-issues-warning-2025-09-17</t>
+          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-news-rahul-gandhi-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%B5%E0%A4%B0-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-marathi-news/vi-AA1MOsp4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-namo-park-scheme-for-pm-narendra-modi-75th-birthday-deputy-cm-eknath-shinde-announcement-3014117</t>
+          <t>https://www.amarujala.com/amp/india-news/maharashtra-deputy-chief-minister-eknath-shinde-s-x-account-hacked-news-in-hindi-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/pratap-sarnaik-comments-on-uddhav-thackeray-sanjay-raut-praises-eknath-shinde-respect-senior-leaders-3016095/amp</t>
+          <t>https://zeenews.india.com/marathi/short-videos/congress-mp-praniti-shinde-criticizes-eknath-shinde/939828</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/video/pm-modi-75th-birthday-piyush-goyal-eknath-shinde-wishes-ytvd-2335022-2025-09-17</t>
+          <t>https://www.jansatta.com/jansatta-special/jansatta-rajpaat-abhay-chautala-haryana-shinde-message-congress-du-election-bihar-seat-dispute-rld-up/4151302/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-deputy-chief-minister-ekanth-shinde-says-rahul-gandhi-s-vote-theft-charges-baseless-2025-09-19</t>
+          <t>https://marathi.abplive.com/news/maharashtra/sanjay-raut-says-eknath-shinde-who-is-there-today-is-because-of-rajan-vichare-sacrifice-marathi-news-update-1385178</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9D%E0%A4%9F%E0%A4%95-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95-%E0%A4%AE%E0%A4%97-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A4%88-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%AE-%E0%A4%B2/ar-AA1wEXx9?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://mahasamvad.in/178645/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6%E0%A4%AA%E0%A4%A5%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6-%E0%A4%96-%E0%A4%B2-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82-%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AA%E0%A4%B2%E0%A4%9F%E0%A4%B5-%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%B8%E0%A5%82%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%97%E0%A4%A1%E0%A4%BC%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%95-%E0%A4%A6-%E0%A4%B5-%E0%A4%97%E0%A4%B2%E0%A4%A4/ar-AA1MRMC6</t>
+          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-at-tembhi-naka-devi-%E0%A4%9F%E0%A5%87%E0%A4%82%E0%A4%AD-%E0%A4%A8-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%B2-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%9A-%E0%A4%86%E0%A4%97%E0%A4%AE%E0%A4%A8-%E0%A4%B8-%E0%A4%B9%E0%A4%B3-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%B8%E0%A5%8D%E0%A4%A5-%E0%A4%A4-n18v/vi-AA1N3TKj</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
+          <t>https://mahasamvad.in/178497/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%AC-%E0%A4%A8%E0%A5%87%E0%A4%9F-%E0%A4%AC%E0%A4%82%E0%A4%9F%E0%A4%B5-%E0%A4%B0%E0%A5%87-%E0%A4%95-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A5%82%E0%A4%B2-%E0%A4%A4%E0%A4%AF-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95-%E0%A4%95-%E0%A4%A4%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6/ar-AA1vHycG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.ndtv.com/maharashtra/thane-ghodbunder-news-good-news-for-thane-kalyan-badlapur-commuters-as-eknath-shinde-orders-restriction-of-heavy-vehicles-untill-midnight-9291074</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/thane-metro-trial-run-on-september-22-thane-residents-dream-to-come-true/articleshow/124004146.cms</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.navodayatimes.in/news/national/maharashtra-deputy-cm-eknath-shinde-ex-handle-hacked/276116/</t>
+          <t>https://mahasamvad.in/179440/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/eknath-shinde-treated-australian-guests-to-a-feast-of-vada-pav-9289261</t>
+          <t>https://marathi.abplive.com/news/mumbai/under-what-authority-were-the-municipal-corporation-notice-to-demolish-buildings-stopped-high-court-ask-on-eknath-shinde-whether-the-dcm-has-the-authority-to-make-that-decision-1384909</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/jansatta-special/jansatta-rajpaat-abhay-chautala-haryana-shinde-message-congress-du-election-bihar-seat-dispute-rld-up/4151302/</t>
+          <t>https://mahasamvad.in/178790/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A4%B0-%E0%A4%85%E0%A4%A8%E0%A4%AC%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%B2%E0%A4%97-%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%95-%E0%A4%AF%E0%A4%A4/ar-AA1G5LqL?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/changes-in-gst-rates-will-lead-to-the-ghatsthapna-of-superpower-in-country-eknath-shinde-96248</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://inshorts.com/hi/amp_news/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6--%E0%A4%A6--%E0%A4%95--x-%E0%A4%85%E0%A4%95-%E0%A4%89-%E0%A4%9F-%E0%A4%B9-%E0%A4%95--%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%B8-%E0%A4%A8--%E0%A4%AA-%E0%A4%B8-%E0%A4%9F-%E0%A4%95-%E0%A4%8F-%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%A4-%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%95--%E0%A4%95--%E0%A4%9D-%E0%A4%A1---1758441470089</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-decision-mandatory-to-construct-administrative-buildings-of-municipal-councils-according-to-the-model-plan-1482062.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/short-videos/congress-mp-praniti-shinde-criticizes-eknath-shinde/939828</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticized-eknath-shinde-for-washing-rajan-vichares-feet-and-taking-a-pilgrimage/923077/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%9A-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B0-%E0%A4%AC%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8-%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%9C-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B0-%E0%A4%B2-%E0%A4%97%E0%A4%A3-%E0%A4%B0%E0%A4%82-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0/ar-AA1MOxAB</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%9D-%E0%A4%AA-%E0%A4%89%E0%A4%A1-%E0%A4%B2-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A6-%E0%A4%B2-%E0%A4%AE-%E0%A4%A0-%E0%A4%87%E0%A4%B6-%E0%A4%B0/ar-AA1N3wGD</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/high-court-on-eknath-shinde-%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A4%9A%E0%A5%87-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%9A%E0%A5%87-%E0%A4%A4-%E0%A4%B6%E0%A5%87%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%95-%E0%A4%AF/ar-AA1MNNcC</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shindes-ex-account-hacked-96111</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178497/</t>
+          <t>https://marathi.abplive.com/news/politics/the-high-court-has-questioned-eknath-shinde-over-the-suspension-of-action-against-illegal-construction-in-navi-mumbai-1384988</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/thane-ghodbunder-news-good-news-for-thane-kalyan-badlapur-commuters-as-eknath-shinde-orders-restriction-of-heavy-vehicles-untill-midnight-9291074</t>
+          <t>https://www.mymahanagar.com/mahamumbai/deputy-chief-minister-eknath-shinde-insistently-served-the-australian-guests-vadapav-a-signature-food-of-mumbai/922213/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/policenamaa/p/DO3KXfUDC5_/</t>
+          <t>https://inshorts.com/hi/amp_news/-%E0%A4%B8%E0%A4%A4-%E0%A4%A4--%E0%A4%95--%E0%A4%B2-%E0%A4%8F-%E0%A4%B0-%E0%A4%AF%E0%A4%B2-%E0%A4%AA-%E0%A4%B0-%E0%A4%9F-------%E0%A4%B6--%E0%A4%A6--%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%AE%E0%A4%B0--%E0%A4%95--%E0%A4%9F-%E0%A4%AA-%E0%A4%AA%E0%A4%A3--%E0%A4%95--%E0%A4%B2-%E0%A4%95%E0%A4%B0-%E0%A4%9C%E0%A4%AF--%E0%A4%AC%E0%A4%9A-%E0%A4%9A%E0%A4%A8-%E0%A4%A8--%E0%A4%A6--%E0%A4%AA-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B0-%E0%A4%AF--1742984239606</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178645/</t>
+          <t>https://www.msn.com/mr-in/news/other/vidhan-parishad-election-2025-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%B9-%E0%A4%B6-%E0%A4%B2%E0%A5%87%E0%A4%A6-%E0%A4%B0-%E0%A4%A0%E0%A4%B0%E0%A4%B2-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%B0%E0%A4%98%E0%A5%81%E0%A4%B5%E0%A4%82%E0%A4%B6-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A3-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%A6-%E0%A4%9A-%E0%A4%B2-%E0%A4%9F%E0%A4%B0-%E0%A4%95%E0%A5%81%E0%A4%A3-%E0%A4%B2/ar-AA1B3F4t?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%B5-%E0%A4%9A-%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%A8%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%B9-%E0%A4%A4-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%82%E0%A4%9A-%E0%A4%96%E0%A5%81%E0%A4%B2-%E0%A4%B8-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%8D%E0%A4%B5%E0%A4%A4-%E0%A4%B9%E0%A5%82%E0%A4%A8-%E0%A4%86%E0%A4%A8%E0%A4%82%E0%A4%A6-%E0%A4%A6-%E0%A4%98%E0%A5%87%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5-%E0%A4%A0%E0%A5%87%E0%A4%B5%E0%A4%B2-%E0%A4%95/ar-AA1MSjEL</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-deputy-chief-minister-eknath-shinde-launches-the-seva-fortnight-chief-minister-samruddhi-panchayat-raj-abhiyan-in-thane-district/922593/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/on-what-authority-did-you-give-the-stay-eknath-shinde-was-asked-in-the-supreme-court-284502/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-many-office-bearers-of-uddhav-thackeray-group-join-shiv-sena-95696</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%95-%E0%A4%A3-%E0%A4%9A-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B0-%E0%A4%AC%E0%A4%B8%E0%A4%A3-%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A5%E0%A5%87%E0%A4%9F-%E0%A4%A8-%E0%A4%B5-%E0%A4%98%E0%A5%87%E0%A4%A4-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1MHE1a</t>
+          <t>https://www.lokmat.com/mumbai/start-preparing-for-mumbai-municipal-corporation-elections-now-says-eknath-shinde-a-a653/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-%E0%A4%AC-%E0%A4%B3-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%82%E0%A4%9A-%E0%A4%A8-%E0%A4%B7%E0%A5%8D%E0%A4%A0-%E0%A4%B5%E0%A4%82%E0%A4%A4-%E0%A4%B8%E0%A5%87%E0%A4%B5%E0%A4%95-%E0%A4%9A%E0%A4%82%E0%A4%AA-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%A5-%E0%A4%AA-%E0%A4%9A-%E0%A4%B6%E0%A4%AA%E0%A4%A5%E0%A4%B5-%E0%A4%A7-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%AE-%E0%A4%A0-%E0%A4%AD%E0%A5%82%E0%A4%AE-%E0%A4%95-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8/ar-AA1vjijr?cvid=5C9E8D07D85E4F0FAB3B201F129171F9&amp;ocid=TIYLnav&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/shiv-sena-corporaters-news-eknath-shinde-on-uddhav-thackeray-mumbai-bmc-election-2025/921652/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/under-what-authority-were-the-municipal-corporation-notice-to-demolish-buildings-stopped-high-court-ask-on-eknath-shinde-whether-the-dcm-has-the-authority-to-make-that-decision-1384909</t>
+          <t>https://prahaar.in/2025/09/22/deputy-chief-minister-eknath-shinde-took-stock-of-the-heavy-rainfall-in-marathwada//</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179440/</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/eknath-shinde-has-revealed-that-the-ladki-bahin-scheme-will-never-be-closed/41518</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticized-eknath-shinde-for-washing-rajan-vichares-feet-and-taking-a-pilgrimage/923077/</t>
+          <t>https://mahasamvad.in/178863/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178790/</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-shinde-first-reaction-on-meenatai-thackeray-dadar-statue-issue-he-will-not-be-released-i-have-spoken-to-the-police-commissioner-1384826</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-decision-mandatory-to-construct-administrative-buildings-of-municipal-councils-according-to-the-model-plan-1482062.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-district-administration-should-remain-alert-in-wake-of-heavy-rains-eknath-shinde-instructs-94887</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
+          <t>https://marathi.abplive.com/news/maharashtra/deputy-chief-minister-eknath-shinde-reaction-to-prime-minister-narendra-modi-s-gst-cut-ladki-bahin-yojana-news-1385846</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A0-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4%E0%A4%B9-%E0%A4%AE-%E0%A4%B8%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%AE-%E0%A4%B3%E0%A4%B5%E0%A5%82%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%8A-%E0%A4%B6%E0%A4%95%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%9A%E0%A5%85%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9C-%E0%A4%A6-%E0%A4%B2%E0%A5%87/ar-AA1MFBoy</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-review-maharashtra-and-mumbai-rain-updates-orders-airlift-beed-ashti-villagers-1480338.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shindes-ex-account-hacked-96111</t>
+          <t>https://mahasamvad.in/178828/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/the-high-court-has-questioned-eknath-shinde-over-the-suspension-of-action-against-illegal-construction-in-navi-mumbai-1384988</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%98-%E0%A4%A1%E0%A4%AC%E0%A4%82%E0%A4%A6%E0%A4%B0-%E0%A4%B0-%E0%A4%A1%E0%A4%B5%E0%A4%B0-%E0%A4%B2-%E0%A4%B5-%E0%A4%B9%E0%A4%A4%E0%A5%82%E0%A4%95-%E0%A4%95-%E0%A4%82%E0%A4%A1-%E0%A4%95%E0%A4%AE-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%89%E0%A4%AA%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A6-%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1MJRsS</t>
+          <t>https://marathi.ndtv.com/cities/cm-fadnavis-change-eknath-shindes-decision-to-ban-heavy-vehicles-from-morning-6-to-12-night-to-solve-traffic-congestion-9316039</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%AD%E0%A4%B0-%E0%A4%A4-%E0%A5%A7%E0%A5%AB-%E0%A4%9C%E0%A5%81%E0%A4%B2%E0%A5%88%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A3-%E0%A4%B8-%E0%A4%A0%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95%E0%A4%B0/ar-AA1DqU7p?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-response-after-sanjay-raut-objected-to-placing-anand-dighes-photo-next-to-balasaheb-thackeray/922799/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/deputy-chief-minister-eknath-shinde-insistently-served-the-australian-guests-vadapav-a-signature-food-of-mumbai/922213/</t>
+          <t>https://www.navarashtra.com/maharashtra/solution-to-traffic-congestion-found-ghodbunder-residents-will-get-relief-eknath-shinde-gives-order-991858.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-many-office-bearers-of-uddhav-thackeray-group-join-shiv-sena-95696</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-feeds-australian-mp-tim-watts-mumbais-vada-pav/922339/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%A8%E0%A5%87%E0%A4%B9-%E0%A4%91%E0%A4%AB%E0%A4%B0-%E0%A4%A6-%E0%A4%B2%E0%A5%87%E0%A4%AF-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%90%E0%A4%95%E0%A4%A4-%E0%A4%9A-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A-%E0%A4%B2%E0%A4%97%E0%A4%AC%E0%A4%97-%E0%A4%98-%E0%A4%88%E0%A4%A8%E0%A5%87-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B6-%E0%A4%B2%E0%A5%87%E0%A4%A6-%E0%A4%B0-%E0%A4%B2-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B2-%E0%A4%A8%E0%A5%87%E0%A4%B2%E0%A4%82-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%95%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2/ar-AA1yRGld?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-big-announces-on-pm-modi-birthday-say-all-municipal-councils-will-be-established-namo-udyan-in-maharashtra-95314</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://x.com/i/broadcasts/1PlJQOgqMRDKE</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-municipal-elections-eknath-shinde-puts-shiv-sena-in-action-mode-with-direct-orders-to-corporators-sharad-pawar-also-eyes-victory-in-corporations-1384728</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/shiv-sena-corporaters-news-eknath-shinde-on-uddhav-thackeray-mumbai-bmc-election-2025/921652/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-ajit-pawar-and-eknath-shinde-reprimand-maharashtra-cabinet-over-performance-and-neglect-of-party-organization-1386101</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-district-administration-should-remain-alert-in-wake-of-heavy-rains-eknath-shinde-instructs-94887</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-rain-heavy-rainfall-in-beed-40-villagers-should-be-airlifted-dcm-eknath-shinde-ordered-9279677</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/cm-fadnavis-change-eknath-shindes-decision-to-ban-heavy-vehicles-from-morning-6-to-12-night-to-solve-traffic-congestion-9316039</t>
+          <t>https://marathi.ndtv.com/cities/now-there-is-only-one-type-plan-for-the-administrative-buildings-of-the-municipal-council-and-municipal-panchayats-eknath-shinde-9294836</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-review-maharashtra-and-mumbai-rain-updates-orders-airlift-beed-ashti-villagers-1480338.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/mumbai-high-court-questioned-eknath-shinde-on-new-mumbai-illegal-construction-case/922756/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179392/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-get-set-back-bmc-scraps-12-crore-project-mumbai-1485014.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178828/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shinde-fadnavis-cold-war-high-court-questions-maharashtra-government-s-legitimacy-amid-brand-battle-corruption-allegations-and-best-depot-controversy-1384960</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-stated-that-the-change-in-gst-rates-will-lead-to-the-establishment-of-a-superpower-in-the-country-from-tomorrow/923694/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ganesh-naik-vs-eknath-shinde-%E0%A4%A0-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A-%E0%A4%B8%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%86%E0%A4%A3-%E0%A4%AF%E0%A4%9A-%E0%A4%85%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%A4%E0%A4%B0-%E0%A4%B0-%E0%A4%B5%E0%A4%A3-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%B9%E0%A4%82%E0%A4%95-%E0%A4%B0-%E0%A4%9A%E0%A5%87-%E0%A4%A6%E0%A4%B9%E0%A4%A8-%E0%A4%95%E0%A4%B0-%E0%A4%B5%E0%A5%87-%E0%A4%B2-%E0%A4%97%E0%A5%87%E0%A4%B2/ar-AA1Mh41w?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.navarashtra.com/maharashtra/dcm-eknath-shinde-get-report-of-the-heavy-rainfall-in-marathwada-weather-update-998693.html</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html?utm_source=District%20Widget&amp;utm_medium=Mobile&amp;utm_campaign=marathi</t>
+          <t>https://www.msn.com/mr-in/news/other/sanjay-raut-%E0%A4%95-%E0%A4%A3-%E0%A4%B6%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA-%E0%A4%B0%E0%A4%97%E0%A4%82-%E0%A4%95%E0%A4%A7-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B9-%E0%A4%A4%E0%A4%82-%E0%A4%95-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%82%E0%A4%A8-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2-%E0%A4%96-%E0%A4%B8%E0%A4%A6-%E0%A4%B0%E0%A4%95-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%95-%E0%A4%9F-%E0%A4%9A-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%B8/ar-AA1MSb0O</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-municipal-elections-eknath-shinde-puts-shiv-sena-in-action-mode-with-direct-orders-to-corporators-sharad-pawar-also-eyes-victory-in-corporations-1384728</t>
+          <t>https://www.mymahanagar.com/maharashtra/deputy-cm-eknath-shinde-on-heavy-rains-and-alert-to-district-administration/921681/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-get-set-back-bmc-scraps-12-crore-project-mumbai-1485014.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/mns-leader-avinash-jadhav-slams-eknath-shinde-over-thane-traffic-issue/articleshow/123926772.cms</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/now-there-is-only-one-type-plan-for-the-administrative-buildings-of-the-municipal-council-and-municipal-panchayats-eknath-shinde-9294836</t>
+          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.mumbaitak.in/political-news/story/eknath-shinde-x-account-hack-turkey-and-pakistani-flag-show-cyber-crime-3203184-2025-09-21</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%A6-%E0%A4%B5-%E0%A4%B3-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%AE-%E0%A4%A0-%E0%A4%AD%E0%A5%82%E0%A4%95%E0%A4%82%E0%A4%AA-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8%E0%A4%B9-%E0%A4%A6%E0%A5%81%E0%A4%9C-%E0%A4%B0/ar-AA1McaIA?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-big-announces-on-pm-modi-birthday-say-all-municipal-councils-will-be-established-namo-udyan-in-maharashtra-95314</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-ghodbandar-road-eknath-shinde-ghodbandar-residents-will-be-free-from-traffic-congestion/922259/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-rain-heavy-rainfall-in-beed-40-villagers-should-be-airlifted-dcm-eknath-shinde-ordered-9279677</t>
+          <t>https://www.bhaskar.com/national/video/eknath-shinde-x-account-hacked-pakistan-turkey-flags-posted-september-2025-135976016.html?index=69</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/mumbai-high-court-questioned-eknath-shinde-on-new-mumbai-illegal-construction-case/922756/</t>
+          <t>https://x.com/i/broadcasts/1rmxPvjzknjGN?ref_src=twsrc%5Egoogle%7Ctwcamp%5Eserp%7Ctwgr%5E</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-stated-that-the-change-in-gst-rates-will-lead-to-the-establishment-of-a-superpower-in-the-country-from-tomorrow/923694/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-working-on-plan-b-for-bmc-election-likely-shock-to-uddhav-thackeray-and-bjp-also-1484790.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-s-x-account-hacked-turkish-and-pakistani-videos-posted-account-recovered-after-team-x-complaint-1385633</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/bombay-high-court-questions-eknath-shinde-illegal-constructions-navi-mumbai-135950643.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shinde-fadnavis-cold-war-high-court-questions-maharashtra-government-s-legitimacy-amid-brand-battle-corruption-allegations-and-best-depot-controversy-1384960</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-for-suspending-demolition-of-societies-with-unauthorized-construction-in-vashi-area/922729/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/local-elections-mahayuti-will-win-in-the-local-self-government-elections-eknath-shinde-is-confident/922171/</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-says-anand-dighe-never-sold-shiv-sena/923100/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/deputy-cm-eknath-shinde-on-heavy-rains-and-alert-to-district-administration/921681/</t>
+          <t>https://www.etvbharat.com/mr/!state/if-you-come-to-power-we-will-show-the-power-of-jai-maharashtra-sanjay-raut-warning-to-eknath-shinde-maharashtra-news-mhs25092001682</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/wadigodri-crime-news-fake-cid-officers-stole-the-golden-ring/</t>
+          <t>https://www.mymahanagar.com/maharashtra/dcm-eknath-shinde-criticized-rahul-gandhi-evm-vote-chori-case/922837/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-for-suspending-demolition-of-societies-with-unauthorized-construction-in-vashi-area/922729/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-palghar-dahanu-shivsena-thackeray-group-office-bearers-from-palghar-dahanu-join-shivsena/922966/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-working-on-plan-b-for-bmc-election-likely-shock-to-uddhav-thackeray-and-bjp-also-1484790.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/local-elections-mahayuti-will-win-in-the-local-self-government-elections-eknath-shinde-is-confident/922171/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-says-anand-dighe-never-sold-shiv-sena/923100/</t>
+          <t>https://www.tv9marathi.com/videos/nashik-journalist-beating-dcm-eknath-shinde-speaks-with-injured-journalist-kiran-tajane-via-video-call-1497047.html</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/mns-leader-avinash-jadhav-slams-eknath-shinde-over-thane-traffic-issue/articleshow/123926772.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/shivsena-thackrey-faction-leader-sanjay-raut-slams-eknath-shinde-and-others-1496593.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-ghodbandar-road-eknath-shinde-ghodbandar-residents-will-be-free-from-traffic-congestion/922259/</t>
+          <t>https://marathi.ndtv.com/maharashtra/solapur-politics-ncp-sharad-pawar-party-mla-narayan-patil-will-joins-eknath-shindes-shiv-sena-9326109</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-today-21st-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-ahmedabad-bullet-train-mega-block-sunday/amp_liveblog/124023319.cms</t>
+          <t>https://marathi.abplive.com/news/thane/ghodbunder-residents-will-be-freed-from-traffic-jams-orders-to-leave-heavy-vehicles-after-12-midnight-eknath-shinde-orders-1384427</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/news/navi-mumbai-munciple-corporation-news-dcm-eknath-shinde-directed-the-commissioner-to-give-immediate-priority-to-water-supply-roads-health-facilities-and-schools-in-14-villages-local18-1483762.html</t>
+          <t>https://news18marathi.com/maharashtra/sharad-pawar-led-ncp-2-mlas-attend-shivsena-eknath-shinde-meeting-political-stir-1486267.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-solve-bmtc-employee-problem-gave-10-lakh-for-compensation-1484524.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-eknath-shinde-s-shiv-sena-in-action-mode-confident-of-mahayuti-victory-in-mumbai-civic-polls-directs-corporators-to-start-work-1384673</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/mumbai-sees-banners-from-eknath-shinde-shiv-sena-celebrating-pm-modi-birthday-spark-discussion-1493541.html</t>
+          <t>https://www.etvbharat.com/mr/!state/parshuram-economic-development-corporation-chairman-ashish-damle-gets-ministerial-status-in-thane-maharashtra-news-mhs25091603365</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/eid-e-milad-2024-public-holiday-on-september-18-announced-by-eknath-shinde-133641576.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-eknath-shinde-s-shiv-sena-in-action-mode-confident-of-mahayuti-victory-in-mumbai-civic-polls-directs-corporators-to-start-work-1384673</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-eknath-shinde-office-call-thackeray-worker-ayodhya-paul-audio-clip-viral-135941678.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-announced-strict-action-will-be-taken-against-those-who-cheated-residents-of-65-buildings-in-kalyan-dombivali-1483839.html</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-solve-bmtc-employee-problem-gave-10-lakh-for-compensation-1484524.html</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/withdrew-the-rs-2-5-crore-fund-given-for-sewage-plant-and-drainage-because-former-corporator-deepmala-badhe-belonged-to-the-thackeray-group/922264/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/pm-narendra-modi-birthday-sharad-pawar-ajit-pawar-and-eknath-shinde-wish-a-happy-birthday-95367</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/thane/bjp-mns-uddhav-sena-alliance-formed-to-target-eknath-shinde-sena-in-shatayushi-sporting-club-elections-thane-a-a629/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/withdrew-the-rs-2-5-crore-fund-given-for-sewage-plant-and-drainage-because-former-corporator-deepmala-badhe-belonged-to-the-thackeray-group/922264/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-former-mla-claim-on-20-crore-make-political-stir-in-maharashtra-1484863.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/sanjay-raut-attacks-eknath-shinde-shrikant-shiv-sena-rahul-modi-presser-135957579.html</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/bjp-leader-nitin-paygude-and-mns-leader-ranji-dhage-join-shiv-sena-shinde-group/articleshow/123998704.cms</t>
+          <t>https://www.mumbaitak.in/political-news/story/sanjay-raut-has-strongly-criticized-eknath-shinde-for-printing-photos-of-balasaheb-thackeray-and-anand-dighe-side-by-side-in-an-advertisement-wishing-pm-modi-a-happy-birthday-3202688-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/bihar-assembly-election-amit-shah-meets-bjp-workers-gives-60-days-plan-ahead-of-poll/articleshow/123995857.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-chairs-shiv-sena-meeting-in-mumbai-strategizes-for-upcoming-elections-and-mumbai-municipal-corporation-polls-sanjay-nirupam-reacts-1384153</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-politics-deputy-cm-eknath-shinde-refutes-evm-allegations-confident-of-mahayuti-victory-in-mumbai-civic-polls-on-development-work-1385031/amp</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-former-mla-claim-on-20-crore-make-political-stir-in-maharashtra-1484863.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-20-september-2025-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbais-ghodbunder-road-new-night-restrictions-to-ease-traffic-jams-1493450.html</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/women-from-shinde-sena-demand-minister-of-state-yogesh-kadam-to-make-deepak-kesarkar-a-minister-a-a746/</t>
+          <t>https://marathi.ndtv.com/videos/after-ajit-pawar-eknath-shinde-will-also-hold-a-road-show-in-nagpur-shinde-s-mission-vidarbha-997770</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/thane-news-ganesh-naik-eknath-shinde-janta-darbar-mumbai-high-court/</t>
+          <t>https://marathi.abplive.com/news/pune/siddharth-shinde-supreme-court-lawyer-passed-away-at-delhi-1384433</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/dispute-between-both-shiv-sena-parties-over-printing-anand-dighe-photo-next-to-balasaheb/940602/amp</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-politics-deputy-cm-eknath-shinde-refutes-evm-allegations-confident-of-mahayuti-victory-in-mumbai-civic-polls-on-development-work-1385031</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/eknath-shinde-x-account-hack/</t>
+          <t>https://marathi.ndtv.com/videos/thane-is-up-for-sale-sanjay-raut-hits-out-at-shinde-fadnavis-997973</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-mumbai-rains-deputy-cm-eknath-shinde-reviews-flood-situation-40-50-people-trapped-in-asti-kateri-being-airlifted-from-nashik-ahilyanagar-1384293</t>
+          <t>https://tamil.getlokalapp.com/amp/maharashtra-news/thane/ambernath/thane-heavy-traffic-jam-continues-even-after-eknath-shinde-s-order-15438856</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-thane-news-sanjay-raut-s-controversial-statements-ignite-political-war-between-shiv-sena-factions-ahead-of-municipal-elections-threats-exchanged-1385570/amp</t>
+          <t>https://www.hindustantimes.com/india-news/paint-thrown-at-bust-of-uddhav-thackerays-late-mother-sena-workers-angry-probe-on-101758106562970.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-namo-gardens-project-eknath-shinde-announces-394-crore-funding-for-394-municipal-councils-on-pm-modi-s-birthday-includes-garden-competition-1384925</t>
+          <t>https://www.tribuneindia.com/news/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://lalluram.com/eknath-shinde-x-account-hack-hacker-puts-pakistan-and-turkey-flags-on-home-page/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/hc-to-shinde-by-what-authority-did-you-stay-navi-mumbai-civic-bodys-notice-to-raze-illegal-buildings/articleshow/123952725.cms</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://grandnews.in/2025/09/21/big-breaking-deputy-chief-minister-eknat/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/eknath-shindes-x-account-hacked-on-the-day-of-the-india-pakistan-match-4277868</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/find-the-masterminds-behind-the-kdmc-illegal-buildings-scam-shinde-101758309996962.html</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://khabarchalisa.com/maharashtra-deputy-cm-eknath-shindes-x-accou/</t>
+          <t>https://www.ptinews.com/story/national/full-page-newspaper-ads-and-slew-of-initiatives-shiv-sena-goes-all-out-to-celebrate-pms-birthday/2925344</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://peoplesupdate.com/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-pakistan-turkey-flags-095613</t>
+          <t>https://www.ptinews.com/story/national/shiv-sena-publishes-full-page-ads-in-dailies-on-pms-birthday-shinde-hails-his-new-india-push/2923561</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.prabhasakshi.com/national/eknath-shinde-says-rahul-gandhi-vote-stealing-allegations-are-completely-baseless</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bombay-hc-can-plea-against-shinde-order-be-a-pil/articleshow/124022877.cms</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/maharashtra-deputy-cm-eknath-shinde-s-x-account-hacked-hackers-posted-flags-of-pakistan-and-t%C3%BCrkiye-news-295659</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/thane-shiv-sena-workers-protest-against-sanjay-raut-s-remark-about-anand-dighe-23594679</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/politics/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother20250916212035/?amp=1</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/acharya-devvrat-sworn-in-as-governor-of-maharashtra-reads-oath-in-sanskrit20250915150141?amp=1</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/hc-seeks-govt-s-stand-on-illegal-stay-on-demolition-by-dy-cm-101758137116362.html</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother/</t>
+          <t>https://www.ptinews.com/story/national/dy-cm-shindes-x-account-hacked-cong-leader-questions-cyber-security/2935531</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://www.ptinews.com/story/national/women-office-bearers-workers-of-sena-ubt-from-palghar-join-shinde-led-sena-ahead-of-local-polls/2927880</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/nation/shindes-x-account-hacked-maharashtras-cyber-security-in-question-uproar-over-eknath-shindes-x-account-being-hacked/</t>
+          <t>https://www.ptinews.com/editor-detail/bjp-gave-up-claim-for-mumbai-mayor-s-post-in-2017-at-request-of-shinde--narvekar--says-cm-fadnavis/2921301</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/eknath-shinde-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A4%B2-%E0%A4%A6%E0%A5%87-%E0%A4%B8%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AA%E0%A4%A6-%E0%A4%B8%E0%A5%87-%E0%A4%87%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%AB-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%B8%E0%A5%87-%E0%A4%86%E0%A4%88-%E0%A4%96%E0%A4%AC%E0%A4%B0/ar-AA1uIeu8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/story/national/ncp-sp-cong-welcome-sc-order-on-maharashtra-local-bodies-polls;-mahayuti-will-win-says-shinde/2920944</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shiv-sena-protests-against-sanjay-raut-of-sena-ubt-for-insulting-eknath-shindes-mentor/2934437</t>
+          <t>https://www.uniindia.com/news/west/disaster-management-cm-shinde/3577807.html</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%A6-%E0%A4%AC-%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AC%E0%A4%A8%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-cm-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%97-%E0%A4%A8-%E0%A4%88%E0%A4%82-5-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%B5%E0%A4%9C%E0%A4%B9%E0%A5%87%E0%A4%82/ar-AA1uIG8l?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/most-of-rs-46000cr-projects-for-marathwada-announced-by-shinde-led-cabinet-in-2023-still-on-paper/articleshow/123907066.cms</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-assembly-election-result-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A4-%E0%A4%9C-%E0%A4%A4-%E0%A4%97%E0%A4%88-%E0%A4%AE%E0%A4%97%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%9F-%E0%A4%95-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A5%81%E0%A4%86/ar-AA1uBWUK?cvid=165226EF5620437992660C8F5EC7383E&amp;ocid=TIYLnav&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.newsband.in/article_detail/acharyadevvrattakes-oath-as-maharashtras-22nd-governor</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A4-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%9C-%E0%A4%A4%E0%A4%A4%E0%A5%87-100-%E0%A4%B8-%E0%A4%9F%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%95-%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5/ar-AA1v4Uzx?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/editor-detail/On-eve-of-PM-s-birthday-Shinde-announces-scheme-to-develop-Namo-Parks-in-Maharashtra/2921302</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-congress-leader-questions-cyber-security/amp_articleshow/124026185.cms</t>
+          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-cm-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2-%E0%A4%AA%E0%A4%B8%E0%A4%82%E0%A4%A6-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9D%E0%A4%9F%E0%A4%95-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A-%E0%A4%9A-%E0%A4%B8%E0%A5%87-%E0%A4%AD-%E0%A4%AA-%E0%A4%9B%E0%A4%A1%E0%A4%BC%E0%A5%87/ar-AA1uxBrL?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/story/national/on-eve-of-pms-birthday-shinde-announces-scheme-to-develop-namo-parks-in-maharashtra/2921302</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/raj-thackeray-%E0%A4%B2-%E0%A4%B2-%E0%A4%AA-%E0%A4%AA-%E0%A4%B2-%E0%A4%97%E0%A5%87%E0%A4%B2%E0%A5%81-%E0%A4%AA%E0%A4%B0-%E0%A4%B2%E0%A5%9C%E0%A4%95-%E0%A4%95-%E0%A4%A1-%E0%A4%82%E0%A4%B8-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A5%9C%E0%A4%95%E0%A5%87-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AA%E0%A5%82%E0%A4%9B-%E0%A4%AF%E0%A4%B9-%E0%A4%B9%E0%A5%88-%E0%A4%B2-%E0%A4%A1%E0%A4%B2-%E0%A4%AC%E0%A4%B9%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8/ar-AA1tuyLy?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/story/national/prioritise-development-in-14-villages-added-to-navi-mumbai-civic-limits-dy-cm-shinde/2930925</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-response-after-sanjay-raut-objected-to-placing-anand-dighes-photo-next-to-balasaheb-thackeray/922799/</t>
+          <t>https://www.newsonair.gov.in/maharashtra-launches-namo-gardens-and-tourism-skill-programme-to-mark-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AD%E0%A5%87%E0%A4%9C-%E0%A4%A6-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%AC-%E0%A4%B9%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%A8-%E0%A4%AE-%E0%A4%AB-%E0%A4%87%E0%A4%A8%E0%A4%B2-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B0-%E0%A4%AE%E0%A4%A6-%E0%A4%B8-%E0%A4%85%E0%A4%A0-%E0%A4%B5%E0%A4%B2%E0%A5%87/ar-AA1uMd6x?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-shiv-sena-leaders-speech-adds-fuel-to-accusations-of-biased-allocation-of-funds-23595109</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://inshorts.com/hi/news/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6--%E0%A4%A6--%E0%A4%95--x-%E0%A4%85%E0%A4%95-%E0%A4%89-%E0%A4%9F-%E0%A4%B9-%E0%A4%95--%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%B8-%E0%A4%A8--%E0%A4%AA-%E0%A4%B8-%E0%A4%9F-%E0%A4%95-%E0%A4%8F-%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%A4-%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%95--%E0%A4%95--%E0%A4%9D-%E0%A4%A1---1758441470089</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3633705-infrastructure-revamp-a-new-dawn-for-navi-mumbais-villages</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/eknath-shinde-mla-aamshya-padvi-tribal-reservation-opposition-abuses-protest-dhangar-banjara-controversy-gs97</t>
+          <t>https://www.patrika.com/en/state-news/thane-metro-begins-trial-run-after-20-year-wait-19966553</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%89%E0%A4%AA%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-eknath-shinde-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A5%E0%A5%87%E0%A4%9F-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B9-%E0%A4%AF%E0%A5%87%E0%A4%A4%E0%A4%9A-%E0%A4%85%E0%A4%B8%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A4%9C%E0%A5%87/ar-AA1BAyul?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.aninews.in/news/national/general-news/mmrda-temporarily-suspends-monorail-services-in-mumbai20250920092952</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/dcm-eknath-shinde-on-bmc-election-with-mahayuti-alliance/videoshow/124025029.cms</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-mmrda-to-suspend-monorail-services-on-september-20-in-mumbai20250917100119/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/sanjay-raut-attacks-eknath-shinde-shrikant-shiv-sena-rahul-modi-presser-135957579.html</t>
+          <t>https://thenewsmill.com/2025/09/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-pm-modi-birthday-eknath-shinde-s-leader-of-the-world-tribute-article-in-loksatta-saamana-omits-ad-1384700</t>
+          <t>https://thenewsmill.com/2025/09/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flag-saamana-online-news/</t>
+          <t>https://www.sakshipost.com/news/shiv-senaubt-continues-attacking-dy-cm-shinde-says-maha-govt-boastful-454108</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/mns-avinash-jadhav-on-vasai-child-dies-due-to-traffic-jam-criticize-eknath-shinde-pratap-sarnaik-1484355.html</t>
+          <t>https://www.latestly.com/quickly/agency-news/devendra-fadnavis-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane-7123779.html</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/thackeray-brothers-meeting-in-thane-thackeray-brothers-election-strategy/940600</t>
+          <t>https://www.khabarfast.com/uploadnews/details/maharashtra-news-deputy-cm-eknath-shinde-x-handle-hacked-hackers-shared-posts-with-pakistan-and-turkey-flags</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/deputy-cm-eknath-shinde-x-account-hack-pakistan-turkey-flag-shown-3016093/amp</t>
+          <t>https://www.loksatta.com/mumbai/dcm-eknath-shinde-orders-district-administration-to-remain-alert-in-wake-of-heavy-rains-zws-70-5373503/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/eknath-shindes-x-account-briefly-hacked-hackers-post-pics-of-pak-turkey-flags-9315607</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/eknath-shinde-mla-aamshya-padvi-tribal-reservation-opposition-abuses-protest-dhangar-banjara-controversy-gs97</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-on-eknath-shinde-maharashtra-ahmedabad-bullet-train-anand-dighe-3015725/amp</t>
+          <t>https://mandalnews.com/other-cities/parashuram-development-board-chairman-given-ministerial-rank/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-strict-against-builders-involved-in-kalyan-dombivali-illegal-buildings-constructing-3015585/amp</t>
+          <t>https://www.msn.com/mr-in/news/other/siddharth-shinde-passes-away-%E0%A4%AE-%E0%A4%9C-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%A8-%E0%A4%A4%E0%A5%82-%E0%A4%95-%E0%A4%AF%E0%A4%A6-%E0%A4%B8-%E0%A4%AA%E0%A5%8D%E0%A4%AF-%E0%A4%AD-%E0%A4%B7%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A4%AE%E0%A4%9C-%E0%A4%B5%E0%A5%82%E0%A4%A8-%E0%A4%B8-%E0%A4%82%E0%A4%97%E0%A4%A3-%E0%A4%B0-%E0%A4%B5-%E0%A4%A7-%E0%A4%9C%E0%A5%8D%E0%A4%9E-%E0%A4%95-%E0%A4%A3-%E0%A4%B9-%E0%A4%A4%E0%A5%87-%E0%A4%B8-%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87/ar-AA1MCHAN</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%AC%E0%A4%97-%E0%A4%B5%E0%A4%A4-%E0%A4%95%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%97%E0%A5%81%E0%A4%B5-%E0%A4%B9-%E0%A4%9F-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%AD-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%95-%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A6%E0%A5%87%E0%A4%96%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B2-%E0%A4%B8%E0%A5%8D%E0%A4%9F/ar-AA1sOwtY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-20-september-2025-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/amp/india/maharashtra/story/eknath-shinde-x-account-hacked-pakistan-turkey-flag-posted-ntc-rptc-2338322-2025-09-21</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/dcm-eknath-shinde-on-bmc-election-with-mahayuti-alliance/videoshow/124025029.cms</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%B8%E0%A4%AD-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%A4%E0%A5%87-%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AB-%E0%A4%B0-%E0%A4%AC%E0%A4%A8%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-cm-%E0%A4%AF%E0%A5%87-%E0%A4%AC-%E0%A4%A4%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A5%8D%E0%A4%B9%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%A4-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%96-%E0%A4%B8/ar-AA1s9G9J?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-eknath-shinde-issues-stern-warning-to-inefficient-maharashtra-cabinet-ministers-over-neglect-of-party-work-and-public-issues-1385985</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/find-the-masterminds-behind-the-kdmc-illegal-buildings-scam-shinde-101758309996962-amp.html</t>
+          <t>https://marathi.ndtv.com/videos/thane-ghodbunder-road-traffic-jaam-controversy-997251</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/stories-detail/national/maharashtra-dy-cm-eknath-shindes-x-account-hacked/2934860/0</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/uddhav-thackeray-led-shiv-sena-leader-ayodhya-poul-patil-received-call-from-eknath-shinde-office-call-recording-goes-viral/videoshow/123934054.cms</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-charges-baseless-says-ekanth-shinde-23594783</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pm-modi-birthday-eknath-shinde-s-leader-of-the-world-tribute-article-in-loksatta-saamana-omits-ad-1384700</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633937-crackdown-on-unauthorized-buildings-in-thane-eknath-shinde-leads-investigation</t>
+          <t>https://www.msn.com/mr-in/news/other/sushma-andhare-%E0%A4%A1%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%9F-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%96%E0%A4%B0%E0%A5%87-%E0%A4%B0%E0%A5%81%E0%A4%AA-%E0%A4%86%E0%A4%9C-%E0%A4%AC-%E0%A4%B9%E0%A5%87%E0%A4%B0-%E0%A4%86%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A5%81%E0%A4%B7%E0%A4%AE-%E0%A4%85%E0%A4%82%E0%A4%A7-%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%98%E0%A4%A3-%E0%A4%98-%E0%A4%A4/ar-AA1HY5L7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-18-september-2025-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://www.tv9marathi.com/videos/sanjay-raut-slams-eknath-shinde-modi-advertisement-and-reply-also-cm-fadnavis-over-thackeray-brand-1495206.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-mumbai-rains-deputy-cm-eknath-shinde-reviews-flood-situation-40-50-people-trapped-in-asti-kateri-being-airlifted-from-nashik-ahilyanagar-1384293/amp</t>
+          <t>https://www.lokmat.com/maharashtra/maharashtra-politics-90-of-shinde-pawar-and-bjp-candidates-became-mlas-by-stealing-votes-sanjay-rauts-criticism-a-a732/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-illegal-construction-high-court-questions-deputy-cm-s-authority-to-stay-navi-mumbai-demolition-notices-for-naivedya-and-albela-buildings-1384927/amp</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-cabinet-discontent-bharat-gogawale-on-eknath-shinde-s-displeasure-ministerial-accountability-and-action-on-inefficient-ministers-1386103</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sada-saravankar-statement-of-mla-fund-mahim-thackeray-group-mahesh-sawant-counterattack-mla-gets-rs-2-crore-but-i-get-rs-20-crore-when-i-am-not-an-mla-1385728/amp</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%B8%E0%A4%A8%E0%A4%B2-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AB-%E0%A4%95-%E0%A4%9B%E0%A5%81%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%8F-%E0%A4%9C-%E0%A4%82%E0%A4%9A-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1zIR9b?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/sanjay-raut-criticized-eknath-shinde-and-pratap-sarnaik-over-anand-dighe/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-images-of-pakistan-turkey-flags-posted/amp_articleshow/124024337.cms</t>
+          <t>https://www.esakal.com/desh/maharashtra-marathi-live-news-23-september-2025-navratri-festival-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/maharashtra-election-results-bjps-best-congresss-worst-ever-show-in-state-traitors-shinde-and-pawar-prove-theyre-true-heirs/ar-AA1uDEAR?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-maharashtra-deputy-cms-ajit-pawar-and-eknath-shinde-express-anger-over-ministerial-inefficiency-neglect-of-party-work-and-janata-darbar-1386067</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/thane-shiv-sena-workers-protest-against-sanjay-raut-s-remark-about-anand-dighe-23594679</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-mumbai-rains-deputy-cm-eknath-shinde-reviews-flood-situation-40-50-people-trapped-in-asti-kateri-being-airlifted-from-nashik-ahilyanagar-1384293</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/amp/news/industry/strict-action-ordered-against-65-illegal-buildings-in-kalyan-dombivli-by-deputy-chief-minister-eknath-shinde/124008652</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/mahayuti-government-reservation-issue-new-controversy-reason-sw79</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3629545-uddhav-thackeray-criticizes-indias-cricket-match-with-pakistan-questions-bjps-patriotism?utm_campaign=Bundle&amp;utm_medium=referral&amp;utm_source=Bundle</t>
+          <t>https://telugu.getlokalapp.com/maharashtra-news/trial-run-of-thane-metro-route-4-and-4a-begins-fadnavis-praises-shinde-15458549</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/acharyadevvrattakes-oath-as-maharashtras-22nd-governor</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-eknath-shinde-continues-his-series-of-meetings-he-will-launch-his-election-campaign-with-a-dussehra-rally-1189598</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-deputy-cm-eknath-shinde-s-twitter-account-hacked-raises-cybersecurity-concerns-201758454098732.amp.html</t>
+          <t>https://www.newsnationtv.com/states/maharashtra/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-shared-post-of-pakistan-and-turkey-flags-10484007</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-polls-an-acid-test-for-shiv-sena-ubt-says-thackeray-101758222779307.html</t>
+          <t>https://www.kisantak.in/politics/story/eknath-shinde-took-a-swipe-at-his-opponents-says-they-feel-depressed-by-farming-1279260-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-planning-for-tourism-development-in-the-kandalvan-area/922599/</t>
+          <t>https://jantaserishta.com/local/maharashtra/metro-project-will-solve-traffic-congestion-problem-in-thane-eknath-shinde-4279685</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/shiv-sena-ubt-mns-bjp-raj-thackeray-uddhav-thackeray-devendra-fadnavis-unite-against-shiv-sena-eknath-shinde-for-thane-sporting-committee-election/articleshow/123938834.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-cm-fadnavis-eknath-shinde-take-metro-ride-during-line-4-and-4a-trial-run-107480/5</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/the-conflict-between-naik-and-shinde-reaches-its-peak-shinde-faction-files-suit-against-naik-in-the-high-court-over-the-janata-darbar/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/heavy-vehicles-banned-on-thanes-ghodbunder-road-during-daytime-23594294</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/the-conflict-between-the-bjp-and-shinde-factions-escalates-in-thane-district/</t>
+          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-15-september-2025-3482219.html</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/mumbai-shiv-sena-leader-seeks-carter-road-be-named-after-rajesh-khanna/ar-AA1Megvm?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/statue-of-uddhav-thackeray-s-mother-defaced-in-mumbai-shiv-sena-ubt-protests-101758095171594.html</t>
+          <t>https://www.livehindustan.com/national/who-will-take-over-the-cpi-after-d-raja-these-two-names-are-in-the-race-201758252502320.html</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%95-%E0%A4%AE%E0%A4%B9-%E0%A4%A8-%E0%A4%AC%E0%A4%A4-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%AC%E0%A5%82-%E0%A4%86%E0%A4%9C%E0%A4%AE-%E0%A4%AA%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%B8%E0%A4%AD-%E0%A4%B8%E0%A5%87-%E0%A4%A8-%E0%A4%B2%E0%A4%82%E0%A4%AC-%E0%A4%A4/ar-AA1AgWGX?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3631323-celebrating-leadership-modis-vision-for-a-new-india-on-his-75th-birthday</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/bmc-election-2025-shivsena-ubt-mns-raj-thackeray-seat-sharing-formula-96240</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/meenatai-thackeray-statue-smeared-with-red-paint-1-held-101758136336233-amp.html</t>
+          <t>https://www.etvbharat.com/mr/!politics/bmc-polls-50-50-seats-for-sena-ubt-mns-in-mumbai-strongholds-60-40-in-others-say-party-leaders-mhs25092103157</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3631328-statue-defacement-stirs-political-emotions-in-mumbai?amp</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/new-jetty-construction-for-vasai-and-uttan-dongri-ro-ro-service-which-will-help-commuters/articleshow/123892530.cms</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3630398-bjps-enduring-commitment-fadnavis-recollects-2017-political-maneuverings-in-mumbai</t>
+          <t>https://www.hindisaamana.com/the-conflict-between-the-bjp-and-shinde-factions-escalates-in-thane-district/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%95-%E0%A4%B5-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%B0-%E0%A4%95-%E0%A4%82%E0%A4%AA-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%A8-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%B2-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A4%A8%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AE-%E0%A4%95/ar-AA1vTcYH?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ibc24.in/maharashtra/rahul-gandhis-vote-theft-allegations-completely-baseless-shinde-3258685.html</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-election-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%AA%E0%A5%81%E0%A4%B2-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A8-%E0%A4%9F-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%AD%E0%A4%B0-%E0%A4%97-%E0%A4%A1%E0%A4%BC-%E0%A4%AA%E0%A4%95%E0%A4%A1%E0%A4%BC-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%89%E0%A4%A4-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%A6-%E0%A4%B5/ar-AA1sGJQE?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.latestly.com/india/good-news-for-thane-residents-metro-trial-runs-will-take-place-on-monday-2758623.html</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/kedar-dighes-sharp-attack-on-shinde-faction-anand-dighe-remembered-as-elections-approach/articleshow/124004160.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-ubt-%E0%A4%A8%E0%A5%87-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B5-%E0%A4%B0-%E0%A4%A7-%E0%A4%97%E0%A4%A4-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%A4-%E0%A4%A8-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%95-%E0%A4%A8-%E0%A4%95-%E0%A4%B2/ar-AA1z6zj4?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.hindustantimes.com/india-news/statue-of-uddhav-thackeray-s-mother-defaced-in-mumbai-shiv-sena-ubt-protests-101758095171594.html</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharastra-paint-thrown-on-statue-of-meenatai-thackeray-at-mumbai-shivaji-park-2025-09-17</t>
+          <t>https://www.ndtv.com/video/ndtv-yuva-conclave-milind-deora-on-which-leader-connects-with-gen-z-better-996976</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A8%E0%A5%87-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%AE%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A5%87%E0%A4%B6-%E0%A4%95-%E0%A4%AF-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%A6-%E0%A4%B5-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B9%E0%A4%AE-%E0%A4%B8-%E0%A4%A5-%E0%A4%AE-%E0%A4%B2%E0%A4%95%E0%A4%B0-%E0%A4%95-%E0%A4%AE-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87/ar-AA1vfwwh?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.amarujala.com/india-news/maharastra-paint-thrown-on-statue-of-meenatai-thackeray-at-mumbai-shivaji-park-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%A6%E0%A4%AC-%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B2%E0%A5%87%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%AF%E0%A5%82%E0%A4%AC-%E0%A4%9F-%E0%A4%A8%E0%A5%87%E0%A4%A4/ar-AA1uTckb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.jansatta.com/national/current-mlas-get-rs-2-crore-and-i-get-rs-20-crore-big-claim-by-former-shiv-sena-mla-sada-sarvankar/4153263/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B5-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%89%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%AA%E0%A5%81%E0%A4%B2-%E0%A4%B8-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%87%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87%E0%A4%AE-%E0%A4%B2-%E0%A4%95%E0%A4%B0-%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%89%E0%A4%A4/ar-AA1t7BTt?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A4%AC-%E0%A4%B9-%E0%A4%97-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%95-%E0%A4%B5-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B0-%E0%A4%95-%E0%A4%A8-%E0%A4%95-%E0%A4%A8-%E0%A4%AC%E0%A4%A8%E0%A5%87%E0%A4%97-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%AE%E0%A4%A8%E0%A5%87-%E0%A4%86%E0%A4%88-%E0%A4%A4-%E0%A4%B0-%E0%A4%96/ar-AA1vowQk?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/uddhav-targets-bjp-over-india-pakistan-cricket-match-in-asia-cup-maharashtra-debt-2025-09-16</t>
+          <t>https://www.abplive.com/states/maharashtra/shiv-sena-leader-ex-mla-sada-sarvankar-claims-20-crore-fund-dispute-sparks-political-stir-3016545</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/blog/india/bjp-shivsena-ncp-congress-local-body-elections-your-bow-and-arrow-but-target-is-ours-drawing-dividing-line-blog-amitabh-srivastava-b507/</t>
+          <t>https://hindi.theprint.in/india/statue-of-bal-thackerays-wife-meenatai-defaced-probe-launched/869900/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%B6-%E0%A4%AE%E0%A4%A4%E0%A4%AD%E0%A5%87%E0%A4%A6-%E0%A4%A8-%E0%A4%B9-%E0%A4%A4-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6%E0%A4%B9-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A5%87%E0%A4%9F-%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1K3Mqc?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.theprint.in/india/mumbai-bal-thackerays-wife-meenatai-thackerays-statue-defaced-by-throwing-paint-on-it-one-person-arrested/870084/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/world/asia/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621?amp=1</t>
+          <t>https://www.amarujala.com/india-news/uddhav-targets-bjp-over-india-pakistan-cricket-match-in-asia-cup-maharashtra-debt-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3635247-modis-nation-address-anticipation-on-eve-of-navratri?amp</t>
+          <t>https://hindi.webdunia.com/maharashtra/bmc-elections-uddhav-thackeray-shivsena-ubt-raj-thackerays-mns-alliance-seat-sharing-formula-125092100051_1.html</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
+          <t>https://www.lokmatnews.in/blog/india/bjp-shivsena-ncp-congress-local-body-elections-your-bow-and-arrow-but-target-is-ours-drawing-dividing-line-blog-amitabh-srivastava-b507/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
+          <t>https://marathi.abplive.com/news/politics/sada-saravankar-statement-of-mla-fund-mahim-thackeray-group-mahesh-sawant-counterattack-mla-gets-rs-2-crore-but-i-get-rs-20-crore-when-i-am-not-an-mla-1385728</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/articleshow/123993653.cms</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189622</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
+          <t>https://gallinews.com/%E0%A4%8F%E0%A4%95%E0%A4%A8%E0%A4%BE%E0%A4%A5-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%B8%E0%A4%BE%E0%A4%B9%E0%A5%87%E0%A4%AC%E0%A4%BE%E0%A4%82%E0%A4%9A%E0%A5%80-%E0%A4%B5%E0%A4%BE/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
+          <t>https://www.msn.com/en-in/lifestyle/smart-living/govt-to-formulate-new-mhada-policy-to-provide-affordable-housing-dy-cm-shinde/ar-AA1y3CdE?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/nawab-malik-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-23-%E0%A4%A8%E0%A4%B5%E0%A4%82%E0%A4%AC%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A6-%E0%A4%95%E0%A5%81%E0%A4%9B-%E0%A4%AD-%E0%A4%B9-%E0%A4%B8%E0%A4%95%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%A8%E0%A4%B5-%E0%A4%AC-%E0%A4%AE%E0%A4%B2-%E0%A4%95-%E0%A4%95-%E0%A4%B8%E0%A4%A8%E0%A4%B8%E0%A4%A8-%E0%A4%96%E0%A5%87%E0%A4%9C-%E0%A4%A6-%E0%A4%B5/ar-AA1ttOeX?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.tribuneindia.com/news/business/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://24city.news/ncp-chintan-camp-ajit-pawar-reveals-people-ask-why-i-leave-sharad-pawars-support/</t>
+          <t>https://www.electronicsforyou.biz/industry-buzz/rrp-electronics-gets-land-for-semiconductor-fab-in-navi-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/gossip-the-grand-alliances-fun-banter-janta-darbar-vs-petition-darbar/</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-cabinet-meeting-maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-8-important-decisions-mumbai-maharashtra-news-mhs25091602614</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ajit-pawars-absence-at-key-guv-events-raises-eyebrows/articleshow/124030467.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/pm-modi-turns-75-highlights-of-initiatives-launched-by-bjp-events-held-in-several-states/articleshow/123949298.cms</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/amp/news/railways/indias-bullet-train-project-tunnelling-to-begin-january-2026-as-tbm-arrives/124025478</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar-3735776</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/world/australian-mps-met-maharashtras-eknath-shinde-discussed-business-cooperation--4269467</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/rajuddhav-tie-up-won-t-have-impact-on-bmc-polls-101758222840140.html</t>
+          <t>https://politalks.news/political-temperature-rises-in-maharashtra-ncp-chief-ajit-pawar-preparing-to-break-away-from-the-mahayuti</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
+          <t>https://www.amarujala.com/india-news/modi-govt-gave-rs-21-000-cr-for-marathwada-rail-lines-rs-450-crore-came-during-upa-time-fadnavis-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/politics-loses-civility-in-maharashtra-101758482600190.html</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/pm-modi-turns-75-highlights-of-initiatives-launched-by-bjp-events-held-in-several-states/articleshow/123949298.cms</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sanjay-raut-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%97-%E0%A4%82%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A5%87-%E0%A4%98%E0%A5%87%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%B5%E0%A5%87%E0%A4%B3-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%B0-%E0%A4%96%E0%A4%A0-%E0%A4%95-%E0%A4%AE%E0%A4%A4/ar-AA1Bwm7B?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-told-party-workers-bmc-elections-are-a-litmus-test-for-us/articleshow/123989198.cms</t>
+          <t>https://curlytales.com/india/ct-scoop/durga-puja-pandals-in-mumbai-where-you-can-spot-bollywood-celebrities/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/raj-thackeray-%E0%A4%AE-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A4-%E0%A4%85%E0%A4%B8%E0%A4%A4-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%97%E0%A4%B0%E0%A4%9C%E0%A4%9A-%E0%A4%95-%E0%A4%AF-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%82-%E0%A4%AE%E0%A4%A8%E0%A4%B8%E0%A5%87%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A5%81%E0%A4%96-%E0%A4%82%E0%A4%A8-%E0%A4%A1-%E0%A4%B5%E0%A4%9A%E0%A4%B2%E0%A4%82/ar-AA1vtzAn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-sanjay-raut-supports-rahul-gandhi-saying-that-90-of-the-mahayuti-mlas-in-maharashtra-won-through-vote-theft/articleshow/124015667.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/meenatai-thackeray-statue-smeared-with-red-paint-1-held-101758136336233.html</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A4%B9-%E0%A4%B2%E0%A4%82-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%95-%E0%A4%81%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A4%9A-%E0%A4%89%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%87%E0%A4%96-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1yazrQ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.asianage.com/nation/ubt-sena-up-in-arms-after-meenatai-thackeray-statue-defaced-1904390</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/amit-thackeray-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%AD%E0%A4%B5%E0%A4%A8-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%82%E0%A4%97%E0%A4%A3-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AE%E0%A5%88%E0%A4%A6-%E0%A4%A8-%E0%A4%A4-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%9F-%E0%A4%95%E0%A4%B2-%E0%A4%AA%E0%A4%A3-%E0%A4%AE-%E0%A4%A4-%E0%A4%B6%E0%A5%8D%E0%A4%B0-%E0%A4%AC%E0%A5%81%E0%A4%9A%E0%A4%95%E0%A4%B3%E0%A5%8D%E0%A4%AF-%E0%A4%A4/ar-AA1sKTT5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA-%E0%A4%A4%E0%A5%83%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%A4-%E0%A4%9A-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%B2-%E0%A4%AC%E0%A4%B8%E0%A4%A3-%E0%A4%B0-%E0%A4%AE-%E0%A4%A0-%E0%A4%B9-%E0%A4%A6%E0%A4%B0-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A6-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%82-%E0%A4%96%E0%A4%B3%E0%A4%AC%E0%A4%B3/ar-AA1MUzvh</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-secret-of-2-5-hour-meeting-at-shivtirth-how-raj-thackeray-prevail-over-uddhav-political-experts-reveal-9622593.html</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/amit-thackeray-%E0%A4%A6%E0%A4%A3%E0%A4%A6%E0%A4%A3-%E0%A4%A4-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A4%B5-%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%B9-%E0%A4%95-%E0%A4%B2-%E0%A4%AE%E0%A4%B2-%E0%A4%B9%E0%A5%87%E0%A4%9A-%E0%A4%B6-%E0%A4%95%E0%A4%B5%E0%A4%A4-%E0%A4%AF-%E0%A4%95/ar-AA1uCiYN?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/mumbai-mina-thackeray-statue-defaced-shivaji-park-shiv-sena-protest-police-action-ntc-dskc-2335896-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-told-party-workers-bmc-elections-are-a-litmus-test-for-us/articleshow/123989198.cms</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-3/921531/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-22-political-news-in-marathi-941153</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-21-september-2025-india-vs-pakistan-%E2%80%93-asia-cup-maharashtra-politics-national-international-live-update-in-marathi-940858</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-sanjay-raut-supports-rahul-gandhi-saying-that-90-of-the-mahayuti-mlas-in-maharashtra-won-through-vote-theft/articleshow/124015667.cms</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-3/921531/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-17-september-2025-pm-narendra-modi-75th-birthday-zp-presidentship-reservation-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-21-september-2025-india-vs-pakistan-%E2%80%93-asia-cup-maharashtra-politics-national-international-live-update-in-marathi-940858</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-17-political-news-in-marathi-939849</t>
+          <t>https://www.tv9marathi.com/videos/ncp-sharad-pawar-expresses-delight-at-potential-thackeray-brothers-mumbai-alliance-and-power-grab-1495154.html</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/breaking-news-today-18-september-monsoon-maratha-reservation-obc-bmc-election-mumbai-local-train-weather-political-doctors-strike-tajya-batmya-in-marathi-940110/amp</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-14-political-news-in-marathi-939050</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/is-the-alliance-between-the-thackeray-brothers-certain-uddhav-thackerays-hint-97844/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-17-political-news-in-marathi-939849</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%82%E0%A4%B8-%E0%A4%AC%E0%A4%A4-%E0%A4%B0-%E0%A4%B9-%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%89%E0%A4%AC-%E0%A4%A0-%E0%A4%B2-%E0%A4%9C-%E0%A4%A8-%E0%A4%9A-%E0%A4%86%E0%A4%A0%E0%A4%B5%E0%A4%A3-%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%AB-%E0%A4%B5-%E0%A4%A7%E0%A5%87%E0%A4%AF%E0%A4%95-%E0%A4%B5%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A1-%E0%A4%B5%E0%A4%9A%E0%A4%B2%E0%A4%82/ar-AA1CdNPz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://politicalmaharashtra.in/the-bomb-of-political-revelation-will-explode-soon-shinde-group-warns-97879/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
+          <t>https://politicalmaharashtra.in/twist-in-mumbai-municipal-corporations-politics-sharad-pawars-new-move-97848/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6-%E0%A4%98%E0%A5%87-%E0%A4%B6%E0%A5%87%E0%A4%B5%E0%A4%9F%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%9C-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A5%81%E0%A4%96-%E0%A4%B9-%E0%A4%A4%E0%A5%87-%E0%A4%86%E0%A4%A3-%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AB-%E0%A4%9F-%E0%A4%AC-%E0%A4%B3-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC-%E0%A4%9C%E0%A5%82%E0%A4%B2-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%9A%E0%A4%82%E0%A4%A1-%E0%A4%9A-%E0%A4%A1%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%A8%E0%A5%8D/ar-AA1MOF6O</t>
+          <t>https://politicalmaharashtra.in/rohit-pawars-janata-darbar-or-assembly-hall-dadagiri-97885/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>http://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%A8%E0%A4%B8%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%B5-%E0%A4%A8-%E0%A4%B6-%E0%A4%9C-%E0%A4%A7%E0%A4%B5-%E0%A4%82%E0%A4%9A-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95-%E0%A4%A5%E0%A5%87%E0%A4%9F-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%89%E0%A4%A4%E0%A4%B0%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%87%E0%A4%B6-%E0%A4%B0-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%95-%E0%A4%A2%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1MFEAF?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/sanjay-raut-slams-eknath-shinde-modi-advertisement-and-reply-also-cm-fadnavis-over-thackeray-brand-1495206.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-bmc-election-latest-update-mumbai-pune-rain-weather-today-devendra-fadnavis-on-uddhav-thackeray-shivsena-news-scj-81-5380824/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/kishori-pednekar-on-two-legs-but-see-what-happens-when-you-go-kishori-pednekars-warning-to-the-shinde-group/923218/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/?noamp=mobile</t>
+          <t>https://www.lokmat.com/mumbai/cm-devendra-fadnavis-slams-thackeray-bandhu-over-best-election-2025-result-and-brand-defeat-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/dadar-shivaji-park-meenatai-thackeray-statue-red-color-thrown-mumbai-crime/articleshow/123936431.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/kishori-pednekar-on-two-legs-but-see-what-happens-when-you-go-kishori-pednekars-warning-to-the-shinde-group/923218/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%96%E0%A5%87%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B2-%E0%A4%B5-%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A5%82-%E0%A4%AD%E0%A4%97%E0%A4%A4-%E0%A4%B2-%E0%A4%82%E0%A4%AC%E0%A4%82-%E0%A4%95%E0%A4%A6%E0%A4%AE-%E0%A4%82%E0%A4%9A-%E0%A4%AD-%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A4%B0-%E0%A4%9C-%E0%A4%A7%E0%A4%B5-%E0%A4%82%E0%A4%AC%E0%A4%A6%E0%A5%8D%E0%A4%A6%E0%A4%B2-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%AF%E0%A4%B8%E0%A5%8D%E0%A4%AB-%E0%A4%9F/ar-AA1Hsx7J?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-navratri-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-monday-22-september-2025-1497734.html</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/top-marathi-news-today-breaking-news-political-news-live-update-crime-news-994890.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/bmc-election-raj-thackeray-will-hand-over-mumbais-subha-to-uddhav-thackeray/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/dadar-shivaji-park-meenatai-thackeray-statue-red-color-thrown-mumbai-crime/articleshow/123936431.cms</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-tejashwi-yadav-calls-cm-nitish-a-cheat-minister-makes-these-big-promises-to-the-public-2025-09-18</t>
+          <t>https://www.navarashtra.com/maharashtra/top-marathi-news-today-breaking-news-political-news-live-update-crime-news-994890.html</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-16-17-september-live-updates-tejashwi-yadav-bihar-adhikar-yatra-election-pm-modi-rahul-gandi-supreme-court-sahastradhara-flood-waqf/4143389/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/bmc-election-raj-thackeray-will-hand-over-mumbais-subha-to-uddhav-thackeray/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%90%E0%A4%A8-%E0%A4%A6-%E0%A4%B5-%E0%A4%B3-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%B2-%E0%A4%97-%E0%A4%B5-%E0%A4%86%E0%A4%A3-%E0%A4%B6%E0%A4%B9%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%A4%E0%A5%81%E0%A4%9F%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AD-%E0%A4%A4-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%9A-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%87%E0%A4%B6-%E0%A4%B0/ar-AA1MTtxO</t>
+          <t>https://www.marathijagran.com/maharashtra/nashik/shardiya-navratri-2025-praveen-togadias-big-statement-at-hindu-hunkar-sabha-said-no-entry-for-muslims-at-garba-places-96201</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/navi-mumbai-city-petition-filed-in-janata-darbar-against-minister-ganesh-naik-by-kishore-patkar/922934/amp/</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-tejashwi-yadav-calls-cm-nitish-a-cheat-minister-makes-these-big-promises-to-the-public-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/navratri-2025-mumbai-police-will-have-strict-security-for-nine-days/amp_articleshow/124024081.cms</t>
+          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-16-17-september-live-updates-tejashwi-yadav-bihar-adhikar-yatra-election-pm-modi-rahul-gandi-supreme-court-sahastradhara-flood-waqf/4143389/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://yashbharat.co.in/maharashtra-deputy-cm-eknath-shindes-ex-handle-hacked-posts-with-pakistan-and-turkey-flags-spark-uproar/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html?utm_source=District%20Widget&amp;utm_medium=Mobile&amp;utm_campaign=marathi</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/shinde-group-rauts-ties-with-pawar-led-to-thackeray-groups-losses-4276178</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A0-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B2-%E0%A4%AD-%E0%A4%88%E0%A4%97-%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B5%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%9A-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A7-%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A5%87%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%A4%E0%A4%9A-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5-%E0%A4%B0-%E0%A4%A7-%E0%A4%A4-%E0%A4%8F%E0%A4%B2%E0%A5%8D%E0%A4%97-%E0%A4%B0/ar-AA1G2Q8d?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/thane-city-challenge-to-eknath-shinde-in-the-fort-itself-bjp-leader-ganesh-naiks-janata-darbar-for-the-third-consecutive-time/</t>
+          <t>https://www.tv9marathi.com/videos/eknath-shinde-shivsena-file-janhit-yachika-in-mumbai-high-court-against-ganesh-naik-janta-darbar-1496267.html</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.theindiadaily.com/india/eknath-shinde-x-account-hacked-cyber-security-pakistan-t%C3%BCrkiye-flags-social-media-security-digital-platforms-cyber-crime-maharashtra-deputy-chief-minister-asia-cup-2025-news-94725</t>
+          <t>https://www.mymahanagar.com/maharashtra/navi-mumbai-city-petition-filed-in-janata-darbar-against-minister-ganesh-naik-by-kishore-patkar/922934/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/uttar-pradesh/bjp-mla-rajeshwar-singh-sarojini-nagar-yogi-praise-clean-image-569853</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/why-is-there-still-no-bjp-chief-minister-in-bihar-nitish-kumar-lalu-prasad-yadav-tejashwi-yadav-limited-grip-on-obc-voters-ebcs-mm76</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/navratri-2025-mumbai-police-will-have-strict-security-for-nine-days/articleshow/124024081.cms</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-dy-cm-eknath-shindes-x-account-hacked-pakistan-turkey-flags-posted-101758428709090.html</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane-politics-petition-against-minister-ganesh-naiks-janata-darbar/922848/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633943-allahabad-high-court-stays-fir-proceedings-against-sambhal-cleric?amp</t>
+          <t>https://www.hindisaamana.com/shinde-factions-credibility-is-falling-deputy-chief-minister-shinde-is-angry-with-inactive-ministers/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/manipur-shuts-schools-in-5-districts-after-heavy-rainfall-70-yr-old-man-goes-missing-101757952408864.html</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189409</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi/</t>
+          <t>https://www.theindiadaily.com/india/eknath-shinde-x-account-hacked-cyber-security-pakistan-t%C3%BCrkiye-flags-social-media-security-digital-platforms-cyber-crime-maharashtra-deputy-chief-minister-asia-cup-2025-news-94725</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://kantoor-amersfoort.nl/sport/matteo-franzoso-non-ce-lha-fatta-morto-lo-sciatore-25enne-caduto-in-allenamento_4njEheZ5JWnJoqYkgr0rTv</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-14-september-2025-asia-cup-cricket-hockey-pakistan-china-pm-modi-rain-alert-trump-israel-ukraine-russia-gaza-war-bjp-congress/liveblog/123877354.cms</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
+          <t>https://www.thehindu.com/news/national/karnataka/karnataka-proposes-law-to-fix-minimum-wage-work-hours-for-domestic-workers/article70074706.ece</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/national-restaurant-association-of-india-urges-maharashtra-government-to-boost-ease-of-doing-business-for-hospitality-sector-in-pune-city/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/government-will-bear-cost-of-expensive-treatment-maharashtra-took-big-decision-19948817</t>
+          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-date-extended-supreme-court-give-new-deadline-31st-january-2026-know-all/articleshow/123920003.cms</t>
+          <t>https://www.bhaskarenglish.in/national/news/india-pakistan-match-protests-asaduddin-owaisi-26-lives-shiv-sena-uddhav-thackeray-135916128.html</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/national-news/no-cap-on-prices-of-cars-for-guv-cm-and-judges-in-maharashtra-vehicle-policy-19954354</t>
+          <t>https://clarionindia.net/ahmednagar-railway-station-renamed-concern-over-erasure-of-muslim-legacy/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/amp/india-news/maharashtra-deputy-chief-minister-eknath-shinde-s-x-account-hacked-news-in-hindi-2025-09-21</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-date-extended-supreme-court-give-new-deadline-31st-january-2026-know-all/articleshow/123920003.cms</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/government-should-take-decision-with-a-common-perspective-regarding-tet-for-teachers/</t>
+          <t>https://www.amarujala.com/india-news/cpwd-floats-tender-to-install-bulletproof-glass-in-chambers-of-eam-foreign-secy-at-jn-bhawan-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/modi-govt-gave-rs-21-000-cr-for-marathwada-rail-lines-rs-450-crore-came-during-upa-time-fadnavis-2025-09-17</t>
+          <t>https://mandalnews.com/amravati/government-should-take-decision-with-a-common-perspective-regarding-tet-for-teachers/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/vhp-s-hindu-only-diktat-for-garba-open-invitation-for-violence-ramdas-athawale-2025-09-21</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-line-4-trials-completed-thane-metro-first-phase-to-open-by-december-2025-fully-operational-by-2027-say-mmrda/articleshow/124058727.cms</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/who-is-justice-chandrashekhar-now-listen-pleas-of-obc-groups-against-maratha-reservation-in-bombay-high-court-after-bench-recuses-from-hearing/articleshow/124060275.cms</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/breaking-news-today-live-updates-20-sept-maharashtra-political-news-rain-updates-shinde-thackeray-ajit-pawar-sharad-pawar-mumbai-pm-modi-940635/amp</t>
+          <t>https://www.msn.com/mr-in/news/other/golden-data-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%97-%E0%A4%B2%E0%A5%8D%E0%A4%A1%E0%A4%A8-%E0%A4%A1%E0%A5%87%E0%A4%9F-%E0%A4%86%E0%A4%A3%E0%A4%B2-%E0%A4%AC-%E0%A4%97%E0%A4%B8-%E0%A4%B2-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%B0-%E0%A4%96%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%AA-%E0%A4%8A%E0%A4%B2-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95-%E0%A4%A1%E0%A5%87%E0%A4%9F-%E0%A4%95-%E0%A4%AF/ar-AA1MSC1D?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/hau-dada-and-shinde-bankrupted-the-state-took-a-loan-of-24-thousand-crores-in-90-days/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/mahatet-exam-2025-mandatory-exam-confusion-for-senior-teachers-application-process-begins-from-15-september/articleshow/123893618.cms</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/world/australian-mps-met-maharashtras-eknath-shinde-discussed-business-cooperation--4269467</t>
+          <t>https://marathi.ndtv.com/videos/shani-shingnapur-devasthan-trust-dissolved-big-decision-of-the-state-government-998165</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/national/ahmednagar-railway-station-renamed-now-it-will-be-known-as-ahilyanagar/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/update-maharashtra-deputy-cm-eknath-shindes-ex-account-hacked-photos-with-pakistan-and-turkey-flags-posted-569771/amp</t>
+          <t>https://thebharatnow.in/national/ahmednagar-railway-station-renamed-now-it-will-be-known-as-ahilyanagar/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://www.theindiadaily.com/india/eknath-shinde-x-account-hacked-cyber-security-pakistan-t%C3%BCrkiye-flags-social-media-security-digital-platforms-cyber-crime-maharashtra-deputy-chief-minister-asia-cup-2025-news-94725/amp</t>
+          <t>https://jantaserishta.com/local/maharashtra/australian-mp-tim-watts-met-maharashtra-deputy-cm-shinde-4270583</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/politics/story/akola-spinning-mill-gets-36-crore-package-relief-for-cotton-farmers-1279315-2025-09-18</t>
+          <t>https://www.gaonjunction.com/khabar-junction/farmer-activists-claim-that-due-to-the-new-order-farmers-will-receive-40-less-compensation-for-crop-loss</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/education/bpsc-71st-cce-2025-answer-key-objection-filing-final-result-1298-posts-569804/amp</t>
+          <t>https://hindi.latestly.com/india/education/latest-and-important-news-of-22nd-september-for-school-assembly-read-the-latest-updates-related-to-national-international-and-sports-2759750.html</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://mahabharti.in/pashusavardhan-vibhag-bharti-2025/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/dcm-eknath-shinde-directs-to-airlift-citizens-stranded-due-to-floods-in-ashti-taluka/132516/amp/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/cpwd-floats-tender-to-install-bulletproof-glass-in-chambers-of-eam-foreign-secy-at-jn-bhawan-2025-09-16</t>
+          <t>https://dainikekmat.com/attorney-general-birendra-saraf-resigns/117476/</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-today-21st-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-ahmedabad-bullet-train-mega-block-sunday/liveblog/124023319.cms</t>
+          <t>https://www.aajtak.in/programmes/mumbai-metro/video/mumbai-metro-ameet-satam-controversial-statement-bmc-election-frvd-2335000-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-september-2025-marathi-live-updates-mumbai-rains-news-flood-situation-political-updates/liveblog/123988202.cms</t>
+          <t>https://www.amarujala.com/india-news/vhp-s-hindu-only-diktat-for-garba-open-invitation-for-violence-ramdas-athawale-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/11-eligible-workers-were-given-cheques-by-eknath-shinde/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%A8-%E0%A4%AE%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%9A-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%B2-%E0%A4%A6-%E0%A4%B2-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%85%E0%A4%A1%E0%A4%9A%E0%A4%A3-%E0%A4%A4-%E0%A4%AF%E0%A5%87%E0%A4%8A-%E0%A4%A8%E0%A4%AF%E0%A5%87-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A5%82%E0%A4%A8/ar-AA1MDxgy</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%8F%E0%A4%95%E0%A4%A8%E0%A4%BE%E0%A4%A5-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B5%E0%A5%80%E0%A4%9F%E0%A4%B0-%E0%A4%96%E0%A4%BE/118128/</t>
+          <t>https://peoplesupdate.com/mumbai-coastal-road-lamborghini-accident-luxury-car-damaged-video-130648</t>
         </is>
       </c>
     </row>
@@ -2804,49 +2804,49 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3635522-canada-recognizes-the-state-of-palestine-a-new-chapter-in-international-relations?amp</t>
+          <t>https://news18marathi.com/maharashtra/thane/thane-traffic-update-heavy-vehicles-entering-city-banned-from-6-am-to-12-midnight-ws-b-1482548.html</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-municipal-election-2025-mns-district-chief-raju-dindorle-will-join-bjp-mm76-rg93</t>
+          <t>https://www.jpnnews.in/2025/09/MLA-Rais-Sheikh-welcomes-Supreme-Courts-order-regarding-Waqf-Board.html</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/thane/thane-traffic-update-heavy-vehicles-entering-city-banned-from-6-am-to-12-midnight-ws-b-1482548.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-govt-fadnavis-cabinet-approves-8-major-decisions-including-expressway-and-new-policies-nck90</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-govt-fadnavis-cabinet-approves-8-major-decisions-including-expressway-and-new-policies-nck90</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-1384548</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-1384548</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-cabinet-decisions-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%85-%E0%A5%85%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B6%E0%A4%A8-vfx-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-%E0%A5%AE-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1MDQ9X</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/control-over-bangladeshi-infiltrators-important-decision-of-the-state-government.html</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-15-september-2025-zp-presidentship-reservation-nepal-violence-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
@@ -2860,1057 +2860,847 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/land-approved-for-bhandara-judges-residence-revenue-minister-chandrashekhar-bawankules-initiative.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/entertainment/tv/ok-tata-bye-bye-paytm-ceo-vijay-shekhar-sharma-deleted-his-post-on-ratan-tata-s-passing-after-facing-backlash/ar-AA1s2Nt7?ocid=hpdhp17&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.marathi.hindusthanpost.com/social/cabinet-decision-read-important-decisions-in-the-state-cabinet-meeting-with-one-click/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/technical-panel-approves-2-stps-along-indrayani-cm/articleshow/124005440.cms</t>
+          <t>https://www.msn.com/en-in/entertainment/tv/ok-tata-bye-bye-paytm-ceo-vijay-shekhar-sharma-deleted-his-post-on-ratan-tata-s-passing-after-facing-backlash/ar-AA1s2Nt7?ocid=hpdhp17&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/technical-panel-approves-2-stps-along-indrayani-cm/articleshow/124005440.cms</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/garware-youth-development-centre-satara-skill-training-helps-13-rural-youths-get-jobs-rds-00-5385521/</t>
+          <t>https://joindia.co.in/news/maharashtra-gets-new-governor-acharya-devvrat-takes-charge-as-the-22nd-governor/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178604/</t>
+          <t>https://www.loksatta.com/maharashtra/garware-youth-development-centre-satara-skill-training-helps-13-rural-youths-get-jobs-rds-00-5385521/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-gifts-namo-gardens-to-394-towns-on-pm-modis-75th-birthday-rs-394-crore-sanctioned/articleshow/123964170.cms</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-gifts-namo-gardens-to-394-towns-on-pm-modis-75th-birthday-rs-394-crore-sanctioned/articleshow/123964170.cms</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/hc-to-shinde-by-what-authority-did-you-stay-navi-mumbai-civic-bodys-notice-to-raze-illegal-buildings/articleshow/123952725.cms</t>
+          <t>https://curlytales.com/india/trending/what-are-namo-gardens-heres-all-about-eknath-shindes-green-gift-on-pm-modis-birthday/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/Newsalert/3630442-like-you-i-am-also-fully-committed-to-taking-india-us-partnership-to-new-heights-pm-modi-to-trump?amp</t>
+          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6-%E0%A4%A6-%E0%A4%A4-%E0%A4%9C-%E0%A4%B0-%E0%A4%AD%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AD-%E0%A4%88-%E0%A4%B8%E0%A4%A2%E0%A4%B3-%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%96%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC%E0%A4%9C%E0%A5%87%E0%A4%9F%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%95%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%AE%E0%A4%A7%E0%A5%82%E0%A4%A8-%E0%A4%87%E0%A4%82%E0%A4%9F%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%82%E0%A4%97-%E0%A4%86%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B8%E0%A4%AE-%E0%A4%B0/ar-AA1wtpDt?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/andhra-pradesh/bjp-highlights-indias-economic-transformation-under-pm-modi-welcomes-gst-reforms/article70051830.ece</t>
+          <t>https://www.newsx.com/india/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-77106/</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/amp_articleshow/123993653.cms</t>
+          <t>https://propnewstime.com/getdetailsStories/MjE0NDY=/kdmc-told-to-file-economic-crime-case-over-65-unauthorized-buildings</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/hardik-pandya-reveals-his-daily-fitness-routine-and-diet-secrets/the-importance-of-recovery/slideshow/123994093.cms</t>
+          <t>https://www.devdiscourse.com/article/business/3635550-metro-rail-lines-promise-to-ease-mumbais-traffic-woes</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/new-updates/navratri-2025-5-garba-looks-that-will-make-you-the-star-of-every-dandiya-night/sustainable-and-minimalist-look/slideshow/124026182.cms</t>
+          <t>https://m.economictimes.com/mf/analysis/amfi-reshuffle-poonawalla-fincorp-gillette-india-among-6-smallcap-stocks-that-may-get-midcap-status/poonawalla-fincorp/slideshow/123940051.cms</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/h3n2-flu-outbreak-in-delhi-ncr-all-about-symptoms-treatment-and-prevention-tips/staying-safe-from-h3n2/slideshow/123977652.cms</t>
+          <t>https://www.newsx.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-71735/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/new-updates/asia-cup-2025-india-vs-pakistan-t20-super-four-dubai-international-stadium-pitch-report-of-tody-match-ind-vs-pak-t20-dubai-weather-forecast-updates-today-match/amp_articleshow/124026458.cms</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-prakash-ambedkar-criticizes-modi-foreign-policy-us-tariff-russia-manipur-statement-135925944.html</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/mumbai-news/mmrda-temporarily-suspends-monorail-services-in-mumbai/amp_articleshow/124009977.cms</t>
+          <t>https://thefocusindia.com/maharashtra-news/ministerial-status-given-to-chairman-of-parashuram-economic-development-corporation-284301/amp/</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/7-breathtaking-indian-sites-join-unesco-tentative-list-from-kerala-to-meghalaya/deccan-traps-at-panchgani-amp-mahabaleshwar-maharashtra/slideshow/124000073.cms</t>
+          <t>https://www.ptinews.com/press-release/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/2938489</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://economictimes.indiatimes.com/news/politics-and-nation/bmc-polls-50-50-seats-for-sena-ubt-mns-in-mumbai-strongholds-60-40-in-others-say-party-leaders/articleshow/124027839.cms</t>
+          <t>https://www.devdiscourse.com/article/technology/3629546-nato-boosts-eastern-european-defense-with-eastern-sentry?amp</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://economictimes.indiatimes.com/news/politics-and-nation/caste-census-communities-make-efforts-to-see-their-dominance-reflected-in-survey-outcome/articleshow/124027718.cms</t>
+          <t>https://www.lokmattimes.com/maharashtra/maharashtra-orders-aadhaar-e-kyc-for-womens-welfare-scheme-beneficiaries-a525/</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-prakash-ambedkar-criticizes-modi-foreign-policy-us-tariff-russia-manipur-statement-135925944.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/technology/3629546-nato-boosts-eastern-european-defense-with-eastern-sentry?amp</t>
+          <t>https://zeenews.india.com/marathi/photos/ladki-bahin-yojana-ekyc-kashi-karaychi-rule-change-by-maharashtra-government-documents-application-process-deadline-ifnormation-every-details-you-need-to-know/940522</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://www.nationalheraldindia.com/amp/story/politics/maharashtra-govt-flips-again-ladki-bahin-payouts-to-resume-for-most-women</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-aditi-tatkare-important-explanation-about-ladki-bahin-yojana/articleshow/123977249.cms</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/ladki-bahin-yojana-beneficiaries-have-not-decreased-says-minister-aditi-tatkare-a517/</t>
+          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/maharashtra-orders-aadhaar-e-kyc-for-womens-welfare-scheme-beneficiaries-a525/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/business/mukhyamantri-ladki-bahin-yojana-ekyc-compulsory-for-all-check-how-complete-this-process-1385224</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/acharya-devvrat-takes-additional-charge-as-maharashtra-governor-101757923599184-amp.html</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/photos/ladki-bahin-yojana-ekyc-kashi-karaychi-rule-change-by-maharashtra-government-documents-application-process-deadline-ifnormation-every-details-you-need-to-know/940522</t>
+          <t>https://thenewsmill.com/2025/09/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother/</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ladki-bahin-scheme-important-information-from-minister-aditi-tatkare-how-to-complete-the-e-kyc-process/articleshow/124024396.cms</t>
+          <t>https://news18marathi.com/maharashtra/trial-of-metro-4-in-thane-begins-in-the-presence-of-chief-minister-devendra-fadnavis-local18-1485682.html</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/bjp-leader-nitin-paygude-and-mns-leader-ranji-dhage-join-shiv-sena-shinde-group/articleshow/123998704.cms</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-aditi-tatkare-important-explanation-about-ladki-bahin-yojana/articleshow/123977249.cms</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/thane-thane-metro-stations-the-35-km-long-metro-will-make-the-journey-of-thane-residents-easier-thane-news-1385989</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde20250922072527</t>
+          <t>https://vsrsnews.in/pimpri-chinchwad/pune-acharya-devvrat-becomes-the-new-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://www.uttamhindu.com/maharashtra-in-turmoil-cm-eknath-shindes-x-account-hacked/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/thane-metro-4-and-4a-span-35-km-with-32-stations-trial-run-inspected-by-devendra-fadnavis-and-eknath-shinde-full-details-in-marathi-article-152872624</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/deepak-kesarkar-a-leader-from-konkan-who-is-in-the-news-for-not-getting-a-place-in-the-state-cabinet-this-year-is-likely-to-get-a-big-responsibility-soon-97814/</t>
+          <t>https://www.thehindu.com/news/national/uttarakhand/uttarakhand-govt-to-buy-produce-from-apple-growers-in-disaster-hit-dharali/article70076273.ece</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/how-the-bjp-alliance-won-maharashtra-101757921779535.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/hc-seeks-govt-s-stand-on-illegal-stay-on-demolition-by-dy-cm-101758137116362.html</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/maharashtra-government-vehicle-policy-revised-2025-ntc-rptc-2336368-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/uttarakhand/uttarakhand-govt-to-buy-produce-from-apple-growers-in-disaster-hit-dharali/article70076273.ece</t>
+          <t>https://hindi.theprint.in/india/argument-between-congress-mp-gaikwad-and-bjp-member-kamboj-over-sra-projects/869161/</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
+          <t>https://lalluram.com/eknath-shinde-x-account-hack-hacker-puts-pakistan-and-turkey-flags-on-home-page/</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
+          <t>https://www.hindisaamana.com/the-mahagathbandhan-leaders-openly-support-corruption-high-court-rebukes-them/</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/maharashtra-government-vehicle-policy-revised-2025-ntc-rptc-2336368-2025-09-18</t>
+          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9F%E0%A4%B5%E0%A4%9F%E0%A4%B5-%E0%A4%A4-%E0%A4%B6%E0%A5%87%E0%A4%A4-%E0%A4%9A%E0%A5%87-%E0%A4%B0%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%A8%E0%A4%82-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2%E0%A4%82-%E0%A4%95%E0%A4%82%E0%A4%9F-%E0%A4%B3-%E0%A4%86%E0%A4%B2-%E0%A4%95-%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%87%E0%A4%B2-%E0%A4%95-%E0%A4%AA%E0%A5%8D%E0%A4%9F%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%B6%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%B0/ar-AA1MRcAj</t>
+          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/business/mukhyamantri-mazi-ladki-bahin-yojana-no-e-kyc-no-rs-1500-all-beneficiaries-can-avail-facility-visiting-web-portal-b507/amp/</t>
+          <t>https://civicmirror.in/maharashtra/deputy-chief-minister-eknath-shindes-announcement-on-the-occasion-of-prime-minister-narendra-modis-birthday/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%B2-%E0%A4%AC%E0%A4%A6%E0%A4%B2%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A4%B0-%E0%A4%A6-%E0%A4%B6-%E0%A4%A4-%E0%A4%9A/ar-AA1vkDcb?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/msrtc-employees-gives-big-warning-to-maharashtra-government/amp_articleshow/123997908.cms</t>
+          <t>https://deshonnati.com/ahmednagar-railway-station-government-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/top-marathi-news-today-live-breaking-news-live-updates-maharashtra-politics-live-news-latest-news-993761.html</t>
+          <t>https://www.bignewsnetwork.com/news/278581344/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/nri/latest-updates/h1b-100k-h-1b-fee-sparks-rush-in-us-flight-bookings-makemytrip/amp_articleshow/124024106.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-marathwada-four-people-died-150-people-were-trapped-in-floods-in-dharashiv/924053/</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/maharashtra-deputy-cm-eknath-shinde-takes-action-against-builders-of-65-illegal-buildings-in-kalyan-dombivli/amp_articleshow/124011193.cms</t>
+          <t>https://royalbulletin.in/desh-pradesh/madhya-pradesh/mp-cm-mohan-yadav-gst-2-0-shopping-bhopal/article-108502</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/amp/maharashtra/eknath-shinde-maharashtra-deputy-cm-x-account-hacked-hackers-post-pakistan-turkey-flags-hacking-sparks-uproar-2025-09-21-1009219</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/how-the-bjp-alliance-won-maharashtra-101757921779535.html</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-71735/</t>
+          <t>https://thenewsmill.com/2025/09/acharya-devvrat-sworn-in-as-governor-of-maharashtra-reads-oath-in-sanskrit/</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%95%E0%A5%87%E0%A4%B2-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0/ar-AA1sjqmA?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-assembly-election-2025-cm-nitish-eyes-the-lost-seats-of-paswan-and-kushwaha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-monsoon-2025-rain-update-maharashtra-rain-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shinde-9/923517/</t>
+          <t>https://www.amarujala.com/video/india-news/tejashwi-yadav-bihar-adhikar-yatra-tejashwi-yadav-afraid-of-rahul-gandhi-bihar-election-2025-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-rahul-gandhi-and-tejashwi-yadav-lalu-yadav-decide-on-seat-sharing-within-mahagathbandhan-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/pil-questions-ganesh-naik-s-right-to-hold-janata-darbars-in-navi-mumbai-101758223019260-amp.html</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-patna-high-court-strict-on-ai-video-made-on-pm-modi-s-mother-nda-gave-this-reply-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/navi-mumbai-city-petition-filed-in-janata-darbar-against-minister-ganesh-naik-by-kishore-patkar/922934/</t>
+          <t>https://www.amarujala.com/video/india-news/chief-minister-bhagwant-mann-launched-mission-chadti-kala-for-flood-victims-in-punjab-made-this-appeal-to-t-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/didnt-do-so-for-power-but-ajit-pawar-on-why-he-split-with-sharad-pawar-101758292291397-amp.html</t>
+          <t>https://www.amarujala.com/video/india-news/disha-patni-house-firing-case-the-accused-of-firing-at-disha-patni-s-house-were-killed-adg-told-the-whole-st-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/opposition-ruling-parties-spar-over-rahuls-fresh-vote-chori-charges-seek-fadnavis-resignation/article70068451.ece</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A-%E0%A4%9C-%E0%A4%97-%E0%A4%B5-%E0%A4%9F%E0%A4%AA-%E0%A4%9A-%E0%A4%85%E0%A4%82%E0%A4%A4-%E0%A4%AE-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%86%E0%A4%9C-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%B8%E0%A4%B9-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%A4-%E0%A4%A6-%E0%A4%96%E0%A4%B2-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9%E0%A4%82%E0%A4%B8-%E0%A4%AC%E0%A4%A4-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95/ar-AA1sw9JT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/kerala/kerala-minister-v-sivankutty-taken-to-hospital-after-experiencing-dizziness-in-assembly/article70068758.ece</t>
+          <t>https://www.msn.com/mr-in/news/other/sanjay-kadam-%E0%A4%95-%E0%A4%95%E0%A4%A3-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A7%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%AF-%E0%A4%97%E0%A5%87%E0%A4%B6-%E0%A4%95%E0%A4%A6%E0%A4%AE-%E0%A4%82%E0%A4%A8-%E0%A4%AD-%E0%A4%A1%E0%A4%A3-%E0%A4%B0-%E0%A4%B0-%E0%A4%AE%E0%A4%A6-%E0%A4%B8-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%9A-%E0%A4%B0-%E0%A4%88%E0%A4%9F-%E0%A4%B9%E0%A4%81%E0%A4%A1-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AA%E0%A4%B0%E0%A4%A4%E0%A4%A3-%E0%A4%B0/ar-AA1B8BOh?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/bjp-led-mahayuti-alliance-to-sweep-maharashtra-predicts-axis-my-india-exit-poll/ar-AA1uvbog?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/acharya-devvrat-is-the-new-governor-of-maharashtra-took-oath-in-the-presence-of-the-chief-minister.amp.html</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/acharya-devvrat-sworn-in-as-governor-of-maharashtra-reads-oath-in-sanskrit20250915150141</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-update-monsoon-2025-rain-update-maharashtra-rain-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shinde-9/923517/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/abp-majha-top-10-headlines-abp-%E0%A4%AE-%E0%A4%9D-%E0%A4%9F-%E0%A4%AA-10-%E0%A4%B9%E0%A5%87%E0%A4%A1%E0%A4%B2-%E0%A4%88%E0%A4%A8%E0%A5%8D%E0%A4%B8-22-%E0%A4%B8%E0%A4%AA%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%82%E0%A4%AC%E0%A4%B0-2025-%E0%A4%B8-%E0%A4%AE%E0%A4%B5-%E0%A4%B0/ar-AA1N3QmU</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/18092025/swachhata-hi-seva/</t>
+          <t>https://marathi.indiatimes.com/india-news/bihar-assembly-election-amit-shah-meets-bjp-workers-gives-60-days-plan-ahead-of-poll/articleshow/123995857.cms</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/maharashtra-mmrda-to-suspend-monorail-services-on-september-20-in-mumbai/</t>
+          <t>https://marathi.ndtv.com/india/maharashtra-politics-live-update-mumbai-rain-first-bullet-train-between-mumbai-and-ahmedabad-9310619</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-assembly-election-2025-cm-nitish-eyes-the-lost-seats-of-paswan-and-kushwaha-2025-09-18</t>
+          <t>https://www.bhaskarhindi.com/other/-2025--1188879</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/business/mukhyamantri-mazi-ladki-bahin-yojana-no-e-kyc-no-rs-1500-all-beneficiaries-can-avail-facility-visiting-web-portal-b507/</t>
+          <t>https://www.bhaskarhindi.com/other/breaking-news-headlines-today-19-september-2025-dainik-bhaskar-hindi-news-live-1188572</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
+          <t>https://indiagroundreport.com/mumbai-acharya-devvrat-took-additional-charge-as-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/tejashwi-yadav-bihar-adhikar-yatra-tejashwi-yadav-afraid-of-rahul-gandhi-bihar-election-2025-2025-09-17</t>
+          <t>https://deshonnati.com/maharashtra-governor-acharya-devvrat-took-the-oath/</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-rahul-gandhi-and-tejashwi-yadav-lalu-yadav-decide-on-seat-sharing-within-mahagathbandhan-2025-09-18</t>
+          <t>https://dainikekmat.com/ministerial-status-to-the-chairman-of-parashuram-corporation/117448/</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/chief-minister-bhagwant-mann-launched-mission-chadti-kala-for-flood-victims-in-punjab-made-this-appeal-to-t-2025-09-17</t>
+          <t>https://www.timemaharashtra.com/maharashtra/maharashtra-governor-acharya-devvrat-takes-oath-as-governor-of-maharashtra/132473/</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/raigad-guardian-minister-%E0%A4%A8-%E0%A4%97-%E0%A4%97-%E0%A4%B5%E0%A4%B2%E0%A5%87-%E0%A4%A8-%E0%A4%A4%E0%A4%9F%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%B0-%E0%A4%AF%E0%A4%97%E0%A4%A1%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%B5%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%97%E0%A5%81%E0%A4%97%E0%A4%B2-%E0%A4%9C%E0%A4%AC-%E0%A4%AC%E0%A4%A6-%E0%A4%B0-%E0%A4%A5%E0%A5%87%E0%A4%9F/ar-AA1yaaoP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.thehindu.com/news/national/karnataka/bk-singh-to-head-sit-formed-to-probe-aland-voter-fraud-case/article70074360.ece</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%AF%E0%A5%82%E0%A4%AA-%E0%A4%AA%E0%A5%85%E0%A4%9F%E0%A4%B0%E0%A5%8D%E0%A4%A8%E0%A4%B2-%E0%A4%AB-%E0%A4%9F-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A5%85%E0%A4%9F%E0%A4%B0%E0%A5%8D%E0%A4%A8%E0%A4%B5%E0%A4%B0-%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%A4-cm-%E0%A4%AA%E0%A4%A6-%E0%A4%B8-%E0%A4%A0-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A5%8D%E0%A4%AF%E0%A5%81%E0%A4%B2/ar-AA1yKFrb?cvid=14C0E25EB3514BFF8311922AA83DAF4A&amp;ocid=nyl&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.thehindu.com/news/national/congress-doing-negative-politics-over-great-nicobar-project-environment-minister/article70067325.ece</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/acharya-devvrat-is-the-new-governor-of-maharashtra-took-oath-in-the-presence-of-the-chief-minister.amp.html</t>
+          <t>https://www.hindustantimes.com/india-news/didnt-do-so-for-power-but-ajit-pawar-on-why-he-split-with-sharad-pawar-101758292291397.html</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/amp_articleshow/124013451.cms</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/articleshow/123993653.cms</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
+          <t>https://nagalandpost.com/bmc-polls-50-50-seats-for-sena-ubt-mns-in-mumbai-strongholds/</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/?amp</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%A0-%E0%A4%85%E0%A4%AA%E0%A4%A1%E0%A5%87%E0%A4%9F-23-%E0%A4%91%E0%A4%95%E0%A5%8D%E0%A4%9F-%E0%A4%AC%E0%A4%B0%E0%A4%B2-%E0%A4%A8-%E0%A4%B2%E0%A5%87%E0%A4%B6-%E0%A4%B0-%E0%A4%A3%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1sBlG7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/shinde-said-the-mahayuti-will-hoist-the-saffron-flag-in-the-municipal-corporations-125092200027_1.html</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://www.primetvindia.com/eknath-shindes-x-account-has-been-hacked-posts-of-pakistani-and-turkish-flags-have-sparked-concern/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/explainer-a-test-of-mahayuti-in-bmc-elections-shiv-sena-bjp-tug-of-war-over-91-seats-article-152842707</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-acharya-devvrat-took-additional-charge-as-governor-of-maharashtra/</t>
+          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/thane-metro-lines-4-and-4a-trial-run-revolutionizing-travel-in-mumbai-metropolitan-region/124060623</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/ministerial-status-to-the-chairman-of-parashuram-corporation/117448/</t>
+          <t>https://www.bignewsnetwork.com/news/278593014/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/2921301</t>
+          <t>https://mahasamvad.in/179580/</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/karnataka/bk-singh-to-head-sit-formed-to-probe-aland-voter-fraud-case/article70074360.ece</t>
+          <t>https://thecsrjournal.in/thane-metro-trial-run-hindi/</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/congress-doing-negative-politics-over-great-nicobar-project-environment-minister/article70067325.ece</t>
+          <t>https://www.bhaskarhindi.com/city/nagpur/nagpur-news-seeem-kee-maujoodagee-mein-mahaajenako-aur-enemaaradeee-ke-beech-hua-anubandh-1187831</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/amp/national/news/bhaskar-evening-wrap-21-09-25-pm-modi-gst-white-house-trump-mithun-manhas-135977196.html</t>
+          <t>https://mahasamvad.in/178444/</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178810/</t>
+          <t>https://jantaserishta.com/others/mahayutis-saffron-flag-will-fly-in-mumbai-municipal-corporation-and-other-municipal-bodies-eknath-shinde-4278209</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/dcm-eknath-shinde-criticized-rahul-gandhi-evm-vote-chori-case/922837/</t>
+          <t>https://www.marathiebatmya.com/political/mou-signed-between-mahagenco-and-nmrda-in-the-presence-of-the-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A4-%E0%A4%96%E0%A4%B0%E0%A5%87%E0%A4%A6-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A4%A4%E0%A5%87%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0%E0%A4%9A-%E0%A4%A7%E0%A4%A8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%A1%E0%A5%87-%E0%A4%A6-%E0%A4%96%E0%A4%B2-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%85%E0%A4%82%E0%A4%9C%E0%A4%B2-%E0%A4%A6%E0%A4%AE-%E0%A4%A8-%E0%A4%AF-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%85%E0%A4%AC%E0%A5%8D%E0%A4%B0%E0%A5%81-%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A4%B8-%E0%A4%A8-%E0%A4%9A-%E0%A4%A6-%E0%A4%B5/ar-AA1yofLg?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://politicalmaharashtra.in/state-level-technical-committee-approves-indrayani-river-improvement-project-mla-mahesh-landages-pursuit-is-successful-97855/</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi20250917174418</t>
+          <t>https://www.sakshipost.com/news/metro-line-connecting-thane-mumbai-be-operational-2026-end-says-cm-fadnavis-455400</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%AE-%E0%A4%B3-%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%82%E0%A4%A4%E0%A4%B0%E0%A4%B9-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%A1%E0%A4%9A%E0%A4%A3-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%B9-%E0%A4%A4-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%B5-%E0%A4%A2%E0%A4%B5%E0%A4%B2%E0%A4%82-%E0%A4%9F%E0%A5%87%E0%A4%A8%E0%A5%8D%E0%A4%B6%E0%A4%A8/ar-AA1vHvrk?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://thefocusindia.com/maharashtra-news/bhujbal-retorts-pawar-did-not-attend-all-party-meeting-reservation-284529/amp/</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/action-should-be-taken-against-deputy-chief-minister-shinde-sanjay-raut-lashed-out/</t>
+          <t>https://www.newsonair.gov.in/union-minister-piyush-goyal-launches-swasth-nari-sashakt-parivar-campaign-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/we-will-get-success-like-the-assembly-chief-minister-shinde/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/opposition-targets-shiv-sena-over-mumbais-gb-hway-traffic-ahead-of-civic-polls/articleshow/124020437.cms</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/rs-20-crores-of-funds-were-received-without-any-mla-shinde-faction-leaders-statement-increases-mahayutis-problems/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/how-can-blood-cricket-flow-together-uddhav-thackeray-opposes-india-pak-match-protests-to-target-pm-modi/articleshow/123878115.cms</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/explainer-a-test-of-mahayuti-in-bmc-elections-shiv-sena-bjp-tug-of-war-over-91-seats-article-152842707</t>
+          <t>https://www.devdiscourse.com/article/politics/3630214-chalo-jeete-hain-bjp-launches-film-tour-across-bihar?amp</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/get-20-crores-even-though-i-am-not-an-mla-sada-saravankar/</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/kumbh-mela-committee-accommodates-representatives-of-bjps-mahayuti-allies-ncp-shiv-sena/articleshow/124020480.cms</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/the-way-sanjay-rauts-tongue-is-slipping-every-day-ubatya-will-soon-have-to-celebrate-a-slip-up-festival-jyoti-waghmare/133177/amp/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-workers-burn-effigy-of-shiv-sena-ubt-mp-sanjay-raut-for-his-remark-about-anand-dighe/articleshow/123981706.cms</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/attorney-general-birendra-saraf-resigns/117476/</t>
+          <t>https://www.newsband.in/article_detail/replicas-diversity-mark-devi-durgeshwari-fest-in-thane</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education/amp/?utm=relatedarticles</t>
+          <t>https://www.newsdrum.in/national/shiv-sena-workers-protest-against-rauts-remark-about-dighe-10476846</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/pm-narendra-modi-a-strong-national-leader-maha-cm-devendra-fadnavis-wishes-pm-modi-on-his-75th-bday-hails-his-vision-to-reshape-indias-fortune</t>
+          <t>https://www.msn.com/hi-in/news/other/mumba-devi-vidhan-sabha-chunav-result-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%B8-%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%A8-%E0%A4%AE-%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%AC-%E0%A4%9C-%E0%A4%AF%E0%A4%B9-%E0%A4%82-%E0%A4%AA%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%A4-%E0%A4%9C-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C%E0%A5%81%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A4%B0-%E0%A4%85%E0%A4%AA%E0%A4%A1%E0%A5%87%E0%A4%9F/ar-AA1uBciC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-polls-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%B5-%E0%A4%A8%E0%A4%96%E0%A5%87%E0%A4%A1%E0%A4%BC%E0%A5%87-%E0%A4%AB-%E0%A4%B0-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%82-mumbai-%E0%A4%95-%E0%A4%87%E0%A4%B8-%E0%A4%B8-%E0%A4%9F-%E0%A4%B8%E0%A5%87-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%85%E0%A4%9F%E0%A4%95%E0%A4%B2%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%9F-%E0%A4%95%E0%A4%9F/ar-AA1spTNA?cvid=BC85FE97FDE740EB8B309A7E01FCE3DD&amp;ocid=hpmsn&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178444/</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-politics-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A5%82%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%B2-%E0%A4%A6%E0%A5%81%E0%A4%B8%E0%A4%B0-%E0%A4%A7%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%B9-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A5%82%E0%A4%A4-%E0%A4%A4-%E0%A4%A8-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A5%81%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%89%E0%A4%B0%E0%A4%B2%E0%A5%87/ar-AA1N2FuN</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://www.tarunmitra.in/state/maharashtra/maharashtra-governments-unique-initiative-plan-to-build-namo-park-on/article-105368</t>
+          <t>https://tamil.getlokalapp.com/maharashtra-news/metro-project-in-thane-raut-s-allegations-shinde-s-response-15458855</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/the-mahayutis-saffron-flag-will-fly-in-other-municipalities-including-the-mumbai-municipal-corporation--4278128</t>
+          <t>https://www.mymahanagar.com/maharashtra/maharashtra-politics-former-mla-sada-saravankar-claims-to-be-getting-rs-20-crore-even-without-being-an-mla/923568/amp</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/mou-signed-between-mahagenco-and-nmrda-in-the-presence-of-the-chief-minister/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/pm-s-birthday-a-black-day-for-democracy-says-congress-mp-praniti-shinde-bjp-hits-back/ar-AA1MFgP7</t>
+          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-gst-rate-is-establishment-of-a-superpower-in-the-country/</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3631054-maharashtra-leaders-hail-pm-modis-visionary-leadership-on-75th-birthday?amp</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/sudhir-mungantiwar_16.html</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-deputy-chief-minister-eknath-shinde-launches-the-seva-fortnight-chief-minister-samruddhi-panchayat-raj-abhiyan-in-thane-district/922593/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/bjps-criticism-of-sanjay-raut/</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/shiv-sena-portfolio-list-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%A8%E0%A5%87-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%97%E0%A5%83%E0%A4%B9-%E0%A4%96-%E0%A4%A4%E0%A4%82-%E0%A4%A6-%E0%A4%B2%E0%A4%82%E0%A4%9A-%E0%A4%A8-%E0%A4%B9-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%B2-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%95-%E0%A4%AF-%E0%A4%AE-%E0%A4%B3-%E0%A4%B2%E0%A4%82/ar-AA1whDCo?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/india/cant-be-on-whims-delhi-hc-raps-centre-over-delay-in-kejriwal-house-allotment-calls-for-clear-policy/articleshow/123976159.cms</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/bhujbal-retorts-pawar-did-not-attend-all-party-meeting-reservation-284529/</t>
+          <t>https://www.newsband.in/article_detail/thane-metro-line-4-train-run-conducted-successfully</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/how-can-blood-cricket-flow-together-uddhav-thackeray-opposes-india-pak-match-protests-to-target-pm-modi/articleshow/123878115.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/iti-students-will-run-cleanliness-campaign-in-750-villages-special-campaign-by-minister-mangal-prabhat-lodha-on-pm-modis-birthday/articleshow/123915570.cms</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3632371-trumps-crackdown-on-antifa-following-kirk-assassination?amp</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA%E0%A4%B0%E0%A4%B6%E0%A5%81%E0%A4%B0-%E0%A4%AE-%E0%A4%86%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%95-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A4%B9-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B2-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%9A-%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%A0-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B2-%E0%A4%86%E0%A4%A3%E0%A4%96-%E0%A4%8F%E0%A4%95-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6/ar-AA1ME5Po</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/dusu-elections-today-all-about-key-candidates-voting-guidelines-traffic-advisory-101758167381891.html</t>
+          <t>https://www.hindisaamana.com/the-state-has-a-debt-of-rs-9-lakh-crores-development-of-the-state-is-stalled-deva-bhau-is-busy-in-advertising/</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-piyush-goyal-launches-swasth-nari-sashakt-parivar-campaign-in-mumbai/</t>
+          <t>https://www.khabarwala24.com/national/mumbai-mahapalika-sahit-anya-nagarpalikaon-mein-mahayuti-ka-bhagwa-jhanda-lahraega-eknath-shinde/104161/</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3630214-chalo-jeete-hain-bjp-launches-film-tour-across-bihar?amp</t>
+          <t>https://lokmanthan.com/arrangements-should-be-made-to-issue-all-relevant-permits-for-industries-in-a-single-application-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/i-call-on-youth-to-root-out-addiction-from-societysukanta-majumdar-joins-namo-yuva-run-in-kolkata20250921104533-75973/amp/</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/ncpap-hints-at-fighting-independently-in-the-upcoming-local-body-elections-in-maharashtra/article70073542.ece</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/kumbh-mela-committee-accommodates-representatives-of-bjps-mahayuti-allies-ncp-shiv-sena/articleshow/124020480.cms</t>
+          <t>https://indianexpress.com/article/cities/mumbai/acharya-devvrat-oath-maharashtra-governor-10250775/</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-workers-burn-effigy-of-shiv-sena-ubt-mp-sanjay-raut-for-his-remark-about-anand-dighe/articleshow/123981706.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/transporters-cite-increased-costs-supply-disruptions-want-new-traffic-curbs-lifted/articleshow/124005110.cms</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/full-page-newspaper-ads-and-slew-of-initiatives-shiv-sena-goes-all-out-to-celebrate-pm-s-birthday/2925344</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/trial-runs-on-metro-4s-cadbury-junction-gaimukh-stretch-to-commence-monday-mumbai-metropolitan-region-development-authority-officials-say-corridor-on-track-for-year-end-operations/articleshow/124001171.cms</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/opposition-targets-shiv-sena-over-mumbais-gb-hway-traffic-ahead-of-civic-polls/articleshow/124020437.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/22/indias-longest-elevated-metro-corridor-in-mumbai-information-from-chief-minister-devendra-fadnavis.html</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3630229-supreme-courts-deadline-sparks-political-reactions-in-maharashtra</t>
+          <t>https://www.loksatta.com/mumbai/ahilyabai-holkar-honoured-as-ahmednagar-railway-station-renamed-as-ahilyanagar-by-maharashtra-government-mumbai-print-news-rds-00-5376825/</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-23595086</t>
+          <t>https://politicalmaharashtra.in/obc-vs-maratha-a-split-in-the-alliance-over-reservations-97877/</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/shiv-sena-workers-protest-against-rauts-remark-about-dighe-10476846</t>
+          <t>https://marathi.abplive.com/news/mumbai/sanjay-raut-statement-on-anand-dighe-thane-balasaheb-thackeray-photo-advertise-shivsena-maharashtra-marathi-news-1385015</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/paint-thrown-on-statue-of-meenatai-thackeray-at-mumbais-shivaji-park-10472418</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/violence-escalates-in-maratha-obc-reservation-dispute-obc-leader-s-car-set-on-fire-in-jalna-125092300009_1.html</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%88%E0%A4%82-%E0%A4%B8%E0%A4%AE%E0%A4%82%E0%A4%A6%E0%A4%B0-%E0%A4%B9%E0%A5%82%E0%A4%82-%E0%A4%B2-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%B5-%E0%A4%AA%E0%A4%B8-%E0%A4%86%E0%A4%8A%E0%A4%82%E0%A4%97-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AC%E0%A4%A8%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%AE%E0%A4%97%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AC%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%A1-%E0%A4%AA%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%8F%E0%A4%AE/ar-AA1uBRUD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/mumba-devi-vidhan-sabha-chunav-result-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%B8-%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%A8-%E0%A4%AE-%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%AC-%E0%A4%9C-%E0%A4%AF%E0%A4%B9-%E0%A4%82-%E0%A4%AA%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%A4-%E0%A4%9C-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C%E0%A5%81%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A4%B0-%E0%A4%85%E0%A4%AA%E0%A4%A1%E0%A5%87%E0%A4%9F/ar-AA1uBcsK?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-148-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-103-%E0%A4%B8-%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A5%87%E0%A4%97-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%95%E0%A5%81%E0%A4%9B-%E0%A4%B8-%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%B8%E0%A5%8D%E0%A4%A5-%E0%A4%A4-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%A8%E0%A4%B9-%E0%A4%82/ar-AA1tbokT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%9A-%E0%A4%B0-%E0%A4%9A-%E0%A4%B6%E0%A4%82%E0%A4%96-%E0%A4%AB%E0%A5%81%E0%A4%82%E0%A4%95%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%9A-%E0%A4%B0-%E0%A4%B8-%E0%A4%A0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%86%E0%A4%98-%E0%A4%A1-%E0%A4%B8%E0%A4%AD%E0%A5%87%E0%A4%9A-%E0%A4%A4-%E0%A4%B0-%E0%A4%96-%E0%A4%86%E0%A4%A3-%E0%A4%B5%E0%A5%87%E0%A4%B3%E0%A4%B9-%E0%A4%A0%E0%A4%B0%E0%A4%B2/ar-AA1toilT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/sushma-andhare-%E0%A4%A1%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%9F-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%96%E0%A4%B0%E0%A5%87-%E0%A4%B0%E0%A5%81%E0%A4%AA-%E0%A4%86%E0%A4%9C-%E0%A4%AC-%E0%A4%B9%E0%A5%87%E0%A4%B0-%E0%A4%86%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A5%81%E0%A4%B7%E0%A4%AE-%E0%A4%85%E0%A4%82%E0%A4%A7-%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%98%E0%A4%A3-%E0%A4%98-%E0%A4%A4/ar-AA1HY5L7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/sanjay-raut-%E0%A4%A4%E0%A5%81%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%9C%E0%A4%B0-%E0%A4%B9-%E0%A4%82%E0%A4%A6%E0%A5%82-%E0%A4%85%E0%A4%B8-%E0%A4%B2-%E0%A4%A4%E0%A4%B0-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%82%E0%A4%9A-%E0%A4%A4-%E0%A4%AB-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%A7%E0%A4%A1-%E0%A4%A1%E0%A4%B2/ar-AA1MsxoR?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/mahayuti-election-strategy-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9D%E0%A5%87%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%B2-%E0%A4%9A-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%81%E0%A4%95-%E0%A4%89%E0%A4%A6%E0%A4%AF-%E0%A4%B8-%E0%A4%AE%E0%A4%82%E0%A4%A4/ar-AA1MsnDU?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/devendra-fadnavis-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%AA-%E0%A4%A0-%E0%A4%82%E0%A4%AC-%E0%A4%95-%E0%A4%A6-%E0%A4%B2-%E0%A4%A8-%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%8F%E0%A4%95-%E0%A4%B5-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B8-%E0%A4%82%E0%A4%97%E0%A5%82%E0%A4%A8-%E0%A4%9F-%E0%A4%95%E0%A4%B2%E0%A5%87/ar-AA1u7Jyx?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/business/3629575-thane-takes-traffic-control-measures-midnight-movement-for-heavy-vehicles</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>https://www.newsdrum.in/national/fadnavis-leads-maharashtra-in-greeting-pm-modi-on-birthday-calls-him-global-statesman-inspiration-10472727</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-polls-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%B5-%E0%A4%A8%E0%A4%96%E0%A5%87%E0%A4%A1%E0%A4%BC%E0%A5%87-%E0%A4%AB-%E0%A4%B0-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%82-mumbai-%E0%A4%95-%E0%A4%87%E0%A4%B8-%E0%A4%B8-%E0%A4%9F-%E0%A4%B8%E0%A5%87-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%85%E0%A4%9F%E0%A4%95%E0%A4%B2%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%9F-%E0%A4%95%E0%A4%9F/ar-AA1spTNA?cvid=BC85FE97FDE740EB8B309A7E01FCE3DD&amp;ocid=hpmsn&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/iti-students-will-run-cleanliness-campaign-in-750-villages-special-campaign-by-minister-mangal-prabhat-lodha-on-pm-modis-birthday/articleshow/123915570.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>https://tamil.getlokalapp.com/amp/maharashtra-news/the-chairman-of-this-corporation-got-ministerial-status-15423436</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>https://deshbandhump.com/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%AA%E0%A4%BE%E0%A4%B2%E0%A4%BF%E0%A4%95%E0%A4%BE-%E0%A4%B8%E0%A4%B9%E0%A4%BF%E0%A4%A4-%E0%A4%85%E0%A4%A8%E0%A5%8D/</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>https://www.hindisaamana.com/the-state-has-a-debt-of-rs-9-lakh-crores-development-of-the-state-is-stalled-deva-bhau-is-busy-in-advertising/</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>https://bharatexpress.com/india/bihar-news-nitish-governments-big-decision-vikas-mitras-to-get-tablets-education-workers-to-get-help-with-smartphones-569758/amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>https://indiagroundreport.com/mumbai-acharya-devvrat-took-additional-charge-as-governor-of-maharashtra/?amp=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/bjps-criticism-of-sanjay-raut/</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>https://lokmanthan.com/arrangements-should-be-made-to-issue-all-relevant-permits-for-industries-in-a-single-application-chief-minister-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-23595086</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/jarange-plans-national-maratha-convention-in-delhi-hake-warns-of-obc-march-to-mumbai/articleshow/123952548.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/india-news/eps-calls-on-amit-shah-in-delhi-meets-vpradhakrishnan-101758052028562.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>https://indianexpress.com/article/cities/mumbai/acharya-devvrat-oath-maharashtra-governor-10250775/</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/international/us/charlie-kirk-memorial-in-arizona-set-to-draw-nearly-100000-people-a-look-at-americas-largest-funerals/amp_articleshow/124025590.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>http://www.uniindia.com/gujarat-governor-acharya-devvrat-sworn-in-as-maharashtra-governor/west/news/3577613.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/transporters-cite-increased-costs-supply-disruptions-want-new-traffic-curbs-lifted/articleshow/124005110.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/modi-likely-to-inaugurate-navi-mumbai-airport-101758050399819.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/national/ashwini-vaishnaw-conducts-breakthrough-of-bullet-train-tunnel-says-first-phase-to-start-in-2027/article70073192.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/trial-runs-on-metro-4s-cadbury-junction-gaimukh-stretch-to-commence-monday-mumbai-metropolitan-region-development-authority-officials-say-corridor-on-track-for-year-end-operations/articleshow/124001171.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/maharashtra-govt-fadnavis-cabinet-approves-8-major-decisions-including-expressway-and-new-policies-nck90</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/mumbai/sanjay-raut-statement-on-anand-dighe-thane-balasaheb-thackeray-photo-advertise-shivsena-maharashtra-marathi-news-1385015</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-metro-4-4a-corridor-improves-transportation-reduce-congestion-on-gb-road-and-connectivity-in-thane-and-mumbai/articleshow/124029480.cms</t>
         </is>
       </c>
     </row>

--- a/Output/Eknath Shinde/extracted_links_Eknath Shinde_failed_links.xlsx
+++ b/Output/Eknath Shinde/extracted_links_Eknath Shinde_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A468"/>
+  <dimension ref="A1:A408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,7 +438,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/eknath-shindes-x-account-briefly-hacked-hackers-post-pics-of-pak-turkey-flags-9315607</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/maharashtra-deputy-cm-eknath-shinde-takes-action-against-builders-of-65-illegal-buildings-in-kalyan-dombivli/articleshow/124011193.cms</t>
         </is>
       </c>
     </row>
@@ -452,56 +452,56 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/not-in-race-to-claim-credit-eknath-shinde-on-ads-featuring-only-d-fadnavis/ar-AA1M0Xg8?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.msn.com/en-in/news/other/thane-metro-4a-trial-run-on-monday-check-station-list-and-other-key-details/ar-AA1MWzkH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/when-i-go-to-villages-i-feel-fresh-my-opponents-get-depressed-says-dy-cm-eknath-shinde-at-launch-of-gram-samruddhi-yojana/articleshow/123964878.cms</t>
+          <t>https://www.indiatvnews.com/maharashtra/eknath-shinde-maharashtra-deputy-cm-x-account-hacked-hackers-post-pakistan-turkey-flags-hacking-sparks-uproar-2025-09-21-1009219</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ahead-of-bmc-elections-eknath-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena-23594416</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-gifts-modi-394-namo-udyans-101758050819661.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/when-i-go-to-villages-i-feel-fresh-my-opponents-get-depressed-says-dy-cm-eknath-shinde-at-launch-of-gram-samruddhi-yojana/articleshow/123964878.cms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-dy-cm-eknath-shindes-x-account-hacked/ar-AA1MZ0l6</t>
+          <t>https://www.hindustantimes.com/india-news/paint-thrown-at-bust-of-uddhav-thackerays-late-mother-sena-workers-angry-probe-on-101758106562970.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/maharashtra-deputy-cm-eknath-shinde-takes-action-against-builders-of-65-illegal-buildings-in-kalyan-dombivli/articleshow/124011193.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/autos/general/maharashtra-dy-cm-eknath-shinde-attends-autofest-2025-in-thane/ar-BB1rljGt?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
         </is>
       </c>
     </row>
@@ -515,525 +515,525 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/stories-detail/national/maharashtra-dy-cm-eknath-shindes-x-account-hacked/2934860/0</t>
+          <t>https://sundayguardianlive.com/news/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-145995/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/gst-rate-cut-will-boost-economy-shield-india-from-us-tariff-hikes-says-maharashtras-deputy-chief-minister-eknath-shinde/articleshow/124002613.cms</t>
+          <t>https://www.tribuneindia.com/news/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-cong-leader-questions-cyber-security-23595093</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/gst-rate-cut-will-boost-economy-shield-india-from-us-tariff-hikes-says-maharashtras-deputy-chief-minister-eknath-shinde/articleshow/124002613.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked-hackers-post-pakistan-turkey-flags-2962608.html</t>
+          <t>https://www.ptinews.com/story/national/ahead-of-bmc-polls-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena/2921488</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-gifts-modi-394-namo-udyans-101758050819661.html</t>
+          <t>https://www.ptinews.com/stories-detail/national/maharashtra-dy-cm-eknath-shindes-x-account-hacked/2934860/0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
+          <t>https://zeenews.india.com/india/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked-hackers-post-pakistan-turkey-flags-2962608.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother20250916212035</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/find-the-masterminds-behind-the-kdmc-illegal-buildings-scam-shinde-101758309996962.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/allies-in-conflict-bjp-shinde-sena-lock-horns-on-dahisar-toll-shift</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde-23595190</t>
+          <t>https://www.newsband.in/article_detail/allies-in-conflict-bjp-shinde-sena-lock-horns-on-dahisar-toll-shift</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-charges-baseless-says-ekanth-shinde-23594783</t>
+          <t>https://www.aninews.in/news/national/politics/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother20250916212035</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/acharya-devvrat-takes-oath-as-maharashtra-governor-101757915941969.html</t>
+          <t>https://www.ptinews.com/story/national/full-page-newspaper-ads-and-slew-of-initiatives-shiv-sena-goes-all-out-to-celebrate-pms-birthday/2925344</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://kashmirlife.net/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-406229/</t>
+          <t>https://www.ptinews.com/story/national/shiv-sena-publishes-full-page-ads-in-dailies-on-pms-birthday-shinde-hails-his-new-india-push/2923561</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/video/news/pm-modi-adopts-nation-first-policy-eknath-shinde-slams-congress-over-remarks-on-pm-s-mother-2025-09-17-1008597</t>
+          <t>https://www.ptinews.com/editor-detail/Dy-CM-Shinde-s-X-account-hacked;-Cong-leader-questions-cyber-security/2935531</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-cm-fadnavis-eknath-shinde-take-metro-ride-during-line-4-and-4a-trial-run-107480</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bombay-hc-can-plea-against-shinde-order-be-a-pil/articleshow/124022877.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/industry/strict-action-ordered-against-65-illegal-buildings-in-kalyan-dombivli-by-deputy-chief-minister-eknath-shinde/124008652</t>
+          <t>https://www.newsband.in/article_detail/awhad-slams-the-states-selective-compassion-over-demolition-notices</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-23595086?button=next</t>
+          <t>https://www.ptinews.com/editor-detail/maharashtra--all-files-to-be-vetted-by-shinde-before-being-sent-to-cm-fadnavis/2429371</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-cm-fadnavis-eknath-shinde-take-metro-ride-during-line-4-and-4a-trial-run-107480/6</t>
+          <t>https://www.indiatvnews.com/video/news/pm-modi-adopts-nation-first-policy-eknath-shinde-slams-congress-over-remarks-on-pm-s-mother-2025-09-17-1008597</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/not-an-mla-but-get-rs-20-cr-in-funds-sena-leader-sarvankar-boasts-later-clarifies/articleshow/124028510.cms</t>
+          <t>https://realty.economictimes.indiatimes.com/news/industry/strict-action-ordered-against-65-illegal-buildings-in-kalyan-dombivli-by-deputy-chief-minister-eknath-shinde/124008652</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/most-of-rs-46000cr-projects-for-marathwada-announced-by-shinde-led-cabinet-in-2023-still-on-paper/articleshow/123907066.cms</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/namo-gardens-to-be-developed-in-394-municipal-councils-and-nagar-panchayats-in-maharashtra-23594437</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278582902/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi</t>
+          <t>https://www.ptinews.com/story/national/dy-cm-shindes-x-account-hacked-cong-leader-questions-cyber-security/2935531</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://menafn.com/1110089200/Maharashtra-Deputy-CM-Eknath-Shindes-X-Account-Hacked-Pakistan-And-Turkey-Flags-Live-Streamed-Report</t>
+          <t>https://www.hindustantimes.com/india-news/acharya-devvrat-takes-oath-as-maharashtra-governor-101757915941969.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/politics/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother20250916212035</t>
+          <t>https://www.heraldgoa.in/goa/sculptor-of-shivajis-statue-held/13663/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane/</t>
+          <t>https://www.babushahi.com/full-news.php?id=211084&amp;headline=GST-cuts-implemented-from-today,-Eknath-Shinde-says-GST-reforms-a-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-pakistan-flag-135976151.html</t>
+          <t>https://www.ptinews.com/editor-detail/heavy-vehicles-banned-on-thane-s-ghodbunder-road-during-daytime/2919586</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-slams-incapable-ministers-after-ajit-pawar-for-ignoring-party-expansion-and-administrative-work/articleshow/124050348.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/19/wrg4-mh-villages-shinde.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flags-9649355.html</t>
+          <t>https://www.newsonair.gov.in/maharashtra-launches-namo-gardens-and-tourism-skill-programme-to-mark-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-strict-against-builders-involved-in-kalyan-dombivali-illegal-buildings-constructing-3015585</t>
+          <t>https://www.aninews.in/news/national/general-news/mmrda-temporarily-suspends-monorail-services-in-mumbai20250920092952</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/sanjay-raut-comments-about-eknath-shinde-mentor-anand-dighe-sparked-an-uproar-201758252385682.html</t>
+          <t>https://aninews.in/news/national/general-news/maharashtra-mmrda-to-suspend-monorail-services-on-september-20-in-mumbai20250917100119/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/DNHindi/photos/%E0%A4%B8%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8%E0%A4%BE%E0%A4%A5-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A4%BE-x-%E0%A4%85%E0%A4%95%E0%A4%BE%E0%A4%89%E0%A4%82%E0%A4%9F-%E0%A4%B9%E0%A5%88%E0%A4%95-%E0%A4%B9%E0%A5%88%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B2%E0%A4%97%E0%A4%BE%E0%A4%88-%E0%A4%AA%E0%A4%BE%E0%A4%95%E0%A4%BF%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A4%BE%E0%A4%A8-%E0%A4%A4%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9D%E0%A4%82%E0%A4%A1%E0%A5%87eknathsi/1251272843711787/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ahead-of-bmc-elections-eknath-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena-23594416</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/eknath-shinde-x-account-hacked-pakistan-turkey-flag-posted-ntc-rptc-2338322-2025-09-21</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-cong-leader-questions-cyber-security-23595093</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/eknath-shinde-party-shiv-sena-will-merge-with-bjp-claims-sanjay-raut-hindi-news-hin25092002104</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-charges-baseless-says-ekanth-shinde-23594783</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/deputy-cm-eknath-shinde-x-account-hacked-hackers-posted-images-of-pakistan-and-turkey-flags/articleshow/124025137.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde-23595190</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/ganesh-naik-vs-eknath-shinde-in-navi-mumbai-tussle-over-janata-darbar-petition-filed-in-high-court/articleshow/123996455.cms</t>
+          <t>https://thenewsmill.com/2025/09/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-claims-mahayuti-saffron-flag-will-fly-in-bmc-and-all-maharashtra-local-body-elections/articleshow/124032659.cms</t>
+          <t>https://www.newsx.com/india/eknath-shinde-account-hacked-during-india-pakistan-asia-cup-cybercrime-cybersecurity-national-flags-of-turkey-and-pakistan-restored-in-45-minutes-75975/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-assembly-election-result-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%A4-%E0%A4%9C-%E0%A4%A4-%E0%A4%97%E0%A4%88-%E0%A4%AE%E0%A4%97%E0%A4%B0-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%9F-%E0%A4%95-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B9%E0%A5%81%E0%A4%86/ar-AA1uBWUK?cvid=165226EF5620437992660C8F5EC7383E&amp;ocid=TIYLnav&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://thenewsmill.com/2025/09/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A0-%E0%A4%A3%E0%A5%87-%E0%A4%95-%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%B6-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%9F-%E0%A4%AA%E0%A5%8D%E0%A4%AA%E0%A4%A3-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A6-%E0%A4%95-%E0%A4%AE%E0%A5%87%E0%A4%A1-%E0%A4%AF%E0%A4%A8-%E0%A4%95%E0%A5%81%E0%A4%A3-%E0%A4%B2-%E0%A4%95-%E0%A4%AE%E0%A4%B0-%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%B9/ar-AA1BxxlJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-claims-bjp-gave-up-on-mayor-s-post-in-2017-on-the-request-of-uddhav-s-aide-107382/2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-bmc-election-eknath-shinde-group-plan-b-revealed-challenge-to-devendra-fadnavis-bjp-9653396.html</t>
+          <t>https://english.varthabharati.in/india/maharashtra-dy-cm-eknath-shindes-x-account-hacked-07712660</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%B8%E0%A4%AD-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%A4%E0%A5%87-%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AB-%E0%A4%B0-%E0%A4%AC%E0%A4%A8%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-cm-%E0%A4%AF%E0%A5%87-%E0%A4%AC-%E0%A4%A4%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A8%E0%A5%8D%E0%A4%B9%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A8-%E0%A4%A4-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%96-%E0%A4%B8/ar-AA1s9G9J?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263?about-us-breakingnews</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%95-%E0%A4%AE%E0%A4%B9-%E0%A4%AE-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%AB-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%B2%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B9-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%A1-%E0%A4%AA%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87/ar-AA1B8Gxe?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.latestly.com/quickly/agency-news/devendra-fadnavis-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane-7123779.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/maharashtra/eknath-shinde-x-account-hacked-pakistani-flags-posted-125092100012_1.html</t>
+          <t>https://thehindustangazette.com/election/eknath-shinde-x-account-hacked-pak-turkey-flags-39959</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/eknath-shinde-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A5-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95%E0%A4%B9-%E0%A4%B5%E0%A4%B9-%E0%A4%97%E0%A4%A0%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%AC%E0%A4%A8-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9%E0%A4%A4%E0%A5%87-%E0%A4%A5%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95-%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A5%9C-%E0%A4%B0%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%AE/ar-AA1Bakv5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/parshuram-economic-development-corporation-chairman-ashish-damle-to-get-ministerial-status-says-maharashtra-govt-23594308</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B5-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%A8%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%97%E0%A5%81%E0%A4%AE%E0%A4%B0-%E0%A4%B9-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AE-%E0%A4%A6-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AD%E0%A5%87%E0%A4%A6%E0%A4%AD-%E0%A4%B5/ar-AA1BUMn4?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.abplive.com/states/maharashtra/deputy-cm-eknath-shinde-x-account-hack-pakistan-turkey-flag-shown-3016093</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-uddhav-thackeray-puts-bold-conditions-for-rebels-nagar-sevak-for-ghar-wapsi-for-shinde-shiv-sena-ahead-of-bmc-polls-know-all/articleshow/123978190.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-slams-incapable-ministers-after-ajit-pawar-for-ignoring-party-expansion-and-administrative-work/articleshow/124050348.cms</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/raj-thackeray-%E0%A4%B2-%E0%A4%B2-%E0%A4%AA-%E0%A4%AA-%E0%A4%B2-%E0%A4%97%E0%A5%87%E0%A4%B2%E0%A5%81-%E0%A4%AA%E0%A4%B0-%E0%A4%B2%E0%A5%9C%E0%A4%95-%E0%A4%95-%E0%A4%A1-%E0%A4%82%E0%A4%B8-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A5%9C%E0%A4%95%E0%A5%87-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AA%E0%A5%82%E0%A4%9B-%E0%A4%AF%E0%A4%B9-%E0%A4%B9%E0%A5%88-%E0%A4%B2-%E0%A4%A1%E0%A4%B2-%E0%A4%AC%E0%A4%B9%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8/ar-AA1tuyLy?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flags-9649355.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.republicbharat.com/india/maharashtra-dy-cm-eknath-shinde-x-account-hacked-posting-images-of-pakistan-and-turkey-flag</t>
+          <t>https://www.livehindustan.com/national/sanjay-raut-comments-about-eknath-shinde-mentor-anand-dighe-sparked-an-uproar-201758252385682.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%B8%E0%A5%8D%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%A6-%E0%A4%96-%E0%A4%88-%E0%A4%94%E0%A4%B0-%E0%A4%87%E0%A4%A8-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%B8-%E0%A4%AF-%E0%A4%B8%E0%A4%A4-%E0%A4%95-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%AF-%E0%A4%9C%E0%A4%B5-%E0%A4%AC/ar-AA1yYRmy?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/eknath-shinde-x-account-hacked-pakistan-turkey-flag-posted-ntc-rptc-2338322-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
+          <t>https://www.facebook.com/DNHindi/photos/%E0%A4%B8%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8%E0%A4%BE%E0%A4%A5-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A4%BE-x-%E0%A4%85%E0%A4%95%E0%A4%BE%E0%A4%89%E0%A4%82%E0%A4%9F-%E0%A4%B9%E0%A5%88%E0%A4%95-%E0%A4%B9%E0%A5%88%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B2%E0%A4%97%E0%A4%BE%E0%A4%88-%E0%A4%AA%E0%A4%BE%E0%A4%95%E0%A4%BF%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A4%BE%E0%A4%A8-%E0%A4%A4%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9D%E0%A4%82%E0%A4%A1%E0%A5%87eknathsi/1251272843711787/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/shiv-sena-mla-sada-sarvankar-met-maharashtra-navnirman-sena-president-raj-thackeray-3016893</t>
+          <t>https://hindi.newsbytesapp.com/news/india/eknath-shinde-s-ex-account-hacked-hackers-posted-flags-of-pakistan-and-turkiye/story</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%A7-%E0%A4%B0%E0%A5%87-%E0%A4%A7-%E0%A4%B0%E0%A5%87-bjp-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%B2-%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%B8%E0%A4%A6-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%89%E0%A4%A4-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1MX3h5</t>
+          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-strict-against-builders-involved-in-kalyan-dombivali-illegal-buildings-constructing-3015585</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-pakistan-turkiye-flag-shown-on-handle/2930969</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/deputy-cm-eknath-shinde-x-account-hacked-hackers-posted-images-of-pakistan-and-turkey-flags/articleshow/124025137.cms</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mva-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%B0-%E0%A4%A8-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%97-%E0%A4%B0%E0%A4%AB%E0%A5%8D%E0%A4%A4-%E0%A4%B0-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%A5-sit-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%9C-%E0%A4%82%E0%A4%9A/ar-AA1ybCn1?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/ganesh-naik-vs-eknath-shinde-in-navi-mumbai-tussle-over-janata-darbar-petition-filed-in-high-court/articleshow/123996455.cms</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-deputy-cm-eknath-shinde-s-twitter-account-hacked-raises-cybersecurity-concerns-201758454098732.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-claims-mahayuti-saffron-flag-will-fly-in-bmc-and-all-maharashtra-local-body-elections/articleshow/124032659.cms</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B0%E0%A5%87-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%95-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%B0%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-ubt-%E0%A4%95-%E0%A4%AA%E0%A4%B2%E0%A4%9F%E0%A4%B5-%E0%A4%B0-%E0%A4%B0-%E0%A4%89%E0%A4%A4-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%A4-%E0%A4%A4-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5/ar-AA1H4TcY?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/eknath-shindes-x-account-hacked-pictures-of-islamic-countries-and-turkish-flags-posted-11708</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%89%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A6%E0%A5%87%E0%A4%82-%E0%A4%9F%E0%A5%82%E0%A4%9F-%E0%A4%82-%E0%A4%B0-%E0%A4%9C-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%95-%E0%A4%B5-%E0%A4%9C%E0%A4%AF-%E0%A4%B0%E0%A5%88%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1I1z7a?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.indiatv.in/maharashtra/sanjay-raut-said-eknath-shinde-mentality-is-very-low-level-there-is-nothing-left-to-talk-about-2025-09-20-1163910</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/pm-modi-birthday-congress-declares-pm-modi-s-birthday-as-black-day-enraged-eknath-shinde-issues-warning-2025-09-17</t>
+          <t>https://www.indiatv.in/maharashtra/maharashtra-deputy-cm-eknath-shinde-x-handle-hacked-hackers-shared-posts-with-pakistan-and-turkey-flags-2025-09-21-1164034</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/deputy-cm-eknath-shinde-x-account-hack-pakistan-turkey-flag-shown-investigation-going-on-hindi-news-1390995.html</t>
+          <t>https://hindi.webdunia.com/maharashtra/eknath-shinde-x-account-hacked-pakistani-flags-posted-125092100012_1.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/eknath-shinde-takes-action-against-kalyan-dombivli-illegal-buildings-builders/articleshow/124011899.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-uddhav-thackeray-puts-bold-conditions-for-rebels-nagar-sevak-for-ghar-wapsi-for-shinde-shiv-sena-ahead-of-bmc-polls-know-all/articleshow/123978190.cms</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-namo-park-scheme-for-pm-narendra-modi-75th-birthday-deputy-cm-eknath-shinde-announcement-3014117</t>
+          <t>https://www.abplive.com/states/maharashtra/shiv-sena-mla-sada-sarvankar-met-maharashtra-navnirman-sena-president-raj-thackeray-3016893</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-deputy-chief-minister-ekanth-shinde-says-rahul-gandhi-s-vote-theft-charges-baseless-2025-09-19</t>
+          <t>https://www.amarujala.com/video/india-news/pm-modi-birthday-congress-declares-pm-modi-s-birthday-as-black-day-enraged-eknath-shinde-issues-warning-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/cm-fadnavis-and-deputy-cm-shinde-flagged-off-trial-run-of-thane-metro-line-4-from-gaimukh-to-cadbury-11720</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B8-%E0%A4%85%E0%A4%95-%E0%A4%89%E0%A4%82%E0%A4%9F-%E0%A4%B9%E0%A5%88%E0%A4%95-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%87%E0%A4%AC%E0%A4%B0-%E0%A4%B8%E0%A5%81%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA%E0%A4%B0-%E0%A4%89%E0%A4%A0-%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8/ar-AA1MZNrX</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-deputy-cm-eknath-shinde-s-twitter-account-hacked-raises-cybersecurity-concerns-201758454098732.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/video/pm-modi-75th-birthday-piyush-goyal-eknath-shinde-wishes-ytvd-2335022-2025-09-17</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%A7-%E0%A4%B0%E0%A5%87-%E0%A4%A7-%E0%A4%B0%E0%A5%87-bjp-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%B2-%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%B8%E0%A4%A6-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%89%E0%A4%A4-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1MX3h5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://inshorts.com/hi/news/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6--%E0%A4%A6--%E0%A4%95--x-%E0%A4%85%E0%A4%95-%E0%A4%89-%E0%A4%9F-%E0%A4%B9-%E0%A4%95--%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%B8-%E0%A4%A8--%E0%A4%AA-%E0%A4%B8-%E0%A4%9F-%E0%A4%95-%E0%A4%8F-%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%A4-%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%95--%E0%A4%95--%E0%A4%9D-%E0%A4%A1---1758441470089</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-namo-park-scheme-for-pm-narendra-modi-75th-birthday-deputy-cm-eknath-shinde-announcement-3014117</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%B8%E0%A4%AD-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%A8%E0%A5%87-45-%E0%A4%89%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%A8-%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%90%E0%A4%B2-%E0%A4%A8-cm-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%87%E0%A4%B8-%E0%A4%B8-%E0%A4%9F-%E0%A4%B8%E0%A5%87-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5/ar-AA1sJkOe?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-deputy-chief-minister-ekanth-shinde-says-rahul-gandhi-s-vote-theft-charges-baseless-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/pratap-sarnaik-comments-on-uddhav-thackeray-sanjay-raut-praises-eknath-shinde-respect-senior-leaders-3016095</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/eknath-shinde-takes-action-against-kalyan-dombivli-illegal-buildings-builders/articleshow/124011899.cms</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/kedar-dighes-sharp-attack-on-shinde-faction-anand-dighe-remembered-as-elections-approach/articleshow/124004160.cms</t>
+          <t>https://inshorts.com/hi/news/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6--%E0%A4%A6--%E0%A4%95--x-%E0%A4%85%E0%A4%95-%E0%A4%89-%E0%A4%9F-%E0%A4%B9-%E0%A4%95--%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%B8-%E0%A4%A8--%E0%A4%AA-%E0%A4%B8-%E0%A4%9F-%E0%A4%95-%E0%A4%8F-%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%A4-%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%95--%E0%A4%95--%E0%A4%9D-%E0%A4%A1---1758441470089</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
+          <t>https://www.aajtak.in/india/maharashtra/video/pm-modi-75th-birthday-piyush-goyal-eknath-shinde-wishes-ytvd-2335022-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://x.com/i/status/1970055402231419183?ref_src=twsrc%5Egoogle%7Ctwcamp%5Eserp%7Ctwgr%5Etweet</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/kedar-dighes-sharp-attack-on-shinde-faction-anand-dighe-remembered-as-elections-approach/articleshow/124004160.cms</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/thane-metro-trial-run-on-september-22-thane-residents-dream-to-come-true/articleshow/124004146.cms</t>
+          <t>https://marathi.abplive.com/news/thane/ghodbunder-residents-will-be-freed-from-traffic-jams-orders-to-leave-heavy-vehicles-after-12-midnight-eknath-shinde-orders-1384427</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.navodayatimes.in/news/national/maharashtra-deputy-cm-eknath-shinde-ex-handle-hacked/276116/</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/thane-metro-trial-run-on-september-22-thane-residents-dream-to-come-true/articleshow/124004146.cms</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/eknath-shinde-treated-australian-guests-to-a-feast-of-vada-pav-9289261</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-news-rahul-gandhi-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%B5%E0%A4%B0-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-marathi-news/vi-AA1MOsp4</t>
+          <t>https://www.navodayatimes.in/news/national/maharashtra-deputy-cm-eknath-shinde-ex-handle-hacked/276116/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/amp/india-news/maharashtra-deputy-chief-minister-eknath-shinde-s-x-account-hacked-news-in-hindi-2025-09-21</t>
+          <t>https://marathi.ndtv.com/cities/eknath-shinde-treated-australian-guests-to-a-feast-of-vada-pav-9289261</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/jansatta-special/jansatta-rajpaat-abhay-chautala-haryana-shinde-message-congress-du-election-bihar-seat-dispute-rld-up/4151302/</t>
+          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-news-rahul-gandhi-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%B5%E0%A4%B0-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-marathi-news/vi-AA1MOsp4</t>
         </is>
       </c>
     </row>
@@ -1068,77 +1068,77 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-at-tembhi-naka-devi-%E0%A4%9F%E0%A5%87%E0%A4%82%E0%A4%AD-%E0%A4%A8-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%B2-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%9A-%E0%A4%86%E0%A4%97%E0%A4%AE%E0%A4%A8-%E0%A4%B8-%E0%A4%B9%E0%A4%B3-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%B8%E0%A5%8D%E0%A4%A5-%E0%A4%A4-n18v/vi-AA1N3TKj</t>
+          <t>https://mahasamvad.in/178497/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178497/</t>
+          <t>https://marathi.abplive.com/news/mumbai/under-what-authority-were-the-municipal-corporation-notice-to-demolish-buildings-stopped-high-court-ask-on-eknath-shinde-whether-the-dcm-has-the-authority-to-make-that-decision-1384909</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/thane-ghodbunder-news-good-news-for-thane-kalyan-badlapur-commuters-as-eknath-shinde-orders-restriction-of-heavy-vehicles-untill-midnight-9291074</t>
+          <t>https://mahasamvad.in/179440/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
+          <t>https://hindi.theprint.in/india/shiv-sena-workers-protest-against-rauts-remarks-about-dighe/870443/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179440/</t>
+          <t>https://mahasamvad.in/179586/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/under-what-authority-were-the-municipal-corporation-notice-to-demolish-buildings-stopped-high-court-ask-on-eknath-shinde-whether-the-dcm-has-the-authority-to-make-that-decision-1384909</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-decision-mandatory-to-construct-administrative-buildings-of-municipal-councils-according-to-the-model-plan-1482062.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178790/</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticized-eknath-shinde-for-washing-rajan-vichares-feet-and-taking-a-pilgrimage/923077/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/changes-in-gst-rates-will-lead-to-the-ghatsthapna-of-superpower-in-country-eknath-shinde-96248</t>
+          <t>https://marathi.abplive.com/news/politics/the-high-court-has-questioned-eknath-shinde-over-the-suspension-of-action-against-illegal-construction-in-navi-mumbai-1384988</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-decision-mandatory-to-construct-administrative-buildings-of-municipal-councils-according-to-the-model-plan-1482062.html</t>
+          <t>https://mahasamvad.in/178790/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticized-eknath-shinde-for-washing-rajan-vichares-feet-and-taking-a-pilgrimage/923077/</t>
+          <t>https://www.tv9marathi.com/maharashtra/shivsena-ubt-sanjay-raut-talk-about-eknath-shinde-rajan-vichare-entry-in-party-1495859.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%9D-%E0%A4%AA-%E0%A4%89%E0%A4%A1-%E0%A4%B2-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A6-%E0%A4%B2-%E0%A4%AE-%E0%A4%A0-%E0%A4%87%E0%A4%B6-%E0%A4%B0/ar-AA1N3wGD</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/changes-in-gst-rates-will-lead-to-the-ghatsthapna-of-superpower-in-country-eknath-shinde-96248</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/the-high-court-has-questioned-eknath-shinde-over-the-suspension-of-action-against-illegal-construction-in-navi-mumbai-1384988</t>
+          <t>https://www.lokmatnews.in/business/mukhyamantri-mazi-ladki-bahin-yojana-no-e-kyc-no-rs-1500-all-beneficiaries-can-avail-facility-visiting-web-portal-b507/</t>
         </is>
       </c>
     </row>
@@ -1166,35 +1166,35 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://inshorts.com/hi/amp_news/-%E0%A4%B8%E0%A4%A4-%E0%A4%A4--%E0%A4%95--%E0%A4%B2-%E0%A4%8F-%E0%A4%B0-%E0%A4%AF%E0%A4%B2-%E0%A4%AA-%E0%A4%B0-%E0%A4%9F-------%E0%A4%B6--%E0%A4%A6--%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%AE%E0%A4%B0--%E0%A4%95--%E0%A4%9F-%E0%A4%AA-%E0%A4%AA%E0%A4%A3--%E0%A4%95--%E0%A4%B2-%E0%A4%95%E0%A4%B0-%E0%A4%9C%E0%A4%AF--%E0%A4%AC%E0%A4%9A-%E0%A4%9A%E0%A4%A8-%E0%A4%A8--%E0%A4%A6--%E0%A4%AA-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B0-%E0%A4%AF--1742984239606</t>
+          <t>https://mahasamvad.in/178863/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/vidhan-parishad-election-2025-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%B9-%E0%A4%B6-%E0%A4%B2%E0%A5%87%E0%A4%A6-%E0%A4%B0-%E0%A4%A0%E0%A4%B0%E0%A4%B2-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%B0%E0%A4%98%E0%A5%81%E0%A4%B5%E0%A4%82%E0%A4%B6-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A3-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%A6-%E0%A4%9A-%E0%A4%B2-%E0%A4%9F%E0%A4%B0-%E0%A4%95%E0%A5%81%E0%A4%A3-%E0%A4%B2/ar-AA1B3F4t?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.ndtv.com/maharashtra/thane-ghodbunder-news-good-news-for-thane-kalyan-badlapur-commuters-as-eknath-shinde-orders-restriction-of-heavy-vehicles-untill-midnight-9291074</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-deputy-chief-minister-eknath-shinde-launches-the-seva-fortnight-chief-minister-samruddhi-panchayat-raj-abhiyan-in-thane-district/922593/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-many-office-bearers-of-uddhav-thackeray-group-join-shiv-sena-95696</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-deputy-chief-minister-eknath-shinde-launches-the-seva-fortnight-chief-minister-samruddhi-panchayat-raj-abhiyan-in-thane-district/922593/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/start-preparing-for-mumbai-municipal-corporation-elections-now-says-eknath-shinde-a-a653/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-many-office-bearers-of-uddhav-thackeray-group-join-shiv-sena-95696</t>
         </is>
       </c>
     </row>
@@ -1208,2497 +1208,2077 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/09/22/deputy-chief-minister-eknath-shinde-took-stock-of-the-heavy-rainfall-in-marathwada//</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-district-administration-should-remain-alert-in-wake-of-heavy-rains-eknath-shinde-instructs-94887</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/eknath-shinde-has-revealed-that-the-ladki-bahin-scheme-will-never-be-closed/41518</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-shinde-first-reaction-on-meenatai-thackeray-dadar-statue-issue-he-will-not-be-released-i-have-spoken-to-the-police-commissioner-1384826</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178863/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-review-maharashtra-and-mumbai-rain-updates-orders-airlift-beed-ashti-villagers-1480338.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/eknath-shinde-first-reaction-on-meenatai-thackeray-dadar-statue-issue-he-will-not-be-released-i-have-spoken-to-the-police-commissioner-1384826</t>
+          <t>https://marathi.abplive.com/news/maharashtra/deputy-chief-minister-eknath-shinde-reaction-to-prime-minister-narendra-modi-s-gst-cut-ladki-bahin-yojana-news-1385846</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-district-administration-should-remain-alert-in-wake-of-heavy-rains-eknath-shinde-instructs-94887</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/deputy-chief-minister-eknath-shinde-reaction-to-prime-minister-narendra-modi-s-gst-cut-ladki-bahin-yojana-news-1385846</t>
+          <t>https://mahasamvad.in/178828/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-review-maharashtra-and-mumbai-rain-updates-orders-airlift-beed-ashti-villagers-1480338.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-response-after-sanjay-raut-objected-to-placing-anand-dighes-photo-next-to-balasaheb-thackeray/922799/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178828/</t>
+          <t>https://marathi.ndtv.com/cities/cm-fadnavis-change-eknath-shindes-decision-to-ban-heavy-vehicles-from-morning-6-to-12-night-to-solve-traffic-congestion-9316039</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-get-set-back-bmc-scraps-12-crore-project-mumbai-1485014.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/cm-fadnavis-change-eknath-shindes-decision-to-ban-heavy-vehicles-from-morning-6-to-12-night-to-solve-traffic-congestion-9316039</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-municipal-elections-eknath-shinde-puts-shiv-sena-in-action-mode-with-direct-orders-to-corporators-sharad-pawar-also-eyes-victory-in-corporations-1384728</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-response-after-sanjay-raut-objected-to-placing-anand-dighes-photo-next-to-balasaheb-thackeray/922799/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/shiv-sena-leader-eknath-shinde-slams-incapable-ministers-for-ignoring-party-expansion-and-administrative-work/articleshow/124045917.cms</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/solution-to-traffic-congestion-found-ghodbunder-residents-will-get-relief-eknath-shinde-gives-order-991858.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-feeds-australian-mp-tim-watts-mumbais-vada-pav/922339/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-feeds-australian-mp-tim-watts-mumbais-vada-pav/922339/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-big-announces-on-pm-modi-birthday-say-all-municipal-councils-will-be-established-namo-udyan-in-maharashtra-95314</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-big-announces-on-pm-modi-birthday-say-all-municipal-councils-will-be-established-namo-udyan-in-maharashtra-95314</t>
+          <t>https://marathi.ndtv.com/cities/now-there-is-only-one-type-plan-for-the-administrative-buildings-of-the-municipal-council-and-municipal-panchayats-eknath-shinde-9294836</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-municipal-elections-eknath-shinde-puts-shiv-sena-in-action-mode-with-direct-orders-to-corporators-sharad-pawar-also-eyes-victory-in-corporations-1384728</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-ajit-pawar-and-eknath-shinde-reprimand-maharashtra-cabinet-over-performance-and-neglect-of-party-organization-1386101</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-ajit-pawar-and-eknath-shinde-reprimand-maharashtra-cabinet-over-performance-and-neglect-of-party-organization-1386101</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-s-x-account-hacked-turkish-and-pakistani-videos-posted-account-recovered-after-team-x-complaint-1385633</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-rain-heavy-rainfall-in-beed-40-villagers-should-be-airlifted-dcm-eknath-shinde-ordered-9279677</t>
+          <t>https://www.mymahanagar.com/maharashtra/mumbai-high-court-questioned-eknath-shinde-on-new-mumbai-illegal-construction-case/922756/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/now-there-is-only-one-type-plan-for-the-administrative-buildings-of-the-municipal-council-and-municipal-panchayats-eknath-shinde-9294836</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shinde-fadnavis-cold-war-high-court-questions-maharashtra-government-s-legitimacy-amid-brand-battle-corruption-allegations-and-best-depot-controversy-1384960</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/mumbai-high-court-questioned-eknath-shinde-on-new-mumbai-illegal-construction-case/922756/</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-rain-heavy-rainfall-in-beed-40-villagers-should-be-airlifted-dcm-eknath-shinde-ordered-9279677</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-get-set-back-bmc-scraps-12-crore-project-mumbai-1485014.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-stated-that-the-change-in-gst-rates-will-lead-to-the-establishment-of-a-superpower-in-the-country-from-tomorrow/923694/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shinde-fadnavis-cold-war-high-court-questions-maharashtra-government-s-legitimacy-amid-brand-battle-corruption-allegations-and-best-depot-controversy-1384960</t>
+          <t>https://www.mymahanagar.com/maharashtra/deputy-cm-eknath-shinde-on-heavy-rains-and-alert-to-district-administration/921681/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-stated-that-the-change-in-gst-rates-will-lead-to-the-establishment-of-a-superpower-in-the-country-from-tomorrow/923694/</t>
+          <t>https://www.etvbharat.com/mr/!state/parshuram-economic-development-corporation-chairman-ashish-damle-gets-ministerial-status-in-thane-maharashtra-news-mhs25091603365</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/dcm-eknath-shinde-get-report-of-the-heavy-rainfall-in-marathwada-weather-update-998693.html</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-ghodbandar-road-eknath-shinde-ghodbandar-residents-will-be-free-from-traffic-congestion/922259/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sanjay-raut-%E0%A4%95-%E0%A4%A3-%E0%A4%B6%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA-%E0%A4%B0%E0%A4%97%E0%A4%82-%E0%A4%95%E0%A4%A7-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B9-%E0%A4%A4%E0%A4%82-%E0%A4%95-%E0%A4%B0-%E0%A4%8A%E0%A4%A4-%E0%A4%82%E0%A4%A8-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2-%E0%A4%96-%E0%A4%B8%E0%A4%A6-%E0%A4%B0%E0%A4%95-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%95-%E0%A4%9F-%E0%A4%9A-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%B8/ar-AA1MSb0O</t>
+          <t>https://www.msn.com/mr-in/news/other/sushma-andhare-%E0%A4%A1%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%9F-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%96%E0%A4%B0%E0%A5%87-%E0%A4%B0%E0%A5%81%E0%A4%AA-%E0%A4%86%E0%A4%9C-%E0%A4%AC-%E0%A4%B9%E0%A5%87%E0%A4%B0-%E0%A4%86%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A5%81%E0%A4%B7%E0%A4%AE-%E0%A4%85%E0%A4%82%E0%A4%A7-%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%98%E0%A4%A3-%E0%A4%98-%E0%A4%A4/ar-AA1HY5L7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/deputy-cm-eknath-shinde-on-heavy-rains-and-alert-to-district-administration/921681/</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-for-suspending-demolition-of-societies-with-unauthorized-construction-in-vashi-area/922729/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/mns-leader-avinash-jadhav-slams-eknath-shinde-over-thane-traffic-issue/articleshow/123926772.cms</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-working-on-plan-b-for-bmc-election-likely-shock-to-uddhav-thackeray-and-bjp-also-1484790.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
+          <t>https://www.mymahanagar.com/mahamumbai/withdrew-the-rs-2-5-crore-fund-given-for-sewage-plant-and-drainage-because-former-corporator-deepmala-badhe-belonged-to-the-thackeray-group/922264/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A4-%E0%A4%A6-%E0%A4%B5-%E0%A4%B3-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%AE-%E0%A4%A0-%E0%A4%AD%E0%A5%82%E0%A4%95%E0%A4%82%E0%A4%AA-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8%E0%A4%B9-%E0%A4%A6%E0%A5%81%E0%A4%9C-%E0%A4%B0/ar-AA1McaIA?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/mns-leader-avinash-jadhav-slams-eknath-shinde-over-thane-traffic-issue/articleshow/123926772.cms</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-ghodbandar-road-eknath-shinde-ghodbandar-residents-will-be-free-from-traffic-congestion/922259/</t>
+          <t>https://www.etvbharat.com/mr/!state/if-you-come-to-power-we-will-show-the-power-of-jai-maharashtra-sanjay-raut-warning-to-eknath-shinde-maharashtra-news-mhs25092001682</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/national/video/eknath-shinde-x-account-hacked-pakistan-turkey-flags-posted-september-2025-135976016.html?index=69</t>
+          <t>https://www.mymahanagar.com/maharashtra/dcm-eknath-shinde-criticized-rahul-gandhi-evm-vote-chori-case/922837/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://x.com/i/broadcasts/1rmxPvjzknjGN?ref_src=twsrc%5Egoogle%7Ctwcamp%5Eserp%7Ctwgr%5E</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-says-anand-dighe-never-sold-shiv-sena/923100/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-working-on-plan-b-for-bmc-election-likely-shock-to-uddhav-thackeray-and-bjp-also-1484790.html</t>
+          <t>https://www.loksatta.com/vasaivirar/eknath-shinde-to-survey-massive-traffic-congestion-on-mumbai-ahmedabad-national-highway-rds-00-5385650/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/bombay-high-court-questions-eknath-shinde-illegal-constructions-navi-mumbai-135950643.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/local-elections-mahayuti-will-win-in-the-local-self-government-elections-eknath-shinde-is-confident/922171/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-for-suspending-demolition-of-societies-with-unauthorized-construction-in-vashi-area/922729/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-palghar-dahanu-shivsena-thackeray-group-office-bearers-from-palghar-dahanu-join-shivsena/922966/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-says-anand-dighe-never-sold-shiv-sena/923100/</t>
+          <t>https://news18marathi.com/news/navi-mumbai-munciple-corporation-news-dcm-eknath-shinde-directed-the-commissioner-to-give-immediate-priority-to-water-supply-roads-health-facilities-and-schools-in-14-villages-local18-1483762.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/if-you-come-to-power-we-will-show-the-power-of-jai-maharashtra-sanjay-raut-warning-to-eknath-shinde-maharashtra-news-mhs25092001682</t>
+          <t>https://www.saamana.com/wadigodri-crime-news-fake-cid-officers-stole-the-golden-ring/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/dcm-eknath-shinde-criticized-rahul-gandhi-evm-vote-chori-case/922837/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-solve-bmtc-employee-problem-gave-10-lakh-for-compensation-1484524.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-palghar-dahanu-shivsena-thackeray-group-office-bearers-from-palghar-dahanu-join-shivsena/922966/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-announced-strict-action-will-be-taken-against-those-who-cheated-residents-of-65-buildings-in-kalyan-dombivali-1483839.html</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/local-elections-mahayuti-will-win-in-the-local-self-government-elections-eknath-shinde-is-confident/922171/</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-politics-deputy-cm-eknath-shindes-twitter-account-hacked-1497198.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/nashik-journalist-beating-dcm-eknath-shinde-speaks-with-injured-journalist-kiran-tajane-via-video-call-1497047.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/pm-narendra-modi-birthday-sharad-pawar-ajit-pawar-and-eknath-shinde-wish-a-happy-birthday-95367</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/shivsena-thackrey-faction-leader-sanjay-raut-slams-eknath-shinde-and-others-1496593.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-shiv-sena-mla-sanjay-gaikwads-controversial-statement-sanjay-gaikwad-claims-that-local-level-elections-cost-rs-3-crores-and-100-goats-have-to-be-slaughtered/923585/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/solapur-politics-ncp-sharad-pawar-party-mla-narayan-patil-will-joins-eknath-shindes-shiv-sena-9326109</t>
+          <t>https://marathi.ndtv.com/videos/after-ajit-pawar-eknath-shinde-will-also-hold-a-road-show-in-nagpur-shinde-s-mission-vidarbha-997770</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/thane/ghodbunder-residents-will-be-freed-from-traffic-jams-orders-to-leave-heavy-vehicles-after-12-midnight-eknath-shinde-orders-1384427</t>
+          <t>https://www.mumbaitak.in/political-news/story/sanjay-raut-has-strongly-criticized-eknath-shinde-for-printing-photos-of-balasaheb-thackeray-and-anand-dighe-side-by-side-in-an-advertisement-wishing-pm-modi-a-happy-birthday-3202688-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/sharad-pawar-led-ncp-2-mlas-attend-shivsena-eknath-shinde-meeting-political-stir-1486267.html</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-eknath-shinde-s-shiv-sena-in-action-mode-confident-of-mahayuti-victory-in-mumbai-civic-polls-directs-corporators-to-start-work-1384673</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-former-mla-claim-on-20-crore-make-political-stir-in-maharashtra-1484863.html</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/parshuram-economic-development-corporation-chairman-ashish-damle-gets-ministerial-status-in-thane-maharashtra-news-mhs25091603365</t>
+          <t>https://www.mymahanagar.com/mahamumbai/shiv-sena-and-bjp-stage-a-strong-show-of-strength-on-the-occasion-of-metro-trial-in-thane-cm-devendra-fadnavis-eknath-shinde-pratap-sarnaik/923787/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/eid-e-milad-2024-public-holiday-on-september-18-announced-by-eknath-shinde-133641576.html</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/thane-sporting-club-election-eknath-shinde-shiv-sena-won-over-bjp-mns-ubt-devendra-fadnavis-uddhav-thackeray-raj-thackeray-maharashtra-politics/articleshow/124041703.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-eknath-shinde-office-call-thackeray-worker-ayodhya-paul-audio-clip-viral-135941678.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-chairs-shiv-sena-meeting-in-mumbai-strategizes-for-upcoming-elections-and-mumbai-municipal-corporation-polls-sanjay-nirupam-reacts-1384153</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-solve-bmtc-employee-problem-gave-10-lakh-for-compensation-1484524.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-politics-deputy-cm-eknath-shinde-refutes-evm-allegations-confident-of-mahayuti-victory-in-mumbai-civic-polls-on-development-work-1385031</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/pm-narendra-modi-birthday-sharad-pawar-ajit-pawar-and-eknath-shinde-wish-a-happy-birthday-95367</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-20-september-2025-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/withdrew-the-rs-2-5-crore-fund-given-for-sewage-plant-and-drainage-because-former-corporator-deepmala-badhe-belonged-to-the-thackeray-group/922264/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/dispute-between-both-shiv-sena-parties-over-printing-anand-dighe-photo-next-to-balasaheb/940602</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/sanjay-raut-attacks-eknath-shinde-shrikant-shiv-sena-rahul-modi-presser-135957579.html</t>
+          <t>https://marathi.ndtv.com/videos/thane-is-up-for-sale-sanjay-raut-hits-out-at-shinde-fadnavis-997973</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.mumbaitak.in/political-news/story/sanjay-raut-has-strongly-criticized-eknath-shinde-for-printing-photos-of-balasaheb-thackeray-and-anand-dighe-side-by-side-in-an-advertisement-wishing-pm-modi-a-happy-birthday-3202688-2025-09-18</t>
+          <t>https://marathi.ndtv.com/videos/thane-ghodbunder-road-traffic-jaam-controversy-997251</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-chairs-shiv-sena-meeting-in-mumbai-strategizes-for-upcoming-elections-and-mumbai-municipal-corporation-polls-sanjay-nirupam-reacts-1384153</t>
+          <t>https://maharashtratimes.com/india-news/bihar-assembly-election-amit-shah-meets-bjp-workers-gives-60-days-plan-ahead-of-poll/articleshow/123995857.cms</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-former-mla-claim-on-20-crore-make-political-stir-in-maharashtra-1484863.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-mumbai-rains-deputy-cm-eknath-shinde-reviews-flood-situation-40-50-people-trapped-in-asti-kateri-being-airlifted-from-nashik-ahilyanagar-1384293</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbais-ghodbunder-road-new-night-restrictions-to-ease-traffic-jams-1493450.html</t>
+          <t>https://www.saamana.com/eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flag-saamana-online-news/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/after-ajit-pawar-eknath-shinde-will-also-hold-a-road-show-in-nagpur-shinde-s-mission-vidarbha-997770</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-namo-gardens-project-eknath-shinde-announces-394-crore-funding-for-394-municipal-councils-on-pm-modi-s-birthday-includes-garden-competition-1384925</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/siddharth-shinde-supreme-court-lawyer-passed-away-at-delhi-1384433</t>
+          <t>https://www.tv9marathi.com/videos/short-videos/eknath-shinde-accuses-uddhav-thackeray-covid-19-corruption</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-politics-deputy-cm-eknath-shinde-refutes-evm-allegations-confident-of-mahayuti-victory-in-mumbai-civic-polls-on-development-work-1385031</t>
+          <t>https://www.newsband.in/article_detail/acharyadevvrattakes-oath-as-maharashtras-22nd-governor</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/thane-is-up-for-sale-sanjay-raut-hits-out-at-shinde-fadnavis-997973</t>
+          <t>https://thenewsmill.com/2025/09/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://tamil.getlokalapp.com/amp/maharashtra-news/thane/ambernath/thane-heavy-traffic-jam-continues-even-after-eknath-shinde-s-order-15438856</t>
+          <t>https://www.sakshipost.com/news/shiv-senaubt-continues-attacking-dy-cm-shinde-says-maha-govt-boastful-454108</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/paint-thrown-at-bust-of-uddhav-thackerays-late-mother-sena-workers-angry-probe-on-101758106562970.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263?2012-mar-breakingnews</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-shiv-sena-leaders-speech-adds-fuel-to-accusations-of-biased-allocation-of-funds-23595109</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/hc-to-shinde-by-what-authority-did-you-stay-navi-mumbai-civic-bodys-notice-to-raze-illegal-buildings/articleshow/123952725.cms</t>
+          <t>https://www.ndtv.com/india-news/eknath-shindes-x-account-briefly-hacked-hackers-post-pics-of-pak-turkey-flags-9315607</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-strict-against-builders-involved-in-kalyan-dombivali-illegal-buildings-constructing-3015585/amp</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/find-the-masterminds-behind-the-kdmc-illegal-buildings-scam-shinde-101758309996962.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-x-%E0%A4%85%E0%A4%95-%E0%A4%89%E0%A4%82%E0%A4%9F-%E0%A4%B9%E0%A5%88%E0%A4%95-%E0%A4%AA-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%A4%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95%E0%A5%87-%E0%A4%9D%E0%A4%82%E0%A4%A1%E0%A5%87-%E0%A4%9C%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%85%E0%A4%9C-%E0%A4%AC-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%88-%E0%A4%9A-%E0%A4%82%E0%A4%A4/ar-AA1MZ2tG</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/full-page-newspaper-ads-and-slew-of-initiatives-shiv-sena-goes-all-out-to-celebrate-pms-birthday/2925344</t>
+          <t>https://www.moneycontrol.com/news/india/rahul-gandhi-s-vote-theft-charges-baseless-says-eknath-shinde-13559796.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shiv-sena-publishes-full-page-ads-in-dailies-on-pms-birthday-shinde-hails-his-new-india-push/2923561</t>
+          <t>https://www.ptinews.com/editor-detail/maharashtra-dy-cm-eknath-shinde-s--x--account-hacked/2934860</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bombay-hc-can-plea-against-shinde-order-be-a-pil/articleshow/124022877.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/eknath-shinde-mla-aamshya-padvi-tribal-reservation-opposition-abuses-protest-dhangar-banjara-controversy-gs97</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/thane-shiv-sena-workers-protest-against-sanjay-raut-s-remark-about-anand-dighe-23594679</t>
+          <t>https://prahaar.in/2025/09/22/deputy-chief-minister-eknath-shinde-took-stock-of-the-heavy-rainfall-in-marathwada//</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-eknath-shinde-issues-stern-warning-to-inefficient-maharashtra-cabinet-ministers-over-neglect-of-party-work-and-public-issues-1385985</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/hc-seeks-govt-s-stand-on-illegal-stay-on-demolition-by-dy-cm-101758137116362.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/uddhav-thackeray-led-shiv-sena-leader-ayodhya-poul-patil-received-call-from-eknath-shinde-office-call-recording-goes-viral/videoshow/123934054.cms</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/dy-cm-shindes-x-account-hacked-cong-leader-questions-cyber-security/2935531</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pm-modi-birthday-eknath-shinde-s-leader-of-the-world-tribute-article-in-loksatta-saamana-omits-ad-1384700</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/women-office-bearers-workers-of-sena-ubt-from-palghar-join-shinde-led-sena-ahead-of-local-polls/2927880</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-cabinet-discontent-bharat-gogawale-on-eknath-shinde-s-displeasure-ministerial-accountability-and-action-on-inefficient-ministers-1386103</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/bjp-gave-up-claim-for-mumbai-mayor-s-post-in-2017-at-request-of-shinde--narvekar--says-cm-fadnavis/2921301</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-maharashtra-deputy-cms-ajit-pawar-and-eknath-shinde-express-anger-over-ministerial-inefficiency-neglect-of-party-work-and-janata-darbar-1386067</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ncp-sp-cong-welcome-sc-order-on-maharashtra-local-bodies-polls;-mahayuti-will-win-says-shinde/2920944</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-cm-shinde-s-stern-warning-to-inefficient-ministers-over-performance-neglect-of-party-work-and-public-issues-secret-meeting-held-1386025</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/news/west/disaster-management-cm-shinde/3577807.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-thane-navratri-deputy-cm-eknath-shinde-attends-devi-arrival-procession-at-tembhinaka-traditional-festivities-begin-1386020</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/most-of-rs-46000cr-projects-for-marathwada-announced-by-shinde-led-cabinet-in-2023-still-on-paper/articleshow/123907066.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-ministers-warning-ajit-pawar-and-eknath-shinde-warn-mahayuti-ministers-over-poor-performance-hint-at-cabinet-reshuffle-before-local-elections-1386093</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/acharyadevvrattakes-oath-as-maharashtras-22nd-governor</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-15-september-2025-zp-presidentship-reservation-nepal-violence-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/On-eve-of-PM-s-birthday-Shinde-announces-scheme-to-develop-Namo-Parks-in-Maharashtra/2921302</t>
+          <t>https://www.kisantak.in/politics/story/eknath-shinde-took-a-swipe-at-his-opponents-says-they-feel-depressed-by-farming-1279260-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://www.bignewsnetwork.com/news/278582902/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/on-eve-of-pms-birthday-shinde-announces-scheme-to-develop-namo-parks-in-maharashtra/2921302</t>
+          <t>https://www.thejbt.com/india/maharashtra-deputy-cm-eknath-shinde-s-x-account-hacked-hackers-posted-flags-of-pakistan-and-t%C3%BCrkiye-news-295659</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/prioritise-development-in-14-villages-added-to-navi-mumbai-civic-limits-dy-cm-shinde/2930925</t>
+          <t>https://www.jansatta.com/jansatta-special/jansatta-rajpaat-abhay-chautala-haryana-shinde-message-congress-du-election-bihar-seat-dispute-rld-up/4151302/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/maharashtra-launches-namo-gardens-and-tourism-skill-programme-to-mark-pm-modis-75th-birthday/</t>
+          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-shiv-sena-leaders-speech-adds-fuel-to-accusations-of-biased-allocation-of-funds-23595109</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-almatti-dam-height-increase-maharashtra-to-move-supreme-court-over-karnataka-s-decision-raising-flood-risk-for-sangli-kolhapur-shiv-sena-mobilizes-in-sambhaji-nagar-1384708</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3633705-infrastructure-revamp-a-new-dawn-for-navi-mumbais-villages</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/state-news/thane-metro-begins-trial-run-after-20-year-wait-19966553</t>
+          <t>https://www.hindi.awazthevoice.in/india-news/maharashtra-deputy-chief-minister-eknath-shinde-s-x-account-hacked-68948.html</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/mmrda-temporarily-suspends-monorail-services-in-mumbai20250920092952</t>
+          <t>https://www.ibc24.in/maharashtra/eknath-shindes-x-account-hacked-congress-leader-raises-questions-on-cyber-security-3261842.html</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-mmrda-to-suspend-monorail-services-on-september-20-in-mumbai20250917100119/</t>
+          <t>https://www.marathiebatmya.com/political/dy-cm-eknath-shinde-visits-the-state-emergency-operations-center/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi/</t>
+          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/shinde-wishes-prime-minister-modi-on-his-birthday-125091700049_1.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/shiv-senaubt-continues-attacking-dy-cm-shinde-says-maha-govt-boastful-454108</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/shinde-reviewed-the-flood-situation-in-marathwada-125092200058_1.html</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/agency-news/devendra-fadnavis-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane-7123779.html</t>
+          <t>https://www.newsx.com/india/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-77106/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.khabarfast.com/uploadnews/details/maharashtra-news-deputy-cm-eknath-shinde-x-handle-hacked-hackers-shared-posts-with-pakistan-and-turkey-flags</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/hc-seeks-govt-s-stand-on-illegal-stay-on-demolition-by-dy-cm-101758137116362.html</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/dcm-eknath-shinde-orders-district-administration-to-remain-alert-in-wake-of-heavy-rains-zws-70-5373503/</t>
+          <t>https://www.patrika.com/en/state-news/thane-metro-begins-trial-run-after-20-year-wait-19966553</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/eknath-shinde-mla-aamshya-padvi-tribal-reservation-opposition-abuses-protest-dhangar-banjara-controversy-gs97</t>
+          <t>https://www.devdiscourse.com/article/politics/3629545-uddhav-thackeray-criticizes-indias-cricket-match-with-pakistan-questions-bjps-patriotism</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/other-cities/parashuram-development-board-chairman-given-ministerial-rank/</t>
+          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-15-september-2025-3482219.html</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/siddharth-shinde-passes-away-%E0%A4%AE-%E0%A4%9C-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%A8-%E0%A4%A4%E0%A5%82-%E0%A4%95-%E0%A4%AF%E0%A4%A6-%E0%A4%B8-%E0%A4%AA%E0%A5%8D%E0%A4%AF-%E0%A4%AD-%E0%A4%B7%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A4%AE%E0%A4%9C-%E0%A4%B5%E0%A5%82%E0%A4%A8-%E0%A4%B8-%E0%A4%82%E0%A4%97%E0%A4%A3-%E0%A4%B0-%E0%A4%B5-%E0%A4%A7-%E0%A4%9C%E0%A5%8D%E0%A4%9E-%E0%A4%95-%E0%A4%A3-%E0%A4%B9-%E0%A4%A4%E0%A5%87-%E0%A4%B8-%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87/ar-AA1MCHAN</t>
+          <t>https://www.patrika.com/mumbai-news/thane-metro-dream-comes-true-after-20-year-new-lifelines-trial-run-begin-on-these-10-stations-19965341</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-20-september-2025-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/dcm-eknath-shinde-on-bmc-election-with-mahayuti-alliance/videoshow/124025029.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-eknath-shinde-issues-stern-warning-to-inefficient-maharashtra-cabinet-ministers-over-neglect-of-party-work-and-public-issues-1385985</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-polls-an-acid-test-for-shiv-sena-ubt-says-thackeray-101758222779307.html</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/thane-ghodbunder-road-traffic-jaam-controversy-997251</t>
+          <t>https://www.afternoonvoice.com/the-chronological-formation-and-political-evolution-of-maharashtra.html</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/uddhav-thackeray-led-shiv-sena-leader-ayodhya-poul-patil-received-call-from-eknath-shinde-office-call-recording-goes-viral/videoshow/123934054.cms</t>
+          <t>https://thecsrjournal.in/thane-metro-trial-run-hindi/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-pm-modi-birthday-eknath-shinde-s-leader-of-the-world-tribute-article-in-loksatta-saamana-omits-ad-1384700</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sushma-andhare-%E0%A4%A1%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%9F-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%96%E0%A4%B0%E0%A5%87-%E0%A4%B0%E0%A5%81%E0%A4%AA-%E0%A4%86%E0%A4%9C-%E0%A4%AC-%E0%A4%B9%E0%A5%87%E0%A4%B0-%E0%A4%86%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A5%81%E0%A4%B7%E0%A4%AE-%E0%A4%85%E0%A4%82%E0%A4%A7-%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%98%E0%A4%A3-%E0%A4%98-%E0%A4%A4/ar-AA1HY5L7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/shiv-sena-ubt-mns-bjp-raj-thackeray-uddhav-thackeray-devendra-fadnavis-unite-against-shiv-sena-eknath-shinde-for-thane-sporting-committee-election/articleshow/123938834.cms</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/sanjay-raut-slams-eknath-shinde-modi-advertisement-and-reply-also-cm-fadnavis-over-thackeray-brand-1495206.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/new-jetty-construction-for-vasai-and-uttan-dongri-ro-ro-service-which-will-help-commuters/articleshow/123892530.cms</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/maharashtra-politics-90-of-shinde-pawar-and-bjp-candidates-became-mlas-by-stealing-votes-sanjay-rauts-criticism-a-a732/</t>
+          <t>https://www.hindisaamana.com/the-conflict-between-naik-and-shinde-reaches-its-peak-shinde-faction-files-suit-against-naik-in-the-high-court-over-the-janata-darbar/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-cabinet-discontent-bharat-gogawale-on-eknath-shinde-s-displeasure-ministerial-accountability-and-action-on-inefficient-ministers-1386103</t>
+          <t>https://hindi.latestly.com/india/good-news-for-thane-residents-metro-trial-runs-will-take-place-on-monday-2758623.html</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%B8%E0%A4%A8%E0%A4%B2-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AB-%E0%A4%95-%E0%A4%9B%E0%A5%81%E0%A4%9F%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A6-%E0%A4%8F-%E0%A4%9C-%E0%A4%82%E0%A4%9A-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1zIR9b?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
+          <t>https://www.hindustantimes.com/india-news/statue-of-uddhav-thackeray-s-mother-defaced-in-mumbai-shiv-sena-ubt-protests-101758095171594.html</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/desh/maharashtra-marathi-live-news-23-september-2025-navratri-festival-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://www.ndtv.com/video/ndtv-yuva-conclave-milind-deora-on-which-leader-connects-with-gen-z-better-996976</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-maharashtra-deputy-cms-ajit-pawar-and-eknath-shinde-express-anger-over-ministerial-inefficiency-neglect-of-party-work-and-janata-darbar-1386067</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/mla-warns-sanjay-raut-over-remarks-on-anand-dighe-shiv-sainiks-protest-in-kalyan-dombivli/articleshow/124011234.cms</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-mumbai-rains-deputy-cm-eknath-shinde-reviews-flood-situation-40-50-people-trapped-in-asti-kateri-being-airlifted-from-nashik-ahilyanagar-1384293</t>
+          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-on-eknath-shinde-maharashtra-ahmedabad-bullet-train-anand-dighe-3015725</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/mahayuti-government-reservation-issue-new-controversy-reason-sw79</t>
+          <t>https://www.amarujala.com/india-news/maharastra-paint-thrown-on-statue-of-meenatai-thackeray-at-mumbai-shivaji-park-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/maharashtra-news/trial-run-of-thane-metro-route-4-and-4a-begins-fadnavis-praises-shinde-15458549</t>
+          <t>https://www.jansatta.com/national/current-mlas-get-rs-2-crore-and-i-get-rs-20-crore-big-claim-by-former-shiv-sena-mla-sada-sarvankar/4153263/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-eknath-shinde-continues-his-series-of-meetings-he-will-launch-his-election-campaign-with-a-dussehra-rally-1189598</t>
+          <t>https://hindi.theprint.in/india/despite-not-being-an-mla-i-received-a-fund-of-rs-20-crore-shiv-sena-leader-sarwankar/871651/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/states/maharashtra/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-shared-post-of-pakistan-and-turkey-flags-10484007</t>
+          <t>https://www.amarujala.com/india-news/uddhav-targets-bjp-over-india-pakistan-cricket-match-in-asia-cup-maharashtra-debt-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/eknath-shinde-took-a-swipe-at-his-opponents-says-they-feel-depressed-by-farming-1279260-2025-09-18</t>
+          <t>https://www.lokmatnews.in/blog/india/bjp-shivsena-ncp-congress-local-body-elections-your-bow-and-arrow-but-target-is-ours-drawing-dividing-line-blog-amitabh-srivastava-b507/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/metro-project-will-solve-traffic-congestion-problem-in-thane-eknath-shinde-4279685</t>
+          <t>https://hindi.financialexpress.com/india-news/ex-mla-sada-sarvankar-sparks-row-with-claim-of-receiving-20-crore-funds-10487968</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-cm-fadnavis-eknath-shinde-take-metro-ride-during-line-4-and-4a-trial-run-107480/5</t>
+          <t>https://www.tribuneindia.com/news/business/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/heavy-vehicles-banned-on-thanes-ghodbunder-road-during-daytime-23594294</t>
+          <t>https://www.electronicsforyou.biz/industry-buzz/rrp-electronics-gets-land-for-semiconductor-fab-in-navi-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-15-september-2025-3482219.html</t>
+          <t>https://www.devdiscourse.com/article/headlines/3630472-himachal-pradeshs-infrastructure-rebuild-a-race-against-time?amp</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/who-will-take-over-the-cpi-after-d-raja-these-two-names-are-in-the-race-201758252502320.html</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-cabinet-meeting-maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-8-important-decisions-mumbai-maharashtra-news-mhs25091602614</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%94%E0%A4%B0%E0%A4%82%E0%A4%97%E0%A4%9C%E0%A5%87%E0%A4%AC-%E0%A4%95-%E0%A4%AE%E0%A4%B9-%E0%A4%A8-%E0%A4%AC%E0%A4%A4-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%AC%E0%A5%82-%E0%A4%86%E0%A4%9C%E0%A4%AE-%E0%A4%AA%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%B8%E0%A4%AD-%E0%A4%B8%E0%A5%87-%E0%A4%A8-%E0%A4%B2%E0%A4%82%E0%A4%AC-%E0%A4%A4/ar-AA1AgWGX?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://prahaar.in/2025/09/16/2-lakh-new-employment-opportunities-in-the-state-investment-of-rs-50-thousand-crores-will-come/amp/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/bmc-election-2025-shivsena-ubt-mns-raj-thackeray-seat-sharing-formula-96240</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar-3735776</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!politics/bmc-polls-50-50-seats-for-sena-ubt-mns-in-mumbai-strongholds-60-40-in-others-say-party-leaders-mhs25092103157</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/new-jetty-construction-for-vasai-and-uttan-dongri-ro-ro-service-which-will-help-commuters/articleshow/123892530.cms</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/pm-modi-turns-75-highlights-of-initiatives-launched-by-bjp-events-held-in-several-states/articleshow/123949298.cms</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/the-conflict-between-the-bjp-and-shinde-factions-escalates-in-thane-district/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ajit-pawars-absence-at-key-guv-events-raises-eyebrows/articleshow/124030467.cms</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/rahul-gandhis-vote-theft-allegations-completely-baseless-shinde-3258685.html</t>
+          <t>https://curlytales.com/india/ct-scoop/durga-puja-pandals-in-mumbai-where-you-can-spot-bollywood-celebrities/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/good-news-for-thane-residents-metro-trial-runs-will-take-place-on-monday-2758623.html</t>
+          <t>https://hindi.latestly.com/india/education/latest-and-important-news-of-22nd-september-for-school-assembly-read-the-latest-updates-related-to-national-international-and-sports-2759750.html</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
+          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/statue-of-uddhav-thackeray-s-mother-defaced-in-mumbai-shiv-sena-ubt-protests-101758095171594.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-secret-of-2-5-hour-meeting-at-shivtirth-how-raj-thackeray-prevail-over-uddhav-political-experts-reveal-9622593.html</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/ndtv-yuva-conclave-milind-deora-on-which-leader-connects-with-gen-z-better-996976</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-told-party-workers-bmc-elections-are-a-litmus-test-for-us/articleshow/123989198.cms</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharastra-paint-thrown-on-statue-of-meenatai-thackeray-at-mumbai-shivaji-park-2025-09-17</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-22-political-news-in-marathi-941153</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/current-mlas-get-rs-2-crore-and-i-get-rs-20-crore-big-claim-by-former-shiv-sena-mla-sada-sarvankar/4153263/</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-sanjay-raut-supports-rahul-gandhi-saying-that-90-of-the-mahayuti-mlas-in-maharashtra-won-through-vote-theft/articleshow/124015667.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A4%AC-%E0%A4%B9-%E0%A4%97-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%95-%E0%A4%B5-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B0-%E0%A4%95-%E0%A4%A8-%E0%A4%95-%E0%A4%A8-%E0%A4%AC%E0%A4%A8%E0%A5%87%E0%A4%97-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%AE%E0%A4%A8%E0%A5%87-%E0%A4%86%E0%A4%88-%E0%A4%A4-%E0%A4%B0-%E0%A4%96/ar-AA1vowQk?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-3/921531/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/shiv-sena-leader-ex-mla-sada-sarvankar-claims-20-crore-fund-dispute-sparks-political-stir-3016545</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-21-september-2025-india-vs-pakistan-%E2%80%93-asia-cup-maharashtra-politics-national-international-live-update-in-marathi-940858</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/statue-of-bal-thackerays-wife-meenatai-defaced-probe-launched/869900/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/mumbai-bal-thackerays-wife-meenatai-thackerays-statue-defaced-by-throwing-paint-on-it-one-person-arrested/870084/</t>
+          <t>https://marathi.ndtv.com/videos/sangli-protest-in-sangli-against-gopichand-padalkar-s-statement-participation-of-eminent-leaders-998015</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/uddhav-targets-bjp-over-india-pakistan-cricket-match-in-asia-cup-maharashtra-debt-2025-09-16</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/maharashtra/bmc-elections-uddhav-thackeray-shivsena-ubt-raj-thackerays-mns-alliance-seat-sharing-formula-125092100051_1.html</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-17-september-2025-pm-narendra-modi-75th-birthday-zp-presidentship-reservation-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/blog/india/bjp-shivsena-ncp-congress-local-body-elections-your-bow-and-arrow-but-target-is-ours-drawing-dividing-line-blog-amitabh-srivastava-b507/</t>
+          <t>https://marathi.ndtv.com/videos/jalna-gunratna-sadavarte-s-car-attacked-while-on-his-way-to-meet-protesters-997494</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sada-saravankar-statement-of-mla-fund-mahim-thackeray-group-mahesh-sawant-counterattack-mla-gets-rs-2-crore-but-i-get-rs-20-crore-when-i-am-not-an-mla-1385728</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-14-political-news-in-marathi-939050</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189622</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-17-political-news-in-marathi-939849</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://gallinews.com/%E0%A4%8F%E0%A4%95%E0%A4%A8%E0%A4%BE%E0%A4%A5-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%B8%E0%A4%BE%E0%A4%B9%E0%A5%87%E0%A4%AC%E0%A4%BE%E0%A4%82%E0%A4%9A%E0%A5%80-%E0%A4%B5%E0%A4%BE/</t>
+          <t>https://www.navarashtra.com/maharashtra/top-marathi-news-today-breaking-news-political-news-live-update-crime-news-994890.html</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/lifestyle/smart-living/govt-to-formulate-new-mhada-policy-to-provide-affordable-housing-dy-cm-shinde/ar-AA1y3CdE?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.electronicsforyou.biz/industry-buzz/rrp-electronics-gets-land-for-semiconductor-fab-in-navi-mumbai/</t>
+          <t>https://www.marathijagran.com/maharashtra/nashik/shardiya-navratri-2025-praveen-togadias-big-statement-at-hindu-hunkar-sabha-said-no-entry-for-muslims-at-garba-places-96201</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-cabinet-meeting-maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-8-important-decisions-mumbai-maharashtra-news-mhs25091602614</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-tejashwi-yadav-calls-cm-nitish-a-cheat-minister-makes-these-big-promises-to-the-public-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
+          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-16-17-september-live-updates-tejashwi-yadav-bihar-adhikar-yatra-election-pm-modi-rahul-gandi-supreme-court-sahastradhara-flood-waqf/4143389/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
+          <t>https://www.mymahanagar.com/maharashtra/navi-mumbai-city-petition-filed-in-janata-darbar-against-minister-ganesh-naik-by-kishore-patkar/922934/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar-3735776</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/why-is-there-still-no-bjp-chief-minister-in-bihar-nitish-kumar-lalu-prasad-yadav-tejashwi-yadav-limited-grip-on-obc-voters-ebcs-mm76</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
+          <t>https://www.tv9marathi.com/videos/eknath-shinde-shivsena-file-janhit-yachika-in-mumbai-high-court-against-ganesh-naik-janta-darbar-1496267.html</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://politalks.news/political-temperature-rises-in-maharashtra-ncp-chief-ajit-pawar-preparing-to-break-away-from-the-mahayuti</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane-politics-petition-against-minister-ganesh-naiks-janata-darbar/922848/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/modi-govt-gave-rs-21-000-cr-for-marathwada-rail-lines-rs-450-crore-came-during-upa-time-fadnavis-2025-09-17</t>
+          <t>https://yashbharat.co.in/maharashtra-deputy-cm-eknath-shindes-ex-handle-hacked-posts-with-pakistan-and-turkey-flags-spark-uproar/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/pm-modi-turns-75-highlights-of-initiatives-launched-by-bjp-events-held-in-several-states/articleshow/123949298.cms</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/thane-city-challenge-to-eknath-shinde-in-the-fort-itself-bjp-leader-ganesh-naiks-janata-darbar-for-the-third-consecutive-time/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
+          <t>https://www.dainikprabhat.com/pimpri-news-shiv-sena-ready-for-elections-avoid-factionalism-get-to-work-shrirang-barnes-instructions-to-office-bearers/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://curlytales.com/india/ct-scoop/durga-puja-pandals-in-mumbai-where-you-can-spot-bollywood-celebrities/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
+          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/meenatai-thackeray-statue-smeared-with-red-paint-1-held-101758136336233.html</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633962-scam-allegations-deepen-in-chhattisgarh-as-key-figures-arrested?amp</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.asianage.com/nation/ubt-sena-up-in-arms-after-meenatai-thackeray-statue-defaced-1904390</t>
+          <t>https://clarionindia.net/ahmednagar-railway-station-renamed-concern-over-erasure-of-muslim-legacy/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
+          <t>https://www.patrika.com/national-news/no-cap-on-prices-of-cars-for-guv-cm-and-judges-in-maharashtra-vehicle-policy-19954354</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-secret-of-2-5-hour-meeting-at-shivtirth-how-raj-thackeray-prevail-over-uddhav-political-experts-reveal-9622593.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-date-extended-supreme-court-give-new-deadline-31st-january-2026-know-all/articleshow/123920003.cms</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/mumbai-mina-thackeray-statue-defaced-shivaji-park-shiv-sena-protest-police-action-ntc-dskc-2335896-2025-09-17</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-told-party-workers-bmc-elections-are-a-litmus-test-for-us/articleshow/123989198.cms</t>
+          <t>https://www.amarujala.com/india-news/vhp-s-hindu-only-diktat-for-garba-open-invitation-for-violence-ramdas-athawale-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-22-political-news-in-marathi-941153</t>
+          <t>https://www.amarujala.com/india-news/cpwd-floats-tender-to-install-bulletproof-glass-in-chambers-of-eam-foreign-secy-at-jn-bhawan-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-sanjay-raut-supports-rahul-gandhi-saying-that-90-of-the-mahayuti-mlas-in-maharashtra-won-through-vote-theft/articleshow/124015667.cms</t>
+          <t>https://mandalnews.com/amravati/government-should-take-decision-with-a-common-perspective-regarding-tet-for-teachers/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-3/921531/</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-pichhade-varg-ke-sarakaaree-chhaatraavaas-ke-vidyaarthiyon-ke-dainik-bhatte-mein-vrddhi-ko-manjooree-1187663</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
+          <t>https://mahasamvad.in/178810/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-21-september-2025-india-vs-pakistan-%E2%80%93-asia-cup-maharashtra-politics-national-international-live-update-in-marathi-940858</t>
+          <t>https://www.lokmat.com/maharashtra/will-maharashtra-local-body-elections-be-delayed-state-election-commission-files-application-in-supreme-court-a-a629/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ncp-sharad-pawar-expresses-delight-at-potential-thackeray-brothers-mumbai-alliance-and-power-grab-1495154.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-14-political-news-in-marathi-939050</t>
+          <t>https://joindia.co.in/news/maharashtra-gets-new-governor-acharya-devvrat-takes-charge-as-the-22nd-governor/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
+          <t>https://www.aajtak.in/programmes/mumbai-metro/video/mumbai-metro-ameet-satam-controversial-statement-bmc-election-frvd-2335000-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-17-political-news-in-marathi-939849</t>
+          <t>https://www.timemaharashtra.com/maharashtra/mumbai/new-rules-will-now-apply-to-administrative-buildings-of-municipal-councils-and-municipal-panchayats-eknath-shindes-decision/132833/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/the-bomb-of-political-revelation-will-explode-soon-shinde-group-warns-97879/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-municipal-election-2025-mns-district-chief-raju-dindorle-will-join-bjp-mm76-rg93</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/twist-in-mumbai-municipal-corporations-politics-sharad-pawars-new-move-97848/</t>
+          <t>https://news18marathi.com/maharashtra/thane/thane-traffic-update-heavy-vehicles-entering-city-banned-from-6-am-to-12-midnight-ws-b-1482548.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/rohit-pawars-janata-darbar-or-assembly-hall-dadagiri-97885/</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-govt-fadnavis-cabinet-approves-8-major-decisions-including-expressway-and-new-policies-nck90</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-bmc-election-latest-update-mumbai-pune-rain-weather-today-devendra-fadnavis-on-uddhav-thackeray-shivsena-news-scj-81-5380824/</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-1384548</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/cm-devendra-fadnavis-slams-thackeray-bandhu-over-best-election-2025-result-and-brand-defeat-a-a719/</t>
+          <t>https://www.msn.com/en-in/entertainment/tv/ok-tata-bye-bye-paytm-ceo-vijay-shekhar-sharma-deleted-his-post-on-ratan-tata-s-passing-after-facing-backlash/ar-AA1s2Nt7?ocid=hpdhp17&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/kishori-pednekar-on-two-legs-but-see-what-happens-when-you-go-kishori-pednekars-warning-to-the-shinde-group/923218/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/technical-panel-approves-2-stps-along-indrayani-cm/articleshow/124005440.cms</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-navratri-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-monday-22-september-2025-1497734.html</t>
+          <t>https://www.loksatta.com/maharashtra/garware-youth-development-centre-satara-skill-training-helps-13-rural-youths-get-jobs-rds-00-5385521/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
+          <t>https://www.mahasamvad.in/page/45/?m=0</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/dadar-shivaji-park-meenatai-thackeray-statue-red-color-thrown-mumbai-crime/articleshow/123936431.cms</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/top-marathi-news-today-breaking-news-political-news-live-update-crime-news-994890.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-gifts-namo-gardens-to-394-towns-on-pm-modis-75th-birthday-rs-394-crore-sanctioned/articleshow/123964170.cms</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/bmc-election-raj-thackeray-will-hand-over-mumbais-subha-to-uddhav-thackeray/</t>
+          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/nashik/shardiya-navratri-2025-praveen-togadias-big-statement-at-hindu-hunkar-sabha-said-no-entry-for-muslims-at-garba-places-96201</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/hc-to-shinde-by-what-authority-did-you-stay-navi-mumbai-civic-bodys-notice-to-raze-illegal-buildings/articleshow/123952725.cms</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-tejashwi-yadav-calls-cm-nitish-a-cheat-minister-makes-these-big-promises-to-the-public-2025-09-18</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-16-17-september-live-updates-tejashwi-yadav-bihar-adhikar-yatra-election-pm-modi-rahul-gandi-supreme-court-sahastradhara-flood-waqf/4143389/</t>
+          <t>https://www.devdiscourse.com/article/politics/3630419-mla-ends-fast-nh-3-negligence-sparks-controversy-in-himachal?amp</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html?utm_source=District%20Widget&amp;utm_medium=Mobile&amp;utm_campaign=marathi</t>
+          <t>https://propnewstime.com/getdetailsStories/MjE0NDY=/kdmc-told-to-file-economic-crime-case-over-65-unauthorized-buildings</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A0-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B2-%E0%A4%AD-%E0%A4%88%E0%A4%97-%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B5%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%9A-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A7-%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A5%87%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%A4%E0%A4%9A-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5-%E0%A4%B0-%E0%A4%A7-%E0%A4%A4-%E0%A4%8F%E0%A4%B2%E0%A5%8D%E0%A4%97-%E0%A4%B0/ar-AA1G2Q8d?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://m.economictimes.com/news/mumbai-news/mmrda-temporarily-suspends-monorail-services-in-mumbai/articleshow/124009977.cms</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/eknath-shinde-shivsena-file-janhit-yachika-in-mumbai-high-court-against-ganesh-naik-janta-darbar-1496267.html</t>
+          <t>https://m.economictimes.com/mf/analysis/amfi-reshuffle-poonawalla-fincorp-gillette-india-among-6-smallcap-stocks-that-may-get-midcap-status/poonawalla-fincorp/slideshow/123940051.cms</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/navi-mumbai-city-petition-filed-in-janata-darbar-against-minister-ganesh-naik-by-kishore-patkar/922934/</t>
+          <t>https://www.newsx.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-71735/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/why-is-there-still-no-bjp-chief-minister-in-bihar-nitish-kumar-lalu-prasad-yadav-tejashwi-yadav-limited-grip-on-obc-voters-ebcs-mm76</t>
+          <t>https://www.thehindu.com/news/national/karnataka/karnataka-proposes-law-to-fix-minimum-wage-work-hours-for-domestic-workers/article70074706.ece</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/navratri-2025-mumbai-police-will-have-strict-security-for-nine-days/articleshow/124024081.cms</t>
+          <t>https://theblunttimes.in/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/51898/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane-politics-petition-against-minister-ganesh-naiks-janata-darbar/922848/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maha-govt-ensures-transparency-in-ladki-bahin-yojana-asks-beneficiaries-to-complete-e-kyc-process-in-two-months-3735616</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/shinde-factions-credibility-is-falling-deputy-chief-minister-shinde-is-angry-with-inactive-ministers/</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/maharashtra-ladki-bahin-yojana-ekyc-mandatory-beneficiaries-207500</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189409</t>
+          <t>https://www.punjabkesari.com/india-news/ladki-bahin-yojana-2/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.theindiadaily.com/india/eknath-shinde-x-account-hacked-cyber-security-pakistan-t%C3%BCrkiye-flags-social-media-security-digital-platforms-cyber-crime-maharashtra-deputy-chief-minister-asia-cup-2025-news-94725</t>
+          <t>https://marathi.abplive.com/business/mukhyamantri-ladki-bahin-yojana-ekyc-compulsory-for-all-check-how-complete-this-process-1385224</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-14-september-2025-asia-cup-cricket-hockey-pakistan-china-pm-modi-rain-alert-trump-israel-ukraine-russia-gaza-war-bjp-congress/liveblog/123877354.cms</t>
+          <t>https://zeenews.india.com/marathi/photos/ladki-bahin-yojana-ekyc-kashi-karaychi-rule-change-by-maharashtra-government-documents-application-process-deadline-ifnormation-every-details-you-need-to-know/940522</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/karnataka/karnataka-proposes-law-to-fix-minimum-wage-work-hours-for-domestic-workers/article70074706.ece</t>
+          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-majhi-ladki-bahin-yojana-ekyc-update-women-beneficiaries-last-date-135957916.html</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/ladki-bahin-e-kyc-otp-issues-maharashtra-women-scheme/41406</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/india-pakistan-match-protests-asaduddin-owaisi-26-lives-shiv-sena-uddhav-thackeray-135916128.html</t>
+          <t>https://marathi.abplive.com/news/chhatrapati-sambhaji-nagar/ladki-bahin-yojana-84-thousand-beloved-sisters-who-are-receiving-two-or-more-benefits-from-the-same-family-will-be-ineligible-1384524</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://clarionindia.net/ahmednagar-railway-station-renamed-concern-over-erasure-of-muslim-legacy/</t>
+          <t>https://www.lokmat.com/agriculture/weather/latest-news-maharashtra-rain-no-chances-monsoon-leave-in-maharashtra-till-september-30-read-in-detail-a-a993/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-date-extended-supreme-court-give-new-deadline-31st-january-2026-know-all/articleshow/123920003.cms</t>
+          <t>https://mahasamvad.in/178873/</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/cpwd-floats-tender-to-install-bulletproof-glass-in-chambers-of-eam-foreign-secy-at-jn-bhawan-2025-09-16</t>
+          <t>https://www.lokmat.com/photos/filmy/marathi-actress-swapnanchya-palikadle-serial-fame-gauri-nalawade-now-looking-glamorous-latest-photo-viral-on-social-media-a-a991/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/government-should-take-decision-with-a-common-perspective-regarding-tet-for-teachers/</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/e-kyc-made-mandatory-for-beneficiaries-of-the-chief-ministers-majhi-laadki-behan-scheme-1360239.html</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-line-4-trials-completed-thane-metro-first-phase-to-open-by-december-2025-fully-operational-by-2027-say-mmrda/articleshow/124058727.cms</t>
+          <t>https://marathi.timesnownews.com/maharashtra/ladki-bahin-yojana-updates-more-than-124000-mahila-disqualified-form-government-scheme-article-152828023</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/who-is-justice-chandrashekhar-now-listen-pleas-of-obc-groups-against-maratha-reservation-in-bombay-high-court-after-bench-recuses-from-hearing/articleshow/124060275.cms</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-21-september-2025-125092100006_1.html</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/golden-data-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%97-%E0%A4%B2%E0%A5%8D%E0%A4%A1%E0%A4%A8-%E0%A4%A1%E0%A5%87%E0%A4%9F-%E0%A4%86%E0%A4%A3%E0%A4%B2-%E0%A4%AC-%E0%A4%97%E0%A4%B8-%E0%A4%B2-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%B0-%E0%A4%96%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%AA-%E0%A4%8A%E0%A4%B2-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95-%E0%A4%A1%E0%A5%87%E0%A4%9F-%E0%A4%95-%E0%A4%AF/ar-AA1MSC1D?ocid=finance-verthp-feeds</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/mahatet-exam-2025-mandatory-exam-confusion-for-senior-teachers-application-process-begins-from-15-september/articleshow/123893618.cms</t>
+          <t>https://thenewsmill.com/2025/09/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/shani-shingnapur-devasthan-trust-dissolved-big-decision-of-the-state-government-998165</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-technical-inspection-of-metro-4-and-4-a-from-gaimukh-to-vijay-garden-107468</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://news18marathi.com/maharashtra/trial-of-metro-4-in-thane-begins-in-the-presence-of-chief-minister-devendra-fadnavis-local18-1485682.html</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/national/ahmednagar-railway-station-renamed-now-it-will-be-known-as-ahilyanagar/</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/thane-gaimukh-to-wadala-metro-4-trial-today-read-its-route-and-other-details/articleshow/124037736.cms</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/australian-mp-tim-watts-met-maharashtra-deputy-cm-shinde-4270583</t>
+          <t>https://vsrsnews.in/pimpri-chinchwad/pune-acharya-devvrat-becomes-the-new-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/farmer-activists-claim-that-due-to-the-new-order-farmers-will-receive-40-less-compensation-for-crop-loss</t>
+          <t>https://marathi.timesnownews.com/maharashtra/thane-metro-4-and-4a-span-35-km-with-32-stations-trial-run-inspected-by-devendra-fadnavis-and-eknath-shinde-full-details-in-marathi-article-152872624</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/education/latest-and-important-news-of-22nd-september-for-school-assembly-read-the-latest-updates-related-to-national-international-and-sports-2759750.html</t>
+          <t>https://www.aninews.in/news/national/general-news/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi20250917174418</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/dcm-eknath-shinde-directs-to-airlift-citizens-stranded-due-to-floods-in-ashti-taluka/132516/amp/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/attorney-general-birendra-saraf-resigns/117476/</t>
+          <t>https://www.thehindu.com/news/national/uttarakhand/uttarakhand-govt-to-buy-produce-from-apple-growers-in-disaster-hit-dharali/article70076273.ece</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/mumbai-metro/video/mumbai-metro-ameet-satam-controversial-statement-bmc-election-frvd-2335000-2025-09-17</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-14-september-2025-asia-cup-cricket-hockey-pakistan-china-pm-modi-rain-alert-trump-israel-ukraine-russia-gaza-war-bjp-congress/liveblog/123877354.cms</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/vhp-s-hindu-only-diktat-for-garba-open-invitation-for-violence-ramdas-athawale-2025-09-21</t>
+          <t>https://www.newsonair.gov.in/heavy-rains-batter-maharashtra-imd-issues-yellow-alert-across-state/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%9C-%E0%A4%A8-%E0%A4%AE%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%A8-%E0%A4%9A-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%B2-%E0%A4%A6-%E0%A4%B2-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%85%E0%A4%A1%E0%A4%9A%E0%A4%A3-%E0%A4%A4-%E0%A4%AF%E0%A5%87%E0%A4%8A-%E0%A4%A8%E0%A4%AF%E0%A5%87-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A5%82%E0%A4%A8/ar-AA1MDxgy</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/maharashtra-government-vehicle-policy-revised-2025-ntc-rptc-2336368-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
+          <t>https://rajbhavan-maharashtra.gov.in/gallery/15-09-2025-%E0%A4%86%E0%A4%9A%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A4%B5%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%AF%E0%A4%BE%E0%A4%82%E0%A4%A8%E0%A5%80-%E0%A4%98%E0%A5%87/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://peoplesupdate.com/mumbai-coastal-road-lamborghini-accident-luxury-car-damaged-video-130648</t>
+          <t>https://hindi.theprint.in/india/trial-run-of-metro-line-4-and-4a-conducted-in-thane/871907/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-police-restrict-heavy-truck-movement-for-eighteen-hours-daily-to-ease-traffic-congestion/articleshow/123927129.cms</t>
+          <t>https://www.ptinews.com/press-release/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/2938489</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/thane/thane-traffic-update-heavy-vehicles-entering-city-banned-from-6-am-to-12-midnight-ws-b-1482548.html</t>
+          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/MLA-Rais-Sheikh-welcomes-Supreme-Courts-order-regarding-Waqf-Board.html</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-govt-fadnavis-cabinet-approves-8-major-decisions-including-expressway-and-new-policies-nck90</t>
+          <t>https://marathi.ndtv.com/videos/beed-to-ahilyanagar-railway-inaugurated-cm-fadnavis-live-995605</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
+          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-1384548</t>
+          <t>https://deshonnati.com/maharashtra-governor-acharya-devvrat-took-the-oath/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-cabinet-decisions-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%85-%E0%A5%85%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B6%E0%A4%A8-vfx-%E0%A4%A7-%E0%A4%B0%E0%A4%A3-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-%E0%A5%AE-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1MDQ9X</t>
+          <t>https://www.bignewsnetwork.com/news/278581344/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-15-september-2025-zp-presidentship-reservation-nepal-violence-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-marathwada-four-people-died-150-people-were-trapped-in-floods-in-dharashiv/924053/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/how-the-bjp-alliance-won-maharashtra-101757921779535.html</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
+          <t>https://timesofindia.indiatimes.com/india/not-an-mla-but-get-rs-20-cr-in-funds-sena-leader-sarvankar-boasts-later-clarifies/articleshow/124028510.cms</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/cabinet-decision-read-important-decisions-in-the-state-cabinet-meeting-with-one-click/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/entertainment/tv/ok-tata-bye-bye-paytm-ceo-vijay-shekhar-sharma-deleted-his-post-on-ratan-tata-s-passing-after-facing-backlash/ar-AA1s2Nt7?ocid=hpdhp17&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-police-restrict-heavy-truck-movement-for-eighteen-hours-daily-to-ease-traffic-congestion/articleshow/123927129.cms</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/technical-panel-approves-2-stps-along-indrayani-cm/articleshow/124005440.cms</t>
+          <t>https://thenewsmill.com/2025/09/acharya-devvrat-sworn-in-as-governor-of-maharashtra-reads-oath-in-sanskrit/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://joindia.co.in/news/maharashtra-gets-new-governor-acharya-devvrat-takes-charge-as-the-22nd-governor/</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-assembly-election-2025-cm-nitish-eyes-the-lost-seats-of-paswan-and-kushwaha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/garware-youth-development-centre-satara-skill-training-helps-13-rural-youths-get-jobs-rds-00-5385521/</t>
+          <t>https://www.amarujala.com/video/india-news/tejashwi-yadav-bihar-adhikar-yatra-tejashwi-yadav-afraid-of-rahul-gandhi-bihar-election-2025-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178604/</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-patna-high-court-strict-on-ai-video-made-on-pm-modi-s-mother-nda-gave-this-reply-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-gifts-namo-gardens-to-394-towns-on-pm-modis-75th-birthday-rs-394-crore-sanctioned/articleshow/123964170.cms</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-rahul-gandhi-and-tejashwi-yadav-lalu-yadav-decide-on-seat-sharing-within-mahagathbandhan-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://curlytales.com/india/trending/what-are-namo-gardens-heres-all-about-eknath-shindes-green-gift-on-pm-modis-birthday/</t>
+          <t>https://www.amarujala.com/video/india-news/chief-minister-bhagwant-mann-launched-mission-chadti-kala-for-flood-victims-in-punjab-made-this-appeal-to-t-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
+          <t>https://www.amarujala.com/video/india-news/disha-patni-house-firing-case-the-accused-of-firing-at-disha-patni-s-house-were-killed-adg-told-the-whole-st-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://www.amarujala.com/video/india-news/gorakhpur-student-murder-case-encounter-in-gorakhpur-student-murder-case-akhilesh-furious-at-the-government-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-77106/</t>
+          <t>https://www.msn.com/mr-in/news/other/abp-majha-top-10-headlines-abp-%E0%A4%AE-%E0%A4%9D-%E0%A4%9F-%E0%A4%AA-10-%E0%A4%B9%E0%A5%87%E0%A4%A1%E0%A4%B2-%E0%A4%88%E0%A4%A8%E0%A5%8D%E0%A4%B8-22-%E0%A4%B8%E0%A4%AA%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%82%E0%A4%AC%E0%A4%B0-2025-%E0%A4%B8-%E0%A4%AE%E0%A4%B5-%E0%A4%B0/ar-AA1N3QmU</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjE0NDY=/kdmc-told-to-file-economic-crime-case-over-65-unauthorized-buildings</t>
+          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3635550-metro-rail-lines-promise-to-ease-mumbais-traffic-woes</t>
+          <t>https://marathi.ndtv.com/india/maharashtra-politics-live-update-mumbai-rain-first-bullet-train-between-mumbai-and-ahmedabad-9310619</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/mf/analysis/amfi-reshuffle-poonawalla-fincorp-gillette-india-among-6-smallcap-stocks-that-may-get-midcap-status/poonawalla-fincorp/slideshow/123940051.cms</t>
+          <t>https://indiagroundreport.com/mumbai-acharya-devvrat-took-additional-charge-as-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-71735/</t>
+          <t>https://www.thehindu.com/news/national/karnataka/bk-singh-to-head-sit-formed-to-probe-aland-voter-fraud-case/article70074360.ece</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-prakash-ambedkar-criticizes-modi-foreign-policy-us-tariff-russia-manipur-statement-135925944.html</t>
+          <t>https://www.thehindu.com/news/national/congress-doing-negative-politics-over-great-nicobar-project-environment-minister/article70067325.ece</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/ministerial-status-given-to-chairman-of-parashuram-economic-development-corporation-284301/amp/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%82%E0%A4%B8-%E0%A4%AC%E0%A4%A4-%E0%A4%B0-%E0%A4%B9-%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%89%E0%A4%AC-%E0%A4%A0-%E0%A4%B2-%E0%A4%9C-%E0%A4%A8-%E0%A4%9A-%E0%A4%86%E0%A4%A0%E0%A4%B5%E0%A4%A3-%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%AB-%E0%A4%B5-%E0%A4%A7%E0%A5%87%E0%A4%AF%E0%A4%95-%E0%A4%B5%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A1-%E0%A4%B5%E0%A4%9A%E0%A4%B2%E0%A4%82/ar-AA1CdNPz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/press-release/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/2938489</t>
+          <t>https://www.hindustantimes.com/india-news/didnt-do-so-for-power-but-ajit-pawar-on-why-he-split-with-sharad-pawar-101758292291397.html</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/technology/3629546-nato-boosts-eastern-european-defense-with-eastern-sentry?amp</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/articleshow/123993653.cms</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/maharashtra-orders-aadhaar-e-kyc-for-womens-welfare-scheme-beneficiaries-a525/</t>
+          <t>https://english.varthabharati.in/india/rahul-gandhis-vote-theft-charges-baseless-says-shinde</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
+          <t>https://marathi.timesnownews.com/maharashtra/explainer-a-test-of-mahayuti-in-bmc-elections-shiv-sena-bjp-tug-of-war-over-91-seats-article-152842707</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/photos/ladki-bahin-yojana-ekyc-kashi-karaychi-rule-change-by-maharashtra-government-documents-application-process-deadline-ifnormation-every-details-you-need-to-know/940522</t>
+          <t>https://www.dainikprabhat.com/rs-20-crores-of-funds-were-received-without-any-mla-shinde-faction-leaders-statement-increases-mahayutis-problems/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-aditi-tatkare-important-explanation-about-ladki-bahin-yojana/articleshow/123977249.cms</t>
+          <t>https://dainikekmat.com/ministerial-status-to-the-chairman-of-parashuram-corporation/117448/</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
+          <t>https://dainikekmat.com/attorney-general-birendra-saraf-resigns/117476/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
+          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/thane-metro-lines-4-and-4a-trial-run-revolutionizing-travel-in-mumbai-metropolitan-region/124060623</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/acharya-devvrat-takes-additional-charge-as-maharashtra-governor-101757923599184-amp.html</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother/</t>
+          <t>https://mahasamvad.in/179580/</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/trial-of-metro-4-in-thane-begins-in-the-presence-of-chief-minister-devendra-fadnavis-local18-1485682.html</t>
+          <t>https://metrorailtoday.com/news/mmrda-commences-trial-test-run-on-mumbai-metro-line-4</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/bjp-leader-nitin-paygude-and-mns-leader-ranji-dhage-join-shiv-sena-shinde-group/articleshow/123998704.cms</t>
+          <t>https://mahasamvad.in/178444/</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/thane-thane-metro-stations-the-35-km-long-metro-will-make-the-journey-of-thane-residents-easier-thane-news-1385989</t>
+          <t>https://www.tarunmitra.in/state/maharashtra/maharashtra-governments-unique-initiative-plan-to-build-namo-park-on/article-105368</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://vsrsnews.in/pimpri-chinchwad/pune-acharya-devvrat-becomes-the-new-governor-of-maharashtra/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/how-can-blood-cricket-flow-together-uddhav-thackeray-opposes-india-pak-match-protests-to-target-pm-modi/articleshow/123878115.cms</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/thane-metro-4-and-4a-span-35-km-with-32-stations-trial-run-inspected-by-devendra-fadnavis-and-eknath-shinde-full-details-in-marathi-article-152872624</t>
+          <t>https://www.newsonair.gov.in/union-minister-piyush-goyal-launches-swasth-nari-sashakt-parivar-campaign-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/uttarakhand/uttarakhand-govt-to-buy-produce-from-apple-growers-in-disaster-hit-dharali/article70076273.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/opposition-targets-shiv-sena-over-mumbais-gb-hway-traffic-ahead-of-civic-polls/articleshow/124020437.cms</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
+          <t>https://thenewsmill.com/2025/09/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/maharashtra-government-vehicle-policy-revised-2025-ntc-rptc-2336368-2025-09-18</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/kumbh-mela-committee-accommodates-representatives-of-bjps-mahayuti-allies-ncp-shiv-sena/articleshow/124020480.cms</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/argument-between-congress-mp-gaikwad-and-bjp-member-kamboj-over-sra-projects/869161/</t>
+          <t>https://www.msn.com/en-in/news/India/bmc-polls-an-acid-test-for-shiv-sena-ubt-says-thackeray/ar-AA1MRllW</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://lalluram.com/eknath-shinde-x-account-hack-hacker-puts-pakistan-and-turkey-flags-on-home-page/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-workers-burn-effigy-of-shiv-sena-ubt-mp-sanjay-raut-for-his-remark-about-anand-dighe/articleshow/123981706.cms</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/the-mahagathbandhan-leaders-openly-support-corruption-high-court-rebukes-them/</t>
+          <t>https://www.newsband.in/article_detail/replicas-diversity-mark-devi-durgeshwari-fest-in-thane</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/sudhir-mungantiwar_16.html</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/deputy-chief-minister-eknath-shindes-announcement-on-the-occasion-of-prime-minister-narendra-modis-birthday/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/bjps-criticism-of-sanjay-raut/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
+          <t>https://timesofindia.indiatimes.com/india/cant-be-on-whims-delhi-hc-raps-centre-over-delay-in-kejriwal-house-allotment-calls-for-clear-policy/articleshow/123976159.cms</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/ahmednagar-railway-station-government-of-maharashtra/</t>
+          <t>https://www.devdiscourse.com/article/politics/3630507-political-shocker-the-shooting-of-charlie-kirk-sparks-nationwide-debate?amp</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278581344/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education</t>
+          <t>https://www.newsband.in/article_detail/thane-metro-line-4-train-run-conducted-successfully</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-marathwada-four-people-died-150-people-were-trapped-in-floods-in-dharashiv/924053/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/iti-students-will-run-cleanliness-campaign-in-750-villages-special-campaign-by-minister-mangal-prabhat-lodha-on-pm-modis-birthday/articleshow/123915570.cms</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://royalbulletin.in/desh-pradesh/madhya-pradesh/mp-cm-mohan-yadav-gst-2-0-shopping-bhopal/article-108502</t>
+          <t>https://www.msn.com/mr-in/news/other/maharashtra-fort-%E0%A4%A6%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%B0-%E0%A4%9C-%E0%A4%B0-%E0%A4%AF%E0%A4%97%E0%A4%A1-%E0%A4%B8%E0%A4%B9-12-%E0%A4%B6-%E0%A4%B5%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%A8%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%95-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9C-%E0%A4%97%E0%A4%A4-%E0%A4%95-%E0%A4%B5-%E0%A4%B0%E0%A4%B8-%E0%A4%AF-%E0%A4%A6-%E0%A4%A4/ar-AA1IsmDX?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/how-the-bjp-alliance-won-maharashtra-101757921779535.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/parashuram-economic-development-corporation-chairman-ministerial-status-to-ashish-damle-thane-news-1384578</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/acharya-devvrat-sworn-in-as-governor-of-maharashtra-reads-oath-in-sanskrit/</t>
+          <t>https://www.hindisaamana.com/the-state-has-a-debt-of-rs-9-lakh-crores-development-of-the-state-is-stalled-deva-bhau-is-busy-in-advertising/</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-assembly-election-2025-cm-nitish-eyes-the-lost-seats-of-paswan-and-kushwaha-2025-09-18</t>
+          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/tejashwi-yadav-bihar-adhikar-yatra-tejashwi-yadav-afraid-of-rahul-gandhi-bihar-election-2025-2025-09-17</t>
+          <t>https://lokmanthan.com/arrangements-should-be-made-to-issue-all-relevant-permits-for-industries-in-a-single-application-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-rahul-gandhi-and-tejashwi-yadav-lalu-yadav-decide-on-seat-sharing-within-mahagathbandhan-2025-09-18</t>
+          <t>https://hindi.gyanhigyan.com/auto/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A5%87%E0%A4%B2%E0%A4%B5%E0%A5%87-%E0%A4%AA%E0%A4%B0%E0%A4%BF%E0%A4%AF%E0%A5%8B%E0%A4%9C%E0%A4%A8%E0%A4%BE%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-21000-%E0%A4%95%E0%A4%B0%E0%A5%8B%E0%A4%A1%E0%A4%BC-%E0%A4%B0%E0%A5%81%E0%A4%AA%E0%A4%AF%E0%A5%87-%E0%A4%95%E0%A4%BE/cid17430694.htm</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-patna-high-court-strict-on-ai-video-made-on-pm-modi-s-mother-nda-gave-this-reply-2025-09-18</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/jarange-plans-national-maratha-convention-in-delhi-hake-warns-of-obc-march-to-mumbai/articleshow/123952548.cms</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/chief-minister-bhagwant-mann-launched-mission-chadti-kala-for-flood-victims-in-punjab-made-this-appeal-to-t-2025-09-17</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maratha-quota-activist-manoj-jarange-patil-announce-chalo-delhi-program-after-mumbai-reservation-protest-know-all/articleshow/123982783.cms</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/disha-patni-house-firing-case-the-accused-of-firing-at-disha-patni-s-house-were-killed-adg-told-the-whole-st-2025-09-18</t>
+          <t>https://sundayguardianlive.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-139969/</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%9A-%E0%A4%9C-%E0%A4%97-%E0%A4%B5-%E0%A4%9F%E0%A4%AA-%E0%A4%9A-%E0%A4%85%E0%A4%82%E0%A4%A4-%E0%A4%AE-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%86%E0%A4%9C-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%B8%E0%A4%B9-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%A4-%E0%A4%A6-%E0%A4%96%E0%A4%B2-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9%E0%A4%82%E0%A4%B8-%E0%A4%AC%E0%A4%A4-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95/ar-AA1sw9JT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/transporters-cite-increased-costs-supply-disruptions-want-new-traffic-curbs-lifted/articleshow/124005110.cms</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sanjay-kadam-%E0%A4%95-%E0%A4%95%E0%A4%A3-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A7%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%AF-%E0%A4%97%E0%A5%87%E0%A4%B6-%E0%A4%95%E0%A4%A6%E0%A4%AE-%E0%A4%82%E0%A4%A8-%E0%A4%AD-%E0%A4%A1%E0%A4%A3-%E0%A4%B0-%E0%A4%B0-%E0%A4%AE%E0%A4%A6-%E0%A4%B8-%E0%A4%AD-%E0%A4%88%E0%A4%82%E0%A4%9A-%E0%A4%B0-%E0%A4%88%E0%A4%9F-%E0%A4%B9%E0%A4%81%E0%A4%A1-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AA%E0%A4%B0%E0%A4%A4%E0%A4%A3-%E0%A4%B0/ar-AA1B8BOh?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://news.abplive.com/cities/eknath-shinde-s-x-account-hacked-images-of-pakistan-turkiye-s-flags-posted-1801504</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/acharya-devvrat-is-the-new-governor-of-maharashtra-took-oath-in-the-presence-of-the-chief-minister.amp.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-prime-minister-narendra-modi-birthday-chhagan-bhujbal-obc-reservation-rain-alert-wednesday-17-september-2025-1494134.html</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-monsoon-2025-rain-update-maharashtra-rain-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shinde-9/923517/</t>
+          <t>https://marathi.abplive.com/news/mumbai/sanjay-raut-statement-on-anand-dighe-thane-balasaheb-thackeray-photo-advertise-shivsena-maharashtra-marathi-news-1385015</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/abp-majha-top-10-headlines-abp-%E0%A4%AE-%E0%A4%9D-%E0%A4%9F-%E0%A4%AA-10-%E0%A4%B9%E0%A5%87%E0%A4%A1%E0%A4%B2-%E0%A4%88%E0%A4%A8%E0%A5%8D%E0%A4%B8-22-%E0%A4%B8%E0%A4%AA%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%82%E0%A4%AC%E0%A4%B0-2025-%E0%A4%B8-%E0%A4%AE%E0%A4%B5-%E0%A4%B0/ar-AA1N3QmU</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/violence-escalates-in-maratha-obc-reservation-dispute-obc-leader-s-car-set-on-fire-in-jalna-125092300009_1.html</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/india-news/bihar-assembly-election-amit-shah-meets-bjp-workers-gives-60-days-plan-ahead-of-poll/articleshow/123995857.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>https://marathi.ndtv.com/india/maharashtra-politics-live-update-mumbai-rain-first-bullet-train-between-mumbai-and-ahmedabad-9310619</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/-2025--1188879</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/breaking-news-headlines-today-19-september-2025-dainik-bhaskar-hindi-news-live-1188572</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>https://indiagroundreport.com/mumbai-acharya-devvrat-took-additional-charge-as-governor-of-maharashtra/</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>https://deshonnati.com/maharashtra-governor-acharya-devvrat-took-the-oath/</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>https://dainikekmat.com/ministerial-status-to-the-chairman-of-parashuram-corporation/117448/</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>https://www.timemaharashtra.com/maharashtra/maharashtra-governor-acharya-devvrat-takes-oath-as-governor-of-maharashtra/132473/</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/national/karnataka/bk-singh-to-head-sit-formed-to-probe-aland-voter-fraud-case/article70074360.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/national/congress-doing-negative-politics-over-great-nicobar-project-environment-minister/article70067325.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/india-news/didnt-do-so-for-power-but-ajit-pawar-on-why-he-split-with-sharad-pawar-101758292291397.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/articleshow/123993653.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>https://nagalandpost.com/bmc-polls-50-50-seats-for-sena-ubt-mns-in-mumbai-strongholds/</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%A0-%E0%A4%85%E0%A4%AA%E0%A4%A1%E0%A5%87%E0%A4%9F-23-%E0%A4%91%E0%A4%95%E0%A5%8D%E0%A4%9F-%E0%A4%AC%E0%A4%B0%E0%A4%B2-%E0%A4%A8-%E0%A4%B2%E0%A5%87%E0%A4%B6-%E0%A4%B0-%E0%A4%A3%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1sBlG7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/shinde-said-the-mahayuti-will-hoist-the-saffron-flag-in-the-municipal-corporations-125092200027_1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>https://marathi.timesnownews.com/maharashtra/explainer-a-test-of-mahayuti-in-bmc-elections-shiv-sena-bjp-tug-of-war-over-91-seats-article-152842707</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/thane-metro-lines-4-and-4a-trial-run-revolutionizing-travel-in-mumbai-metropolitan-region/124060623</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>https://www.bignewsnetwork.com/news/278593014/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/179580/</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>https://thecsrjournal.in/thane-metro-trial-run-hindi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/city/nagpur/nagpur-news-seeem-kee-maujoodagee-mein-mahaajenako-aur-enemaaradeee-ke-beech-hua-anubandh-1187831</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178444/</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/others/mahayutis-saffron-flag-will-fly-in-mumbai-municipal-corporation-and-other-municipal-bodies-eknath-shinde-4278209</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/mou-signed-between-mahagenco-and-nmrda-in-the-presence-of-the-chief-minister/</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>https://politicalmaharashtra.in/state-level-technical-committee-approves-indrayani-river-improvement-project-mla-mahesh-landages-pursuit-is-successful-97855/</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>https://www.sakshipost.com/news/metro-line-connecting-thane-mumbai-be-operational-2026-end-says-cm-fadnavis-455400</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>https://thefocusindia.com/maharashtra-news/bhujbal-retorts-pawar-did-not-attend-all-party-meeting-reservation-284529/amp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>https://www.newsonair.gov.in/union-minister-piyush-goyal-launches-swasth-nari-sashakt-parivar-campaign-in-mumbai/</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/opposition-targets-shiv-sena-over-mumbais-gb-hway-traffic-ahead-of-civic-polls/articleshow/124020437.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/how-can-blood-cricket-flow-together-uddhav-thackeray-opposes-india-pak-match-protests-to-target-pm-modi/articleshow/123878115.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/politics/3630214-chalo-jeete-hain-bjp-launches-film-tour-across-bihar?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/kumbh-mela-committee-accommodates-representatives-of-bjps-mahayuti-allies-ncp-shiv-sena/articleshow/124020480.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-workers-burn-effigy-of-shiv-sena-ubt-mp-sanjay-raut-for-his-remark-about-anand-dighe/articleshow/123981706.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>https://www.newsband.in/article_detail/replicas-diversity-mark-devi-durgeshwari-fest-in-thane</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>https://www.newsdrum.in/national/shiv-sena-workers-protest-against-rauts-remark-about-dighe-10476846</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/mumba-devi-vidhan-sabha-chunav-result-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%B8-%E0%A4%9F-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%A8-%E0%A4%AE-%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%AC-%E0%A4%9C-%E0%A4%AF%E0%A4%B9-%E0%A4%82-%E0%A4%AA%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%A4-%E0%A4%9C-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C%E0%A5%81%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A4%B0-%E0%A4%85%E0%A4%AA%E0%A4%A1%E0%A5%87%E0%A4%9F/ar-AA1uBciC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-polls-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%B5-%E0%A4%A8%E0%A4%96%E0%A5%87%E0%A4%A1%E0%A4%BC%E0%A5%87-%E0%A4%AB-%E0%A4%B0-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%82-mumbai-%E0%A4%95-%E0%A4%87%E0%A4%B8-%E0%A4%B8-%E0%A4%9F-%E0%A4%B8%E0%A5%87-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%85%E0%A4%9F%E0%A4%95%E0%A4%B2%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%9F-%E0%A4%95%E0%A4%9F/ar-AA1spTNA?cvid=BC85FE97FDE740EB8B309A7E01FCE3DD&amp;ocid=hpmsn&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-politics-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A5%82%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%B2-%E0%A4%A6%E0%A5%81%E0%A4%B8%E0%A4%B0-%E0%A4%A7%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%B9-%E0%A4%AA%E0%A4%B0-%E0%A4%AD%E0%A5%82%E0%A4%A4-%E0%A4%A4-%E0%A4%A8-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%AA%E0%A5%81%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%89%E0%A4%B0%E0%A4%B2%E0%A5%87/ar-AA1N2FuN</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>https://tamil.getlokalapp.com/maharashtra-news/metro-project-in-thane-raut-s-allegations-shinde-s-response-15458855</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/maharashtra-politics-former-mla-sada-saravankar-claims-to-be-getting-rs-20-crore-even-without-being-an-mla/923568/amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-gst-rate-is-establishment-of-a-superpower-in-the-country/</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/sudhir-mungantiwar_16.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/bjps-criticism-of-sanjay-raut/</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/india/cant-be-on-whims-delhi-hc-raps-centre-over-delay-in-kejriwal-house-allotment-calls-for-clear-policy/articleshow/123976159.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>https://www.newsband.in/article_detail/thane-metro-line-4-train-run-conducted-successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/iti-students-will-run-cleanliness-campaign-in-750-villages-special-campaign-by-minister-mangal-prabhat-lodha-on-pm-modis-birthday/articleshow/123915570.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA%E0%A4%B0%E0%A4%B6%E0%A5%81%E0%A4%B0-%E0%A4%AE-%E0%A4%86%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%95-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A4%B9-%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B3-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B2-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%9A-%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%A0-%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B2-%E0%A4%86%E0%A4%A3%E0%A4%96-%E0%A4%8F%E0%A4%95-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6/ar-AA1ME5Po</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>https://www.hindisaamana.com/the-state-has-a-debt-of-rs-9-lakh-crores-development-of-the-state-is-stalled-deva-bhau-is-busy-in-advertising/</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>https://www.khabarwala24.com/national/mumbai-mahapalika-sahit-anya-nagarpalikaon-mein-mahayuti-ka-bhagwa-jhanda-lahraega-eknath-shinde/104161/</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>https://lokmanthan.com/arrangements-should-be-made-to-issue-all-relevant-permits-for-industries-in-a-single-application-chief-minister-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/ncpap-hints-at-fighting-independently-in-the-upcoming-local-body-elections-in-maharashtra/article70073542.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>https://indianexpress.com/article/cities/mumbai/acharya-devvrat-oath-maharashtra-governor-10250775/</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/transporters-cite-increased-costs-supply-disruptions-want-new-traffic-curbs-lifted/articleshow/124005110.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/trial-runs-on-metro-4s-cadbury-junction-gaimukh-stretch-to-commence-monday-mumbai-metropolitan-region-development-authority-officials-say-corridor-on-track-for-year-end-operations/articleshow/124001171.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/22/indias-longest-elevated-metro-corridor-in-mumbai-information-from-chief-minister-devendra-fadnavis.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/mumbai/ahilyabai-holkar-honoured-as-ahmednagar-railway-station-renamed-as-ahilyanagar-by-maharashtra-government-mumbai-print-news-rds-00-5376825/</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>https://politicalmaharashtra.in/obc-vs-maratha-a-split-in-the-alliance-over-reservations-97877/</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/mumbai/sanjay-raut-statement-on-anand-dighe-thane-balasaheb-thackeray-photo-advertise-shivsena-maharashtra-marathi-news-1385015</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/violence-escalates-in-maratha-obc-reservation-dispute-obc-leader-s-car-set-on-fire-in-jalna-125092300009_1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
         <is>
           <t>https://timesofindia.indiatimes.com/city/mumbai/thane-metro-4-4a-corridor-improves-transportation-reduce-congestion-on-gb-road-and-connectivity-in-thane-and-mumbai/articleshow/124029480.cms</t>
         </is>

--- a/Output/Eknath Shinde/extracted_links_Eknath Shinde_failed_links.xlsx
+++ b/Output/Eknath Shinde/extracted_links_Eknath Shinde_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A408"/>
+  <dimension ref="A1:A359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,63 +438,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/maharashtra-deputy-cm-eknath-shinde-takes-action-against-builders-of-65-illegal-buildings-in-kalyan-dombivli/articleshow/124011193.cms</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/eknath-shindes-x-account-hacked-congress-raises-alarm-over-cyber-security/article70077295.ece</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/maharashtra-deputy-cm-eknath-shindes-x-account-hacked/</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/maharashtra-deputy-cm-eknath-shinde-takes-action-against-builders-of-65-illegal-buildings-in-kalyan-dombivli/articleshow/124011193.cms</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/thane-metro-4a-trial-run-on-monday-check-station-list-and-other-key-details/ar-AA1MWzkH</t>
+          <t>https://www.tribuneindia.com/news/india/maharashtra-deputy-cm-eknath-shindes-x-account-hacked/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/eknath-shinde-maharashtra-deputy-cm-x-account-hacked-hackers-post-pakistan-turkey-flags-hacking-sparks-uproar-2025-09-21-1009219</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
+          <t>https://www.indiatvnews.com/maharashtra/eknath-shinde-maharashtra-deputy-cm-x-account-hacked-hackers-post-pakistan-turkey-flags-hacking-sparks-uproar-2025-09-21-1009219</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-gifts-modi-394-namo-udyans-101758050819661.html</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked/2934860</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/when-i-go-to-villages-i-feel-fresh-my-opponents-get-depressed-says-dy-cm-eknath-shinde-at-launch-of-gram-samruddhi-yojana/articleshow/123964878.cms</t>
+          <t>https://www.indiatoday.in/india/story/eknath-shinde-x-handle-hacked-briefly-photos-of-pakistan-turkey-flags-posted-2790861-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/paint-thrown-at-bust-of-uddhav-thackerays-late-mother-sena-workers-angry-probe-on-101758106562970.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/when-i-go-to-villages-i-feel-fresh-my-opponents-get-depressed-says-dy-cm-eknath-shinde-at-launch-of-gram-samruddhi-yojana/articleshow/123964878.cms</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/news/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-145995/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
         </is>
       </c>
     </row>
@@ -529,455 +529,455 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/gst-rate-cut-will-boost-economy-shield-india-from-us-tariff-hikes-says-maharashtras-deputy-chief-minister-eknath-shinde/articleshow/124002613.cms</t>
+          <t>https://www.heraldgoa.in/globe-nation/kunal-kamra-summoned-again-over-derogatory-remarks-about-eknath-shinde-political-debate-intensifies/11957/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ahead-of-bmc-polls-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena/2921488</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/gst-rate-cut-will-boost-economy-shield-india-from-us-tariff-hikes-says-maharashtras-deputy-chief-minister-eknath-shinde/articleshow/124002613.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/stories-detail/national/maharashtra-dy-cm-eknath-shindes-x-account-hacked/2934860/0</t>
+          <t>https://www.ptinews.com/story/national/ahead-of-bmc-polls-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena/2921488</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked-hackers-post-pakistan-turkey-flags-2962608.html</t>
+          <t>https://www.hindustantimes.com/india-news/paint-thrown-at-bust-of-uddhav-thackerays-late-mother-sena-workers-angry-probe-on-101758106562970.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/find-the-masterminds-behind-the-kdmc-illegal-buildings-scam-shinde-101758309996962.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/hc-seeks-govt-s-stand-on-illegal-stay-on-demolition-by-dy-cm-101758137116362.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
+          <t>https://www.newsband.in/article_detail/awhad-slams-the-states-selective-compassion-over-demolition-notices</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/allies-in-conflict-bjp-shinde-sena-lock-horns-on-dahisar-toll-shift</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/most-of-rs-46000cr-projects-for-marathwada-announced-by-shinde-led-cabinet-in-2023-still-on-paper/articleshow/123907066.cms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother20250916212035</t>
+          <t>https://www.ptinews.com/story/national/shiv-sena-publishes-full-page-ads-in-dailies-on-pms-birthday-shinde-hails-his-new-india-push/2923561</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/full-page-newspaper-ads-and-slew-of-initiatives-shiv-sena-goes-all-out-to-celebrate-pms-birthday/2925344</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bombay-hc-can-plea-against-shinde-order-be-a-pil/articleshow/124022877.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shiv-sena-publishes-full-page-ads-in-dailies-on-pms-birthday-shinde-hails-his-new-india-push/2923561</t>
+          <t>https://realty.economictimes.indiatimes.com/news/industry/strict-action-ordered-against-65-illegal-buildings-in-kalyan-dombivli-by-deputy-chief-minister-eknath-shinde/124008652</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Dy-CM-Shinde-s-X-account-hacked;-Cong-leader-questions-cyber-security/2935531</t>
+          <t>https://www.aninews.in/news/national/general-news/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi20250917174418</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bombay-hc-can-plea-against-shinde-order-be-a-pil/articleshow/124022877.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/find-the-masterminds-behind-the-kdmc-illegal-buildings-scam-shinde-101758309996962.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/awhad-slams-the-states-selective-compassion-over-demolition-notices</t>
+          <t>https://www.aninews.in/news/national/politics/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother20250916212035</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maharashtra--all-files-to-be-vetted-by-shinde-before-being-sent-to-cm-fadnavis/2429371</t>
+          <t>https://www.newsband.in/article_detail/allies-in-conflict-bjp-shinde-sena-lock-horns-on-dahisar-toll-shift</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/video/news/pm-modi-adopts-nation-first-policy-eknath-shinde-slams-congress-over-remarks-on-pm-s-mother-2025-09-17-1008597</t>
+          <t>https://www.heraldgoa.in/globe-nation/kunal-kamra-stands-by-his-right-to-freedom-of-speech-amid-backlash-over-remarks-on-eknath-shinde/11949/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/industry/strict-action-ordered-against-65-illegal-buildings-in-kalyan-dombivli-by-deputy-chief-minister-eknath-shinde/124008652</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-gifts-modi-394-namo-udyans-101758050819661.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/most-of-rs-46000cr-projects-for-marathwada-announced-by-shinde-led-cabinet-in-2023-still-on-paper/articleshow/123907066.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/hc-to-shinde-by-what-authority-did-you-stay-navi-mumbai-civic-bodys-notice-to-raze-illegal-buildings/articleshow/123952725.cms</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://zeenews.india.com/india/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked-hackers-post-pakistan-turkey-flags-2962608.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/dy-cm-shindes-x-account-hacked-cong-leader-questions-cyber-security/2935531</t>
+          <t>https://www.indiatvnews.com/video/news/pm-modi-adopts-nation-first-policy-eknath-shinde-slams-congress-over-remarks-on-pm-s-mother-2025-09-17-1008597</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/acharya-devvrat-takes-oath-as-maharashtra-governor-101757915941969.html</t>
+          <t>https://www.ptinews.com/editor-detail/full-page-newspaper-ads-and-slew-of-initiatives--shiv-sena-goes-all-out-to-celebrate-pm-s-birthday/2925344</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/goa/sculptor-of-shivajis-statue-held/13663/</t>
+          <t>https://www.ptinews.com/story/national/dy-cm-shindes-x-account-hacked-cong-leader-questions-cyber-security/2935531</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.babushahi.com/full-news.php?id=211084&amp;headline=GST-cuts-implemented-from-today,-Eknath-Shinde-says-GST-reforms-a-</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-police-restrict-heavy-truck-movement-for-eighteen-hours-daily-to-ease-traffic-congestion/articleshow/123927129.cms</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://timesofindia.indiatimes.com/india/not-an-mla-but-get-rs-20-cr-in-funds-sena-leader-sarvankar-boasts-later-clarifies/articleshow/124028510.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/heavy-vehicles-banned-on-thane-s-ghodbunder-road-during-daytime/2919586</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-polls-an-acid-test-for-shiv-sena-ubt-says-thackeray-101758222779307.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/19/wrg4-mh-villages-shinde.html</t>
+          <t>https://www.ptinews.com/editor-detail/heavy-vehicles-banned-on-thane-s-ghodbunder-road-during-daytime/2919586</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/maharashtra-launches-namo-gardens-and-tourism-skill-programme-to-mark-pm-modis-75th-birthday/</t>
+          <t>https://www.heraldgoa.in/globe-nation/fadnavis-meeting-with-thackeray-sparks-speculation-of-alliance/9016/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/mmrda-temporarily-suspends-monorail-services-in-mumbai20250920092952</t>
+          <t>https://www.ptinews.com/editor-detail/prioritise-development-in-14-villages-added-to-navi-mumbai-civic-limits--dy-cm-shinde/2930925</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-mmrda-to-suspend-monorail-services-on-september-20-in-mumbai20250917100119/</t>
+          <t>https://www.newsonair.gov.in/maharashtra-launches-namo-gardens-and-tourism-skill-programme-to-mark-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ahead-of-bmc-elections-eknath-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena-23594416</t>
+          <t>https://www.aninews.in/news/national/general-news/mmrda-temporarily-suspends-monorail-services-in-mumbai20250920092952</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-cong-leader-questions-cyber-security-23595093</t>
+          <t>https://www.mumbailive.com/en/politics/government-will-pay-inr-200-crores-owed-to-shiv-bhojan-thali-kendra-operators-90025</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-charges-baseless-says-ekanth-shinde-23594783</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ahead-of-bmc-elections-eknath-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena-23594416</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde-23595190</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-cong-leader-questions-cyber-security-23595093</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-charges-baseless-says-ekanth-shinde-23594783</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/eknath-shinde-account-hacked-during-india-pakistan-asia-cup-cybercrime-cybersecurity-national-flags-of-turkey-and-pakistan-restored-in-45-minutes-75975/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde-23595190</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/thane-shiv-sena-workers-protest-against-sanjay-raut-s-remark-about-anand-dighe-23594679</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-cm-devendra-fadnavis-claims-bjp-gave-up-on-mayor-s-post-in-2017-on-the-request-of-uddhav-s-aide-107382/2</t>
+          <t>https://www.socialnews.xyz/2025/09/15/mumbai-acharya-devvrat-sworn-in-as-maharashtra-governor-gallery/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/india/maharashtra-dy-cm-eknath-shindes-x-account-hacked-07712660</t>
+          <t>https://www.sakshipost.com/news/shiv-senaubt-continues-attacking-dy-cm-shinde-says-maha-govt-boastful-454108</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263?about-us-breakingnews</t>
+          <t>https://thenewsmill.com/2025/09/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/agency-news/devendra-fadnavis-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane-7123779.html</t>
+          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://thehindustangazette.com/election/eknath-shinde-x-account-hacked-pak-turkey-flags-39959</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/parshuram-economic-development-corporation-chairman-ashish-damle-to-get-ministerial-status-says-maharashtra-govt-23594308</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/namo-gardens-to-be-developed-in-394-municipal-councils-and-nagar-panchayats-in-maharashtra-23594437</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/deputy-cm-eknath-shinde-x-account-hack-pakistan-turkey-flag-shown-3016093</t>
+          <t>https://www.newsdrum.in/national/on-eve-of-pms-birthday-shinde-announces-scheme-to-develop-namo-parks-in-maharashtra-10471206</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-slams-incapable-ministers-after-ajit-pawar-for-ignoring-party-expansion-and-administrative-work/articleshow/124050348.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/parshuram-economic-development-corporation-chairman-ashish-damle-to-get-ministerial-status-says-maharashtra-govt-23594308</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flags-9649355.html</t>
+          <t>https://thehindustangazette.com/election/eknath-shinde-x-account-hacked-pak-turkey-flags-39959</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/sanjay-raut-comments-about-eknath-shinde-mentor-anand-dighe-sparked-an-uproar-201758252385682.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-21-news-updates-live-updates-weather-update-mumbai-monsoon-18331429</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/eknath-shinde-x-account-hacked-pakistan-turkey-flag-posted-ntc-rptc-2338322-2025-09-21</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-slams-incapable-ministers-after-ajit-pawar-for-ignoring-party-expansion-and-administrative-work/articleshow/124050348.cms</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/DNHindi/photos/%E0%A4%B8%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8%E0%A4%BE%E0%A4%A5-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A4%BE-x-%E0%A4%85%E0%A4%95%E0%A4%BE%E0%A4%89%E0%A4%82%E0%A4%9F-%E0%A4%B9%E0%A5%88%E0%A4%95-%E0%A4%B9%E0%A5%88%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B2%E0%A4%97%E0%A4%BE%E0%A4%88-%E0%A4%AA%E0%A4%BE%E0%A4%95%E0%A4%BF%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A4%BE%E0%A4%A8-%E0%A4%A4%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9D%E0%A4%82%E0%A4%A1%E0%A5%87eknathsi/1251272843711787/</t>
+          <t>https://www.abplive.com/states/maharashtra/deputy-cm-eknath-shinde-x-account-hack-pakistan-turkey-flag-shown-3016093</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://hindi.newsbytesapp.com/news/india/eknath-shinde-s-ex-account-hacked-hackers-posted-flags-of-pakistan-and-turkiye/story</t>
+          <t>https://thecsrjournal.in/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hindi/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-strict-against-builders-involved-in-kalyan-dombivali-illegal-buildings-constructing-3015585</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flags-9649355.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/deputy-cm-eknath-shinde-x-account-hacked-hackers-posted-images-of-pakistan-and-turkey-flags/articleshow/124025137.cms</t>
+          <t>https://www.facebook.com/DNHindi/photos/%E0%A4%B8%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8%E0%A4%BE%E0%A4%A5-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A4%BE-x-%E0%A4%85%E0%A4%95%E0%A4%BE%E0%A4%89%E0%A4%82%E0%A4%9F-%E0%A4%B9%E0%A5%88%E0%A4%95-%E0%A4%B9%E0%A5%88%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B2%E0%A4%97%E0%A4%BE%E0%A4%88-%E0%A4%AA%E0%A4%BE%E0%A4%95%E0%A4%BF%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A4%BE%E0%A4%A8-%E0%A4%A4%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9D%E0%A4%82%E0%A4%A1%E0%A5%87eknathsi/1251272843711787/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/ganesh-naik-vs-eknath-shinde-in-navi-mumbai-tussle-over-janata-darbar-petition-filed-in-high-court/articleshow/123996455.cms</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-deputy-cm-eknath-shinde-s-twitter-account-hacked-raises-cybersecurity-concerns-201758454098732.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-claims-mahayuti-saffron-flag-will-fly-in-bmc-and-all-maharashtra-local-body-elections/articleshow/124032659.cms</t>
+          <t>https://hindi.newsbytesapp.com/news/india/eknath-shinde-s-ex-account-hacked-hackers-posted-flags-of-pakistan-and-turkiye/story</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/eknath-shindes-x-account-hacked-pictures-of-islamic-countries-and-turkish-flags-posted-11708</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-claims-mahayuti-saffron-flag-will-fly-in-bmc-and-all-maharashtra-local-body-elections/articleshow/124032659.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/sanjay-raut-said-eknath-shinde-mentality-is-very-low-level-there-is-nothing-left-to-talk-about-2025-09-20-1163910</t>
+          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-strict-against-builders-involved-in-kalyan-dombivali-illegal-buildings-constructing-3015585</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-deputy-cm-eknath-shinde-x-handle-hacked-hackers-shared-posts-with-pakistan-and-turkey-flags-2025-09-21-1164034</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/deputy-cm-eknath-shinde-x-account-hacked-hackers-posted-images-of-pakistan-and-turkey-flags/articleshow/124025137.cms</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/maharashtra/eknath-shinde-x-account-hacked-pakistani-flags-posted-125092100012_1.html</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/ganesh-naik-vs-eknath-shinde-in-navi-mumbai-tussle-over-janata-darbar-petition-filed-in-high-court/articleshow/123996455.cms</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-uddhav-thackeray-puts-bold-conditions-for-rebels-nagar-sevak-for-ghar-wapsi-for-shinde-shiv-sena-ahead-of-bmc-polls-know-all/articleshow/123978190.cms</t>
+          <t>https://www.livehindustan.com/national/sanjay-raut-comments-about-eknath-shinde-mentor-anand-dighe-sparked-an-uproar-201758252385682.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/shiv-sena-mla-sada-sarvankar-met-maharashtra-navnirman-sena-president-raj-thackeray-3016893</t>
+          <t>https://www.indiatv.in/maharashtra/sanjay-raut-said-eknath-shinde-mentality-is-very-low-level-there-is-nothing-left-to-talk-about-2025-09-20-1163910</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/pm-modi-birthday-congress-declares-pm-modi-s-birthday-as-black-day-enraged-eknath-shinde-issues-warning-2025-09-17</t>
+          <t>https://hindi.webdunia.com/maharashtra/eknath-shinde-x-account-hacked-pakistani-flags-posted-125092100012_1.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
+          <t>https://www.indiatv.in/maharashtra/maharashtra-deputy-cm-eknath-shinde-x-handle-hacked-hackers-shared-posts-with-pakistan-and-turkey-flags-2025-09-21-1164034</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-deputy-cm-eknath-shinde-s-twitter-account-hacked-raises-cybersecurity-concerns-201758454098732.html</t>
+          <t>https://www.amarujala.com/video/india-news/pm-modi-birthday-congress-declares-pm-modi-s-birthday-as-black-day-enraged-eknath-shinde-issues-warning-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%A7-%E0%A4%B0%E0%A5%87-%E0%A4%A7-%E0%A4%B0%E0%A5%87-bjp-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%B2-%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%B8%E0%A4%A6-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%B0-%E0%A4%89%E0%A4%A4-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A4%AE%E0%A4%B2/ar-AA1MX3h5</t>
+          <t>https://www.abplive.com/states/maharashtra/shiv-sena-mla-sada-sarvankar-met-maharashtra-navnirman-sena-president-raj-thackeray-3016893</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-namo-park-scheme-for-pm-narendra-modi-75th-birthday-deputy-cm-eknath-shinde-announcement-3014117</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/eknath-shindes-x-account-hacked-pictures-of-islamic-countries-and-turkish-flags-posted-11708</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-deputy-chief-minister-ekanth-shinde-says-rahul-gandhi-s-vote-theft-charges-baseless-2025-09-19</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/eknath-shinde-takes-action-against-kalyan-dombivli-illegal-buildings-builders/articleshow/124011899.cms</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-deputy-chief-minister-ekanth-shinde-says-rahul-gandhi-s-vote-theft-charges-baseless-2025-09-19</t>
         </is>
       </c>
     </row>
@@ -998,35 +998,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/kedar-dighes-sharp-attack-on-shinde-faction-anand-dighe-remembered-as-elections-approach/articleshow/124004160.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-uddhav-thackeray-puts-bold-conditions-for-rebels-nagar-sevak-for-ghar-wapsi-for-shinde-shiv-sena-ahead-of-bmc-polls-know-all/articleshow/123978190.cms</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/thane/ghodbunder-residents-will-be-freed-from-traffic-jams-orders-to-leave-heavy-vehicles-after-12-midnight-eknath-shinde-orders-1384427</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-namo-park-scheme-for-pm-narendra-modi-75th-birthday-deputy-cm-eknath-shinde-announcement-3014117</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/thane-metro-trial-run-on-september-22-thane-residents-dream-to-come-true/articleshow/124004146.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/eknath-shinde-takes-action-against-kalyan-dombivli-illegal-buildings-builders/articleshow/124011899.cms</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/pratap-sarnaik-comments-on-uddhav-thackeray-sanjay-raut-praises-eknath-shinde-respect-senior-leaders-3016095</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.navodayatimes.in/news/national/maharashtra-deputy-cm-eknath-shinde-ex-handle-hacked/276116/</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/thane-metro-trial-run-on-september-22-thane-residents-dream-to-come-true/articleshow/124004146.cms</t>
         </is>
       </c>
     </row>
@@ -1040,2245 +1040,1902 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/short-videos/congress-mp-praniti-shinde-criticizes-eknath-shinde/939828</t>
+          <t>https://www.msn.com/hi-in/news/other/maharashtra-diwali-bonus-bmc-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%9A-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%AC-%E0%A4%A8%E0%A4%B8-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8-%E0%A4%86%E0%A4%9A-%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%B9-%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1sk1rp?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eknath-shinde-news-rahul-gandhi-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%86%E0%A4%AF-%E0%A4%97-%E0%A4%B5%E0%A4%B0-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-marathi-news/vi-AA1MOsp4</t>
+          <t>https://zeenews.india.com/marathi/short-videos/congress-mp-praniti-shinde-criticizes-eknath-shinde/939828</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/sanjay-raut-says-eknath-shinde-who-is-there-today-is-because-of-rajan-vichare-sacrifice-marathi-news-update-1385178</t>
+          <t>https://marathi.abplive.com/news/thane/ghodbunder-residents-will-be-freed-from-traffic-jams-orders-to-leave-heavy-vehicles-after-12-midnight-eknath-shinde-orders-1384427</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178645/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178497/</t>
+          <t>https://www.bakharlive.com/maharashtra/deputy-chief-minister-eknath-shinde-announces-to-set-up-namo-parks-in-394-cities-of-the-state/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/under-what-authority-were-the-municipal-corporation-notice-to-demolish-buildings-stopped-high-court-ask-on-eknath-shinde-whether-the-dcm-has-the-authority-to-make-that-decision-1384909</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-decision-mandatory-to-construct-administrative-buildings-of-municipal-councils-according-to-the-model-plan-1482062.html</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179440/</t>
+          <t>https://mahasamvad.in/178790/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/shiv-sena-workers-protest-against-rauts-remarks-about-dighe/870443/</t>
+          <t>https://marathi.abplive.com/news/politics/the-high-court-has-questioned-eknath-shinde-over-the-suspension-of-action-against-illegal-construction-in-navi-mumbai-1384988</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179586/</t>
+          <t>https://marathi.ndtv.com/maharashtra/thane-ghodbunder-news-good-news-for-thane-kalyan-badlapur-commuters-as-eknath-shinde-orders-restriction-of-heavy-vehicles-untill-midnight-9291074</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-decision-mandatory-to-construct-administrative-buildings-of-municipal-councils-according-to-the-model-plan-1482062.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/deputy-chief-minister-eknath-shinde-reaction-to-prime-minister-narendra-modi-s-gst-cut-ladki-bahin-yojana-news-1385846</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticized-eknath-shinde-for-washing-rajan-vichares-feet-and-taking-a-pilgrimage/923077/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/deputy-chief-minister-eknath-shinde-insistently-served-the-australian-guests-vadapav-a-signature-food-of-mumbai/922213/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/the-high-court-has-questioned-eknath-shinde-over-the-suspension-of-action-against-illegal-construction-in-navi-mumbai-1384988</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/changes-in-gst-rates-will-lead-to-the-ghatsthapna-of-superpower-in-country-eknath-shinde-96248</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178790/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/shivsena-ubt-sanjay-raut-talk-about-eknath-shinde-rajan-vichare-entry-in-party-1495859.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shindes-ex-account-hacked-96111</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/changes-in-gst-rates-will-lead-to-the-ghatsthapna-of-superpower-in-country-eknath-shinde-96248</t>
+          <t>https://www.lokmatnews.in/business/mukhyamantri-mazi-ladki-bahin-yojana-no-e-kyc-no-rs-1500-all-beneficiaries-can-avail-facility-visiting-web-portal-b507/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shindes-ex-account-hacked-96111</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-deputy-chief-minister-eknath-shinde-launches-the-seva-fortnight-chief-minister-samruddhi-panchayat-raj-abhiyan-in-thane-district/922593/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/business/mukhyamantri-mazi-ladki-bahin-yojana-no-e-kyc-no-rs-1500-all-beneficiaries-can-avail-facility-visiting-web-portal-b507/</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-shinde-first-reaction-on-meenatai-thackeray-dadar-statue-issue-he-will-not-be-released-i-have-spoken-to-the-police-commissioner-1384826</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/deputy-chief-minister-eknath-shinde-insistently-served-the-australian-guests-vadapav-a-signature-food-of-mumbai/922213/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/shiv-sena-leader-eknath-shinde-slams-incapable-ministers-for-ignoring-party-expansion-and-administrative-work/articleshow/124045917.cms</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178863/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-municipal-elections-eknath-shinde-puts-shiv-sena-in-action-mode-with-direct-orders-to-corporators-sharad-pawar-also-eyes-victory-in-corporations-1384728</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/thane-ghodbunder-news-good-news-for-thane-kalyan-badlapur-commuters-as-eknath-shinde-orders-restriction-of-heavy-vehicles-untill-midnight-9291074</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/shiv-sena-corporaters-news-eknath-shinde-on-uddhav-thackeray-mumbai-bmc-election-2025/921652/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-many-office-bearers-of-uddhav-thackeray-group-join-shiv-sena-95696</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-deputy-chief-minister-eknath-shinde-launches-the-seva-fortnight-chief-minister-samruddhi-panchayat-raj-abhiyan-in-thane-district/922593/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-many-office-bearers-of-uddhav-thackeray-group-join-shiv-sena-95696</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-review-maharashtra-and-mumbai-rain-updates-orders-airlift-beed-ashti-villagers-1480338.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/shiv-sena-corporaters-news-eknath-shinde-on-uddhav-thackeray-mumbai-bmc-election-2025/921652/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-ajit-pawar-and-eknath-shinde-reprimand-maharashtra-cabinet-over-performance-and-neglect-of-party-organization-1386101</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-district-administration-should-remain-alert-in-wake-of-heavy-rains-eknath-shinde-instructs-94887</t>
+          <t>https://marathi.ndtv.com/cities/cm-fadnavis-change-eknath-shindes-decision-to-ban-heavy-vehicles-from-morning-6-to-12-night-to-solve-traffic-congestion-9316039</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/eknath-shinde-first-reaction-on-meenatai-thackeray-dadar-statue-issue-he-will-not-be-released-i-have-spoken-to-the-police-commissioner-1384826</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-response-after-sanjay-raut-objected-to-placing-anand-dighes-photo-next-to-balasaheb-thackeray/922799/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-review-maharashtra-and-mumbai-rain-updates-orders-airlift-beed-ashti-villagers-1480338.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-district-administration-should-remain-alert-in-wake-of-heavy-rains-eknath-shinde-instructs-94887</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/deputy-chief-minister-eknath-shinde-reaction-to-prime-minister-narendra-modi-s-gst-cut-ladki-bahin-yojana-news-1385846</t>
+          <t>https://marathi.ndtv.com/cities/now-there-is-only-one-type-plan-for-the-administrative-buildings-of-the-municipal-council-and-municipal-panchayats-eknath-shinde-9294836</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-feeds-australian-mp-tim-watts-mumbais-vada-pav/922339/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178828/</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-rain-heavy-rainfall-in-beed-40-villagers-should-be-airlifted-dcm-eknath-shinde-ordered-9279677</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-response-after-sanjay-raut-objected-to-placing-anand-dighes-photo-next-to-balasaheb-thackeray/922799/</t>
+          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/cm-fadnavis-change-eknath-shindes-decision-to-ban-heavy-vehicles-from-morning-6-to-12-night-to-solve-traffic-congestion-9316039</t>
+          <t>https://www.mymahanagar.com/maharashtra/mumbai-high-court-questioned-eknath-shinde-on-new-mumbai-illegal-construction-case/922756/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-get-set-back-bmc-scraps-12-crore-project-mumbai-1485014.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-big-announces-on-pm-modi-birthday-say-all-municipal-councils-will-be-established-namo-udyan-in-maharashtra-95314</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-municipal-elections-eknath-shinde-puts-shiv-sena-in-action-mode-with-direct-orders-to-corporators-sharad-pawar-also-eyes-victory-in-corporations-1384728</t>
+          <t>https://www.mymahanagar.com/maharashtra/deputy-cm-eknath-shinde-on-heavy-rains-and-alert-to-district-administration/921681/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/shiv-sena-leader-eknath-shinde-slams-incapable-ministers-for-ignoring-party-expansion-and-administrative-work/articleshow/124045917.cms</t>
+          <t>https://www.loksatta.com/thane/nevali-farmer-protesters-demand-eknath-shinde-to-revoke-cases-against-farmers-in-kalyan-thane-css-98-5381565/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-feeds-australian-mp-tim-watts-mumbais-vada-pav/922339/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-eknath-shinde-s-shiv-sena-in-action-mode-confident-of-mahayuti-victory-in-mumbai-civic-polls-directs-corporators-to-start-work-1384673</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-big-announces-on-pm-modi-birthday-say-all-municipal-councils-will-be-established-namo-udyan-in-maharashtra-95314</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-working-on-plan-b-for-bmc-election-likely-shock-to-uddhav-thackeray-and-bjp-also-1484790.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/now-there-is-only-one-type-plan-for-the-administrative-buildings-of-the-municipal-council-and-municipal-panchayats-eknath-shinde-9294836</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-ghodbandar-road-eknath-shinde-ghodbandar-residents-will-be-free-from-traffic-congestion/922259/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-ajit-pawar-and-eknath-shinde-reprimand-maharashtra-cabinet-over-performance-and-neglect-of-party-organization-1386101</t>
+          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-s-x-account-hacked-turkish-and-pakistani-videos-posted-account-recovered-after-team-x-complaint-1385633</t>
+          <t>https://www.saamana.com/wadigodri-crime-news-fake-cid-officers-stole-the-golden-ring/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/mumbai-high-court-questioned-eknath-shinde-on-new-mumbai-illegal-construction-case/922756/</t>
+          <t>https://www.mymahanagar.com/maharashtra/local-elections-mahayuti-will-win-in-the-local-self-government-elections-eknath-shinde-is-confident/922171/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shinde-fadnavis-cold-war-high-court-questions-maharashtra-government-s-legitimacy-amid-brand-battle-corruption-allegations-and-best-depot-controversy-1384960</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-for-suspending-demolition-of-societies-with-unauthorized-construction-in-vashi-area/922729/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-rain-heavy-rainfall-in-beed-40-villagers-should-be-airlifted-dcm-eknath-shinde-ordered-9279677</t>
+          <t>https://www.mymahanagar.com/maharashtra/dcm-eknath-shinde-criticized-rahul-gandhi-evm-vote-chori-case/922837/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-stated-that-the-change-in-gst-rates-will-lead-to-the-establishment-of-a-superpower-in-the-country-from-tomorrow/923694/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-solve-bmtc-employee-problem-gave-10-lakh-for-compensation-1484524.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/deputy-cm-eknath-shinde-on-heavy-rains-and-alert-to-district-administration/921681/</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-says-anand-dighe-never-sold-shiv-sena/923100/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/parshuram-economic-development-corporation-chairman-ashish-damle-gets-ministerial-status-in-thane-maharashtra-news-mhs25091603365</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/mns-leader-avinash-jadhav-slams-eknath-shinde-over-thane-traffic-issue/articleshow/123926772.cms</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-ghodbandar-road-eknath-shinde-ghodbandar-residents-will-be-free-from-traffic-congestion/922259/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-palghar-dahanu-shivsena-thackeray-group-office-bearers-from-palghar-dahanu-join-shivsena/922966/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sushma-andhare-%E0%A4%A1%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%9F-%E0%A4%B6-%E0%A4%B5%E0%A4%B8%E0%A5%87%E0%A4%A8%E0%A5%87%E0%A4%9A%E0%A5%87-%E0%A4%96%E0%A4%B0%E0%A5%87-%E0%A4%B0%E0%A5%81%E0%A4%AA-%E0%A4%86%E0%A4%9C-%E0%A4%AC-%E0%A4%B9%E0%A5%87%E0%A4%B0-%E0%A4%86%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A5%81%E0%A4%B7%E0%A4%AE-%E0%A4%85%E0%A4%82%E0%A4%A7-%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%9A-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%98%E0%A4%A3-%E0%A4%98-%E0%A4%A4/ar-AA1HY5L7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mymahanagar.com/mahamumbai/withdrew-the-rs-2-5-crore-fund-given-for-sewage-plant-and-drainage-because-former-corporator-deepmala-badhe-belonged-to-the-thackeray-group/922264/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-for-suspending-demolition-of-societies-with-unauthorized-construction-in-vashi-area/922729/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/pm-narendra-modi-birthday-sharad-pawar-ajit-pawar-and-eknath-shinde-wish-a-happy-birthday-95367</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-working-on-plan-b-for-bmc-election-likely-shock-to-uddhav-thackeray-and-bjp-also-1484790.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-shiv-sena-mla-sanjay-gaikwads-controversial-statement-sanjay-gaikwad-claims-that-local-level-elections-cost-rs-3-crores-and-100-goats-have-to-be-slaughtered/923585/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/withdrew-the-rs-2-5-crore-fund-given-for-sewage-plant-and-drainage-because-former-corporator-deepmala-badhe-belonged-to-the-thackeray-group/922264/</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/mns-leader-avinash-jadhav-slams-eknath-shinde-over-thane-traffic-issue/articleshow/123926772.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-chairs-shiv-sena-meeting-in-mumbai-strategizes-for-upcoming-elections-and-mumbai-municipal-corporation-polls-sanjay-nirupam-reacts-1384153</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/if-you-come-to-power-we-will-show-the-power-of-jai-maharashtra-sanjay-raut-warning-to-eknath-shinde-maharashtra-news-mhs25092001682</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-politics-deputy-cm-eknath-shinde-refutes-evm-allegations-confident-of-mahayuti-victory-in-mumbai-civic-polls-on-development-work-1385031</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/dcm-eknath-shinde-criticized-rahul-gandhi-evm-vote-chori-case/922837/</t>
+          <t>https://maharashtratimes.com/india-news/bihar-assembly-election-amit-shah-meets-bjp-workers-gives-60-days-plan-ahead-of-poll/articleshow/123995857.cms</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-says-anand-dighe-never-sold-shiv-sena/923100/</t>
+          <t>https://marathi.ndtv.com/videos/after-ajit-pawar-eknath-shinde-will-also-hold-a-road-show-in-nagpur-shinde-s-mission-vidarbha-997770</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/vasaivirar/eknath-shinde-to-survey-massive-traffic-congestion-on-mumbai-ahmedabad-national-highway-rds-00-5385650/</t>
+          <t>https://marathi.ndtv.com/videos/thane-is-up-for-sale-sanjay-raut-hits-out-at-shinde-fadnavis-997973</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/local-elections-mahayuti-will-win-in-the-local-self-government-elections-eknath-shinde-is-confident/922171/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-20-september-2025-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-palghar-dahanu-shivsena-thackeray-group-office-bearers-from-palghar-dahanu-join-shivsena/922966/</t>
+          <t>https://marathi.abplive.com/news/thane/thane-tembhi-naka-devi-festival-shiv-sena-eknath-shinde-vs-rajan-vichare-dispute-anand-dighe-marathi-news-1386015</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/news/navi-mumbai-munciple-corporation-news-dcm-eknath-shinde-directed-the-commissioner-to-give-immediate-priority-to-water-supply-roads-health-facilities-and-schools-in-14-villages-local18-1483762.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/uddhav-thackeray-and-raj-thackeray-election-strategy-in-the-home-ground-of-eknath-shinde-shrikant-shinde/940495</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/wadigodri-crime-news-fake-cid-officers-stole-the-golden-ring/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-thackeray-vs-shinde-balasaheb-thackeray-s-legacy-shiv-sena-leadership-and-call-for-eknath-shinde-s-introspection-on-maharashtra-politics-1385211</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-solve-bmtc-employee-problem-gave-10-lakh-for-compensation-1484524.html</t>
+          <t>https://www.kisantak.in/politics/story/eknath-shinde-took-a-swipe-at-his-opponents-says-they-feel-depressed-by-farming-1279260-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-announced-strict-action-will-be-taken-against-those-who-cheated-residents-of-65-buildings-in-kalyan-dombivali-1483839.html</t>
+          <t>https://www.thejbt.com/india/maharashtra-deputy-cm-eknath-shinde-s-x-account-hacked-hackers-posted-flags-of-pakistan-and-t%C3%BCrkiye-news-295659</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-politics-deputy-cm-eknath-shindes-twitter-account-hacked-1497198.html</t>
+          <t>https://ahilyawani.com/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-posts-with-pakistan-and-turkey-flags-spark-uproar-account-recovered-police-investigating/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/pm-narendra-modi-birthday-sharad-pawar-ajit-pawar-and-eknath-shinde-wish-a-happy-birthday-95367</t>
+          <t>https://www.hindisaamana.com/the-mahagathbandhan-leaders-openly-support-corruption-high-court-rebukes-them/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-shiv-sena-mla-sanjay-gaikwads-controversial-statement-sanjay-gaikwad-claims-that-local-level-elections-cost-rs-3-crores-and-100-goats-have-to-be-slaughtered/923585/</t>
+          <t>https://www.tarunmitra.in/state/maharashtra/maharashtra-deputy-cm-shindes-x-account-hack-account-posted-pictures/article-105819</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/after-ajit-pawar-eknath-shinde-will-also-hold-a-road-show-in-nagpur-shinde-s-mission-vidarbha-997770</t>
+          <t>https://www.marathiebatmya.com/political/dy-cm-eknath-shinde-visits-the-state-emergency-operations-center/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.mumbaitak.in/political-news/story/sanjay-raut-has-strongly-criticized-eknath-shinde-for-printing-photos-of-balasaheb-thackeray-and-anand-dighe-side-by-side-in-an-advertisement-wishing-pm-modi-a-happy-birthday-3202688-2025-09-18</t>
+          <t>https://vedantsamachar.in/x-account-hacked-deputy-chief-minister-eknath-shindes-x-account-hack/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
+          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-former-mla-claim-on-20-crore-make-political-stir-in-maharashtra-1484863.html</t>
+          <t>https://www.dainikprabhat.com/eknath-shindes-political-game-will-fail-this-leader-warns-of-being-dragged-directly-to-court/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/shiv-sena-and-bjp-stage-a-strong-show-of-strength-on-the-occasion-of-metro-trial-in-thane-cm-devendra-fadnavis-eknath-shinde-pratap-sarnaik/923787/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/shinde-made-the-announcement-on-modi-s-birthday-125091700051_1.html</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/thane-sporting-club-election-eknath-shinde-shiv-sena-won-over-bjp-mns-ubt-devendra-fadnavis-uddhav-thackeray-raj-thackeray-maharashtra-politics/articleshow/124041703.cms</t>
+          <t>https://www.newsband.in/article_detail/acharyadevvrattakes-oath-as-maharashtras-22nd-governor</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-chairs-shiv-sena-meeting-in-mumbai-strategizes-for-upcoming-elections-and-mumbai-municipal-corporation-polls-sanjay-nirupam-reacts-1384153</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-gifts-namo-gardens-to-394-towns-on-pm-modis-75th-birthday-rs-394-crore-sanctioned/articleshow/123964170.cms</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-politics-deputy-cm-eknath-shinde-refutes-evm-allegations-confident-of-mahayuti-victory-in-mumbai-civic-polls-on-development-work-1385031</t>
+          <t>https://thenewsmill.com/2025/09/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-20-september-2025-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-shiv-sena-leaders-speech-adds-fuel-to-accusations-of-biased-allocation-of-funds-23595109</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/dispute-between-both-shiv-sena-parties-over-printing-anand-dighe-photo-next-to-balasaheb/940602</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/heavy-vehicles-banned-on-thanes-ghodbunder-road-during-daytime-23594294</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/thane-is-up-for-sale-sanjay-raut-hits-out-at-shinde-fadnavis-997973</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/eknath-shinde-mla-aamshya-padvi-tribal-reservation-opposition-abuses-protest-dhangar-banjara-controversy-gs97</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/thane-ghodbunder-road-traffic-jaam-controversy-997251</t>
+          <t>https://www.jansatta.com/jansatta-special/jansatta-rajpaat-abhay-chautala-haryana-shinde-message-congress-du-election-bihar-seat-dispute-rld-up/4151302/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/india-news/bihar-assembly-election-amit-shah-meets-bjp-workers-gives-60-days-plan-ahead-of-poll/articleshow/123995857.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pm-modi-birthday-eknath-shinde-s-leader-of-the-world-tribute-article-in-loksatta-saamana-omits-ad-1384700</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-mumbai-rains-deputy-cm-eknath-shinde-reviews-flood-situation-40-50-people-trapped-in-asti-kateri-being-airlifted-from-nashik-ahilyanagar-1384293</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/uddhav-thackeray-led-shiv-sena-leader-ayodhya-poul-patil-received-call-from-eknath-shinde-office-call-recording-goes-viral/videoshow/123934054.cms</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flag-saamana-online-news/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-almatti-dam-height-increase-maharashtra-to-move-supreme-court-over-karnataka-s-decision-raising-flood-risk-for-sangli-kolhapur-shiv-sena-mobilizes-in-sambhaji-nagar-1384708</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-namo-gardens-project-eknath-shinde-announces-394-crore-funding-for-394-municipal-councils-on-pm-modi-s-birthday-includes-garden-competition-1384925</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-maharashtra-deputy-cms-ajit-pawar-and-eknath-shinde-express-anger-over-ministerial-inefficiency-neglect-of-party-work-and-janata-darbar-1386067</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/short-videos/eknath-shinde-accuses-uddhav-thackeray-covid-19-corruption</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-cabinet-discontent-bharat-gogawale-on-eknath-shinde-s-displeasure-ministerial-accountability-and-action-on-inefficient-ministers-1386103</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/acharyadevvrattakes-oath-as-maharashtras-22nd-governor</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-thane-navratri-deputy-cm-eknath-shinde-attends-devi-arrival-procession-at-tembhinaka-traditional-festivities-begin-1386020</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/shiv-senaubt-continues-attacking-dy-cm-shinde-says-maha-govt-boastful-454108</t>
+          <t>https://www.bignewsnetwork.com/news/278582902/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263?2012-mar-breakingnews</t>
+          <t>https://marathi.ndtv.com/videos/thane-ghodbunder-road-traffic-jaam-controversy-997251</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-shiv-sena-leaders-speech-adds-fuel-to-accusations-of-biased-allocation-of-funds-23595109</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-15-september-2025-zp-presidentship-reservation-nepal-violence-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/eknath-shindes-x-account-briefly-hacked-hackers-post-pics-of-pak-turkey-flags-9315607</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-govt-fadnavis-cabinet-approves-8-major-decisions-including-expressway-and-new-policies-nck90</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-strict-against-builders-involved-in-kalyan-dombivali-illegal-buildings-constructing-3015585/amp</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/mahayuti-government-reservation-issue-new-controversy-reason-sw79</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95-x-%E0%A4%85%E0%A4%95-%E0%A4%89%E0%A4%82%E0%A4%9F-%E0%A4%B9%E0%A5%88%E0%A4%95-%E0%A4%AA-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%A4%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%95%E0%A5%87-%E0%A4%9D%E0%A4%82%E0%A4%A1%E0%A5%87-%E0%A4%9C%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%85%E0%A4%9C-%E0%A4%AC-%E0%A4%AA-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%88-%E0%A4%9A-%E0%A4%82%E0%A4%A4/ar-AA1MZ2tG</t>
+          <t>https://www.patrika.com/en/state-news/thane-metro-begins-trial-run-after-20-year-wait-19966553</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/rahul-gandhi-s-vote-theft-charges-baseless-says-eknath-shinde-13559796.html</t>
+          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-15-september-2025-3482219.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/maharashtra-dy-cm-eknath-shinde-s--x--account-hacked/2934860</t>
+          <t>https://www.amarujala.com/video/india-news/pm-modi-s-75th-birthday-netanyahu-vladimir-putin-giorgia-meloni-extend-birthday-wishes-to-pm-modi-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/eknath-shinde-mla-aamshya-padvi-tribal-reservation-opposition-abuses-protest-dhangar-banjara-controversy-gs97</t>
+          <t>https://www.patrika.com/mumbai-news/thane-metro-dream-comes-true-after-20-year-new-lifelines-trial-run-begin-on-these-10-stations-19965341</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/09/22/deputy-chief-minister-eknath-shinde-took-stock-of-the-heavy-rainfall-in-marathwada//</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-eknath-shinde-issues-stern-warning-to-inefficient-maharashtra-cabinet-ministers-over-neglect-of-party-work-and-public-issues-1385985</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/uddhav-thackeray-led-shiv-sena-leader-ayodhya-poul-patil-received-call-from-eknath-shinde-office-call-recording-goes-viral/videoshow/123934054.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/shiv-sena-ubt-mns-bjp-raj-thackeray-uddhav-thackeray-devendra-fadnavis-unite-against-shiv-sena-eknath-shinde-for-thane-sporting-committee-election/articleshow/123938834.cms</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-pm-modi-birthday-eknath-shinde-s-leader-of-the-world-tribute-article-in-loksatta-saamana-omits-ad-1384700</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-cabinet-discontent-bharat-gogawale-on-eknath-shinde-s-displeasure-ministerial-accountability-and-action-on-inefficient-ministers-1386103</t>
+          <t>https://www.hindustantimes.com/india-news/statue-of-uddhav-thackeray-s-mother-defaced-in-mumbai-shiv-sena-ubt-protests-101758095171594.html</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-maharashtra-deputy-cms-ajit-pawar-and-eknath-shinde-express-anger-over-ministerial-inefficiency-neglect-of-party-work-and-janata-darbar-1386067</t>
+          <t>https://www.ndtv.com/video/ndtv-yuva-conclave-milind-deora-on-which-leader-connects-with-gen-z-better-996976</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-cm-shinde-s-stern-warning-to-inefficient-ministers-over-performance-neglect-of-party-work-and-public-issues-secret-meeting-held-1386025</t>
+          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-on-eknath-shinde-maharashtra-ahmedabad-bullet-train-anand-dighe-3015725</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-thane-navratri-deputy-cm-eknath-shinde-attends-devi-arrival-procession-at-tembhinaka-traditional-festivities-begin-1386020</t>
+          <t>https://www.amarujala.com/india-news/maharastra-paint-thrown-on-statue-of-meenatai-thackeray-at-mumbai-shivaji-park-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-ministers-warning-ajit-pawar-and-eknath-shinde-warn-mahayuti-ministers-over-poor-performance-hint-at-cabinet-reshuffle-before-local-elections-1386093</t>
+          <t>https://www.jansatta.com/national/current-mlas-get-rs-2-crore-and-i-get-rs-20-crore-big-claim-by-former-shiv-sena-mla-sada-sarvankar/4153263/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-15-september-2025-zp-presidentship-reservation-nepal-violence-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://hindi.theprint.in/india/shiv-sena-workers-protest-against-rauts-remarks-about-dighe/870443/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/eknath-shinde-took-a-swipe-at-his-opponents-says-they-feel-depressed-by-farming-1279260-2025-09-18</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/kedar-dighes-sharp-attack-on-shinde-faction-anand-dighe-remembered-as-elections-approach/articleshow/124004160.cms</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278582902/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi</t>
+          <t>https://www.abplive.com/states/maharashtra/shiv-sena-leader-ex-mla-sada-sarvankar-claims-20-crore-fund-dispute-sparks-political-stir-3016545</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/maharashtra-deputy-cm-eknath-shinde-s-x-account-hacked-hackers-posted-flags-of-pakistan-and-t%C3%BCrkiye-news-295659</t>
+          <t>https://hindi.theprint.in/india/meenatai-thackerays-statue-defaced-at-mumbais-shivaji-park/869722/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/jansatta-special/jansatta-rajpaat-abhay-chautala-haryana-shinde-message-congress-du-election-bihar-seat-dispute-rld-up/4151302/</t>
+          <t>https://hindi.theprint.in/india/despite-not-being-an-mla-i-received-a-fund-of-rs-20-crore-shiv-sena-leader-sarwankar/871651/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
+          <t>https://www.amarujala.com/india-news/uddhav-targets-bjp-over-india-pakistan-cricket-match-in-asia-cup-maharashtra-debt-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-almatti-dam-height-increase-maharashtra-to-move-supreme-court-over-karnataka-s-decision-raising-flood-risk-for-sangli-kolhapur-shiv-sena-mobilizes-in-sambhaji-nagar-1384708</t>
+          <t>https://www.lokmatnews.in/blog/india/bjp-shivsena-ncp-congress-local-body-elections-your-bow-and-arrow-but-target-is-ours-drawing-dividing-line-blog-amitabh-srivastava-b507/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.hindi.awazthevoice.in/india-news/maharashtra-deputy-chief-minister-eknath-shinde-s-x-account-hacked-68948.html</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/articleshow/123993653.cms</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/eknath-shindes-x-account-hacked-congress-leader-raises-questions-on-cyber-security-3261842.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/dy-cm-eknath-shinde-visits-the-state-emergency-operations-center/</t>
+          <t>https://www.heraldgoa.in/edit/invest-time-in-learning-about-the-world-we-live-in/5419/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/pm-modi-turns-75-highlights-of-initiatives-launched-by-bjp-events-held-in-several-states/articleshow/123949298.cms</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/shinde-wishes-prime-minister-modi-on-his-birthday-125091700049_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ajit-pawars-absence-at-key-guv-events-raises-eyebrows/articleshow/124030467.cms</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/shinde-reviewed-the-flood-situation-in-marathwada-125092200058_1.html</t>
+          <t>https://curlytales.com/india/ct-scoop/durga-puja-pandals-in-mumbai-where-you-can-spot-bollywood-celebrities/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-77106/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/meenatai-thackeray-statue-smeared-with-red-paint-1-held-101758136336233.html</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/hc-seeks-govt-s-stand-on-illegal-stay-on-demolition-by-dy-cm-101758137116362.html</t>
+          <t>https://www.heraldgoa.in/globe-nation/thackeray-brothers-hint-at-reunion-possible-political-realignment-in-maharashtra/16395/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/state-news/thane-metro-begins-trial-run-after-20-year-wait-19966553</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-secret-of-2-5-hour-meeting-at-shivtirth-how-raj-thackeray-prevail-over-uddhav-political-experts-reveal-9622593.html</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3629545-uddhav-thackeray-criticizes-indias-cricket-match-with-pakistan-questions-bjps-patriotism</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/mumbai-mina-thackeray-statue-defaced-shivaji-park-shiv-sena-protest-police-action-ntc-dskc-2335896-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-15-september-2025-3482219.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-told-party-workers-bmc-elections-are-a-litmus-test-for-us/articleshow/123989198.cms</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/thane-metro-dream-comes-true-after-20-year-new-lifelines-trial-run-begin-on-these-10-stations-19965341</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-3/921531/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-22-political-news-in-marathi-941153</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-sanjay-raut-supports-rahul-gandhi-saying-that-90-of-the-mahayuti-mlas-in-maharashtra-won-through-vote-theft/articleshow/124015667.cms</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-polls-an-acid-test-for-shiv-sena-ubt-says-thackeray-101758222779307.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/the-chronological-formation-and-political-evolution-of-maharashtra.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-21-september-2025-india-vs-pakistan-%E2%80%93-asia-cup-maharashtra-politics-national-international-live-update-in-marathi-940858</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/thane-metro-trial-run-hindi/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-17-september-2025-pm-narendra-modi-75th-birthday-zp-presidentship-reservation-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/shiv-sena-ubt-mns-bjp-raj-thackeray-uddhav-thackeray-devendra-fadnavis-unite-against-shiv-sena-eknath-shinde-for-thane-sporting-committee-election/articleshow/123938834.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-14-political-news-in-marathi-939050</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/new-jetty-construction-for-vasai-and-uttan-dongri-ro-ro-service-which-will-help-commuters/articleshow/123892530.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-17-political-news-in-marathi-939849</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/the-conflict-between-naik-and-shinde-reaches-its-peak-shinde-faction-files-suit-against-naik-in-the-high-court-over-the-janata-darbar/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/good-news-for-thane-residents-metro-trial-runs-will-take-place-on-monday-2758623.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/dadar-shivaji-park-meenatai-thackeray-statue-red-color-thrown-mumbai-crime/articleshow/123936431.cms</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/statue-of-uddhav-thackeray-s-mother-defaced-in-mumbai-shiv-sena-ubt-protests-101758095171594.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/ndtv-yuva-conclave-milind-deora-on-which-leader-connects-with-gen-z-better-996976</t>
+          <t>https://www.navarashtra.com/maharashtra/top-marathi-news-today-breaking-news-political-news-live-update-crime-news-994890.html</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/mla-warns-sanjay-raut-over-remarks-on-anand-dighe-shiv-sainiks-protest-in-kalyan-dombivli/articleshow/124011234.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-navratri-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-monday-22-september-2025-1497734.html</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-on-eknath-shinde-maharashtra-ahmedabad-bullet-train-anand-dighe-3015725</t>
+          <t>https://www.marathijagran.com/maharashtra/nashik/shardiya-navratri-2025-praveen-togadias-big-statement-at-hindu-hunkar-sabha-said-no-entry-for-muslims-at-garba-places-96201</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharastra-paint-thrown-on-statue-of-meenatai-thackeray-at-mumbai-shivaji-park-2025-09-17</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-tejashwi-yadav-calls-cm-nitish-a-cheat-minister-makes-these-big-promises-to-the-public-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/current-mlas-get-rs-2-crore-and-i-get-rs-20-crore-big-claim-by-former-shiv-sena-mla-sada-sarvankar/4153263/</t>
+          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-16-17-september-live-updates-tejashwi-yadav-bihar-adhikar-yatra-election-pm-modi-rahul-gandi-supreme-court-sahastradhara-flood-waqf/4143389/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/despite-not-being-an-mla-i-received-a-fund-of-rs-20-crore-shiv-sena-leader-sarwankar/871651/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/uddhav-targets-bjp-over-india-pakistan-cricket-match-in-asia-cup-maharashtra-debt-2025-09-16</t>
+          <t>https://www.mymahanagar.com/maharashtra/navi-mumbai-city-petition-filed-in-janata-darbar-against-minister-ganesh-naik-by-kishore-patkar/922934/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/blog/india/bjp-shivsena-ncp-congress-local-body-elections-your-bow-and-arrow-but-target-is-ours-drawing-dividing-line-blog-amitabh-srivastava-b507/</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/why-is-there-still-no-bjp-chief-minister-in-bihar-nitish-kumar-lalu-prasad-yadav-tejashwi-yadav-limited-grip-on-obc-voters-ebcs-mm76</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://hindi.financialexpress.com/india-news/ex-mla-sada-sarvankar-sparks-row-with-claim-of-receiving-20-crore-funds-10487968</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/thane-city-challenge-to-eknath-shinde-in-the-fort-itself-bjp-leader-ganesh-naiks-janata-darbar-for-the-third-consecutive-time/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/</t>
+          <t>https://www.marathi.hindusthanpost.com/social/administration-should-be-alert-for-relief-and-rescue-operations-in-the-wake-of-heavy-rains-dcm-eknath-shindes-advice/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.electronicsforyou.biz/industry-buzz/rrp-electronics-gets-land-for-semiconductor-fab-in-navi-mumbai/</t>
+          <t>https://dainikekmat.com/%E0%A4%86%E0%A4%AE%E0%A4%9A%E0%A5%80-%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A5%80-%E0%A4%B8%E0%A4%9C%E0%A5%8D%E0%A4%9C/117544/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630472-himachal-pradeshs-infrastructure-rebuild-a-race-against-time?amp</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
+          <t>https://m.thewire.in/article/politics/bhakti-for-modi-at-75-from-newspaper-ads-to-prayers-and-coordinated-social-media-posts</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-cabinet-meeting-maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-8-important-decisions-mumbai-maharashtra-news-mhs25091602614</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/09/16/2-lakh-new-employment-opportunities-in-the-state-investment-of-rs-50-thousand-crores-will-come/amp/</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/nanded-farmers-to-get-100-crop-loss-relief-553-crore-payout-begins-sep-22-minister/article70076412.ece</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar-3735776</t>
+          <t>https://www.ahmedabadmirror.com/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/81899457.html</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
+          <t>https://www.afternoonvoice.com/the-chronological-formation-and-political-evolution-of-maharashtra.html</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/pm-modi-turns-75-highlights-of-initiatives-launched-by-bjp-events-held-in-several-states/articleshow/123949298.cms</t>
+          <t>https://www.freepressjournal.in/education/study-abroad/canada-tightens-international-student-visa-rules-as-rejections-hit-record-highs</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ajit-pawars-absence-at-key-guv-events-raises-eyebrows/articleshow/124030467.cms</t>
+          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://curlytales.com/india/ct-scoop/durga-puja-pandals-in-mumbai-where-you-can-spot-bollywood-celebrities/</t>
+          <t>https://clarionindia.net/ahmednagar-railway-station-renamed-concern-over-erasure-of-muslim-legacy/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/education/latest-and-important-news-of-22nd-september-for-school-assembly-read-the-latest-updates-related-to-national-international-and-sports-2759750.html</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
+          <t>https://www.amarujala.com/india-news/vhp-s-hindu-only-diktat-for-garba-open-invitation-for-violence-ramdas-athawale-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-secret-of-2-5-hour-meeting-at-shivtirth-how-raj-thackeray-prevail-over-uddhav-political-experts-reveal-9622593.html</t>
+          <t>https://www.amarujala.com/india-news/modi-govt-gave-rs-21-000-cr-for-marathwada-rail-lines-rs-450-crore-came-during-upa-time-fadnavis-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-told-party-workers-bmc-elections-are-a-litmus-test-for-us/articleshow/123989198.cms</t>
+          <t>https://www.amarujala.com/india-news/cpwd-floats-tender-to-install-bulletproof-glass-in-chambers-of-eam-foreign-secy-at-jn-bhawan-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-22-political-news-in-marathi-941153</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-date-extended-supreme-court-give-new-deadline-31st-january-2026-know-all/articleshow/123920003.cms</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-sanjay-raut-supports-rahul-gandhi-saying-that-90-of-the-mahayuti-mlas-in-maharashtra-won-through-vote-theft/articleshow/124015667.cms</t>
+          <t>https://www.aajtak.in/programmes/mumbai-metro/video/mumbai-metro-ameet-satam-controversial-statement-bmc-election-frvd-2335000-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-3/921531/</t>
+          <t>https://mandalnews.com/amravati/government-should-take-decision-with-a-common-perspective-regarding-tet-for-teachers/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-21-september-2025-india-vs-pakistan-%E2%80%93-asia-cup-maharashtra-politics-national-international-live-update-in-marathi-940858</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-pichhade-varg-ke-sarakaaree-chhaatraavaas-ke-vidyaarthiyon-ke-dainik-bhatte-mein-vrddhi-ko-manjooree-1187663</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
+          <t>https://maharashtratimes.com/career/career-news/mahatet-exam-2025-mandatory-exam-confusion-for-senior-teachers-application-process-begins-from-15-september/articleshow/123893618.cms</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/sangli-protest-in-sangli-against-gopichand-padalkar-s-statement-participation-of-eminent-leaders-998015</t>
+          <t>https://navbharatlive.com/bihar/bihar-vidhansabha-chunav-2025-election-dates-announcement-soon-cec-gyanesh-kumar-visit-patna-1363416.html</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
+          <t>https://thebharatnow.in/national/ahmednagar-railway-station-renamed-now-it-will-be-known-as-ahilyanagar/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-17-september-2025-pm-narendra-modi-75th-birthday-zp-presidentship-reservation-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://hindi.latestly.com/india/education/latest-and-important-news-of-22nd-september-for-school-assembly-read-the-latest-updates-related-to-national-international-and-sports-2759750.html</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/jalna-gunratna-sadavarte-s-car-attacked-while-on-his-way-to-meet-protesters-997494</t>
+          <t>https://hindi.latestly.com/india/school-assembly-news-headlines-for-23-september-national-international-sports-big-updates-2760357.html</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-14-political-news-in-marathi-939050</t>
+          <t>https://joindia.co.in/news/maharashtra-gets-new-governor-acharya-devvrat-takes-charge-as-the-22nd-governor/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-17-political-news-in-marathi-939849</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/top-marathi-news-today-breaking-news-political-news-live-update-crime-news-994890.html</t>
+          <t>https://dainikekmat.com/attorney-general-birendra-saraf-resigns/117476/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/maharashtra-cm-devendra-fadnavis-talk-on-obc-reservation/articleshow/123889715.cms</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/breaking-news-today-21st-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-ahmedabad-bullet-train-mega-block-sunday/liveblog/124023319.cms</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/nashik/shardiya-navratri-2025-praveen-togadias-big-statement-at-hindu-hunkar-sabha-said-no-entry-for-muslims-at-garba-places-96201</t>
+          <t>https://navbharatlive.com/world/priyanka-gandhi-questions-centre-policy-on-palestine-issue-1363252.html</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-tejashwi-yadav-calls-cm-nitish-a-cheat-minister-makes-these-big-promises-to-the-public-2025-09-18</t>
+          <t>https://navbharatlive.com/india/mehbooba-mufti-letter-to-amit-shah-for-yasin-malik-humanitarian-appeal-1361078.html</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-16-17-september-live-updates-tejashwi-yadav-bihar-adhikar-yatra-election-pm-modi-rahul-gandi-supreme-court-sahastradhara-flood-waqf/4143389/</t>
+          <t>https://maharashtratimes.com/video/mt-originals/ghodbunder-residents-anger-eknath-shindes-big-decision-these-vehicles-are-not-allowed-in-thane/videoshow/123919177.cms</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/navi-mumbai-city-petition-filed-in-janata-darbar-against-minister-ganesh-naik-by-kishore-patkar/922934/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-municipal-election-2025-mns-district-chief-raju-dindorle-will-join-bjp-mm76-rg93</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/why-is-there-still-no-bjp-chief-minister-in-bihar-nitish-kumar-lalu-prasad-yadav-tejashwi-yadav-limited-grip-on-obc-voters-ebcs-mm76</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/eknath-shinde-shivsena-file-janhit-yachika-in-mumbai-high-court-against-ganesh-naik-janta-darbar-1496267.html</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-1384548</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane-politics-petition-against-minister-ganesh-naiks-janata-darbar/922848/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://yashbharat.co.in/maharashtra-deputy-cm-eknath-shindes-ex-handle-hacked-posts-with-pakistan-and-turkey-flags-spark-uproar/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/technical-panel-approves-2-stps-along-indrayani-cm/articleshow/124005440.cms</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/thane-city-challenge-to-eknath-shinde-in-the-fort-itself-bjp-leader-ganesh-naiks-janata-darbar-for-the-third-consecutive-time/</t>
+          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pimpri-news-shiv-sena-ready-for-elections-avoid-factionalism-get-to-work-shrirang-barnes-instructions-to-office-bearers/</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
+          <t>https://www.loksatta.com/maharashtra/garware-youth-development-centre-satara-skill-training-helps-13-rural-youths-get-jobs-rds-00-5385521/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
+          <t>https://www.thehindu.com/news/national/tamil-nadu/state-floats-tender-to-prepare-master-plan-for-a-global-city/article70062521.ece</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633962-scam-allegations-deepen-in-chhattisgarh-as-key-figures-arrested?amp</t>
+          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://clarionindia.net/ahmednagar-railway-station-renamed-concern-over-erasure-of-muslim-legacy/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/national-news/no-cap-on-prices-of-cars-for-guv-cm-and-judges-in-maharashtra-vehicle-policy-19954354</t>
+          <t>https://www.devdiscourse.com/article/politics/3630419-mla-ends-fast-nh-3-negligence-sparks-controversy-in-himachal?amp</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-date-extended-supreme-court-give-new-deadline-31st-january-2026-know-all/articleshow/123920003.cms</t>
+          <t>https://www.newsx.com/india/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-77106/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
+          <t>https://propnewstime.com/getdetailsStories/MjE0NDY=/kdmc-told-to-file-economic-crime-case-over-65-unauthorized-buildings</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/vhp-s-hindu-only-diktat-for-garba-open-invitation-for-violence-ramdas-athawale-2025-09-21</t>
+          <t>https://www.theaustraliatoday.com.au/tim-watts-explores-cultural-collaboration-and-youth-initiatives-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/cpwd-floats-tender-to-install-bulletproof-glass-in-chambers-of-eam-foreign-secy-at-jn-bhawan-2025-09-16</t>
+          <t>https://m.economictimes.com/news/mumbai-news/mmrda-temporarily-suspends-monorail-services-in-mumbai/articleshow/124009977.cms</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/government-should-take-decision-with-a-common-perspective-regarding-tet-for-teachers/</t>
+          <t>https://www.newsx.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-71735/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-pichhade-varg-ke-sarakaaree-chhaatraavaas-ke-vidyaarthiyon-ke-dainik-bhatte-mein-vrddhi-ko-manjooree-1187663</t>
+          <t>https://www.ptinews.com/press-release/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/2938489</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178810/</t>
+          <t>https://www.thehindu.com/news/national/karnataka/karnataka-proposes-law-to-fix-minimum-wage-work-hours-for-domestic-workers/article70074706.ece</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/will-maharashtra-local-body-elections-be-delayed-state-election-commission-files-application-in-supreme-court-a-a629/</t>
+          <t>https://navbharatlive.com/religion/aaj-ka-rashifal-19-september-2025-today-horoscope-insights-for-your-lucky-zodiac-sign-1359827.html</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/maharashtra-ladki-bahin-yojana-ekyc-mandatory-beneficiaries-207500</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://joindia.co.in/news/maharashtra-gets-new-governor-acharya-devvrat-takes-charge-as-the-22nd-governor/</t>
+          <t>https://www.punjabkesari.com/india-news/ladki-bahin-yojana-2/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/mumbai-metro/video/mumbai-metro-ameet-satam-controversial-statement-bmc-election-frvd-2335000-2025-09-17</t>
+          <t>https://zeenews.india.com/marathi/photos/ladki-bahin-yojana-ekyc-kashi-karaychi-rule-change-by-maharashtra-government-documents-application-process-deadline-ifnormation-every-details-you-need-to-know/940522</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/mumbai/new-rules-will-now-apply-to-administrative-buildings-of-municipal-councils-and-municipal-panchayats-eknath-shindes-decision/132833/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-aditi-tatkare-important-explanation-about-ladki-bahin-yojana/articleshow/123977249.cms</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-municipal-election-2025-mns-district-chief-raju-dindorle-will-join-bjp-mm76-rg93</t>
+          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/thane/thane-traffic-update-heavy-vehicles-entering-city-banned-from-6-am-to-12-midnight-ws-b-1482548.html</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/e-kyc-made-mandatory-for-beneficiaries-of-the-chief-ministers-majhi-laadki-behan-scheme-1360239.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-govt-fadnavis-cabinet-approves-8-major-decisions-including-expressway-and-new-policies-nck90</t>
+          <t>https://dainikmaval.com/majhi-ladki-bhaeen-yojana-documents-are-required-for-e-kyc-know-website-and-process/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/ladki-bahin-yojana-updates-more-than-124000-mahila-disqualified-form-government-scheme-article-152828023</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-1384548</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
+          <t>https://thenewsmill.com/2025/09/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/entertainment/tv/ok-tata-bye-bye-paytm-ceo-vijay-shekhar-sharma-deleted-his-post-on-ratan-tata-s-passing-after-facing-backlash/ar-AA1s2Nt7?ocid=hpdhp17&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-technical-inspection-of-metro-4-and-4-a-from-gaimukh-to-vijay-garden-107468</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/technical-panel-approves-2-stps-along-indrayani-cm/articleshow/124005440.cms</t>
+          <t>https://news18marathi.com/maharashtra/trial-of-metro-4-in-thane-begins-in-the-presence-of-chief-minister-devendra-fadnavis-local18-1485682.html</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/garware-youth-development-centre-satara-skill-training-helps-13-rural-youths-get-jobs-rds-00-5385521/</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/thane-gaimukh-to-wadala-metro-4-trial-today-read-its-route-and-other-details/articleshow/124037736.cms</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/45/?m=0</t>
+          <t>https://vsrsnews.in/pimpri-chinchwad/pune-acharya-devvrat-becomes-the-new-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178604/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/thane-metro-4-and-4a-span-35-km-with-32-stations-trial-run-inspected-by-devendra-fadnavis-and-eknath-shinde-full-details-in-marathi-article-152872624</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-gifts-namo-gardens-to-394-towns-on-pm-modis-75th-birthday-rs-394-crore-sanctioned/articleshow/123964170.cms</t>
+          <t>https://marathi.timesnownews.com/maharashtra/explainer-a-test-of-mahayuti-in-bmc-elections-shiv-sena-bjp-tug-of-war-over-91-seats-article-152842707</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
+          <t>https://www.thehindu.com/news/national/uttarakhand/uttarakhand-govt-to-buy-produce-from-apple-growers-in-disaster-hit-dharali/article70076273.ece</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/hc-to-shinde-by-what-authority-did-you-stay-navi-mumbai-civic-bodys-notice-to-raze-illegal-buildings/articleshow/123952725.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/bhubaneswar/odisha-sees-over-10-fold-increase-in-revenue-from-gutka-paan-masala-and-cigarette-sales/articleshow/124053527.cms</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-14-september-2025-asia-cup-cricket-hockey-pakistan-china-pm-modi-rain-alert-trump-israel-ukraine-russia-gaza-war-bjp-congress/liveblog/123877354.cms</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3630419-mla-ends-fast-nh-3-negligence-sparks-controversy-in-himachal?amp</t>
+          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjE0NDY=/kdmc-told-to-file-economic-crime-case-over-65-unauthorized-buildings</t>
+          <t>https://timesofindia.indiatimes.com/india/i-repeat-rahul-gandhis-weak-pm-jibe-after-trump-imposes-100000-fee-on-h-1b-visas-reshares-old-post/articleshow/124012869.cms</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/mumbai-news/mmrda-temporarily-suspends-monorail-services-in-mumbai/articleshow/124009977.cms</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/mf/analysis/amfi-reshuffle-poonawalla-fincorp-gillette-india-among-6-smallcap-stocks-that-may-get-midcap-status/poonawalla-fincorp/slideshow/123940051.cms</t>
+          <t>https://deshonnati.com/ahmednagar-railway-station-government-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-71735/</t>
+          <t>https://www.bignewsnetwork.com/news/278581344/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/karnataka/karnataka-proposes-law-to-fix-minimum-wage-work-hours-for-domestic-workers/article70074706.ece</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-marathwada-four-people-died-150-people-were-trapped-in-floods-in-dharashiv/924053/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://theblunttimes.in/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/51898/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/how-the-bjp-alliance-won-maharashtra-101757921779535.html</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maha-govt-ensures-transparency-in-ladki-bahin-yojana-asks-beneficiaries-to-complete-e-kyc-process-in-two-months-3735616</t>
+          <t>https://www.thehindu.com/news/national/kerala/kerala-minister-v-sivankutty-taken-to-hospital-after-experiencing-dizziness-in-assembly/article70068758.ece</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/maharashtra-ladki-bahin-yojana-ekyc-mandatory-beneficiaries-207500</t>
+          <t>https://www.thehindu.com/elections/bihar-assembly/prashant-kishor-has-raised-hundreds-of-crores-of-rupees-through-shell-companies-alleges-bihar-bjp/article70075218.ece</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.com/india-news/ladki-bahin-yojana-2/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/business/mukhyamantri-ladki-bahin-yojana-ekyc-compulsory-for-all-check-how-complete-this-process-1385224</t>
+          <t>https://thenewsmill.com/2025/09/acharya-devvrat-sworn-in-as-governor-of-maharashtra-reads-oath-in-sanskrit/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/photos/ladki-bahin-yojana-ekyc-kashi-karaychi-rule-change-by-maharashtra-government-documents-application-process-deadline-ifnormation-every-details-you-need-to-know/940522</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-assembly-election-2025-cm-nitish-eyes-the-lost-seats-of-paswan-and-kushwaha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
+          <t>https://www.amarujala.com/video/india-news/tejashwi-yadav-bihar-adhikar-yatra-tejashwi-yadav-afraid-of-rahul-gandhi-bihar-election-2025-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-majhi-ladki-bahin-yojana-ekyc-update-women-beneficiaries-last-date-135957916.html</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-rahul-gandhi-and-tejashwi-yadav-lalu-yadav-decide-on-seat-sharing-within-mahagathbandhan-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/ladki-bahin-e-kyc-otp-issues-maharashtra-women-scheme/41406</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-patna-hc-directs-congress-to-remove-ai-video-featuring-pm-modi-s-mother-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chhatrapati-sambhaji-nagar/ladki-bahin-yojana-84-thousand-beloved-sisters-who-are-receiving-two-or-more-benefits-from-the-same-family-will-be-ineligible-1384524</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-patna-high-court-strict-on-ai-video-made-on-pm-modi-s-mother-nda-gave-this-reply-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/weather/latest-news-maharashtra-rain-no-chances-monsoon-leave-in-maharashtra-till-september-30-read-in-detail-a-a993/</t>
+          <t>https://www.amarujala.com/video/india-news/chief-minister-bhagwant-mann-launched-mission-chadti-kala-for-flood-victims-in-punjab-made-this-appeal-to-t-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178873/</t>
+          <t>https://www.amarujala.com/video/india-news/disha-patni-house-firing-case-the-accused-of-firing-at-disha-patni-s-house-were-killed-adg-told-the-whole-st-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/photos/filmy/marathi-actress-swapnanchya-palikadle-serial-fame-gauri-nalawade-now-looking-glamorous-latest-photo-viral-on-social-media-a-a991/</t>
+          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/e-kyc-made-mandatory-for-beneficiaries-of-the-chief-ministers-majhi-laadki-behan-scheme-1360239.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/acharya-devvrat-is-the-new-governor-of-maharashtra-took-oath-in-the-presence-of-the-chief-minister.html</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/ladki-bahin-yojana-updates-more-than-124000-mahila-disqualified-form-government-scheme-article-152828023</t>
+          <t>https://dainikekmat.com/ministerial-status-to-the-chairman-of-parashuram-corporation/117448/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-breaking-news-live-in-marathi-21-september-2025-125092100006_1.html</t>
+          <t>https://www.thehindu.com/news/national/congress-doing-negative-politics-over-great-nicobar-project-environment-minister/article70067325.ece</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
+          <t>https://www.thehindu.com/news/national/karnataka/bk-singh-to-head-sit-formed-to-probe-aland-voter-fraud-case/article70074360.ece</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother/</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-technical-inspection-of-metro-4-and-4-a-from-gaimukh-to-vijay-garden-107468</t>
+          <t>https://www.esakal.com/satara/patan-taluka-tourism-development-projects-mini-train-adventure-activities-infrastructure-shambhuraj-desai-bam92</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/trial-of-metro-4-in-thane-begins-in-the-presence-of-chief-minister-devendra-fadnavis-local18-1485682.html</t>
+          <t>https://www.freepressjournal.in/mumbai/pm-narendra-modi-a-strong-national-leader-maha-cm-devendra-fadnavis-wishes-pm-modi-on-his-75th-bday-hails-his-vision-to-reshape-indias-fortune</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/thane-gaimukh-to-wadala-metro-4-trial-today-read-its-route-and-other-details/articleshow/124037736.cms</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://vsrsnews.in/pimpri-chinchwad/pune-acharya-devvrat-becomes-the-new-governor-of-maharashtra/</t>
+          <t>https://metrorailtoday.com/news/mmrda-commences-trial-test-run-on-mumbai-metro-line-4</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/thane-metro-4-and-4a-span-35-km-with-32-stations-trial-run-inspected-by-devendra-fadnavis-and-eknath-shinde-full-details-in-marathi-article-152872624</t>
+          <t>https://thecsrjournal.in/thane-metro-trial-run-hindi/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi20250917174418</t>
+          <t>https://mahasamvad.in/179135/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
+          <t>https://www.newsonair.gov.in/union-minister-piyush-goyal-launches-swasth-nari-sashakt-parivar-campaign-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/uttarakhand/uttarakhand-govt-to-buy-produce-from-apple-growers-in-disaster-hit-dharali/article70076273.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/opposition-targets-shiv-sena-over-mumbais-gb-hway-traffic-ahead-of-civic-polls/articleshow/124020437.cms</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-14-september-2025-asia-cup-cricket-hockey-pakistan-china-pm-modi-rain-alert-trump-israel-ukraine-russia-gaza-war-bjp-congress/liveblog/123877354.cms</t>
+          <t>https://www.devdiscourse.com/article/politics/3630507-political-shocker-the-shooting-of-charlie-kirk-sparks-nationwide-debate?amp</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/heavy-rains-batter-maharashtra-imd-issues-yellow-alert-across-state/</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/kumbh-mela-committee-accommodates-representatives-of-bjps-mahayuti-allies-ncp-shiv-sena/articleshow/124020480.cms</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/maharashtra-government-vehicle-policy-revised-2025-ntc-rptc-2336368-2025-09-18</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-workers-burn-effigy-of-shiv-sena-ubt-mp-sanjay-raut-for-his-remark-about-anand-dighe/articleshow/123981706.cms</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/gallery/15-09-2025-%E0%A4%86%E0%A4%9A%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A4%B5%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%AF%E0%A4%BE%E0%A4%82%E0%A4%A8%E0%A5%80-%E0%A4%98%E0%A5%87/</t>
+          <t>https://www.newsband.in/article_detail/replicas-diversity-mark-devi-durgeshwari-fest-in-thane</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/trial-run-of-metro-line-4-and-4a-conducted-in-thane/871907/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/press-release/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/2938489</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/sudhir-mungantiwar_16.html</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/bjps-criticism-of-sanjay-raut/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
+          <t>https://timesofindia.indiatimes.com/india/cant-be-on-whims-delhi-hc-raps-centre-over-delay-in-kejriwal-house-allotment-calls-for-clear-policy/articleshow/123976159.cms</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/beed-to-ahilyanagar-railway-inaugurated-cm-fadnavis-live-995605</t>
+          <t>https://scanx.trade/stock-market-news/stocks/hudco-re-appoints-baldeo-purushartha-as-government-nominee-director/19487527</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
+          <t>https://www.heraldgoa.in/globe-nation/atlantic-journalist-claims-he-was-accidentally-sent-u-s-war-plans-trump-responds/11525/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/maharashtra-governor-acharya-devvrat-took-the-oath/</t>
+          <t>https://www.newsband.in/article_detail/thane-metro-line-4-train-run-conducted-successfully</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278581344/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education</t>
+          <t>https://hindi.theprint.in/india/trial-run-of-metro-line-4-and-4a-conducted-in-thane/871907/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-marathwada-four-people-died-150-people-were-trapped-in-floods-in-dharashiv/924053/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/iti-students-will-run-cleanliness-campaign-in-750-villages-special-campaign-by-minister-mangal-prabhat-lodha-on-pm-modis-birthday/articleshow/123915570.cms</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/how-the-bjp-alliance-won-maharashtra-101757921779535.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/parashuram-economic-development-corporation-chairman-ministerial-status-to-ashish-damle-thane-news-1384578</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/not-an-mla-but-get-rs-20-cr-in-funds-sena-leader-sarvankar-boasts-later-clarifies/articleshow/124028510.cms</t>
+          <t>https://www.hindisaamana.com/the-state-has-a-debt-of-rs-9-lakh-crores-development-of-the-state-is-stalled-deva-bhau-is-busy-in-advertising/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
+          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-police-restrict-heavy-truck-movement-for-eighteen-hours-daily-to-ease-traffic-congestion/articleshow/123927129.cms</t>
+          <t>https://lokmanthan.com/arrangements-should-be-made-to-issue-all-relevant-permits-for-industries-in-a-single-application-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/acharya-devvrat-sworn-in-as-governor-of-maharashtra-reads-oath-in-sanskrit/</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/jarange-plans-national-maratha-convention-in-delhi-hake-warns-of-obc-march-to-mumbai/articleshow/123952548.cms</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-assembly-election-2025-cm-nitish-eyes-the-lost-seats-of-paswan-and-kushwaha-2025-09-18</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maratha-quota-activist-manoj-jarange-patil-announce-chalo-delhi-program-after-mumbai-reservation-protest-know-all/articleshow/123982783.cms</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/tejashwi-yadav-bihar-adhikar-yatra-tejashwi-yadav-afraid-of-rahul-gandhi-bihar-election-2025-2025-09-17</t>
+          <t>https://indianexpress.com/article/cities/mumbai/acharya-devvrat-oath-maharashtra-governor-10250775/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-patna-high-court-strict-on-ai-video-made-on-pm-modi-s-mother-nda-gave-this-reply-2025-09-18</t>
+          <t>https://www.thehindu.com/sport/cricket/former-delhi-captain-mithun-manhas-set-to-be-next-bcci-president/article70075244.ece</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-rahul-gandhi-and-tejashwi-yadav-lalu-yadav-decide-on-seat-sharing-within-mahagathbandhan-2025-09-18</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/transporters-cite-increased-costs-supply-disruptions-want-new-traffic-curbs-lifted/articleshow/124005110.cms</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/chief-minister-bhagwant-mann-launched-mission-chadti-kala-for-flood-victims-in-punjab-made-this-appeal-to-t-2025-09-17</t>
+          <t>https://news.abplive.com/cities/eknath-shinde-s-x-account-hacked-images-of-pakistan-turkiye-s-flags-posted-1801504</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/disha-patni-house-firing-case-the-accused-of-firing-at-disha-patni-s-house-were-killed-adg-told-the-whole-st-2025-09-18</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/gorakhpur-student-murder-case-encounter-in-gorakhpur-student-murder-case-akhilesh-furious-at-the-government-2025-09-18</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/violence-escalates-in-maratha-obc-reservation-dispute-obc-leader-s-car-set-on-fire-in-jalna-125092300009_1.html</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/abp-majha-top-10-headlines-abp-%E0%A4%AE-%E0%A4%9D-%E0%A4%9F-%E0%A4%AA-10-%E0%A4%B9%E0%A5%87%E0%A4%A1%E0%A4%B2-%E0%A4%88%E0%A4%A8%E0%A5%8D%E0%A4%B8-22-%E0%A4%B8%E0%A4%AA%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%82%E0%A4%AC%E0%A4%B0-2025-%E0%A4%B8-%E0%A4%AE%E0%A4%B5-%E0%A4%B0/ar-AA1N3QmU</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>https://marathi.ndtv.com/india/maharashtra-politics-live-update-mumbai-rain-first-bullet-train-between-mumbai-and-ahmedabad-9310619</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>https://indiagroundreport.com/mumbai-acharya-devvrat-took-additional-charge-as-governor-of-maharashtra/</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/national/karnataka/bk-singh-to-head-sit-formed-to-probe-aland-voter-fraud-case/article70074360.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/national/congress-doing-negative-politics-over-great-nicobar-project-environment-minister/article70067325.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%82%E0%A4%B8-%E0%A4%AC%E0%A4%A4-%E0%A4%B0-%E0%A4%B9-%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%89%E0%A4%AC-%E0%A4%A0-%E0%A4%B2-%E0%A4%9C-%E0%A4%A8-%E0%A4%9A-%E0%A4%86%E0%A4%A0%E0%A4%B5%E0%A4%A3-%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%AB-%E0%A4%B5-%E0%A4%A7%E0%A5%87%E0%A4%AF%E0%A4%95-%E0%A4%B5%E0%A4%B0%E0%A5%82%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A1-%E0%A4%B5%E0%A4%9A%E0%A4%B2%E0%A4%82/ar-AA1CdNPz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/india-news/didnt-do-so-for-power-but-ajit-pawar-on-why-he-split-with-sharad-pawar-101758292291397.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/articleshow/123993653.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>https://english.varthabharati.in/india/rahul-gandhis-vote-theft-charges-baseless-says-shinde</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>https://marathi.timesnownews.com/maharashtra/explainer-a-test-of-mahayuti-in-bmc-elections-shiv-sena-bjp-tug-of-war-over-91-seats-article-152842707</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>https://www.dainikprabhat.com/rs-20-crores-of-funds-were-received-without-any-mla-shinde-faction-leaders-statement-increases-mahayutis-problems/</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>https://dainikekmat.com/ministerial-status-to-the-chairman-of-parashuram-corporation/117448/</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>https://dainikekmat.com/attorney-general-birendra-saraf-resigns/117476/</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/thane-metro-lines-4-and-4a-trial-run-revolutionizing-travel-in-mumbai-metropolitan-region/124060623</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/179580/</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>https://metrorailtoday.com/news/mmrda-commences-trial-test-run-on-mumbai-metro-line-4</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178444/</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>https://www.tarunmitra.in/state/maharashtra/maharashtra-governments-unique-initiative-plan-to-build-namo-park-on/article-105368</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/how-can-blood-cricket-flow-together-uddhav-thackeray-opposes-india-pak-match-protests-to-target-pm-modi/articleshow/123878115.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>https://www.newsonair.gov.in/union-minister-piyush-goyal-launches-swasth-nari-sashakt-parivar-campaign-in-mumbai/</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/opposition-targets-shiv-sena-over-mumbais-gb-hway-traffic-ahead-of-civic-polls/articleshow/124020437.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>https://thenewsmill.com/2025/09/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education/</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/kumbh-mela-committee-accommodates-representatives-of-bjps-mahayuti-allies-ncp-shiv-sena/articleshow/124020480.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/en-in/news/India/bmc-polls-an-acid-test-for-shiv-sena-ubt-says-thackeray/ar-AA1MRllW</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-workers-burn-effigy-of-shiv-sena-ubt-mp-sanjay-raut-for-his-remark-about-anand-dighe/articleshow/123981706.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>https://www.newsband.in/article_detail/replicas-diversity-mark-devi-durgeshwari-fest-in-thane</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/sudhir-mungantiwar_16.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/bjps-criticism-of-sanjay-raut/</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/india/cant-be-on-whims-delhi-hc-raps-centre-over-delay-in-kejriwal-house-allotment-calls-for-clear-policy/articleshow/123976159.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/politics/3630507-political-shocker-the-shooting-of-charlie-kirk-sparks-nationwide-debate?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>https://www.newsband.in/article_detail/thane-metro-line-4-train-run-conducted-successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/iti-students-will-run-cleanliness-campaign-in-750-villages-special-campaign-by-minister-mangal-prabhat-lodha-on-pm-modis-birthday/articleshow/123915570.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-fort-%E0%A4%A6%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%B0-%E0%A4%9C-%E0%A4%B0-%E0%A4%AF%E0%A4%97%E0%A4%A1-%E0%A4%B8%E0%A4%B9-12-%E0%A4%B6-%E0%A4%B5%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%A8%E0%A5%87%E0%A4%B8%E0%A5%8D%E0%A4%95-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9C-%E0%A4%97%E0%A4%A4-%E0%A4%95-%E0%A4%B5-%E0%A4%B0%E0%A4%B8-%E0%A4%AF-%E0%A4%A6-%E0%A4%A4/ar-AA1IsmDX?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/maharashtra/parashuram-economic-development-corporation-chairman-ministerial-status-to-ashish-damle-thane-news-1384578</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>https://www.hindisaamana.com/the-state-has-a-debt-of-rs-9-lakh-crores-development-of-the-state-is-stalled-deva-bhau-is-busy-in-advertising/</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>https://lokmanthan.com/arrangements-should-be-made-to-issue-all-relevant-permits-for-industries-in-a-single-application-chief-minister-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>https://hindi.gyanhigyan.com/auto/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A5%87%E0%A4%B2%E0%A4%B5%E0%A5%87-%E0%A4%AA%E0%A4%B0%E0%A4%BF%E0%A4%AF%E0%A5%8B%E0%A4%9C%E0%A4%A8%E0%A4%BE%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-21000-%E0%A4%95%E0%A4%B0%E0%A5%8B%E0%A4%A1%E0%A4%BC-%E0%A4%B0%E0%A5%81%E0%A4%AA%E0%A4%AF%E0%A5%87-%E0%A4%95%E0%A4%BE/cid17430694.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/jarange-plans-national-maratha-convention-in-delhi-hake-warns-of-obc-march-to-mumbai/articleshow/123952548.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maratha-quota-activist-manoj-jarange-patil-announce-chalo-delhi-program-after-mumbai-reservation-protest-know-all/articleshow/123982783.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>https://sundayguardianlive.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-139969/</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/transporters-cite-increased-costs-supply-disruptions-want-new-traffic-curbs-lifted/articleshow/124005110.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>https://news.abplive.com/cities/eknath-shinde-s-x-account-hacked-images-of-pakistan-turkiye-s-flags-posted-1801504</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-prime-minister-narendra-modi-birthday-chhagan-bhujbal-obc-reservation-rain-alert-wednesday-17-september-2025-1494134.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/mumbai/sanjay-raut-statement-on-anand-dighe-thane-balasaheb-thackeray-photo-advertise-shivsena-maharashtra-marathi-news-1385015</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/violence-escalates-in-maratha-obc-reservation-dispute-obc-leader-s-car-set-on-fire-in-jalna-125092300009_1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
         <is>
           <t>https://timesofindia.indiatimes.com/city/mumbai/thane-metro-4-4a-corridor-improves-transportation-reduce-congestion-on-gb-road-and-connectivity-in-thane-and-mumbai/articleshow/124029480.cms</t>
         </is>

--- a/Output/Eknath Shinde/extracted_links_Eknath Shinde_failed_links.xlsx
+++ b/Output/Eknath Shinde/extracted_links_Eknath Shinde_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A359"/>
+  <dimension ref="A1:A349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,147 +438,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/eknath-shindes-x-account-hacked-congress-raises-alarm-over-cyber-security/article70077295.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/maharashtra-deputy-cm-eknath-shinde-takes-action-against-builders-of-65-illegal-buildings-in-kalyan-dombivli/articleshow/124011193.cms</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/maharashtra-deputy-cm-eknath-shinde-takes-action-against-builders-of-65-illegal-buildings-in-kalyan-dombivli/articleshow/124011193.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ahead-of-bmc-elections-eknath-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena-23594416</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/maharashtra-deputy-cm-eknath-shindes-x-account-hacked/</t>
+          <t>https://www.indiatvnews.com/maharashtra/eknath-shinde-maharashtra-deputy-cm-x-account-hacked-hackers-post-pakistan-turkey-flags-hacking-sparks-uproar-2025-09-21-1009219</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/find-the-masterminds-behind-the-kdmc-illegal-buildings-scam-shinde-101758309996962.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/eknath-shinde-maharashtra-deputy-cm-x-account-hacked-hackers-post-pakistan-turkey-flags-hacking-sparks-uproar-2025-09-21-1009219</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/when-i-go-to-villages-i-feel-fresh-my-opponents-get-depressed-says-dy-cm-eknath-shinde-at-launch-of-gram-samruddhi-yojana/articleshow/123964878.cms</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked/2934860</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-images-of-pakistan-turkey-flags-posted/articleshow/124024337.cms</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/eknath-shinde-x-handle-hacked-briefly-photos-of-pakistan-turkey-flags-posted-2790861-2025-09-21</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/when-i-go-to-villages-i-feel-fresh-my-opponents-get-depressed-says-dy-cm-eknath-shinde-at-launch-of-gram-samruddhi-yojana/articleshow/123964878.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
+          <t>https://www.indiatoday.in/india/story/eknath-shinde-x-handle-hacked-briefly-photos-of-pakistan-turkey-flags-posted-2790861-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-images-of-pakistan-turkey-flags-posted/articleshow/124024337.cms</t>
+          <t>https://www.hindustantimes.com/india-news/paint-thrown-at-bust-of-uddhav-thackerays-late-mother-sena-workers-angry-probe-on-101758106562970.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-cong-leader-questions-cyber-security-23595093</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education/</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/mla-warns-sanjay-raut-over-remarks-on-anand-dighe-shiv-sainiks-protest-in-kalyan-dombivli/articleshow/124011234.cms</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/globe-nation/kunal-kamra-summoned-again-over-derogatory-remarks-about-eknath-shinde-political-debate-intensifies/11957/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/gst-rate-cut-will-boost-economy-shield-india-from-us-tariff-hikes-says-maharashtras-deputy-chief-minister-eknath-shinde/articleshow/124002613.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/gst-rate-cut-will-boost-economy-shield-india-from-us-tariff-hikes-says-maharashtras-deputy-chief-minister-eknath-shinde/articleshow/124002613.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ahead-of-bmc-polls-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena/2921488</t>
+          <t>https://www.heraldgoa.in/globe-nation/kunal-kamras-controversial-joke-targeting-eknath-shinde-sparks-backlash-from-shiv-sena-leaders/11935/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/paint-thrown-at-bust-of-uddhav-thackerays-late-mother-sena-workers-angry-probe-on-101758106562970.html</t>
+          <t>https://www.ptinews.com/story/national/full-page-newspaper-ads-and-slew-of-initiatives-shiv-sena-goes-all-out-to-celebrate-pm-s-birthday/2925344</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/hc-seeks-govt-s-stand-on-illegal-stay-on-demolition-by-dy-cm-101758137116362.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/thane-shiv-sena-workers-protest-against-sanjay-raut-s-remark-about-anand-dighe-23594679</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/awhad-slams-the-states-selective-compassion-over-demolition-notices</t>
+          <t>https://realty.economictimes.indiatimes.com/news/industry/strict-action-ordered-against-65-illegal-buildings-in-kalyan-dombivli-by-deputy-chief-minister-eknath-shinde/124008652</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/most-of-rs-46000cr-projects-for-marathwada-announced-by-shinde-led-cabinet-in-2023-still-on-paper/articleshow/123907066.cms</t>
+          <t>https://www.ptinews.com/story/national/ahead-of-bmc-polls-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena/2921488</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shiv-sena-publishes-full-page-ads-in-dailies-on-pms-birthday-shinde-hails-his-new-india-push/2923561</t>
+          <t>https://www.ptinews.com/stories-detail/national/maharashtra-dy-cm-eknath-shindes-x-account-hacked/2934860/0</t>
         </is>
       </c>
     </row>
@@ -592,21 +592,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/industry/strict-action-ordered-against-65-illegal-buildings-in-kalyan-dombivli-by-deputy-chief-minister-eknath-shinde/124008652</t>
+          <t>https://www.ptinews.com/story/national/shiv-sena-publishes-full-page-ads-in-dailies-on-pms-birthday-shinde-hails-his-new-india-push/2923561</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi20250917174418</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-charges-baseless-says-ekanth-shinde-23594783</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/find-the-masterminds-behind-the-kdmc-illegal-buildings-scam-shinde-101758309996962.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde-23595190</t>
         </is>
       </c>
     </row>
@@ -620,49 +620,49 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/allies-in-conflict-bjp-shinde-sena-lock-horns-on-dahisar-toll-shift</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-gifts-modi-394-namo-udyans-101758050819661.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/globe-nation/kunal-kamra-stands-by-his-right-to-freedom-of-speech-amid-backlash-over-remarks-on-eknath-shinde/11949/</t>
+          <t>https://www.newsband.in/article_detail/awhad-slams-the-states-selective-compassion-over-demolition-notices</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-gifts-modi-394-namo-udyans-101758050819661.html</t>
+          <t>https://zeenews.india.com/india/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked-hackers-post-pakistan-turkey-flags-2962608.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/hc-to-shinde-by-what-authority-did-you-stay-navi-mumbai-civic-bodys-notice-to-raze-illegal-buildings/articleshow/123952725.cms</t>
+          <t>https://timesofindia.indiatimes.com/india/not-an-mla-but-get-rs-20-cr-in-funds-sena-leader-sarvankar-boasts-later-clarifies/articleshow/124028510.cms</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked-hackers-post-pakistan-turkey-flags-2962608.html</t>
+          <t>https://www.newsband.in/article_detail/allies-in-conflict-bjp-shinde-sena-lock-horns-on-dahisar-toll-shift</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/video/news/pm-modi-adopts-nation-first-policy-eknath-shinde-slams-congress-over-remarks-on-pm-s-mother-2025-09-17-1008597</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/most-of-rs-46000cr-projects-for-marathwada-announced-by-shinde-led-cabinet-in-2023-still-on-paper/articleshow/123907066.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/full-page-newspaper-ads-and-slew-of-initiatives--shiv-sena-goes-all-out-to-celebrate-pm-s-birthday/2925344</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831</t>
         </is>
       </c>
     </row>
@@ -676,168 +676,168 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-police-restrict-heavy-truck-movement-for-eighteen-hours-daily-to-ease-traffic-congestion/articleshow/123927129.cms</t>
+          <t>https://www.indiatvnews.com/video/news/pm-modi-adopts-nation-first-policy-eknath-shinde-slams-congress-over-remarks-on-pm-s-mother-2025-09-17-1008597</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/not-an-mla-but-get-rs-20-cr-in-funds-sena-leader-sarvankar-boasts-later-clarifies/articleshow/124028510.cms</t>
+          <t>https://www.ptinews.com/story/national/heavy-vehicles-banned-on-thane-s-ghodbunder-road-during-daytime/2919586</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-polls-an-acid-test-for-shiv-sena-ubt-says-thackeray-101758222779307.html</t>
+          <t>https://www.ptinews.com/story/national/prioritise-development-in-14-villages-added-to-navi-mumbai-civic-limits-dy-cm-shinde/2930925</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/heavy-vehicles-banned-on-thane-s-ghodbunder-road-during-daytime/2919586</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/hc-to-shinde-by-what-authority-did-you-stay-navi-mumbai-civic-bodys-notice-to-raze-illegal-buildings/articleshow/123952725.cms</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/globe-nation/fadnavis-meeting-with-thackeray-sparks-speculation-of-alliance/9016/</t>
+          <t>https://www.sakshipost.com/news/shiv-senaubt-continues-attacking-dy-cm-shinde-says-maha-govt-boastful-454108</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/prioritise-development-in-14-villages-added-to-navi-mumbai-civic-limits--dy-cm-shinde/2930925</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-polls-an-acid-test-for-shiv-sena-ubt-says-thackeray-101758222779307.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/maharashtra-launches-namo-gardens-and-tourism-skill-programme-to-mark-pm-modis-75th-birthday/</t>
+          <t>http://www.uniindia.com/~/district-administration-should-remain-alert-for-relief-and-rescue-operations-in-wake-of-heavy-rains-says-deputy-cm-shinde/States/news/3577807.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/mmrda-temporarily-suspends-monorail-services-in-mumbai20250920092952</t>
+          <t>https://www.ptinews.com/story/national/women-office-bearers-workers-of-sena-ubt-from-palghar-join-shinde-led-sena-ahead-of-local-polls/2927880</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/en/politics/government-will-pay-inr-200-crores-owed-to-shiv-bhojan-thali-kendra-operators-90025</t>
+          <t>https://www.newsband.in/article_detail/acharyadevvrattakes-oath-as-maharashtras-22nd-governor</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ahead-of-bmc-elections-eknath-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena-23594416</t>
+          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-cong-leader-questions-cyber-security-23595093</t>
+          <t>https://thewire.in/politics/bhakti-for-modi-at-75-from-newspaper-ads-to-prayers-and-coordinated-social-media-posts</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-charges-baseless-says-ekanth-shinde-23594783</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/namo-gardens-to-be-developed-in-394-municipal-councils-and-nagar-panchayats-in-maharashtra-23594437</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde-23595190</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/parshuram-economic-development-corporation-chairman-ashish-damle-to-get-ministerial-status-says-maharashtra-govt-23594308</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/thane-shiv-sena-workers-protest-against-sanjay-raut-s-remark-about-anand-dighe-23594679</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-shiv-sena-leaders-speech-adds-fuel-to-accusations-of-biased-allocation-of-funds-23595109?lifestyle-dr-love-breakingnews</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/mumbai-acharya-devvrat-sworn-in-as-maharashtra-governor-gallery/</t>
+          <t>http://www.uniindia.com/bombay-hc-challenges-shinde-s-halt-to-navi-mumbai-demolitions/west/news/3581496.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/shiv-senaubt-continues-attacking-dy-cm-shinde-says-maha-govt-boastful-454108</t>
+          <t>https://www.heraldgoa.in/globe-nation/kunal-kamra-challenges-fir-over-gaddar-jibe-at-maharashtra-deputy-cm-in-bombay-high-court/11930/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/heavy-vehicles-banned-on-thanes-ghodbunder-road-during-daytime-23594294</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://www.aninews.in/news/national/general-news/mmrda-temporarily-suspends-monorail-services-in-mumbai20250920092952</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-21-news-updates-live-updates-weather-update-mumbai-monsoon-18331429</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/namo-gardens-to-be-developed-in-394-municipal-councils-and-nagar-panchayats-in-maharashtra-23594437</t>
+          <t>https://www.mumbailive.com/en/politics/government-will-pay-inr-200-crores-owed-to-shiv-bhojan-thali-kendra-operators-90025</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/on-eve-of-pms-birthday-shinde-announces-scheme-to-develop-namo-parks-in-maharashtra-10471206</t>
+          <t>https://www.newsx.com/india/eknath-shinde-account-hacked-during-india-pakistan-asia-cup-cybercrime-cybersecurity-national-flags-of-turkey-and-pakistan-restored-in-45-minutes-75975/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/parshuram-economic-development-corporation-chairman-ashish-damle-to-get-ministerial-status-says-maharashtra-govt-23594308</t>
+          <t>https://thenewsmill.com/2025/09/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://thehindustangazette.com/election/eknath-shinde-x-account-hacked-pak-turkey-flags-39959</t>
+          <t>https://thenewsmill.com/2025/09/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-21-news-updates-live-updates-weather-update-mumbai-monsoon-18331429</t>
+          <t>https://thehindustangazette.com/election/eknath-shinde-x-account-hacked-pak-turkey-flags-39959</t>
         </is>
       </c>
     </row>
@@ -851,14 +851,14 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/deputy-cm-eknath-shinde-x-account-hack-pakistan-turkey-flag-shown-3016093</t>
+          <t>https://thecsrjournal.in/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hindi/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hindi/</t>
+          <t>https://www.abplive.com/states/maharashtra/deputy-cm-eknath-shinde-x-account-hack-pakistan-turkey-flag-shown-3016093</t>
         </is>
       </c>
     </row>
@@ -872,21 +872,21 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/DNHindi/photos/%E0%A4%B8%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8%E0%A4%BE%E0%A4%A5-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A4%BE-x-%E0%A4%85%E0%A4%95%E0%A4%BE%E0%A4%89%E0%A4%82%E0%A4%9F-%E0%A4%B9%E0%A5%88%E0%A4%95-%E0%A4%B9%E0%A5%88%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B2%E0%A4%97%E0%A4%BE%E0%A4%88-%E0%A4%AA%E0%A4%BE%E0%A4%95%E0%A4%BF%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A4%BE%E0%A4%A8-%E0%A4%A4%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9D%E0%A4%82%E0%A4%A1%E0%A5%87eknathsi/1251272843711787/</t>
+          <t>https://www.livehindustan.com/national/sanjay-raut-comments-about-eknath-shinde-mentor-anand-dighe-sparked-an-uproar-201758252385682.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-deputy-cm-eknath-shinde-s-twitter-account-hacked-raises-cybersecurity-concerns-201758454098732.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/deputy-cm-eknath-shinde-x-account-hacked-hackers-posted-images-of-pakistan-and-turkey-flags/articleshow/124025137.cms</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://hindi.newsbytesapp.com/news/india/eknath-shinde-s-ex-account-hacked-hackers-posted-flags-of-pakistan-and-turkiye/story</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-bmc-election-eknath-shinde-group-plan-b-revealed-challenge-to-devendra-fadnavis-bjp-9653396.html</t>
         </is>
       </c>
     </row>
@@ -900,154 +900,154 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-strict-against-builders-involved-in-kalyan-dombivali-illegal-buildings-constructing-3015585</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/ganesh-naik-vs-eknath-shinde-in-navi-mumbai-tussle-over-janata-darbar-petition-filed-in-high-court/articleshow/123996455.cms</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/deputy-cm-eknath-shinde-x-account-hacked-hackers-posted-images-of-pakistan-and-turkey-flags/articleshow/124025137.cms</t>
+          <t>https://www.republicbharat.com/india/maharashtra-dy-cm-eknath-shinde-x-account-hacked-posting-images-of-pakistan-and-turkey-flag</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/ganesh-naik-vs-eknath-shinde-in-navi-mumbai-tussle-over-janata-darbar-petition-filed-in-high-court/articleshow/123996455.cms</t>
+          <t>https://www.indiatv.in/maharashtra/maharashtra-deputy-cm-eknath-shinde-x-handle-hacked-hackers-shared-posts-with-pakistan-and-turkey-flags-2025-09-21-1164034</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/sanjay-raut-comments-about-eknath-shinde-mentor-anand-dighe-sparked-an-uproar-201758252385682.html</t>
+          <t>https://hindi.newsbytesapp.com/news/india/eknath-shinde-s-ex-account-hacked-hackers-posted-flags-of-pakistan-and-turkiye/story</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/sanjay-raut-said-eknath-shinde-mentality-is-very-low-level-there-is-nothing-left-to-talk-about-2025-09-20-1163910</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-uddhav-thackeray-puts-bold-conditions-for-rebels-nagar-sevak-for-ghar-wapsi-for-shinde-shiv-sena-ahead-of-bmc-polls-know-all/articleshow/123978190.cms</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/maharashtra/eknath-shinde-x-account-hacked-pakistani-flags-posted-125092100012_1.html</t>
+          <t>https://www.indiatv.in/maharashtra/sanjay-raut-said-eknath-shinde-mentality-is-very-low-level-there-is-nothing-left-to-talk-about-2025-09-20-1163910</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-deputy-cm-eknath-shinde-x-handle-hacked-hackers-shared-posts-with-pakistan-and-turkey-flags-2025-09-21-1164034</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/pm-modi-birthday-congress-declares-pm-modi-s-birthday-as-black-day-enraged-eknath-shinde-issues-warning-2025-09-17</t>
+          <t>https://hindi.webdunia.com/maharashtra/eknath-shinde-x-account-hacked-pakistani-flags-posted-125092100012_1.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/shiv-sena-mla-sada-sarvankar-met-maharashtra-navnirman-sena-president-raj-thackeray-3016893</t>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-deputy-cm-eknath-shinde-s-twitter-account-hacked-raises-cybersecurity-concerns-201758454098732.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/eknath-shindes-x-account-hacked-pictures-of-islamic-countries-and-turkish-flags-posted-11708</t>
+          <t>https://www.amarujala.com/video/india-news/pm-modi-birthday-congress-declares-pm-modi-s-birthday-as-black-day-enraged-eknath-shinde-issues-warning-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
+          <t>https://zeenews.india.com/hindi/india/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-pakistan-turkiye-flag-shown-on-handle/2930969</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-deputy-chief-minister-ekanth-shinde-says-rahul-gandhi-s-vote-theft-charges-baseless-2025-09-19</t>
+          <t>https://www.abplive.com/states/maharashtra/shiv-sena-mla-sada-sarvankar-met-maharashtra-navnirman-sena-president-raj-thackeray-3016893</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://inshorts.com/hi/news/%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6--%E0%A4%A6--%E0%A4%95--x-%E0%A4%85%E0%A4%95-%E0%A4%89-%E0%A4%9F-%E0%A4%B9-%E0%A4%95--%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%B8-%E0%A4%A8--%E0%A4%AA-%E0%A4%B8-%E0%A4%9F-%E0%A4%95-%E0%A4%8F-%E0%A4%AA-%E0%A4%95-%E0%A4%B8-%E0%A4%A4-%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%95--%E0%A4%95--%E0%A4%9D-%E0%A4%A1---1758441470089</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-deputy-chief-minister-ekanth-shinde-says-rahul-gandhi-s-vote-theft-charges-baseless-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/video/pm-modi-75th-birthday-piyush-goyal-eknath-shinde-wishes-ytvd-2335022-2025-09-17</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/eknath-shinde-takes-action-against-kalyan-dombivli-illegal-buildings-builders/articleshow/124011899.cms</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-uddhav-thackeray-puts-bold-conditions-for-rebels-nagar-sevak-for-ghar-wapsi-for-shinde-shiv-sena-ahead-of-bmc-polls-know-all/articleshow/123978190.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-namo-park-scheme-for-pm-narendra-modi-75th-birthday-deputy-cm-eknath-shinde-announcement-3014117</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-namo-park-scheme-for-pm-narendra-modi-75th-birthday-deputy-cm-eknath-shinde-announcement-3014117</t>
+          <t>https://hindi.theprint.in/politics/focus-on-administration-and-oversight-shinde-launches-mission-mumbai-for-bmc-elections/871175/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/eknath-shinde-takes-action-against-kalyan-dombivli-illegal-buildings-builders/articleshow/124011899.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/pratap-sarnaik-comments-on-uddhav-thackeray-sanjay-raut-praises-eknath-shinde-respect-senior-leaders-3016095</t>
+          <t>https://www.aajtak.in/india/maharashtra/video/pm-modi-75th-birthday-piyush-goyal-eknath-shinde-wishes-ytvd-2335022-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/thane-metro-trial-run-on-september-22-thane-residents-dream-to-come-true/articleshow/124004146.cms</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/kedar-dighes-sharp-attack-on-shinde-faction-anand-dighe-remembered-as-elections-approach/articleshow/124004160.cms</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/eknath-shinde-treated-australian-guests-to-a-feast-of-vada-pav-9289261</t>
+          <t>https://www.abplive.com/states/maharashtra/pratap-sarnaik-comments-on-uddhav-thackeray-sanjay-raut-praises-eknath-shinde-respect-senior-leaders-3016095</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/maharashtra-diwali-bonus-bmc-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%9A-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%AC-%E0%A4%A8%E0%A4%B8-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8-%E0%A4%86%E0%A4%9A-%E0%A4%B0-%E0%A4%B8%E0%A4%82%E0%A4%B9-%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%8F%E0%A4%95%E0%A4%A8-%E0%A4%A5-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1sk1rp?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/thane-metro-trial-run-on-september-22-thane-residents-dream-to-come-true/articleshow/124004146.cms</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/short-videos/congress-mp-praniti-shinde-criticizes-eknath-shinde/939828</t>
+          <t>https://marathi.abplive.com/news/mumbai/under-what-authority-were-the-municipal-corporation-notice-to-demolish-buildings-stopped-high-court-ask-on-eknath-shinde-whether-the-dcm-has-the-authority-to-make-that-decision-1384909</t>
         </is>
       </c>
     </row>
@@ -1061,168 +1061,168 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
+          <t>https://marathi.ndtv.com/cities/eknath-shinde-treated-australian-guests-to-a-feast-of-vada-pav-9289261</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.bakharlive.com/maharashtra/deputy-chief-minister-eknath-shinde-announces-to-set-up-namo-parks-in-394-cities-of-the-state/</t>
+          <t>https://www.jansatta.com/jansatta-special/jansatta-rajpaat-abhay-chautala-haryana-shinde-message-congress-du-election-bihar-seat-dispute-rld-up/4151302/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-decision-mandatory-to-construct-administrative-buildings-of-municipal-councils-according-to-the-model-plan-1482062.html</t>
+          <t>https://zeenews.india.com/marathi/short-videos/congress-mp-praniti-shinde-criticizes-eknath-shinde/939828</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178790/</t>
+          <t>https://marathi.abplive.com/news/politics/the-high-court-has-questioned-eknath-shinde-over-the-suspension-of-action-against-illegal-construction-in-navi-mumbai-1384988</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/the-high-court-has-questioned-eknath-shinde-over-the-suspension-of-action-against-illegal-construction-in-navi-mumbai-1384988</t>
+          <t>https://marathi.abplive.com/news/maharashtra/sanjay-raut-says-eknath-shinde-who-is-there-today-is-because-of-rajan-vichare-sacrifice-marathi-news-update-1385178</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/thane-ghodbunder-news-good-news-for-thane-kalyan-badlapur-commuters-as-eknath-shinde-orders-restriction-of-heavy-vehicles-untill-midnight-9291074</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/shiv-sena-leader-eknath-shinde-slams-incapable-ministers-for-ignoring-party-expansion-and-administrative-work/articleshow/124045917.cms</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/deputy-chief-minister-eknath-shinde-reaction-to-prime-minister-narendra-modi-s-gst-cut-ladki-bahin-yojana-news-1385846</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticized-eknath-shinde-for-washing-rajan-vichares-feet-and-taking-a-pilgrimage/923077/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/deputy-chief-minister-eknath-shinde-insistently-served-the-australian-guests-vadapav-a-signature-food-of-mumbai/922213/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-decision-mandatory-to-construct-administrative-buildings-of-municipal-councils-according-to-the-model-plan-1482062.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/changes-in-gst-rates-will-lead-to-the-ghatsthapna-of-superpower-in-country-eknath-shinde-96248</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-bala-saheb-was-brand-not-you-fadnavis-attacks-uddhav-thackeray-reveals-2019-bmc-election-truth-ws-l-9635814.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
+          <t>https://marathi.abplive.com/news/maharashtra/deputy-chief-minister-eknath-shinde-reaction-to-prime-minister-narendra-modi-s-gst-cut-ladki-bahin-yojana-news-1385846</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shindes-ex-account-hacked-96111</t>
+          <t>https://marathi.ndtv.com/maharashtra/thane-ghodbunder-news-good-news-for-thane-kalyan-badlapur-commuters-as-eknath-shinde-orders-restriction-of-heavy-vehicles-untill-midnight-9291074</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/business/mukhyamantri-mazi-ladki-bahin-yojana-no-e-kyc-no-rs-1500-all-beneficiaries-can-avail-facility-visiting-web-portal-b507/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/deputy-chief-minister-eknath-shinde-insistently-served-the-australian-guests-vadapav-a-signature-food-of-mumbai/922213/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-deputy-chief-minister-eknath-shinde-launches-the-seva-fortnight-chief-minister-samruddhi-panchayat-raj-abhiyan-in-thane-district/922593/</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-shinde-first-reaction-on-meenatai-thackeray-dadar-statue-issue-he-will-not-be-released-i-have-spoken-to-the-police-commissioner-1384826</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/eknath-shinde-first-reaction-on-meenatai-thackeray-dadar-statue-issue-he-will-not-be-released-i-have-spoken-to-the-police-commissioner-1384826</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-deputy-chief-minister-eknath-shinde-launches-the-seva-fortnight-chief-minister-samruddhi-panchayat-raj-abhiyan-in-thane-district/922593/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/shiv-sena-leader-eknath-shinde-slams-incapable-ministers-for-ignoring-party-expansion-and-administrative-work/articleshow/124045917.cms</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/changes-in-gst-rates-will-lead-to-the-ghatsthapna-of-superpower-in-country-eknath-shinde-96248</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-municipal-elections-eknath-shinde-puts-shiv-sena-in-action-mode-with-direct-orders-to-corporators-sharad-pawar-also-eyes-victory-in-corporations-1384728</t>
+          <t>https://marathi.ndtv.com/cities/cm-fadnavis-change-eknath-shindes-decision-to-ban-heavy-vehicles-from-morning-6-to-12-night-to-solve-traffic-congestion-9316039</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/shiv-sena-corporaters-news-eknath-shinde-on-uddhav-thackeray-mumbai-bmc-election-2025/921652/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-many-office-bearers-of-uddhav-thackeray-group-join-shiv-sena-95696</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/shiv-sena-corporaters-news-eknath-shinde-on-uddhav-thackeray-mumbai-bmc-election-2025/921652/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shindes-ex-account-hacked-96111</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-review-maharashtra-and-mumbai-rain-updates-orders-airlift-beed-ashti-villagers-1480338.html</t>
+          <t>https://mandalnews.com/other-cities/parashuram-development-board-chairman-given-ministerial-rank/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-ajit-pawar-and-eknath-shinde-reprimand-maharashtra-cabinet-over-performance-and-neglect-of-party-organization-1386101</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-municipal-elections-eknath-shinde-puts-shiv-sena-in-action-mode-with-direct-orders-to-corporators-sharad-pawar-also-eyes-victory-in-corporations-1384728</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/cm-fadnavis-change-eknath-shindes-decision-to-ban-heavy-vehicles-from-morning-6-to-12-night-to-solve-traffic-congestion-9316039</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-response-after-sanjay-raut-objected-to-placing-anand-dighes-photo-next-to-balasaheb-thackeray/922799/</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-rain-heavy-rainfall-in-beed-40-villagers-should-be-airlifted-dcm-eknath-shinde-ordered-9279677</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-district-administration-should-remain-alert-in-wake-of-heavy-rains-eknath-shinde-instructs-94887</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/mns-leader-avinash-jadhav-slams-eknath-shinde-over-thane-traffic-issue/articleshow/123926772.cms</t>
         </is>
       </c>
     </row>
@@ -1243,1699 +1243,1629 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-rain-heavy-rainfall-in-beed-40-villagers-should-be-airlifted-dcm-eknath-shinde-ordered-9279677</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-response-after-sanjay-raut-objected-to-placing-anand-dighes-photo-next-to-balasaheb-thackeray/922799/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-review-maharashtra-and-mumbai-rain-updates-orders-airlift-beed-ashti-villagers-1480338.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/mumbai-high-court-questioned-eknath-shinde-on-new-mumbai-illegal-construction-case/922756/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-many-office-bearers-of-uddhav-thackeray-group-join-shiv-sena-95696</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-big-announces-on-pm-modi-birthday-say-all-municipal-councils-will-be-established-namo-udyan-in-maharashtra-95314</t>
+          <t>https://www.mymahanagar.com/maharashtra/mumbai-high-court-questioned-eknath-shinde-on-new-mumbai-illegal-construction-case/922756/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/deputy-cm-eknath-shinde-on-heavy-rains-and-alert-to-district-administration/921681/</t>
+          <t>https://www.loksatta.com/thane/video-eknath-shinde-orders-urgent-relief-marathwada-floods-districts-ndrfs-airlift-operations-vsd-99-5391648/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/nevali-farmer-protesters-demand-eknath-shinde-to-revoke-cases-against-farmers-in-kalyan-thane-css-98-5381565/</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-eknath-shinde-s-shiv-sena-in-action-mode-confident-of-mahayuti-victory-in-mumbai-civic-polls-directs-corporators-to-start-work-1384673</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-for-suspending-demolition-of-societies-with-unauthorized-construction-in-vashi-area/922729/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-working-on-plan-b-for-bmc-election-likely-shock-to-uddhav-thackeray-and-bjp-also-1484790.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-district-administration-should-remain-alert-in-wake-of-heavy-rains-eknath-shinde-instructs-94887</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-ghodbandar-road-eknath-shinde-ghodbandar-residents-will-be-free-from-traffic-congestion/922259/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-big-announces-on-pm-modi-birthday-say-all-municipal-councils-will-be-established-namo-udyan-in-maharashtra-95314</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-working-on-plan-b-for-bmc-election-likely-shock-to-uddhav-thackeray-and-bjp-also-1484790.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/wadigodri-crime-news-fake-cid-officers-stole-the-golden-ring/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-solve-bmtc-employee-problem-gave-10-lakh-for-compensation-1484524.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/local-elections-mahayuti-will-win-in-the-local-self-government-elections-eknath-shinde-is-confident/922171/</t>
+          <t>https://www.mymahanagar.com/maharashtra/deputy-cm-eknath-shinde-on-heavy-rains-and-alert-to-district-administration/921681/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-for-suspending-demolition-of-societies-with-unauthorized-construction-in-vashi-area/922729/</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/thane-sporting-club-election-eknath-shinde-shiv-sena-won-over-bjp-mns-ubt-devendra-fadnavis-uddhav-thackeray-raj-thackeray-maharashtra-politics/articleshow/124041703.cms</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/dcm-eknath-shinde-criticized-rahul-gandhi-evm-vote-chori-case/922837/</t>
+          <t>https://www.saamana.com/wadigodri-crime-news-fake-cid-officers-stole-the-golden-ring/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-solve-bmtc-employee-problem-gave-10-lakh-for-compensation-1484524.html</t>
+          <t>https://www.mumbaitak.in/political-news/story/sanjay-raut-has-strongly-criticized-eknath-shinde-for-printing-photos-of-balasaheb-thackeray-and-anand-dighe-side-by-side-in-an-advertisement-wishing-pm-modi-a-happy-birthday-3202688-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-says-anand-dighe-never-sold-shiv-sena/923100/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-eknath-shinde-s-shiv-sena-in-action-mode-confident-of-mahayuti-victory-in-mumbai-civic-polls-directs-corporators-to-start-work-1384673</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/mns-leader-avinash-jadhav-slams-eknath-shinde-over-thane-traffic-issue/articleshow/123926772.cms</t>
+          <t>https://www.tv9marathi.com/videos/thane-metro-controversy-dcm-eknath-shinde-reply-to-sanjay-raut-thane-metro-halt-criticism-i-removed-the-speed-breaker-1497959.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-palghar-dahanu-shivsena-thackeray-group-office-bearers-from-palghar-dahanu-join-shivsena/922966/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-ghodbandar-road-eknath-shinde-ghodbandar-residents-will-be-free-from-traffic-congestion/922259/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/withdrew-the-rs-2-5-crore-fund-given-for-sewage-plant-and-drainage-because-former-corporator-deepmala-badhe-belonged-to-the-thackeray-group/922264/</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-says-anand-dighe-never-sold-shiv-sena/923100/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/pm-narendra-modi-birthday-sharad-pawar-ajit-pawar-and-eknath-shinde-wish-a-happy-birthday-95367</t>
+          <t>https://www.mymahanagar.com/maharashtra/local-elections-mahayuti-will-win-in-the-local-self-government-elections-eknath-shinde-is-confident/922171/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-shiv-sena-mla-sanjay-gaikwads-controversial-statement-sanjay-gaikwad-claims-that-local-level-elections-cost-rs-3-crores-and-100-goats-have-to-be-slaughtered/923585/</t>
+          <t>https://marathi.abplive.com/news/politics/shivsena-dasara-melava-shiv-sena-shinde-group-planning-finalized-special-responsibility-on-mumbai-mlas-and-newly-elected-department-heads-maharashtra-politics-marathi-news-1385340</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-chairs-shiv-sena-meeting-in-mumbai-strategizes-for-upcoming-elections-and-mumbai-municipal-corporation-polls-sanjay-nirupam-reacts-1384153</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-eknath-shinde-chairs-shiv-sena-meeting-in-mumbai-strategizes-for-upcoming-elections-and-mumbai-municipal-corporation-polls-sanjay-nirupam-reacts-1384153</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-palghar-dahanu-shivsena-thackeray-group-office-bearers-from-palghar-dahanu-join-shivsena/922966/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-politics-deputy-cm-eknath-shinde-refutes-evm-allegations-confident-of-mahayuti-victory-in-mumbai-civic-polls-on-development-work-1385031</t>
+          <t>https://www.loksatta.com/mumbai/high-court-orders-deputy-chief-minister-eknath-shinde-mumbai-print-news-phm-00-5381244/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/india-news/bihar-assembly-election-amit-shah-meets-bjp-workers-gives-60-days-plan-ahead-of-poll/articleshow/123995857.cms</t>
+          <t>https://www.tv9marathi.com/videos/nashik-journalist-beating-dcm-eknath-shinde-speaks-with-injured-journalist-kiran-tajane-via-video-call-1497047.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/after-ajit-pawar-eknath-shinde-will-also-hold-a-road-show-in-nagpur-shinde-s-mission-vidarbha-997770</t>
+          <t>https://www.mymahanagar.com/mahamumbai/withdrew-the-rs-2-5-crore-fund-given-for-sewage-plant-and-drainage-because-former-corporator-deepmala-badhe-belonged-to-the-thackeray-group/922264/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/thane-is-up-for-sale-sanjay-raut-hits-out-at-shinde-fadnavis-997973</t>
+          <t>https://marathi.timesnownews.com/maharashtra/explainer-a-test-of-mahayuti-in-bmc-elections-shiv-sena-bjp-tug-of-war-over-91-seats-article-152842707</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-20-september-2025-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://maharashtratimes.com/india-news/bihar-assembly-election-amit-shah-meets-bjp-workers-gives-60-days-plan-ahead-of-poll/articleshow/123995857.cms</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/thane/thane-tembhi-naka-devi-festival-shiv-sena-eknath-shinde-vs-rajan-vichare-dispute-anand-dighe-marathi-news-1386015</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-shiv-sena-mla-sanjay-gaikwads-controversial-statement-sanjay-gaikwad-claims-that-local-level-elections-cost-rs-3-crores-and-100-goats-have-to-be-slaughtered/923585/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/uddhav-thackeray-and-raj-thackeray-election-strategy-in-the-home-ground-of-eknath-shinde-shrikant-shinde/940495</t>
+          <t>https://www.tv9marathi.com/videos/ministers-dispute-court-case-highlights-rift-in-ruling-coalition-bjp-minister-ganesh-naik-public-hearing-spark-conflict-with-dcm-shinde-1496585.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-thackeray-vs-shinde-balasaheb-thackeray-s-legacy-shiv-sena-leadership-and-call-for-eknath-shinde-s-introspection-on-maharashtra-politics-1385211</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/pm-narendra-modi-birthday-sharad-pawar-ajit-pawar-and-eknath-shinde-wish-a-happy-birthday-95367</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/eknath-shinde-took-a-swipe-at-his-opponents-says-they-feel-depressed-by-farming-1279260-2025-09-18</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-20-september-2025-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/maharashtra-deputy-cm-eknath-shinde-s-x-account-hacked-hackers-posted-flags-of-pakistan-and-t%C3%BCrkiye-news-295659</t>
+          <t>https://marathi.ndtv.com/videos/thane-is-up-for-sale-sanjay-raut-hits-out-at-shinde-fadnavis-997973</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://ahilyawani.com/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-posts-with-pakistan-and-turkey-flags-spark-uproar-account-recovered-police-investigating/</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-beed-floods-airlift-rescue-operation-eknath-shinde-suresh-dhas-1493005.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/the-mahagathbandhan-leaders-openly-support-corruption-high-court-rebukes-them/</t>
+          <t>https://www.loksatta.com/thane/eknath-shinde-daytime-heavy-vehicle-ban-in-ghodbandar-thane-to-badlapur-until-october-2-sud-02-5381060/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.tarunmitra.in/state/maharashtra/maharashtra-deputy-cm-shindes-x-account-hack-account-posted-pictures/article-105819</t>
+          <t>https://news18marathi.com/maharashtra/bmc-elections-latest-news-bjp-preparing-fight-on-150-seats-in-mumbai-shiv-sena-shinde-claim-on-how-many-seats-bmc-election-1480865.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/dy-cm-eknath-shinde-visits-the-state-emergency-operations-center/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/thane-metro-4-and-4a-span-35-km-with-32-stations-trial-run-inspected-by-devendra-fadnavis-and-eknath-shinde-full-details-in-marathi-article-152872624</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://vedantsamachar.in/x-account-hacked-deputy-chief-minister-eknath-shindes-x-account-hack/</t>
+          <t>https://www.navarashtra.com/maharashtra/thane/sanajy-raut-questions-eknath-shinde-banner-placing-anand-dighe-photo-protest-against-sanjay-raut-in-thane-994107.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
+          <t>https://www.kisantak.in/politics/story/eknath-shinde-took-a-swipe-at-his-opponents-says-they-feel-depressed-by-farming-1279260-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/eknath-shindes-political-game-will-fail-this-leader-warns-of-being-dragged-directly-to-court/</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-dy-cm-eknath-shindes-x-account-hacked/2934860</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/shinde-made-the-announcement-on-modi-s-birthday-125091700051_1.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/acharyadevvrattakes-oath-as-maharashtras-22nd-governor</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/uddhav-thackeray-led-shiv-sena-leader-ayodhya-poul-patil-received-call-from-eknath-shinde-office-call-recording-goes-viral/videoshow/123934054.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-gifts-namo-gardens-to-394-towns-on-pm-modis-75th-birthday-rs-394-crore-sanctioned/articleshow/123964170.cms</t>
+          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/eknath-shinde-mla-aamshya-padvi-tribal-reservation-opposition-abuses-protest-dhangar-banjara-controversy-gs97</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-shiv-sena-leaders-speech-adds-fuel-to-accusations-of-biased-allocation-of-funds-23595109</t>
+          <t>https://marathi.ndtv.com/videos/thane-ghodbunder-road-traffic-jaam-controversy-997251</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/heavy-vehicles-banned-on-thanes-ghodbunder-road-during-daytime-23594294</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pm-modi-birthday-eknath-shinde-s-leader-of-the-world-tribute-article-in-loksatta-saamana-omits-ad-1384700</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/eknath-shinde-mla-aamshya-padvi-tribal-reservation-opposition-abuses-protest-dhangar-banjara-controversy-gs97</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-thane-navratri-deputy-cm-eknath-shinde-attends-devi-arrival-procession-at-tembhinaka-traditional-festivities-begin-1386020</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/jansatta-special/jansatta-rajpaat-abhay-chautala-haryana-shinde-message-congress-du-election-bihar-seat-dispute-rld-up/4151302/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-maharashtra-deputy-cms-ajit-pawar-and-eknath-shinde-express-anger-over-ministerial-inefficiency-neglect-of-party-work-and-janata-darbar-1386067</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-pm-modi-birthday-eknath-shinde-s-leader-of-the-world-tribute-article-in-loksatta-saamana-omits-ad-1384700</t>
+          <t>https://lokmat.news18.com/videos/video/gadchiroli-news-merger-week-in-maoist-affected-areas-high-alert-issued-in-dandakarna-marathi-news-1075805.html</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/uddhav-thackeray-led-shiv-sena-leader-ayodhya-poul-patil-received-call-from-eknath-shinde-office-call-recording-goes-viral/videoshow/123934054.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-on-eknath-shinde-maharashtra-ahmedabad-bullet-train-anand-dighe-3015725</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-almatti-dam-height-increase-maharashtra-to-move-supreme-court-over-karnataka-s-decision-raising-flood-risk-for-sangli-kolhapur-shiv-sena-mobilizes-in-sambhaji-nagar-1384708</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-15-september-2025-zp-presidentship-reservation-nepal-violence-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-maharashtra-deputy-cms-ajit-pawar-and-eknath-shinde-express-anger-over-ministerial-inefficiency-neglect-of-party-work-and-janata-darbar-1386067</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-cabinet-discontent-bharat-gogawale-on-eknath-shinde-s-displeasure-ministerial-accountability-and-action-on-inefficient-ministers-1386103</t>
+          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-15-september-2025-3482219.html</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-thane-navratri-deputy-cm-eknath-shinde-attends-devi-arrival-procession-at-tembhinaka-traditional-festivities-begin-1386020</t>
+          <t>https://www.livehindustan.com/maharashtra/shiv-sena-ubt-mp-sanjay-raut-says-many-mlas-because-of-vote-chori-in-maharashtra-201758358063004.html</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
+          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278582902/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/thane-ghodbunder-road-traffic-jaam-controversy-997251</t>
+          <t>https://nagalandpost.com/bmc-polls-50-50-seats-for-sena-ubt-mns-in-mumbai-strongholds/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-15-september-2025-zp-presidentship-reservation-nepal-violence-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://www.afternoonvoice.com/the-chronological-formation-and-political-evolution-of-maharashtra.html</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-govt-fadnavis-cabinet-approves-8-major-decisions-including-expressway-and-new-policies-nck90</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/shiv-sena-ubt-mns-bjp-raj-thackeray-uddhav-thackeray-devendra-fadnavis-unite-against-shiv-sena-eknath-shinde-for-thane-sporting-committee-election/articleshow/123938834.cms</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/mahayuti-government-reservation-issue-new-controversy-reason-sw79</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-bmc-election-uddhav-thackeray-and-raj-thackeray-led-shiv-sena-and-mns-alliance-final-know-seat-sharing-formula-against-mahayuti/articleshow/124037610.cms</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/state-news/thane-metro-begins-trial-run-after-20-year-wait-19966553</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-15-september-2025-3482219.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/meenatai-thackeray-statue-smeared-with-red-paint-1-held-101758136336233.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/pm-modi-s-75th-birthday-netanyahu-vladimir-putin-giorgia-meloni-extend-birthday-wishes-to-pm-modi-2025-09-17</t>
+          <t>https://m.thewire.in/article/ptiprnews/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/thane-metro-dream-comes-true-after-20-year-new-lifelines-trial-run-begin-on-these-10-stations-19965341</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-state-cabinet-meeting-decision-devendra-fadnavis-eknath-shinde-ajit-pawar/articleshow/123917768.cms</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-decision-taken-i.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/shiv-sena-ubt-mns-bjp-raj-thackeray-uddhav-thackeray-devendra-fadnavis-unite-against-shiv-sena-eknath-shinde-for-thane-sporting-committee-election/articleshow/123938834.cms</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/articleshow/123993653.cms</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/statue-of-uddhav-thackeray-s-mother-defaced-in-mumbai-shiv-sena-ubt-protests-101758095171594.html</t>
+          <t>https://politalks.news/political-temperature-rises-in-maharashtra-ncp-chief-ajit-pawar-preparing-to-break-away-from-the-mahayuti</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/ndtv-yuva-conclave-milind-deora-on-which-leader-connects-with-gen-z-better-996976</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/pm-modi-turns-75-highlights-of-initiatives-launched-by-bjp-events-held-in-several-states/articleshow/123949298.cms</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-on-eknath-shinde-maharashtra-ahmedabad-bullet-train-anand-dighe-3015725</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ajit-pawars-absence-at-key-guv-events-raises-eyebrows/articleshow/124030467.cms</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharastra-paint-thrown-on-statue-of-meenatai-thackeray-at-mumbai-shivaji-park-2025-09-17</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/current-mlas-get-rs-2-crore-and-i-get-rs-20-crore-big-claim-by-former-shiv-sena-mla-sada-sarvankar/4153263/</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/raj-thackerays-cartoon-targets-amit-shah-son-over-indo-pak-match/article70061713.ece</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/shiv-sena-workers-protest-against-rauts-remarks-about-dighe/870443/</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/paint-thrown-at-statue-of-bal-thackerays-wife-meenatai-in-mumbai/article70062302.ece</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/kedar-dighes-sharp-attack-on-shinde-faction-anand-dighe-remembered-as-elections-approach/articleshow/124004160.cms</t>
+          <t>https://www.patrika.com/mumbai-news/uddhav-thackeray-mother-meenatai-statue-colour-thrown-accused-upendra-pawaskar-held-19954266</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/shiv-sena-leader-ex-mla-sada-sarvankar-claims-20-crore-fund-dispute-sparks-political-stir-3016545</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-sanjay-raut-supports-rahul-gandhi-saying-that-90-of-the-mahayuti-mlas-in-maharashtra-won-through-vote-theft/articleshow/124015667.cms</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/meenatai-thackerays-statue-defaced-at-mumbais-shivaji-park/869722/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-22-political-news-in-marathi-941153</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/despite-not-being-an-mla-i-received-a-fund-of-rs-20-crore-shiv-sena-leader-sarwankar/871651/</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-3/921531/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/uddhav-targets-bjp-over-india-pakistan-cricket-match-in-asia-cup-maharashtra-debt-2025-09-16</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-21-september-2025-india-vs-pakistan-%E2%80%93-asia-cup-maharashtra-politics-national-international-live-update-in-marathi-940858</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/blog/india/bjp-shivsena-ncp-congress-local-body-elections-your-bow-and-arrow-but-target-is-ours-drawing-dividing-line-blog-amitabh-srivastava-b507/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-17-political-news-in-marathi-939849</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/articleshow/123993653.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-14-political-news-in-marathi-939050</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/edit/invest-time-in-learning-about-the-world-we-live-in/5419/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-bmc-election-latest-update-mumbai-pune-rain-weather-today-devendra-fadnavis-on-uddhav-thackeray-shivsena-news-scj-81-5380824/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/pm-modi-turns-75-highlights-of-initiatives-launched-by-bjp-events-held-in-several-states/articleshow/123949298.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/dadar-shivaji-park-meenatai-thackeray-statue-red-color-thrown-mumbai-crime/articleshow/123936431.cms</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ajit-pawars-absence-at-key-guv-events-raises-eyebrows/articleshow/124030467.cms</t>
+          <t>https://marathi.ndtv.com/videos/fadnavis-is-an-uncivilized-chief-minister-sapkal-criticizes-fadnavis-996634</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://curlytales.com/india/ct-scoop/durga-puja-pandals-in-mumbai-where-you-can-spot-bollywood-celebrities/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-pm-narendra-modi-birthday-bmc-election-latest-update-mumbai-pune-rain-weather-today-devendra-fadnavis-on-uddhav-thackeray-shivsena-breaking-news-rak-94-5377898/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/meenatai-thackeray-statue-smeared-with-red-paint-1-held-101758136336233.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/breaking-news-today-live-updates-20-sept-maharashtra-political-news-rain-updates-shinde-thackeray-ajit-pawar-sharad-pawar-mumbai-pm-modi-940635</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/globe-nation/thackeray-brothers-hint-at-reunion-possible-political-realignment-in-maharashtra/16395/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-navratri-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-monday-22-september-2025-1497734.html</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-secret-of-2-5-hour-meeting-at-shivtirth-how-raj-thackeray-prevail-over-uddhav-political-experts-reveal-9622593.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/mumbai-mina-thackeray-statue-defaced-shivaji-park-shiv-sena-protest-police-action-ntc-dskc-2335896-2025-09-17</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/breaking-news-today-18-september-monsoon-maratha-reservation-obc-bmc-election-mumbai-local-train-weather-political-doctors-strike-tajya-batmya-in-marathi-940110</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-told-party-workers-bmc-elections-are-a-litmus-test-for-us/articleshow/123989198.cms</t>
+          <t>https://www.marathijagran.com/maharashtra/nashik/shardiya-navratri-2025-praveen-togadias-big-statement-at-hindu-hunkar-sabha-said-no-entry-for-muslims-at-garba-places-96201</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-3/921531/</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-tejashwi-yadav-calls-cm-nitish-a-cheat-minister-makes-these-big-promises-to-the-public-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-22-political-news-in-marathi-941153</t>
+          <t>https://www.republicbharat.com/pradhan-sevak/pm-modi-75th-birthday-today-bjp-seva-pakhwada-celebration-plan-congress-rahul-gandhi-trump-live-updates-live-news</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-sanjay-raut-supports-rahul-gandhi-saying-that-90-of-the-mahayuti-mlas-in-maharashtra-won-through-vote-theft/articleshow/124015667.cms</t>
+          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-16-17-september-live-updates-tejashwi-yadav-bihar-adhikar-yatra-election-pm-modi-rahul-gandi-supreme-court-sahastradhara-flood-waqf/4143389/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
+          <t>https://www.timesnowhindi.com/cities/aaj-ka-mausam-22-september-2025-up-bihar-jharkhand-himachal-uttarakhand-other-states-in-india-monsoon-flood-cloudburst-barish-hogi-ya-nhi-aaj-ka-mausam-kaisa-rahega-purvanuman-news-live-today-liveblog-152869390</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-21-september-2025-india-vs-pakistan-%E2%80%93-asia-cup-maharashtra-politics-national-international-live-update-in-marathi-940858</t>
+          <t>https://www.amarujala.com/video/india-news/pm-modi-gave-the-mantra-of-swadeshi-to-the-people-from-madhya-pradesh-told-this-method-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-17-september-2025-pm-narendra-modi-75th-birthday-zp-presidentship-reservation-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-ajit-pawat-led-ncp-hold-rashtravadi-chintan-shivir-in-nagpur-on-sept-19-ahead-of-local-body-polls/articleshow/123980165.cms</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/why-is-there-still-no-bjp-chief-minister-in-bihar-nitish-kumar-lalu-prasad-yadav-tejashwi-yadav-limited-grip-on-obc-voters-ebcs-mm76</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-14-political-news-in-marathi-939050</t>
+          <t>https://dainikekmat.com/%E0%A4%86%E0%A4%AE%E0%A4%9A%E0%A5%80-%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A5%80-%E0%A4%B8%E0%A4%9C%E0%A5%8D%E0%A4%9C/117544/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-17-political-news-in-marathi-939849</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/how-the-bjp-alliance-won-maharashtra-101757921779535.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/supreme-court-local-body-polls-order-a-slap-on-govt-face-says-opposition-in-maharashtra/articleshow/123928457.cms</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-gifts-namo-gardens-to-394-towns-on-pm-modis-75th-birthday-rs-394-crore-sanctioned/articleshow/123964170.cms</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/dadar-shivaji-park-meenatai-thackeray-statue-red-color-thrown-mumbai-crime/articleshow/123936431.cms</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/nanded-farmers-to-get-100-crop-loss-relief-553-crore-payout-begins-sep-22-minister/article70076412.ece</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/tet-exam-applications-open-from-monday-mandatory-for-teachers-up-to-53-years/articleshow/123887331.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/top-marathi-news-today-breaking-news-political-news-live-update-crime-news-994890.html</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/ola-uber-rapido-get-provisional-licences-for-bike-taxi-services-in-mumbai/article70055523.ece</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-navratri-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-monday-22-september-2025-1497734.html</t>
+          <t>https://www.newsonair.gov.in/maharashtra-launches-namo-gardens-and-tourism-skill-programme-to-mark-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/nashik/shardiya-navratri-2025-praveen-togadias-big-statement-at-hindu-hunkar-sabha-said-no-entry-for-muslims-at-garba-places-96201</t>
+          <t>https://thenewsmill.com/2025/09/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-tejashwi-yadav-calls-cm-nitish-a-cheat-minister-makes-these-big-promises-to-the-public-2025-09-18</t>
+          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-16-17-september-live-updates-tejashwi-yadav-bihar-adhikar-yatra-election-pm-modi-rahul-gandi-supreme-court-sahastradhara-flood-waqf/4143389/</t>
+          <t>https://clarionindia.net/ahmednagar-railway-station-renamed-concern-over-erasure-of-muslim-legacy/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://www.amarujala.com/india-news/maharastra-paint-thrown-on-statue-of-meenatai-thackeray-at-mumbai-shivaji-park-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/navi-mumbai-city-petition-filed-in-janata-darbar-against-minister-ganesh-naik-by-kishore-patkar/922934/</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/why-is-there-still-no-bjp-chief-minister-in-bihar-nitish-kumar-lalu-prasad-yadav-tejashwi-yadav-limited-grip-on-obc-voters-ebcs-mm76</t>
+          <t>https://www.amarujala.com/india-news/uddhav-targets-bjp-over-india-pakistan-cricket-match-in-asia-cup-maharashtra-debt-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/thane-city-challenge-to-eknath-shinde-in-the-fort-itself-bjp-leader-ganesh-naiks-janata-darbar-for-the-third-consecutive-time/</t>
+          <t>https://mandalnews.com/amravati/government-should-take-decision-with-a-common-perspective-regarding-tet-for-teachers/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/administration-should-be-alert-for-relief-and-rescue-operations-in-the-wake-of-heavy-rains-dcm-eknath-shindes-advice/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-date-extended-supreme-court-give-new-deadline-31st-january-2026-know-all/articleshow/123920003.cms</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%86%E0%A4%AE%E0%A4%9A%E0%A5%80-%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A5%80-%E0%A4%B8%E0%A4%9C%E0%A5%8D%E0%A4%9C/117544/</t>
+          <t>https://www.jansatta.com/national/prime-minister-narendra-modi-address-the-nation-live-today/4152510/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
+          <t>https://www.amarujala.com/india-news/cpwd-floats-tender-to-install-bulletproof-glass-in-chambers-of-eam-foreign-secy-at-jn-bhawan-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/politics/bhakti-for-modi-at-75-from-newspaper-ads-to-prayers-and-coordinated-social-media-posts</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-pichhade-varg-ke-sarakaaree-chhaatraavaas-ke-vidyaarthiyon-ke-dainik-bhatte-mein-vrddhi-ko-manjooree-1187663</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
+          <t>https://maharashtratimes.com/career/career-news/mahatet-exam-2025-mandatory-exam-confusion-for-senior-teachers-application-process-begins-from-15-september/articleshow/123893618.cms</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/nanded-farmers-to-get-100-crop-loss-relief-553-crore-payout-begins-sep-22-minister/article70076412.ece</t>
+          <t>https://www.etvbharat.com/mr/!state/teacher-mlas-demand-reconsideration-of-tet-mandatory-decision-in-maharashtra-maharashtra-news-mhs25091904556</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.ahmedabadmirror.com/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/81899457.html</t>
+          <t>https://dainikekmat.com/attorney-general-birendra-saraf-resigns/117476/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/the-chronological-formation-and-political-evolution-of-maharashtra.html</t>
+          <t>https://www.amarujala.com/india-news/vhp-s-hindu-only-diktat-for-garba-open-invitation-for-violence-ramdas-athawale-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/study-abroad/canada-tightens-international-student-visa-rules-as-rejections-hit-record-highs</t>
+          <t>https://www.aajtak.in/programmes/mumbai-metro/video/mumbai-metro-ameet-satam-controversial-statement-bmc-election-frvd-2335000-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/breaking-news-today-21st-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-ahmedabad-bullet-train-mega-block-sunday/liveblog/124023319.cms</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://clarionindia.net/ahmednagar-railway-station-renamed-concern-over-erasure-of-muslim-legacy/</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/maharashtra-cm-devendra-fadnavis-talk-on-obc-reservation/articleshow/123889715.cms</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/vhp-s-hindu-only-diktat-for-garba-open-invitation-for-violence-ramdas-athawale-2025-09-21</t>
+          <t>https://timesofindia.indiatimes.com/india/i-repeat-rahul-gandhis-weak-pm-jibe-after-trump-imposes-100000-fee-on-h-1b-visas-reshares-old-post/articleshow/124012869.cms</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/modi-govt-gave-rs-21-000-cr-for-marathwada-rail-lines-rs-450-crore-came-during-upa-time-fadnavis-2025-09-17</t>
+          <t>https://timesofindia.indiatimes.com/world/us/greatest-evangelist-for-american-liberty-donald-trump-pays-tribute-to-charlie-kirk-calls-him-immortal/articleshow/124034943.cms</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/cpwd-floats-tender-to-install-bulletproof-glass-in-chambers-of-eam-foreign-secy-at-jn-bhawan-2025-09-16</t>
+          <t>https://www.thehindu.com/news/cities/Tiruchirapalli/tamil-nadu-teachers-form-council-to-challenge-supreme-courts-ruling-on-eligibility-test/article70077321.ece</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-date-extended-supreme-court-give-new-deadline-31st-january-2026-know-all/articleshow/123920003.cms</t>
+          <t>https://timesofindia.indiatimes.com/india/tariffs-a-mistake-bolton-urges-india-us-talks-slams-donald-trumps-incoherent-approach/articleshow/123948590.cms</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/mumbai-metro/video/mumbai-metro-ameet-satam-controversial-statement-bmc-election-frvd-2335000-2025-09-17</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-police-restrict-heavy-truck-movement-for-eighteen-hours-daily-to-ease-traffic-congestion/articleshow/123927129.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/government-should-take-decision-with-a-common-perspective-regarding-tet-for-teachers/</t>
+          <t>https://maharashtratimes.com/video/mt-originals/ghodbunder-residents-anger-eknath-shindes-big-decision-these-vehicles-are-not-allowed-in-thane/videoshow/123919177.cms</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-pichhade-varg-ke-sarakaaree-chhaatraavaas-ke-vidyaarthiyon-ke-dainik-bhatte-mein-vrddhi-ko-manjooree-1187663</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-municipal-election-2025-mns-district-chief-raju-dindorle-will-join-bjp-mm76-rg93</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/career/career-news/mahatet-exam-2025-mandatory-exam-confusion-for-senior-teachers-application-process-begins-from-15-september/articleshow/123893618.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/bihar/bihar-vidhansabha-chunav-2025-election-dates-announcement-soon-cec-gyanesh-kumar-visit-patna-1363416.html</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-1384548</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/national/ahmednagar-railway-station-renamed-now-it-will-be-known-as-ahilyanagar/</t>
+          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/education/latest-and-important-news-of-22nd-september-for-school-assembly-read-the-latest-updates-related-to-national-international-and-sports-2759750.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/technical-panel-approves-2-stps-along-indrayani-cm/articleshow/124005440.cms</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/school-assembly-news-headlines-for-23-september-national-international-sports-big-updates-2760357.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/nashik-zilla-parishad-to-send-students-from-first-batch-of-super-50-to-nasa-for-educational-trip/articleshow/124003718.cms</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://joindia.co.in/news/maharashtra-gets-new-governor-acharya-devvrat-takes-charge-as-the-22nd-governor/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://joindia.co.in/news/maharashtra-gets-new-governor-acharya-devvrat-takes-charge-as-the-22nd-governor/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/attorney-general-birendra-saraf-resigns/117476/</t>
+          <t>https://curlytales.com/india/trending/what-are-namo-gardens-heres-all-about-eknath-shindes-green-gift-on-pm-modis-birthday/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/pune-news/maharashtra-cm-devendra-fadnavis-talk-on-obc-reservation/articleshow/123889715.cms</t>
+          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/breaking-news-today-21st-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-ahmedabad-bullet-train-mega-block-sunday/liveblog/124023319.cms</t>
+          <t>https://www.thehindu.com/news/national/tamil-nadu/state-floats-tender-to-prepare-master-plan-for-a-global-city/article70062521.ece</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/world/priyanka-gandhi-questions-centre-policy-on-palestine-issue-1363252.html</t>
+          <t>https://www.devdiscourse.com/article/business/3635550-metro-rail-lines-promise-to-ease-mumbais-traffic-woes</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/india/mehbooba-mufti-letter-to-amit-shah-for-yasin-malik-humanitarian-appeal-1361078.html</t>
+          <t>https://m.economictimes.com/news/mumbai-news/mmrda-temporarily-suspends-monorail-services-in-mumbai/articleshow/124009977.cms</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/video/mt-originals/ghodbunder-residents-anger-eknath-shindes-big-decision-these-vehicles-are-not-allowed-in-thane/videoshow/123919177.cms</t>
+          <t>https://www.newsx.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-71735/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-municipal-election-2025-mns-district-chief-raju-dindorle-will-join-bjp-mm76-rg93</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/maharashtra-ladki-bahin-yojana-ekyc-mandatory-beneficiaries-207500</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
+          <t>https://www.etvbharat.com/en/!state/fir-filed-against-tejashwi-yadav-india-bloc-leaders-in-alleged-welfare-scheme-fraud-case-in-bihar-darbhanga-enn25091601745</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-1384548</t>
+          <t>https://www.lokmattimes.com/aurangabad/no-new-proposals-from-marathwada/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
+          <t>https://thenewsmill.com/2025/09/mmrda-temporarily-suspends-monorail-services-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/technical-panel-approves-2-stps-along-indrayani-cm/articleshow/124005440.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-makes-e-kyc-mandatory-for-ladki-bahin-scheme-beneficiaries-sets-2-month-deadline-23594786</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
+          <t>https://www.patrika.com/mumbai-news/ladki-behna-e-kyc-mandatory-maharashtra-mukhyamantri-meri-ladli-behen-scheme-19958911</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178604/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maha-govt-ensures-transparency-in-ladki-bahin-yojana-asks-beneficiaries-to-complete-e-kyc-process-in-two-months-3735616</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/garware-youth-development-centre-satara-skill-training-helps-13-rural-youths-get-jobs-rds-00-5385521/</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/e-kyc-made-mandatory-for-beneficiaries-of-the-chief-ministers-majhi-laadki-behan-scheme-1360239.html</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/tamil-nadu/state-floats-tender-to-prepare-master-plan-for-a-global-city/article70062521.ece</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-aditi-tatkare-important-explanation-about-ladki-bahin-yojana/articleshow/123977249.cms</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
+          <t>https://marathi.abplive.com/business/mukhyamantri-ladki-bahin-yojana-ekyc-compulsory-for-all-check-how-complete-this-process-1385224</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://zeenews.india.com/marathi/photos/ladki-bahin-yojana-ekyc-kashi-karaychi-rule-change-by-maharashtra-government-documents-application-process-deadline-ifnormation-every-details-you-need-to-know/940522</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3630419-mla-ends-fast-nh-3-negligence-sparks-controversy-in-himachal?amp</t>
+          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831-77106/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/trial-run-held-for-metro-lines-4-and-4a-in-thane-project-to-cut-travel-time-significantly-101758530168095.html</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://propnewstime.com/getdetailsStories/MjE0NDY=/kdmc-told-to-file-economic-crime-case-over-65-unauthorized-buildings</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.theaustraliatoday.com.au/tim-watts-explores-cultural-collaboration-and-youth-initiatives-in-mumbai/</t>
+          <t>https://www.patrika.com/en/state-news/thane-metro-begins-trial-run-after-20-year-wait-19966553</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/mumbai-news/mmrda-temporarily-suspends-monorail-services-in-mumbai/articleshow/124009977.cms</t>
+          <t>https://marathi.ndtv.com/cities/mumbai-metro-4-thane-metro-trial-run-between-gaimukh-to-cadbury-junction-today-22-september-station-list-9319633</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-71735/</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/thane-thane-metro-stations-the-35-km-long-metro-will-make-the-journey-of-thane-residents-easier-thane-news-1385989</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/press-release/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/2938489</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/thane-gaimukh-to-wadala-metro-4-trial-today-read-its-route-and-other-details/articleshow/124037736.cms</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/karnataka/karnataka-proposes-law-to-fix-minimum-wage-work-hours-for-domestic-workers/article70074706.ece</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/hc-seeks-govt-s-stand-on-illegal-stay-on-demolition-by-dy-cm-101758137116362.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/religion/aaj-ka-rashifal-19-september-2025-today-horoscope-insights-for-your-lucky-zodiac-sign-1359827.html</t>
+          <t>https://www.ptinews.com/press-release/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/2938489</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/maharashtra-ladki-bahin-yojana-ekyc-mandatory-beneficiaries-207500</t>
+          <t>https://www.thehindu.com/news/national/uttarakhand/uttarakhand-govt-to-buy-produce-from-apple-growers-in-disaster-hit-dharali/article70076273.ece</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.com/india-news/ladki-bahin-yojana-2/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/photos/ladki-bahin-yojana-ekyc-kashi-karaychi-rule-change-by-maharashtra-government-documents-application-process-deadline-ifnormation-every-details-you-need-to-know/940522</t>
+          <t>https://www.freepressjournal.in/mumbai/cm-devendra-fadnavis-dycm-ajit-pawar-to-inaugurate-beedahilyanagar-rail-line-on-marathwada-mukti-sangram-din</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-aditi-tatkare-important-explanation-about-ladki-bahin-yojana/articleshow/123977249.cms</t>
+          <t>https://www.etvbharat.com/mr/!politics/maharashtra-total-debt-of-rs-9-lakh-32-thousand-crores-ajit-pawars-clarification-mhs25091906423</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
+          <t>https://timesofindia.indiatimes.com/world/us/charlie-kirk-assassination-did-tyler-robinson-confess-fbi-director-kash-patel-cites-dna-link-a-threatening-text/articleshow/123911719.cms</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/e-kyc-made-mandatory-for-beneficiaries-of-the-chief-ministers-majhi-laadki-behan-scheme-1360239.html</t>
+          <t>https://timesofindia.indiatimes.com/sports/cricket/asia-cup/asia-cup-abhishek-sharma-haris-rauf-in-heated-face-off-during-ind-vs-pak-clash-watch/articleshow/124031346.cms</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://dainikmaval.com/majhi-ladki-bhaeen-yojana-documents-are-required-for-e-kyc-know-website-and-process/</t>
+          <t>https://www.mypunepulse.com/acharya-devvrat-appointed-as-new-governor-of-maharashtra-to-take-oath-on-monday-know-his-gujarat-connection/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/ladki-bahin-yojana-updates-more-than-124000-mahila-disqualified-form-government-scheme-article-152828023</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
+          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/breaking-live-updates-22nd-september-marathi-news-maharashtra-weather-rain-alert-navratri-2025-ajit-pawar-devendra-fadnavis/liveblog/124035851.cms</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-technical-inspection-of-metro-4-and-4-a-from-gaimukh-to-vijay-garden-107468</t>
+          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/trial-of-metro-4-in-thane-begins-in-the-presence-of-chief-minister-devendra-fadnavis-local18-1485682.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-marathwada-four-people-died-150-people-were-trapped-in-floods-in-dharashiv/924053/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/thane-gaimukh-to-wadala-metro-4-trial-today-read-its-route-and-other-details/articleshow/124037736.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/bhubaneswar/odisha-sees-over-10-fold-increase-in-revenue-from-gutka-paan-masala-and-cigarette-sales/articleshow/124053527.cms</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://vsrsnews.in/pimpri-chinchwad/pune-acharya-devvrat-becomes-the-new-governor-of-maharashtra/</t>
+          <t>https://www.thehindu.com/elections/bihar-assembly/prashant-kishor-has-raised-hundreds-of-crores-of-rupees-through-shell-companies-alleges-bihar-bjp/article70075218.ece</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/thane-metro-4-and-4a-span-35-km-with-32-stations-trial-run-inspected-by-devendra-fadnavis-and-eknath-shinde-full-details-in-marathi-article-152872624</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/111-teachers-felicitated-with-krantijyoti-savitribai-phule-state-teacher-awards-101758565502417.html</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/explainer-a-test-of-mahayuti-in-bmc-elections-shiv-sena-bjp-tug-of-war-over-91-seats-article-152842707</t>
+          <t>https://thenewsmill.com/2025/09/acharya-devvrat-sworn-in-as-governor-of-maharashtra-reads-oath-in-sanskrit/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/uttarakhand/uttarakhand-govt-to-buy-produce-from-apple-growers-in-disaster-hit-dharali/article70076273.ece</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-assembly-election-2025-cm-nitish-eyes-the-lost-seats-of-paswan-and-kushwaha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bhubaneswar/odisha-sees-over-10-fold-increase-in-revenue-from-gutka-paan-masala-and-cigarette-sales/articleshow/124053527.cms</t>
+          <t>https://www.amarujala.com/video/india-news/tejashwi-yadav-bihar-adhikar-yatra-tejashwi-yadav-afraid-of-rahul-gandhi-bihar-election-2025-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-14-september-2025-asia-cup-cricket-hockey-pakistan-china-pm-modi-rain-alert-trump-israel-ukraine-russia-gaza-war-bjp-congress/liveblog/123877354.cms</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-rahul-gandhi-and-tejashwi-yadav-lalu-yadav-decide-on-seat-sharing-within-mahagathbandhan-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
+          <t>https://www.amarujala.com/video/india-news/chief-minister-bhagwant-mann-launched-mission-chadti-kala-for-flood-victims-in-punjab-made-this-appeal-to-t-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/i-repeat-rahul-gandhis-weak-pm-jibe-after-trump-imposes-100000-fee-on-h-1b-visas-reshares-old-post/articleshow/124012869.cms</t>
+          <t>https://www.amarujala.com/video/india-news/disha-patni-house-firing-case-the-accused-of-firing-at-disha-patni-s-house-were-killed-adg-told-the-whole-st-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
+          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/ahmednagar-railway-station-government-of-maharashtra/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/acharya-devvrat-is-the-new-governor-of-maharashtra-took-oath-in-the-presence-of-the-chief-minister.html</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278581344/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education</t>
+          <t>https://www.etvbharat.com/mr/!state/bengali-navratra-2025-in-pune-artists-craft-goddess-idols-from-bengals-sacred-soil-maharashtra-news-mhs25092001990</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-marathwada-four-people-died-150-people-were-trapped-in-floods-in-dharashiv/924053/</t>
+          <t>https://dainikekmat.com/ministerial-status-to-the-chairman-of-parashuram-corporation/117448/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/how-the-bjp-alliance-won-maharashtra-101757921779535.html</t>
+          <t>https://www.thehindu.com/news/national/congress-doing-negative-politics-over-great-nicobar-project-environment-minister/article70067325.ece</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/kerala/kerala-minister-v-sivankutty-taken-to-hospital-after-experiencing-dizziness-in-assembly/article70068758.ece</t>
+          <t>https://www.thehindu.com/news/national/karnataka/bk-singh-to-head-sit-formed-to-probe-aland-voter-fraud-case/article70074360.ece</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/elections/bihar-assembly/prashant-kishor-has-raised-hundreds-of-crores-of-rupees-through-shell-companies-alleges-bihar-bjp/article70075218.ece</t>
+          <t>https://www.aninews.in/news/national/general-news/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi20250917174418</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
+          <t>https://sundayguardianlive.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-139969/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/acharya-devvrat-sworn-in-as-governor-of-maharashtra-reads-oath-in-sanskrit/</t>
+          <t>https://www.devdiscourse.com/article/business/3636158-metro-milestone-thane-moves-closer-to-seamless-connectivity</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-assembly-election-2025-cm-nitish-eyes-the-lost-seats-of-paswan-and-kushwaha-2025-09-18</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/tejashwi-yadav-bihar-adhikar-yatra-tejashwi-yadav-afraid-of-rahul-gandhi-bihar-election-2025-2025-09-17</t>
+          <t>https://thecsrjournal.in/thane-metro-trial-run-hindi/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-rahul-gandhi-and-tejashwi-yadav-lalu-yadav-decide-on-seat-sharing-within-mahagathbandhan-2025-09-18</t>
+          <t>https://www.sakshipost.com/news/metro-line-connecting-thane-mumbai-be-operational-2026-end-says-cm-fadnavis-455400</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-patna-hc-directs-congress-to-remove-ai-video-featuring-pm-modi-s-mother-2025-09-17</t>
+          <t>https://www.thehindu.com/news/national/karnataka/congress-leaders-launch-campaign-alleging-vote-theft/article70080896.ece</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-patna-high-court-strict-on-ai-video-made-on-pm-modi-s-mother-nda-gave-this-reply-2025-09-18</t>
+          <t>https://www.newsonair.gov.in/union-minister-piyush-goyal-launches-swasth-nari-sashakt-parivar-campaign-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/chief-minister-bhagwant-mann-launched-mission-chadti-kala-for-flood-victims-in-punjab-made-this-appeal-to-t-2025-09-17</t>
+          <t>https://timesofindia.indiatimes.com/business/india-business/ai-startup-krutrim-faces-reality-check/articleshow/123908669.cms</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/disha-patni-house-firing-case-the-accused-of-firing-at-disha-patni-s-house-were-killed-adg-told-the-whole-st-2025-09-18</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/kumbh-mela-committee-accommodates-representatives-of-bjps-mahayuti-allies-ncp-shiv-sena/articleshow/124020480.cms</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/opposition-targets-shiv-sena-over-mumbais-gb-hway-traffic-ahead-of-civic-polls/articleshow/124020437.cms</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/acharya-devvrat-is-the-new-governor-of-maharashtra-took-oath-in-the-presence-of-the-chief-minister.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-workers-burn-effigy-of-shiv-sena-ubt-mp-sanjay-raut-for-his-remark-about-anand-dighe/articleshow/123981706.cms</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/ministerial-status-to-the-chairman-of-parashuram-corporation/117448/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/paint-thrown-on-statue-of-meenatai-thackeray-at-mumbai-s-shivaji-park-101758093317894.html</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/congress-doing-negative-politics-over-great-nicobar-project-environment-minister/article70067325.ece</t>
+          <t>https://www.newsband.in/article_detail/replicas-diversity-mark-devi-durgeshwari-fest-in-thane</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/karnataka/bk-singh-to-head-sit-formed-to-probe-aland-voter-fraud-case/article70074360.ece</t>
+          <t>https://www.jansatta.com/national/current-mlas-get-rs-2-crore-and-i-get-rs-20-crore-big-claim-by-former-shiv-sena-mla-sada-sarvankar/4153263/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831</t>
+          <t>https://hindi.theprint.in/india/despite-not-being-an-mla-i-received-a-fund-of-rs-20-crore-shiv-sena-leader-sarwankar/871651/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/satara/patan-taluka-tourism-development-projects-mini-train-adventure-activities-infrastructure-shambhuraj-desai-bam92</t>
+          <t>https://www.lokmatnews.in/blog/india/bjp-shivsena-ncp-congress-local-body-elections-your-bow-and-arrow-but-target-is-ours-drawing-dividing-line-blog-amitabh-srivastava-b507/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/pm-narendra-modi-a-strong-national-leader-maha-cm-devendra-fadnavis-wishes-pm-modi-on-his-75th-bday-hails-his-vision-to-reshape-indias-fortune</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://www.dainikprabhat.com/pimpri-news-shiv-sena-ready-for-elections-avoid-factionalism-get-to-work-shrirang-barnes-instructions-to-office-bearers/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://metrorailtoday.com/news/mmrda-commences-trial-test-run-on-mumbai-metro-line-4</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/sudhir-mungantiwar_16.html</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/thane-metro-trial-run-hindi/</t>
+          <t>https://scanx.trade/stock-market-news/stocks/hudco-re-appoints-baldeo-purushartha-as-government-nominee-director/19487527</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179135/</t>
+          <t>https://www.heraldgoa.in/globe-nation/atlantic-journalist-claims-he-was-accidentally-sent-u-s-war-plans-trump-responds/11525/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-piyush-goyal-launches-swasth-nari-sashakt-parivar-campaign-in-mumbai/</t>
+          <t>https://timesofindia.indiatimes.com/india/cant-be-on-whims-delhi-hc-raps-centre-over-delay-in-kejriwal-house-allotment-calls-for-clear-policy/articleshow/123976159.cms</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/opposition-targets-shiv-sena-over-mumbais-gb-hway-traffic-ahead-of-civic-polls/articleshow/124020437.cms</t>
+          <t>https://www.newsband.in/article_detail/thane-metro-line-4-train-run-conducted-successfully</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3630507-political-shocker-the-shooting-of-charlie-kirk-sparks-nationwide-debate?amp</t>
+          <t>https://hindi.theprint.in/india/trial-run-of-metro-line-4-and-4a-conducted-in-thane/871907/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/kumbh-mela-committee-accommodates-representatives-of-bjps-mahayuti-allies-ncp-shiv-sena/articleshow/124020480.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/iti-students-will-run-cleanliness-campaign-in-750-villages-special-campaign-by-minister-mangal-prabhat-lodha-on-pm-modis-birthday/articleshow/123915570.cms</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-workers-burn-effigy-of-shiv-sena-ubt-mp-sanjay-raut-for-his-remark-about-anand-dighe/articleshow/123981706.cms</t>
+          <t>https://www.hindisaamana.com/the-state-has-a-debt-of-rs-9-lakh-crores-development-of-the-state-is-stalled-deva-bhau-is-busy-in-advertising/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/replicas-diversity-mark-devi-durgeshwari-fest-in-thane</t>
+          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
+          <t>https://lokmanthan.com/arrangements-should-be-made-to-issue-all-relevant-permits-for-industries-in-a-single-application-chief-minister-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/sudhir-mungantiwar_16.html</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/jarange-plans-national-maratha-convention-in-delhi-hake-warns-of-obc-march-to-mumbai/articleshow/123952548.cms</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/bjps-criticism-of-sanjay-raut/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maratha-quota-activist-manoj-jarange-patil-announce-chalo-delhi-program-after-mumbai-reservation-protest-know-all/articleshow/123982783.cms</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/cant-be-on-whims-delhi-hc-raps-centre-over-delay-in-kejriwal-house-allotment-calls-for-clear-policy/articleshow/123976159.cms</t>
+          <t>https://indianexpress.com/article/cities/mumbai/acharya-devvrat-oath-maharashtra-governor-10250775/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/stocks/hudco-re-appoints-baldeo-purushartha-as-government-nominee-director/19487527</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-14-september-2025-asia-cup-cricket-hockey-pakistan-china-pm-modi-rain-alert-trump-israel-ukraine-russia-gaza-war-bjp-congress/liveblog/123877354.cms</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/globe-nation/atlantic-journalist-claims-he-was-accidentally-sent-u-s-war-plans-trump-responds/11525/</t>
+          <t>https://news.abplive.com/cities/eknath-shinde-s-x-account-hacked-images-of-pakistan-turkiye-s-flags-posted-1801504</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/thane-metro-line-4-train-run-conducted-successfully</t>
+          <t>https://www.thehindu.com/sport/cricket/former-delhi-captain-mithun-manhas-set-to-be-next-bcci-president/article70075244.ece</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/trial-run-of-metro-line-4-and-4a-conducted-in-thane/871907/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/transporters-cite-increased-costs-supply-disruptions-want-new-traffic-curbs-lifted/articleshow/124005110.cms</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/iti-students-will-run-cleanliness-campaign-in-750-villages-special-campaign-by-minister-mangal-prabhat-lodha-on-pm-modis-birthday/articleshow/123915570.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/trial-runs-on-metro-4s-cadbury-junction-gaimukh-stretch-to-commence-monday-mumbai-metropolitan-region-development-authority-officials-say-corridor-on-track-for-year-end-operations/articleshow/124001171.cms</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/parashuram-economic-development-corporation-chairman-ministerial-status-to-ashish-damle-thane-news-1384578</t>
+          <t>https://marathi.abplive.com/news/mumbai/sanjay-raut-statement-on-anand-dighe-thane-balasaheb-thackeray-photo-advertise-shivsena-maharashtra-marathi-news-1385015</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/the-state-has-a-debt-of-rs-9-lakh-crores-development-of-the-state-is-stalled-deva-bhau-is-busy-in-advertising/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/violence-escalates-in-maratha-obc-reservation-dispute-obc-leader-s-car-set-on-fire-in-jalna-125092300009_1.html</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>https://lokmanthan.com/arrangements-should-be-made-to-issue-all-relevant-permits-for-industries-in-a-single-application-chief-minister-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/jarange-plans-national-maratha-convention-in-delhi-hake-warns-of-obc-march-to-mumbai/articleshow/123952548.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maratha-quota-activist-manoj-jarange-patil-announce-chalo-delhi-program-after-mumbai-reservation-protest-know-all/articleshow/123982783.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>https://indianexpress.com/article/cities/mumbai/acharya-devvrat-oath-maharashtra-governor-10250775/</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/sport/cricket/former-delhi-captain-mithun-manhas-set-to-be-next-bcci-president/article70075244.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/transporters-cite-increased-costs-supply-disruptions-want-new-traffic-curbs-lifted/articleshow/124005110.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>https://news.abplive.com/cities/eknath-shinde-s-x-account-hacked-images-of-pakistan-turkiye-s-flags-posted-1801504</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/violence-escalates-in-maratha-obc-reservation-dispute-obc-leader-s-car-set-on-fire-in-jalna-125092300009_1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
         <is>
           <t>https://timesofindia.indiatimes.com/city/mumbai/thane-metro-4-4a-corridor-improves-transportation-reduce-congestion-on-gb-road-and-connectivity-in-thane-and-mumbai/articleshow/124029480.cms</t>
         </is>

--- a/Output/Eknath Shinde/extracted_links_Eknath Shinde_failed_links.xlsx
+++ b/Output/Eknath Shinde/extracted_links_Eknath Shinde_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A349"/>
+  <dimension ref="A1:A348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,231 +445,231 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ahead-of-bmc-elections-eknath-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena-23594416</t>
+          <t>https://www.tribuneindia.com/news/india/maharashtra-deputy-cm-eknath-shindes-x-account-hacked/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/eknath-shinde-maharashtra-deputy-cm-x-account-hacked-hackers-post-pakistan-turkey-flags-hacking-sparks-uproar-2025-09-21-1009219</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ahead-of-bmc-elections-eknath-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena-23594416</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/find-the-masterminds-behind-the-kdmc-illegal-buildings-scam-shinde-101758309996962.html</t>
+          <t>https://www.indiatvnews.com/maharashtra/eknath-shinde-maharashtra-deputy-cm-x-account-hacked-hackers-post-pakistan-turkey-flags-hacking-sparks-uproar-2025-09-21-1009219</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/when-i-go-to-villages-i-feel-fresh-my-opponents-get-depressed-says-dy-cm-eknath-shinde-at-launch-of-gram-samruddhi-yojana/articleshow/123964878.cms</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked/2934860</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-images-of-pakistan-turkey-flags-posted/articleshow/124024337.cms</t>
+          <t>https://www.oneindia.com/mumbai/eknath-shinde-twitter-account-hacked-and-sec-011-7866705.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
+          <t>https://www.thehindu.com/news/national/rahul-gandhis-vote-theft-charges-baseless-says-eknath-shinde/article70068660.ece</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/when-i-go-to-villages-i-feel-fresh-my-opponents-get-depressed-says-dy-cm-eknath-shinde-at-launch-of-gram-samruddhi-yojana/articleshow/123964878.cms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
+          <t>https://www.tribuneindia.com/news/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/eknath-shinde-x-handle-hacked-briefly-photos-of-pakistan-turkey-flags-posted-2790861-2025-09-21</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-images-of-pakistan-turkey-flags-posted/articleshow/124024337.cms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/paint-thrown-at-bust-of-uddhav-thackerays-late-mother-sena-workers-angry-probe-on-101758106562970.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/deputy-chief-minister-eknath-shindes-x-account-hacked-congress-leader-nana-patole-questions-cyber-security-in-maharashtra/articleshow/124029347.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-cong-leader-questions-cyber-security-23595093</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis/articleshow/123927714.cms</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/mla-warns-sanjay-raut-over-remarks-on-anand-dighe-shiv-sainiks-protest-in-kalyan-dombivli/articleshow/124011234.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-3737722</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/gst-rate-cut-will-boost-economy-shield-india-from-us-tariff-hikes-says-maharashtras-deputy-chief-minister-eknath-shinde/articleshow/124002613.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-gifts-modi-394-namo-udyans-101758050819661.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/gst-rate-cut-will-boost-economy-shield-india-from-us-tariff-hikes-says-maharashtras-deputy-chief-minister-eknath-shinde/articleshow/124002613.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/globe-nation/kunal-kamras-controversial-joke-targeting-eknath-shinde-sparks-backlash-from-shiv-sena-leaders/11935/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-dy-cm-eknath-shindes-x-account-hacked-cong-leader-questions-cyber-security-23595093</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/full-page-newspaper-ads-and-slew-of-initiatives-shiv-sena-goes-all-out-to-celebrate-pm-s-birthday/2925344</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/find-the-masterminds-behind-the-kdmc-illegal-buildings-scam-shinde-101758309996962.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/thane-shiv-sena-workers-protest-against-sanjay-raut-s-remark-about-anand-dighe-23594679</t>
+          <t>https://www.hindustantimes.com/india-news/paint-thrown-at-bust-of-uddhav-thackerays-late-mother-sena-workers-angry-probe-on-101758106562970.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/industry/strict-action-ordered-against-65-illegal-buildings-in-kalyan-dombivli-by-deputy-chief-minister-eknath-shinde/124008652</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/mla-warns-sanjay-raut-over-remarks-on-anand-dighe-shiv-sainiks-protest-in-kalyan-dombivli/articleshow/124011234.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ahead-of-bmc-polls-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena/2921488</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/thane-shiv-sena-workers-protest-against-sanjay-raut-s-remark-about-anand-dighe-23594679</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/stories-detail/national/maharashtra-dy-cm-eknath-shindes-x-account-hacked/2934860/0</t>
+          <t>https://realty.economictimes.indiatimes.com/news/industry/strict-action-ordered-against-65-illegal-buildings-in-kalyan-dombivli-by-deputy-chief-minister-eknath-shinde/124008652</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bombay-hc-can-plea-against-shinde-order-be-a-pil/articleshow/124022877.cms</t>
+          <t>https://www.ptinews.com/story/national/ahead-of-bmc-polls-shinde-asks-ex-corporators-to-tell-people-about-work-done-by-shiv-sena/2921488</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shiv-sena-publishes-full-page-ads-in-dailies-on-pms-birthday-shinde-hails-his-new-india-push/2923561</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/hc-seeks-govt-s-stand-on-illegal-stay-on-demolition-by-dy-cm-101758137116362.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-charges-baseless-says-ekanth-shinde-23594783</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bombay-hc-can-plea-against-shinde-order-be-a-pil/articleshow/124022877.cms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde-23595190</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thane-becomes-maharashtras-fifth-city-to-get-metro-services-3738811</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother20250916212035</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-charges-baseless-says-ekanth-shinde-23594783</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shinde-gifts-modi-394-namo-udyans-101758050819661.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde-23595190</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/awhad-slams-the-states-selective-compassion-over-demolition-notices</t>
+          <t>https://zeenews.india.com/india/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked-hackers-post-pakistan-turkey-flags-2962608.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-dy-cm-eknath-shinde-s-x-account-hacked-hackers-post-pakistan-turkey-flags-2962608.html</t>
+          <t>https://www.newsband.in/article_detail/awhad-slams-the-states-selective-compassion-over-demolition-notices</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/not-an-mla-but-get-rs-20-cr-in-funds-sena-leader-sarvankar-boasts-later-clarifies/articleshow/124028510.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/hc-to-shinde-by-what-authority-did-you-stay-navi-mumbai-civic-bodys-notice-to-raze-illegal-buildings/articleshow/123952725.cms</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/allies-in-conflict-bjp-shinde-sena-lock-horns-on-dahisar-toll-shift</t>
+          <t>https://www.ptinews.com/story/national/shiv-sena-publishes-full-page-ads-in-dailies-on-pms-birthday-shinde-hails-his-new-india-push/2923561</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/most-of-rs-46000cr-projects-for-marathwada-announced-by-shinde-led-cabinet-in-2023-still-on-paper/articleshow/123907066.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831</t>
+          <t>https://www.aninews.in/news/national/politics/public-will-teach-a-lesson-to-congress-eknath-shinde-over-deepfake-of-pm-modis-late-mother20250916212035</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/dy-cm-shindes-x-account-hacked-cong-leader-questions-cyber-security/2935531</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/most-of-rs-46000cr-projects-for-marathwada-announced-by-shinde-led-cabinet-in-2023-still-on-paper/articleshow/123907066.cms</t>
         </is>
       </c>
     </row>
@@ -683,455 +683,455 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/heavy-vehicles-banned-on-thane-s-ghodbunder-road-during-daytime/2919586</t>
+          <t>https://www.devdiscourse.com/article/politics/3630506-shinde-gears-up-for-mumbai-civic-polls-with-strategic-directives</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/prioritise-development-in-14-villages-added-to-navi-mumbai-civic-limits-dy-cm-shinde/2930925</t>
+          <t>https://www.socialnews.xyz/2025/09/15/mumbai-acharya-devvrat-sworn-in-as-maharashtra-governor-gallery/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/hc-to-shinde-by-what-authority-did-you-stay-navi-mumbai-civic-bodys-notice-to-raze-illegal-buildings/articleshow/123952725.cms</t>
+          <t>https://kashmirlife.net/maharashtra-deputy-cm-eknath-shindes-x-account-hacked-406229/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/shiv-senaubt-continues-attacking-dy-cm-shinde-says-maha-govt-boastful-454108</t>
+          <t>https://timesofindia.indiatimes.com/india/not-an-mla-but-get-rs-20-cr-in-funds-sena-leader-sarvankar-boasts-later-clarifies/articleshow/124028510.cms</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-polls-an-acid-test-for-shiv-sena-ubt-says-thackeray-101758222779307.html</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane20250922143831</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/~/district-administration-should-remain-alert-for-relief-and-rescue-operations-in-wake-of-heavy-rains-says-deputy-cm-shinde/States/news/3577807.html</t>
+          <t>https://www.ptinews.com/story/national/women-office-bearers-workers-of-sena-ubt-from-palghar-join-shinde-led-sena-ahead-of-local-polls/2927880</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/women-office-bearers-workers-of-sena-ubt-from-palghar-join-shinde-led-sena-ahead-of-local-polls/2927880</t>
+          <t>https://www.newsband.in/article_detail/replicas-diversity-mark-devi-durgeshwari-fest-in-thane</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/acharyadevvrattakes-oath-as-maharashtras-22nd-governor</t>
+          <t>https://www.devdiscourse.com/article/politics/3629545-uddhav-thackeray-criticizes-indias-cricket-match-with-pakistan-questions-bjps-patriotism</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-polls-an-acid-test-for-shiv-sena-ubt-says-thackeray-101758222779307.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://thewire.in/politics/bhakti-for-modi-at-75-from-newspaper-ads-to-prayers-and-coordinated-social-media-posts</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-police-restrict-heavy-truck-movement-for-eighteen-hours-daily-to-ease-traffic-congestion/articleshow/123927129.cms</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/namo-gardens-to-be-developed-in-394-municipal-councils-and-nagar-panchayats-in-maharashtra-23594437</t>
+          <t>https://www.deccanherald.com/india/maharashtra/massive-rains-hit-marathwada-region-of-maharashtra-3739003</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/parshuram-economic-development-corporation-chairman-ashish-damle-to-get-ministerial-status-says-maharashtra-govt-23594308</t>
+          <t>https://www.ptinews.com/story/national/take-action-against-those-involved-in-constructing-65-illegal-buildings-in-kalyan-dombivali-shinde/2931430</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-shiv-sena-leaders-speech-adds-fuel-to-accusations-of-biased-allocation-of-funds-23595109?lifestyle-dr-love-breakingnews</t>
+          <t>https://www.ptinews.com/story/national/ncp-sp-cong-welcome-sc-order-on-maharashtra-local-bodies-polls-mahayuti-will-win-says-shinde/2920944</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/bombay-hc-challenges-shinde-s-halt-to-navi-mumbai-demolitions/west/news/3581496.html</t>
+          <t>http://www.uniindia.com/~/district-administration-should-remain-alert-for-relief-and-rescue-operations-in-wake-of-heavy-rains-says-deputy-cm-shinde/States/news/3577807.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/globe-nation/kunal-kamra-challenges-fir-over-gaddar-jibe-at-maharashtra-deputy-cm-in-bombay-high-court/11930/</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3633705-infrastructure-revamp-a-new-dawn-for-navi-mumbais-villages</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/heavy-vehicles-banned-on-thanes-ghodbunder-road-during-daytime-23594294</t>
+          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/mmrda-temporarily-suspends-monorail-services-in-mumbai20250920092952</t>
+          <t>https://www.devdiscourse.com/article/law-order/3635208-hacking-scandal-deputy-cms-account-breached-ahead-of-asia-cup-clash</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-21-news-updates-live-updates-weather-update-mumbai-monsoon-18331429</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/parshuram-economic-development-corporation-chairman-ashish-damle-to-get-ministerial-status-says-maharashtra-govt-23594308</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/en/politics/government-will-pay-inr-200-crores-owed-to-shiv-bhojan-thali-kendra-operators-90025</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/eknath-shinde-account-hacked-during-india-pakistan-asia-cup-cybercrime-cybersecurity-national-flags-of-turkey-and-pakistan-restored-in-45-minutes-75975/</t>
+          <t>https://www.outlookindia.com/national/maharashtra-reaffirms-commitment-to-ladki-bahin-yojana-ahead-of-elections</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi/</t>
+          <t>https://www.aninews.in/news/national/general-news/mmrda-temporarily-suspends-monorail-services-in-mumbai20250920092952</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/live-blog/mumbai-news-live-updates-india-national-news-2025-september-21-news-updates-live-updates-weather-update-mumbai-monsoon-18331429</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://thehindustangazette.com/election/eknath-shinde-x-account-hacked-pak-turkey-flags-39959</t>
+          <t>https://www.bignewsnetwork.com/news/278582902/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-slams-incapable-ministers-after-ajit-pawar-for-ignoring-party-expansion-and-administrative-work/articleshow/124050348.cms</t>
+          <t>https://www.newsx.com/india/eknath-shinde-account-hacked-during-india-pakistan-asia-cup-cybercrime-cybersecurity-national-flags-of-turkey-and-pakistan-restored-in-45-minutes-75975/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hindi/</t>
+          <t>https://thenewsmill.com/2025/09/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/deputy-cm-eknath-shinde-x-account-hack-pakistan-turkey-flag-shown-3016093</t>
+          <t>https://www.onenewspage.com/n/India/1zs7f2zwo6/Eknath-Shinde-rallies-former-corporators-to-showcase-Shiv.htm</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flags-9649355.html</t>
+          <t>https://thehindustangazette.com/election/eknath-shinde-x-account-hacked-pak-turkey-flags-39959</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/sanjay-raut-comments-about-eknath-shinde-mentor-anand-dighe-sparked-an-uproar-201758252385682.html</t>
+          <t>https://www.abplive.com/states/maharashtra/deputy-cm-eknath-shinde-x-account-hack-pakistan-turkey-flag-shown-3016093</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/deputy-cm-eknath-shinde-x-account-hacked-hackers-posted-images-of-pakistan-and-turkey-flags/articleshow/124025137.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-slams-incapable-ministers-after-ajit-pawar-for-ignoring-party-expansion-and-administrative-work/articleshow/124050348.cms</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-bmc-election-eknath-shinde-group-plan-b-revealed-challenge-to-devendra-fadnavis-bjp-9653396.html</t>
+          <t>https://thecsrjournal.in/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hindi/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-claims-mahayuti-saffron-flag-will-fly-in-bmc-and-all-maharashtra-local-body-elections/articleshow/124032659.cms</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-deputy-cm-eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flags-9649355.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/ganesh-naik-vs-eknath-shinde-in-navi-mumbai-tussle-over-janata-darbar-petition-filed-in-high-court/articleshow/123996455.cms</t>
+          <t>https://www.facebook.com/DNHindi/photos/%E0%A4%B8%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%8F%E0%A4%95%E0%A4%A8%E0%A4%BE%E0%A4%A5-%E0%A4%B6%E0%A4%BF%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%95%E0%A4%BE-x-%E0%A4%85%E0%A4%95%E0%A4%BE%E0%A4%89%E0%A4%82%E0%A4%9F-%E0%A4%B9%E0%A5%88%E0%A4%95-%E0%A4%B9%E0%A5%88%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%B2%E0%A4%97%E0%A4%BE%E0%A4%88-%E0%A4%AA%E0%A4%BE%E0%A4%95%E0%A4%BF%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A4%BE%E0%A4%A8-%E0%A4%A4%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9D%E0%A4%82%E0%A4%A1%E0%A5%87eknathsi/1251272843711787/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.republicbharat.com/india/maharashtra-dy-cm-eknath-shinde-x-account-hacked-posting-images-of-pakistan-and-turkey-flag</t>
+          <t>https://www.livehindustan.com/national/sanjay-raut-comments-about-eknath-shinde-mentor-anand-dighe-sparked-an-uproar-201758252385682.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-deputy-cm-eknath-shinde-x-handle-hacked-hackers-shared-posts-with-pakistan-and-turkey-flags-2025-09-21-1164034</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/eknath-shinde-x-account-hacked-pakistan-turkey-flag-posted-ntc-rptc-2338322-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://hindi.newsbytesapp.com/news/india/eknath-shinde-s-ex-account-hacked-hackers-posted-flags-of-pakistan-and-turkiye/story</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/deputy-cm-eknath-shinde-x-account-hacked-hackers-posted-images-of-pakistan-and-turkey-flags/articleshow/124025137.cms</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-uddhav-thackeray-puts-bold-conditions-for-rebels-nagar-sevak-for-ghar-wapsi-for-shinde-shiv-sena-ahead-of-bmc-polls-know-all/articleshow/123978190.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-on-eknath-shinde-maharashtra-ahmedabad-bullet-train-anand-dighe-3015725</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/sanjay-raut-said-eknath-shinde-mentality-is-very-low-level-there-is-nothing-left-to-talk-about-2025-09-20-1163910</t>
+          <t>https://www.abplive.com/states/maharashtra/eknath-shinde-strict-against-builders-involved-in-kalyan-dombivali-illegal-buildings-constructing-3015585</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/ganesh-naik-vs-eknath-shinde-in-navi-mumbai-tussle-over-janata-darbar-petition-filed-in-high-court/articleshow/123996455.cms</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/maharashtra/eknath-shinde-x-account-hacked-pakistani-flags-posted-125092100012_1.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/eknath-shinde-claims-mahayuti-saffron-flag-will-fly-in-bmc-and-all-maharashtra-local-body-elections/articleshow/124032659.cms</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-deputy-cm-eknath-shinde-s-twitter-account-hacked-raises-cybersecurity-concerns-201758454098732.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-bmc-election-eknath-shinde-group-plan-b-revealed-challenge-to-devendra-fadnavis-bjp-9653396.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/pm-modi-birthday-congress-declares-pm-modi-s-birthday-as-black-day-enraged-eknath-shinde-issues-warning-2025-09-17</t>
+          <t>https://hindi.newsbytesapp.com/news/india/eknath-shinde-s-ex-account-hacked-hackers-posted-flags-of-pakistan-and-turkiye/story</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/maharashtra-deputy-cm-eknath-shinde-x-account-hacked-pakistan-turkiye-flag-shown-on-handle/2930969</t>
+          <t>https://www.indiatv.in/maharashtra/maharashtra-deputy-cm-eknath-shinde-x-handle-hacked-hackers-shared-posts-with-pakistan-and-turkey-flags-2025-09-21-1164034</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/shiv-sena-mla-sada-sarvankar-met-maharashtra-navnirman-sena-president-raj-thackeray-3016893</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-uddhav-thackeray-puts-bold-conditions-for-rebels-nagar-sevak-for-ghar-wapsi-for-shinde-shiv-sena-ahead-of-bmc-polls-know-all/articleshow/123978190.cms</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-deputy-chief-minister-ekanth-shinde-says-rahul-gandhi-s-vote-theft-charges-baseless-2025-09-19</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-warning-for-eknath-shinde-ajit-pawar-ncp-sharad-pawar-bjp-in-war-over-devendra-fadnavis-bmc-polls-claim-9632643.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/eknath-shinde-takes-action-against-kalyan-dombivli-illegal-buildings-builders/articleshow/124011899.cms</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/eknath-shindes-x-account-hacked-pictures-of-islamic-countries-and-turkish-flags-posted-11708</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-namo-park-scheme-for-pm-narendra-modi-75th-birthday-deputy-cm-eknath-shinde-announcement-3014117</t>
+          <t>https://www.amarujala.com/video/india-news/pm-modi-birthday-congress-declares-pm-modi-s-birthday-as-black-day-enraged-eknath-shinde-issues-warning-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/politics/focus-on-administration-and-oversight-shinde-launches-mission-mumbai-for-bmc-elections/871175/</t>
+          <t>https://hindi.webdunia.com/maharashtra/eknath-shinde-x-account-hacked-pakistani-flags-posted-125092100012_1.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
+          <t>https://www.indiatv.in/maharashtra/sanjay-raut-said-eknath-shinde-mentality-is-very-low-level-there-is-nothing-left-to-talk-about-2025-09-20-1163910</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/video/pm-modi-75th-birthday-piyush-goyal-eknath-shinde-wishes-ytvd-2335022-2025-09-17</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-deputy-chief-minister-ekanth-shinde-says-rahul-gandhi-s-vote-theft-charges-baseless-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/kedar-dighes-sharp-attack-on-shinde-faction-anand-dighe-remembered-as-elections-approach/articleshow/124004160.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/shiv-sena-mla-sada-sarvankar-met-maharashtra-navnirman-sena-president-raj-thackeray-3016893</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/pratap-sarnaik-comments-on-uddhav-thackeray-sanjay-raut-praises-eknath-shinde-respect-senior-leaders-3016095</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-namo-park-scheme-for-pm-narendra-modi-75th-birthday-deputy-cm-eknath-shinde-announcement-3014117</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/thane-metro-trial-run-on-september-22-thane-residents-dream-to-come-true/articleshow/124004146.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/eknath-shinde-takes-action-against-kalyan-dombivli-illegal-buildings-builders/articleshow/124011899.cms</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/under-what-authority-were-the-municipal-corporation-notice-to-demolish-buildings-stopped-high-court-ask-on-eknath-shinde-whether-the-dcm-has-the-authority-to-make-that-decision-1384909</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbai-metro-4-trial-cadbury-junction-gaimukh-devendra-fadnavis-eknath-shinde-and-ajit-pawar-to-join/articleshow/124035219.cms</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/thane/ghodbunder-residents-will-be-freed-from-traffic-jams-orders-to-leave-heavy-vehicles-after-12-midnight-eknath-shinde-orders-1384427</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/kedar-dighes-sharp-attack-on-shinde-faction-anand-dighe-remembered-as-elections-approach/articleshow/124004160.cms</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/eknath-shinde-treated-australian-guests-to-a-feast-of-vada-pav-9289261</t>
+          <t>https://www.abplive.com/states/maharashtra/pratap-sarnaik-comments-on-uddhav-thackeray-sanjay-raut-praises-eknath-shinde-respect-senior-leaders-3016095</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/jansatta-special/jansatta-rajpaat-abhay-chautala-haryana-shinde-message-congress-du-election-bihar-seat-dispute-rld-up/4151302/</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/thane-metro-trial-run-on-september-22-thane-residents-dream-to-come-true/articleshow/124004146.cms</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/short-videos/congress-mp-praniti-shinde-criticizes-eknath-shinde/939828</t>
+          <t>https://www.jansatta.com/jansatta-special/jansatta-rajpaat-abhay-chautala-haryana-shinde-message-congress-du-election-bihar-seat-dispute-rld-up/4151302/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/the-high-court-has-questioned-eknath-shinde-over-the-suspension-of-action-against-illegal-construction-in-navi-mumbai-1384988</t>
+          <t>https://marathi.ndtv.com/maharashtra/thane-ghodbunder-news-good-news-for-thane-kalyan-badlapur-commuters-as-eknath-shinde-orders-restriction-of-heavy-vehicles-untill-midnight-9291074</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/sanjay-raut-says-eknath-shinde-who-is-there-today-is-because-of-rajan-vichare-sacrifice-marathi-news-update-1385178</t>
+          <t>https://marathi.abplive.com/news/politics/the-high-court-has-questioned-eknath-shinde-over-the-suspension-of-action-against-illegal-construction-in-navi-mumbai-1384988</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/shiv-sena-leader-eknath-shinde-slams-incapable-ministers-for-ignoring-party-expansion-and-administrative-work/articleshow/124045917.cms</t>
+          <t>https://marathi.abplive.com/news/mumbai/under-what-authority-were-the-municipal-corporation-notice-to-demolish-buildings-stopped-high-court-ask-on-eknath-shinde-whether-the-dcm-has-the-authority-to-make-that-decision-1384909</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticized-eknath-shinde-for-washing-rajan-vichares-feet-and-taking-a-pilgrimage/923077/</t>
+          <t>https://www.bakharlive.com/maharashtra/deputy-chief-minister-eknath-shinde-announces-to-set-up-namo-parks-in-394-cities-of-the-state/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-decision-mandatory-to-construct-administrative-buildings-of-municipal-councils-according-to-the-model-plan-1482062.html</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/shiv-sena-leader-eknath-shinde-slams-incapable-ministers-for-ignoring-party-expansion-and-administrative-work/articleshow/124045917.cms</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-bala-saheb-was-brand-not-you-fadnavis-attacks-uddhav-thackeray-reveals-2019-bmc-election-truth-ws-l-9635814.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticized-eknath-shinde-for-washing-rajan-vichares-feet-and-taking-a-pilgrimage/923077/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/deputy-chief-minister-eknath-shinde-reaction-to-prime-minister-narendra-modi-s-gst-cut-ladki-bahin-yojana-news-1385846</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-decision-mandatory-to-construct-administrative-buildings-of-municipal-councils-according-to-the-model-plan-1482062.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/thane-ghodbunder-news-good-news-for-thane-kalyan-badlapur-commuters-as-eknath-shinde-orders-restriction-of-heavy-vehicles-untill-midnight-9291074</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-bala-saheb-was-brand-not-you-fadnavis-attacks-uddhav-thackeray-reveals-2019-bmc-election-truth-ws-l-9635814.html</t>
         </is>
       </c>
     </row>
@@ -1145,35 +1145,35 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/eknath-shinde-first-reaction-on-meenatai-thackeray-dadar-statue-issue-he-will-not-be-released-i-have-spoken-to-the-police-commissioner-1384826</t>
+          <t>https://marathi.abplive.com/news/maharashtra/sanjay-raut-says-eknath-shinde-who-is-there-today-is-because-of-rajan-vichare-sacrifice-marathi-news-update-1385178</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-deputy-chief-minister-eknath-shinde-launches-the-seva-fortnight-chief-minister-samruddhi-panchayat-raj-abhiyan-in-thane-district/922593/</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-shinde-first-reaction-on-meenatai-thackeray-dadar-statue-issue-he-will-not-be-released-i-have-spoken-to-the-police-commissioner-1384826</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/changes-in-gst-rates-will-lead-to-the-ghatsthapna-of-superpower-in-country-eknath-shinde-96248</t>
+          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/cm-fadnavis-change-eknath-shindes-decision-to-ban-heavy-vehicles-from-morning-6-to-12-night-to-solve-traffic-congestion-9316039</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-many-office-bearers-of-uddhav-thackeray-group-join-shiv-sena-95696</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-ajit-pawar-and-eknath-shinde-reprimand-maharashtra-cabinet-over-performance-and-neglect-of-party-organization-1386101</t>
         </is>
       </c>
     </row>
@@ -1187,77 +1187,77 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shindes-ex-account-hacked-96111</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/changes-in-gst-rates-will-lead-to-the-ghatsthapna-of-superpower-in-country-eknath-shinde-96248</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/other-cities/parashuram-development-board-chairman-given-ministerial-rank/</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-response-after-sanjay-raut-objected-to-placing-anand-dighes-photo-next-to-balasaheb-thackeray/922799/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-municipal-elections-eknath-shinde-puts-shiv-sena-in-action-mode-with-direct-orders-to-corporators-sharad-pawar-also-eyes-victory-in-corporations-1384728</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-meeting-with-mla-from-mumbai-preparing-bmc-elections-likely-scared-of-vote-chori-1480939.html</t>
+          <t>https://marathi.ndtv.com/cities/cm-fadnavis-change-eknath-shindes-decision-to-ban-heavy-vehicles-from-morning-6-to-12-night-to-solve-traffic-congestion-9316039</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-rain-heavy-rainfall-in-beed-40-villagers-should-be-airlifted-dcm-eknath-shinde-ordered-9279677</t>
+          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/mns-leader-avinash-jadhav-slams-eknath-shinde-over-thane-traffic-issue/articleshow/123926772.cms</t>
+          <t>https://marathi.abplive.com/news/thane/ghodbunder-residents-will-be-freed-from-traffic-jams-orders-to-leave-heavy-vehicles-after-12-midnight-eknath-shinde-orders-1384427</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/now-there-is-only-one-type-plan-for-the-administrative-buildings-of-the-municipal-council-and-municipal-panchayats-eknath-shinde-9294836</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/i-am-not-an-mla-yet-i-received-20-crore-rupees-statement-by-former-mla-saravankar-a-supporter-of-shinde-1189597</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-feeds-australian-mp-tim-watts-mumbais-vada-pav/922339/</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-rain-heavy-rainfall-in-beed-40-villagers-should-be-airlifted-dcm-eknath-shinde-ordered-9279677</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shindes-response-after-sanjay-raut-objected-to-placing-anand-dighes-photo-next-to-balasaheb-thackeray/922799/</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-review-maharashtra-and-mumbai-rain-updates-orders-airlift-beed-ashti-villagers-1480338.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-review-maharashtra-and-mumbai-rain-updates-orders-airlift-beed-ashti-villagers-1480338.html</t>
+          <t>https://marathi.ndtv.com/cities/now-there-is-only-one-type-plan-for-the-administrative-buildings-of-the-municipal-council-and-municipal-panchayats-eknath-shinde-9294836</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-many-office-bearers-of-uddhav-thackeray-group-join-shiv-sena-95696</t>
+          <t>https://www.mumbaitak.in/political-news/story/eknath-shinde-x-account-hack-turkey-and-pakistani-flag-show-cyber-crime-3203184-2025-09-21</t>
         </is>
       </c>
     </row>
@@ -1271,14 +1271,14 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/video-eknath-shinde-orders-urgent-relief-marathwada-floods-districts-ndrfs-airlift-operations-vsd-99-5391648/</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/mns-leader-avinash-jadhav-slams-eknath-shinde-over-thane-traffic-issue/articleshow/123926772.cms</t>
         </is>
       </c>
     </row>
@@ -1292,98 +1292,98 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-district-administration-should-remain-alert-in-wake-of-heavy-rains-eknath-shinde-instructs-94887</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-big-announces-on-pm-modi-birthday-say-all-municipal-councils-will-be-established-namo-udyan-in-maharashtra-95314</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/eknath-shinde-big-announces-on-pm-modi-birthday-say-all-municipal-councils-will-be-established-namo-udyan-in-maharashtra-95314</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/17/namo-udyan-will-be-developed-in-all-municipal-councils-and-nagar-panchayats-in-the-state-deputy-chief-minister.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-working-on-plan-b-for-bmc-election-likely-shock-to-uddhav-thackeray-and-bjp-also-1484790.html</t>
+          <t>https://www.loksatta.com/mumbai/high-court-orders-deputy-chief-minister-eknath-shinde-mumbai-print-news-phm-00-5381244/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-solve-bmtc-employee-problem-gave-10-lakh-for-compensation-1484524.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-rains-district-administration-should-remain-alert-in-wake-of-heavy-rains-eknath-shinde-instructs-94887</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/deputy-cm-eknath-shinde-on-heavy-rains-and-alert-to-district-administration/921681/</t>
+          <t>https://www.mumbaitak.in/political-news/story/sanjay-raut-has-strongly-criticized-eknath-shinde-for-printing-photos-of-balasaheb-thackeray-and-anand-dighe-side-by-side-in-an-advertisement-wishing-pm-modi-a-happy-birthday-3202688-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/thane-sporting-club-election-eknath-shinde-shiv-sena-won-over-bjp-mns-ubt-devendra-fadnavis-uddhav-thackeray-raj-thackeray-maharashtra-politics/articleshow/124041703.cms</t>
+          <t>https://www.loksatta.com/navimumbai/court-petition-challenges-ganesh-naik-janata-darbar-navi-mumbai-amid-eknath-shinde-naik-controversy-vsd-99-5383895/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/wadigodri-crime-news-fake-cid-officers-stole-the-golden-ring/</t>
+          <t>https://www.mymahanagar.com/maharashtra/deputy-cm-eknath-shinde-on-heavy-rains-and-alert-to-district-administration/921681/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.mumbaitak.in/political-news/story/sanjay-raut-has-strongly-criticized-eknath-shinde-for-printing-photos-of-balasaheb-thackeray-and-anand-dighe-side-by-side-in-an-advertisement-wishing-pm-modi-a-happy-birthday-3202688-2025-09-18</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-eknath-shinde-office-call-thackeray-worker-ayodhya-paul-audio-clip-viral-135941678.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-eknath-shinde-s-shiv-sena-in-action-mode-confident-of-mahayuti-victory-in-mumbai-civic-polls-directs-corporators-to-start-work-1384673</t>
+          <t>https://www.mymahanagar.com/mahamumbai/withdrew-the-rs-2-5-crore-fund-given-for-sewage-plant-and-drainage-because-former-corporator-deepmala-badhe-belonged-to-the-thackeray-group/922264/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/thane-metro-controversy-dcm-eknath-shinde-reply-to-sanjay-raut-thane-metro-halt-criticism-i-removed-the-speed-breaker-1497959.html</t>
+          <t>https://news18marathi.com/maharashtra/eknath-shinde-led-shiv-sena-working-on-plan-b-for-bmc-election-likely-shock-to-uddhav-thackeray-and-bjp-also-1484790.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-ghodbandar-road-eknath-shinde-ghodbandar-residents-will-be-free-from-traffic-congestion/922259/</t>
+          <t>https://marathi.ndtv.com/videos/after-ajit-pawar-eknath-shinde-will-also-hold-a-road-show-in-nagpur-shinde-s-mission-vidarbha-997770</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-says-anand-dighe-never-sold-shiv-sena/923100/</t>
+          <t>https://www.loksatta.com/thane/ghodbunder-protest-ghodbunder-road-heavy-vehicle-restrictions-eknath-shinde-traffic-orders-zws-70-5377800/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/local-elections-mahayuti-will-win-in-the-local-self-government-elections-eknath-shinde-is-confident/922171/</t>
+          <t>https://maharashtratimes.com/india-news/bihar-assembly-election-amit-shah-meets-bjp-workers-gives-60-days-plan-ahead-of-poll/articleshow/123995857.cms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/shivsena-dasara-melava-shiv-sena-shinde-group-planning-finalized-special-responsibility-on-mumbai-mlas-and-newly-elected-department-heads-maharashtra-politics-marathi-news-1385340</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-ghodbandar-road-eknath-shinde-ghodbandar-residents-will-be-free-from-traffic-congestion/922259/</t>
         </is>
       </c>
     </row>
@@ -1397,42 +1397,42 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-palghar-dahanu-shivsena-thackeray-group-office-bearers-from-palghar-dahanu-join-shivsena/922966/</t>
+          <t>https://www.saamana.com/wadigodri-crime-news-fake-cid-officers-stole-the-golden-ring/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/high-court-orders-deputy-chief-minister-eknath-shinde-mumbai-print-news-phm-00-5381244/</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-eknath-shinde-says-anand-dighe-never-sold-shiv-sena/923100/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/nashik-journalist-beating-dcm-eknath-shinde-speaks-with-injured-journalist-kiran-tajane-via-video-call-1497047.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/local-elections-mahayuti-will-win-in-the-local-self-government-elections-eknath-shinde-is-confident/922171/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/withdrew-the-rs-2-5-crore-fund-given-for-sewage-plant-and-drainage-because-former-corporator-deepmala-badhe-belonged-to-the-thackeray-group/922264/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/thane/thane-eknath-shinde-palghar-dahanu-shivsena-thackeray-group-office-bearers-from-palghar-dahanu-join-shivsena/922966/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/explainer-a-test-of-mahayuti-in-bmc-elections-shiv-sena-bjp-tug-of-war-over-91-seats-article-152842707</t>
+          <t>https://marathi.abplive.com/news/pune/siddharth-shinde-supreme-court-lawyer-passed-away-at-delhi-1384433</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/india-news/bihar-assembly-election-amit-shah-meets-bjp-workers-gives-60-days-plan-ahead-of-poll/articleshow/123995857.cms</t>
+          <t>https://marathi.timesnownews.com/maharashtra/explainer-a-test-of-mahayuti-in-bmc-elections-shiv-sena-bjp-tug-of-war-over-91-seats-article-152842707</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ministers-dispute-court-case-highlights-rift-in-ruling-coalition-bjp-minister-ganesh-naik-public-hearing-spark-conflict-with-dcm-shinde-1496585.html</t>
+          <t>https://maharashtratimes.com/video/mt-originals/ghodbunder-residents-anger-eknath-shindes-big-decision-these-vehicles-are-not-allowed-in-thane/videoshow/123919177.cms</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-20-september-2025-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://marathi.abplive.com/news/thane/thane-tembhi-naka-devi-festival-shiv-sena-eknath-shinde-vs-rajan-vichare-dispute-anand-dighe-marathi-news-1386015</t>
         </is>
       </c>
     </row>
@@ -1474,14 +1474,14 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-beed-floods-airlift-rescue-operation-eknath-shinde-suresh-dhas-1493005.html</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-20-september-2025-jayant-patil-gopichand-padalkar-controversy-rahul-gandhi-election-commission-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/eknath-shinde-daytime-heavy-vehicle-ban-in-ghodbandar-thane-to-badlapur-until-october-2-sud-02-5381060/</t>
+          <t>https://marathi.abplive.com/news/mumbai/sanjay-raut-statement-on-anand-dighe-thane-balasaheb-thackeray-photo-advertise-shivsena-maharashtra-marathi-news-1385015</t>
         </is>
       </c>
     </row>
@@ -1495,189 +1495,189 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/thane-metro-4-and-4a-span-35-km-with-32-stations-trial-run-inspected-by-devendra-fadnavis-and-eknath-shinde-full-details-in-marathi-article-152872624</t>
+          <t>https://www.saamana.com/eknath-shinde-x-account-hacked-hackers-post-pakistan-and-turkey-flag-saamana-online-news/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/thane/sanajy-raut-questions-eknath-shinde-banner-placing-anand-dighe-photo-protest-against-sanjay-raut-in-thane-994107.html</t>
+          <t>https://www.lokmat.com/mumbai/an-elected-mla-gets-rs-2-crore-but-i-get-rs-20-crore-even-though-i-am-not-an-mla-sada-saravankar-controversial-statement-a-a629/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/eknath-shinde-took-a-swipe-at-his-opponents-says-they-feel-depressed-by-farming-1279260-2025-09-18</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/breaking-news-today-21st-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-ahmedabad-bullet-train-mega-block-sunday/liveblog/124023319.cms</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-dy-cm-eknath-shindes-x-account-hacked/2934860</t>
+          <t>https://marathi.ndtv.com/videos/thane-ghodbunder-road-traffic-jaam-controversy-997251</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/after-successful-metro-lines-4-and-4a-trial-run-cm-fadnavis-says-all-phases-to-open-by-end-of-2026-23595263</t>
+          <t>https://www.saamana.com/sanjay-raut-criticized-eknath-shinde-and-pratap-sarnaik-over-anand-dighe/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/uddhav-thackeray-led-shiv-sena-leader-ayodhya-poul-patil-received-call-from-eknath-shinde-office-call-recording-goes-viral/videoshow/123934054.cms</t>
+          <t>https://www.kisantak.in/politics/story/eknath-shinde-took-a-swipe-at-his-opponents-says-they-feel-depressed-by-farming-1279260-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/maharashtra-mahayuti-alliance-ncp-bjp-shiv-sena-ajit-pawar-said-in-chintan-shivir-thank-pm-modi-cm-devendra-fadnavis-they-showed-big-heart-b507/</t>
+          <t>https://www.thejbt.com/india/maharashtra-deputy-cm-eknath-shinde-s-x-account-hacked-hackers-posted-flags-of-pakistan-and-t%C3%BCrkiye-news-295659</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/eknath-shinde-mla-aamshya-padvi-tribal-reservation-opposition-abuses-protest-dhangar-banjara-controversy-gs97</t>
+          <t>https://www.marathiebatmya.com/political/dy-cm-eknath-shinde-visits-the-state-emergency-operations-center/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/thane-ghodbunder-road-traffic-jaam-controversy-997251</t>
+          <t>https://www.dainikprabhat.com/eknath-shindes-political-game-will-fail-this-leader-warns-of-being-dragged-directly-to-court/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-pm-modi-birthday-eknath-shinde-s-leader-of-the-world-tribute-article-in-loksatta-saamana-omits-ad-1384700</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/shinde-reviewed-the-flood-situation-in-marathwada-125092200058_1.html</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-thane-navratri-deputy-cm-eknath-shinde-attends-devi-arrival-procession-at-tembhinaka-traditional-festivities-begin-1386020</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/eknath-shindes-bold-warning-to-ministers/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ministers-warned-maharashtra-deputy-cms-ajit-pawar-and-eknath-shinde-express-anger-over-ministerial-inefficiency-neglect-of-party-work-and-janata-darbar-1386067</t>
+          <t>https://www.marathi.hindusthanpost.com/social/eknath-shinde-shindes-midnight-plan-in-thane-a-big-relief-for-citizens/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/gadchiroli-news-merger-week-in-maoist-affected-areas-high-alert-issued-in-dandakarna-marathi-news-1075805.html</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/thane-city-challenge-to-eknath-shinde-in-the-fort-itself-bjp-leader-ganesh-naiks-janata-darbar-for-the-third-consecutive-time/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-on-eknath-shinde-maharashtra-ahmedabad-bullet-train-anand-dighe-3015725</t>
+          <t>https://www.timemaharashtra.com/maharashtra/dcm-eknath-shinde-directs-to-airlift-citizens-stranded-due-to-floods-in-ashti-taluka/132516/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-15-september-2025-zp-presidentship-reservation-nepal-violence-maratha-obc-reservation-manoj-jarange-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://www.dainikprabhat.com/an-unknown-person-threw-red-paint-on-the-statue-of-late-meenatai-thackeray-thackeray-group-is-aggressive/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
+          <t>https://www.ptinews.com/story/national/full-page-newspaper-ads-and-slew-of-initiatives-shiv-sena-goes-all-out-to-celebrate-pms-birthday/2925344</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-15-september-2025-3482219.html</t>
+          <t>https://www.aninews.in/news/national/general-news/gst-reforms-a-diwali-dhamaka-will-boost-consumption-and-employment-eknath-shinde20250922072527</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/shiv-sena-ubt-mp-sanjay-raut-says-many-mlas-because-of-vote-chori-in-maharashtra-201758358063004.html</t>
+          <t>https://www.newsband.in/article_detail/acharyadevvrattakes-oath-as-maharashtras-22nd-governor</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/thane-metro-trial-run-live-updates-mumbai-metro-line-4-news-cadbury-junction-to-gaumukh-thane-news-9320048</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-shiv-sena-leaders-speech-adds-fuel-to-accusations-of-biased-allocation-of-funds-23595109</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
+          <t>https://thenewsmill.com/2025/09/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://nagalandpost.com/bmc-polls-50-50-seats-for-sena-ubt-mns-in-mumbai-strongholds/</t>
+          <t>https://www.lokshakti.in/india/maharashtra-deputy-cm-eknath-shindes-x-account-hacked/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/the-chronological-formation-and-political-evolution-of-maharashtra.html</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/uddhav-thackeray-led-shiv-sena-leader-ayodhya-poul-patil-received-call-from-eknath-shinde-office-call-recording-goes-viral/videoshow/123934054.cms</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/shiv-sena-ubt-mns-bjp-raj-thackeray-uddhav-thackeray-devendra-fadnavis-unite-against-shiv-sena-eknath-shinde-for-thane-sporting-committee-election/articleshow/123938834.cms</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-bmc-election-uddhav-thackeray-and-raj-thackeray-led-shiv-sena-and-mns-alliance-final-know-seat-sharing-formula-against-mahayuti/articleshow/124037610.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/eknath-shinde-mla-aamshya-padvi-tribal-reservation-opposition-abuses-protest-dhangar-banjara-controversy-gs97</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/sitting-mlas-receive-rs-2-crore-from-maharashtra-govt-i-am-ex-mla-but-got-rs-20-crore-shiv-sena-leader-sarvankar-from-mumbai/articleshow/124029409.cms</t>
+          <t>https://marathi.ndtv.com/videos/eknath-shinde-shiv-sena-holds-important-meeting-regarding-dussehra-gathering-today-996478</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/meenatai-thackeray-statue-smeared-with-red-paint-1-held-101758136336233.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-almatti-dam-height-increase-maharashtra-to-move-supreme-court-over-karnataka-s-decision-raising-flood-risk-for-sangli-kolhapur-shiv-sena-mobilizes-in-sambhaji-nagar-1384708</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/ptiprnews/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-3/921531/</t>
         </is>
       </c>
     </row>
@@ -1691,1169 +1691,1169 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-decision-taken-i.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-govt-fadnavis-cabinet-approves-8-major-decisions-including-expressway-and-new-policies-nck90</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
+          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-15-september-2025-3482219.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/articleshow/123993653.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/maharashtra-cm-fadnavis-start-trial-run-of-metro-till-thane-at-mumbai-metro-line-4-4a-pm-modi-inaugurate-fully-completed-metro-3-aqua-line-on-september-30-know-all/articleshow/124043749.cms</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-19-political-news-in-marathi-940384</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://politalks.news/political-temperature-rises-in-maharashtra-ncp-chief-ajit-pawar-preparing-to-break-away-from-the-mahayuti</t>
+          <t>https://www.lokmatnews.in/india/up-politics-swami-prasad-wandering-alone-will-again-seek-refuge-in-mayawati-b628/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/pm-modi-turns-75-highlights-of-initiatives-launched-by-bjp-events-held-in-several-states/articleshow/123949298.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/shiv-sena-ubt-mns-bjp-raj-thackeray-uddhav-thackeray-devendra-fadnavis-unite-against-shiv-sena-eknath-shinde-for-thane-sporting-committee-election/articleshow/123938834.cms</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ajit-pawars-absence-at-key-guv-events-raises-eyebrows/articleshow/124030467.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-bmc-election-uddhav-thackeray-and-raj-thackeray-led-shiv-sena-and-mns-alliance-final-know-seat-sharing-formula-against-mahayuti/articleshow/124037610.cms</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/bmc-election-2025-shivsena-ubt-mns-raj-thackeray-seat-sharing-formula-96240</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/raj-thackerays-cartoon-targets-amit-shah-son-over-indo-pak-match/article70061713.ece</t>
+          <t>https://www.jansatta.com/national/current-mlas-get-rs-2-crore-and-i-get-rs-20-crore-big-claim-by-former-shiv-sena-mla-sada-sarvankar/4153263/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/paint-thrown-at-statue-of-bal-thackerays-wife-meenatai-in-mumbai/article70062302.ece</t>
+          <t>https://www.amarujala.com/india-news/maharastra-paint-thrown-on-statue-of-meenatai-thackeray-at-mumbai-shivaji-park-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/uddhav-thackeray-mother-meenatai-statue-colour-thrown-accused-upendra-pawaskar-held-19954266</t>
+          <t>https://hindi.oneindia.com/news/india/shiv-sena-celebrates-pm-narendra-modi-birthday-initiatives-011-1388481.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-sanjay-raut-supports-rahul-gandhi-saying-that-90-of-the-mahayuti-mlas-in-maharashtra-won-through-vote-theft/articleshow/124015667.cms</t>
+          <t>https://hindi.theprint.in/india/shiv-sena-workers-protest-against-rauts-remarks-about-dighe/870443/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-22-political-news-in-marathi-941153</t>
+          <t>https://www.abplive.com/states/maharashtra/shiv-sena-leader-ex-mla-sada-sarvankar-claims-20-crore-fund-dispute-sparks-political-stir-3016545</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-3/921531/</t>
+          <t>https://hindi.theprint.in/india/meenatai-thackerays-statue-defaced-at-mumbais-shivaji-park/869722/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-21-september-2025-india-vs-pakistan-%E2%80%93-asia-cup-maharashtra-politics-national-international-live-update-in-marathi-940858</t>
+          <t>https://www.lokmatnews.in/blog/india/bjp-shivsena-ncp-congress-local-body-elections-your-bow-and-arrow-but-target-is-ours-drawing-dividing-line-blog-amitabh-srivastava-b507/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
+          <t>https://www.amarujala.com/india-news/uddhav-targets-bjp-over-india-pakistan-cricket-match-in-asia-cup-maharashtra-debt-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-17-political-news-in-marathi-939849</t>
+          <t>https://marathi.abplive.com/news/politics/sada-saravankar-statement-of-mla-fund-mahim-thackeray-group-mahesh-sawant-counterattack-mla-gets-rs-2-crore-but-i-get-rs-20-crore-when-i-am-not-an-mla-1385728</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-14-political-news-in-marathi-939050</t>
+          <t>https://mradubhashi.com/news.php?id=despite-being-balasahebs-dear-associate-dighe-was-not-even-the-deputy-leader-of-the-party-577519</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://www.cnbctv18.com/infrastructure/pm-modi-to-inaugurate-mumbai-metro-3-on-september-30-says-devendra-fadnavis-19677024.htm</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-bmc-election-latest-update-mumbai-pune-rain-weather-today-devendra-fadnavis-on-uddhav-thackeray-shivsena-news-scj-81-5380824/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-decision-taken-i.html</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/dadar-shivaji-park-meenatai-thackeray-statue-red-color-thrown-mumbai-crime/articleshow/123936431.cms</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/fadnavis-is-an-uncivilized-chief-minister-sapkal-criticizes-fadnavis-996634</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/ncp-still-in-mahayuti-due-to-mutual-respect-commitment-to-maharashtras-progress-ajit-pawar/articleshow/123993653.cms</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-pm-narendra-modi-birthday-bmc-election-latest-update-mumbai-pune-rain-weather-today-devendra-fadnavis-on-uddhav-thackeray-shivsena-breaking-news-rak-94-5377898/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/breaking-news-today-live-updates-20-sept-maharashtra-political-news-rain-updates-shinde-thackeray-ajit-pawar-sharad-pawar-mumbai-pm-modi-940635</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-navratri-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-monday-22-september-2025-1497734.html</t>
+          <t>https://politalks.news/political-temperature-rises-in-maharashtra-ncp-chief-ajit-pawar-preparing-to-break-away-from-the-mahayuti</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
+          <t>https://www.amarujala.com/india-news/modi-govt-gave-rs-21-000-cr-for-marathwada-rail-lines-rs-450-crore-came-during-upa-time-fadnavis-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/breaking-news-today-18-september-monsoon-maratha-reservation-obc-bmc-election-mumbai-local-train-weather-political-doctors-strike-tajya-batmya-in-marathi-940110</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/pm-modi-turns-75-highlights-of-initiatives-launched-by-bjp-events-held-in-several-states/articleshow/123949298.cms</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/nashik/shardiya-navratri-2025-praveen-togadias-big-statement-at-hindu-hunkar-sabha-said-no-entry-for-muslims-at-garba-places-96201</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ajit-pawars-absence-at-key-guv-events-raises-eyebrows/articleshow/124030467.cms</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-tejashwi-yadav-calls-cm-nitish-a-cheat-minister-makes-these-big-promises-to-the-public-2025-09-18</t>
+          <t>https://www.lokmattimes.com/business/tlooto-ai-highlights-academicgpt-at-startup-mahakumbh-2025-indias-largest-startup-and-innovation-event/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.republicbharat.com/pradhan-sevak/pm-modi-75th-birthday-today-bjp-seva-pakhwada-celebration-plan-congress-rahul-gandhi-trump-live-updates-live-news</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-16-17-september-live-updates-tejashwi-yadav-bihar-adhikar-yatra-election-pm-modi-rahul-gandi-supreme-court-sahastradhara-flood-waqf/4143389/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/technical-panel-approves-2-stps-along-indrayani-cm/articleshow/124005440.cms</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/cities/aaj-ka-mausam-22-september-2025-up-bihar-jharkhand-himachal-uttarakhand-other-states-in-india-monsoon-flood-cloudburst-barish-hogi-ya-nhi-aaj-ka-mausam-kaisa-rahega-purvanuman-news-live-today-liveblog-152869390</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/raj-thackerays-cartoon-targets-amit-shah-son-over-indo-pak-match/article70061713.ece</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/pm-modi-gave-the-mantra-of-swadeshi-to-the-people-from-madhya-pradesh-told-this-method-2025-09-17</t>
+          <t>https://timesofindia.indiatimes.com/india/bmc-polls-an-acid-test-for-us-uddhav-tells-party-workers/articleshow/123987657.cms</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-ajit-pawat-led-ncp-hold-rashtravadi-chintan-shivir-in-nagpur-on-sept-19-ahead-of-local-body-polls/articleshow/123980165.cms</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/paint-thrown-at-statue-of-bal-thackerays-wife-meenatai-in-mumbai/article70062302.ece</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/why-is-there-still-no-bjp-chief-minister-in-bihar-nitish-kumar-lalu-prasad-yadav-tejashwi-yadav-limited-grip-on-obc-voters-ebcs-mm76</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/mumbai-mina-thackeray-statue-defaced-shivaji-park-shiv-sena-protest-police-action-ntc-dskc-2335896-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%86%E0%A4%AE%E0%A4%9A%E0%A5%80-%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A5%80-%E0%A4%B8%E0%A4%9C%E0%A5%8D%E0%A4%9C/117544/</t>
+          <t>https://ndtv.in/maharashtra-news/bmc-election-strategy-in-place-what-will-be-the-seat-sharing-formula-between-the-shiv-sena-ubt-and-mns-9318835</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/how-the-bjp-alliance-won-maharashtra-101757921779535.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/uddhav-thackeray-told-party-workers-bmc-elections-are-a-litmus-test-for-us/articleshow/123989198.cms</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/supreme-court-local-body-polls-order-a-slap-on-govt-face-says-opposition-in-maharashtra/articleshow/123928457.cms</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-sanjay-raut-supports-rahul-gandhi-saying-that-90-of-the-mahayuti-mlas-in-maharashtra-won-through-vote-theft/articleshow/124015667.cms</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-gifts-namo-gardens-to-394-towns-on-pm-modis-75th-birthday-rs-394-crore-sanctioned/articleshow/123964170.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-22-political-news-in-marathi-941153</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/nanded-farmers-to-get-100-crop-loss-relief-553-crore-payout-begins-sep-22-minister/article70076412.ece</t>
+          <t>https://marathi.abplive.com/news/politics/shivsena-dasara-melava-shiv-sena-shinde-group-planning-finalized-special-responsibility-on-mumbai-mlas-and-newly-elected-department-heads-maharashtra-politics-marathi-news-1385340</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/tet-exam-applications-open-from-monday-mandatory-for-teachers-up-to-53-years/articleshow/123887331.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/ola-uber-rapido-get-provisional-licences-for-bike-taxi-services-in-mumbai/article70055523.ece</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-live-updates-21-september-2025-india-vs-pakistan-%E2%80%93-asia-cup-maharashtra-politics-national-international-live-update-in-marathi-940858</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/maharashtra-launches-namo-gardens-and-tourism-skill-programme-to-mark-pm-modis-75th-birthday/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-14-political-news-in-marathi-939050</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-18-political-news-in-marathi-940102</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/breaking-news-today-18-september-monsoon-maratha-reservation-obc-bmc-election-mumbai-local-train-weather-political-doctors-strike-tajya-batmya-in-marathi-940110</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://clarionindia.net/ahmednagar-railway-station-renamed-concern-over-erasure-of-muslim-legacy/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-17-political-news-in-marathi-939849</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharastra-paint-thrown-on-statue-of-meenatai-thackeray-at-mumbai-shivaji-park-2025-09-17</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-bmc-election-latest-update-mumbai-pune-rain-weather-today-devendra-fadnavis-on-uddhav-thackeray-shivsena-news-scj-81-5380824/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-18-september-2025-uddhav-thackeray-raj-thackeray-meenatai-statue-maharashtra-weather-mumbai-rains-maratha-obc-reservation-1384894</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/uddhav-targets-bjp-over-india-pakistan-cricket-match-in-asia-cup-maharashtra-debt-2025-09-16</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/government-should-take-decision-with-a-common-perspective-regarding-tet-for-teachers/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/dadar-shivaji-park-meenatai-thackeray-statue-red-color-thrown-mumbai-crime/articleshow/123936431.cms</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-date-extended-supreme-court-give-new-deadline-31st-january-2026-know-all/articleshow/123920003.cms</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-pm-narendra-modi-birthday-bmc-election-latest-update-mumbai-pune-rain-weather-today-devendra-fadnavis-on-uddhav-thackeray-shivsena-breaking-news-rak-94-5377898/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/prime-minister-narendra-modi-address-the-nation-live-today/4152510/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/breaking-news-today-live-updates-20-sept-maharashtra-political-news-rain-updates-shinde-thackeray-ajit-pawar-sharad-pawar-mumbai-pm-modi-940635</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/cpwd-floats-tender-to-install-bulletproof-glass-in-chambers-of-eam-foreign-secy-at-jn-bhawan-2025-09-16</t>
+          <t>https://www.mymahanagar.com/maharashtra/sanjay-raut-criticizes-devendra-fadnavis-eknath-shinde-and-ajit-pawar-after-maharashtra-faces-a-debt-burden-of-rs-8-55-lakh-crore/921949/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-pichhade-varg-ke-sarakaaree-chhaatraavaas-ke-vidyaarthiyon-ke-dainik-bhatte-mein-vrddhi-ko-manjooree-1187663</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-navratri-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-monday-22-september-2025-1497734.html</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/career/career-news/mahatet-exam-2025-mandatory-exam-confusion-for-senior-teachers-application-process-begins-from-15-september/articleshow/123893618.cms</t>
+          <t>https://marathi.abplive.com/news/politics/mns-leader-sandeep-deshpande-troll-by-bjp-over-induri-chaat-dadar-hotel-also-dragged-raj-thackeray-into-controversy-mumbai-maharashtra-politics-marathi-news-1385397</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/teacher-mlas-demand-reconsideration-of-tet-mandatory-decision-in-maharashtra-maharashtra-news-mhs25091904556</t>
+          <t>https://www.marathijagran.com/maharashtra/nashik/shardiya-navratri-2025-praveen-togadias-big-statement-at-hindu-hunkar-sabha-said-no-entry-for-muslims-at-garba-places-96201</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/attorney-general-birendra-saraf-resigns/117476/</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-tejashwi-yadav-calls-cm-nitish-a-cheat-minister-makes-these-big-promises-to-the-public-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/vhp-s-hindu-only-diktat-for-garba-open-invitation-for-violence-ramdas-athawale-2025-09-21</t>
+          <t>https://www.lokmatnews.in/spirituality/aaj-ka-panchang-18-sepember-2025-know-from-when-to-when-is-the-time-of-rahukaal-and-abhijeet-muhurta-today-b628/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/mumbai-metro/video/mumbai-metro-ameet-satam-controversial-statement-bmc-election-frvd-2335000-2025-09-17</t>
+          <t>https://www.republicbharat.com/pradhan-sevak/pm-modi-75th-birthday-today-bjp-seva-pakhwada-celebration-plan-congress-rahul-gandhi-trump-live-updates-live-news</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/breaking-news-today-21st-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-ahmedabad-bullet-train-mega-block-sunday/liveblog/124023319.cms</t>
+          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-16-17-september-live-updates-tejashwi-yadav-bihar-adhikar-yatra-election-pm-modi-rahul-gandi-supreme-court-sahastradhara-flood-waqf/4143389/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/pune-news/maharashtra-cm-devendra-fadnavis-talk-on-obc-reservation/articleshow/123889715.cms</t>
+          <t>https://www.timesnowhindi.com/cities/aaj-ka-mausam-22-september-2025-up-bihar-jharkhand-himachal-uttarakhand-other-states-in-india-monsoon-flood-cloudburst-barish-hogi-ya-nhi-aaj-ka-mausam-kaisa-rahega-purvanuman-news-live-today-liveblog-152869390</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-ajit-pawat-led-ncp-hold-rashtravadi-chintan-shivir-in-nagpur-on-sept-19-ahead-of-local-body-polls/articleshow/123980165.cms</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/i-repeat-rahul-gandhis-weak-pm-jibe-after-trump-imposes-100000-fee-on-h-1b-visas-reshares-old-post/articleshow/124012869.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/navi-mumbai-city-petition-filed-in-janata-darbar-against-minister-ganesh-naik-by-kishore-patkar/922934/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/world/us/greatest-evangelist-for-american-liberty-donald-trump-pays-tribute-to-charlie-kirk-calls-him-immortal/articleshow/124034943.cms</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/why-is-there-still-no-bjp-chief-minister-in-bihar-nitish-kumar-lalu-prasad-yadav-tejashwi-yadav-limited-grip-on-obc-voters-ebcs-mm76</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/Tiruchirapalli/tamil-nadu-teachers-form-council-to-challenge-supreme-courts-ruling-on-eligibility-test/article70077321.ece</t>
+          <t>https://marathi.abplive.com/news/maharashtra/marathwada-cloudburst-like-rain-overnight-deluge-submerges-roads-cuts-off-villages-1385939</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/tariffs-a-mistake-bolton-urges-india-us-talks-slams-donald-trumps-incoherent-approach/articleshow/123948590.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/how-the-bjp-alliance-won-maharashtra-101757921779535.html</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-police-restrict-heavy-truck-movement-for-eighteen-hours-daily-to-ease-traffic-congestion/articleshow/123927129.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/supreme-court-local-body-polls-order-a-slap-on-govt-face-says-opposition-in-maharashtra/articleshow/123928457.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/video/mt-originals/ghodbunder-residents-anger-eknath-shindes-big-decision-these-vehicles-are-not-allowed-in-thane/videoshow/123919177.cms</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/maharashtra-signs-9-mous-worth-rs-81000-crore-industrial-projects-207559</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-municipal-election-2025-mns-district-chief-raju-dindorle-will-join-bjp-mm76-rg93</t>
+          <t>https://www.thehindu.com/news/international/trump-administration-cancels-us-hunger-survey/article70076256.ece</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-gifts-namo-gardens-to-394-towns-on-pm-modis-75th-birthday-rs-394-crore-sanctioned/articleshow/123964170.cms</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-1384548</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/nanded-farmers-to-get-100-crop-loss-relief-553-crore-payout-begins-sep-22-minister/article70076412.ece</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-indrayani-river-rejuvenation-project-gets-green-signal-from-state-technical-committee/</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-14-september-2025-asia-cup-cricket-hockey-pakistan-china-pm-modi-rain-alert-trump-israel-ukraine-russia-gaza-war-bjp-congress/liveblog/123877354.cms</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/technical-panel-approves-2-stps-along-indrayani-cm/articleshow/124005440.cms</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/maharashtra-ladki-bahin-yojana-ekyc-mandatory-beneficiaries-207500</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/nashik-zilla-parishad-to-send-students-from-first-batch-of-super-50-to-nasa-for-educational-trip/articleshow/124003718.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/tet-exam-applications-open-from-monday-mandatory-for-teachers-up-to-53-years/articleshow/123887331.cms</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://joindia.co.in/news/maharashtra-gets-new-governor-acharya-devvrat-takes-charge-as-the-22nd-governor/</t>
+          <t>https://lawchakra.in/legal-updates/maharashtra-advocate-birendra-resigns/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://curlytales.com/india/trending/what-are-namo-gardens-heres-all-about-eknath-shindes-green-gift-on-pm-modis-birthday/</t>
+          <t>https://thenewsmill.com/2025/09/maharashtra-cm-devendra-fadnavis-dy-cm-eknath-shinde-flag-off-trial-run-of-metro-line-4-4a-in-thane/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
+          <t>https://clarionindia.net/ahmednagar-railway-station-renamed-concern-over-erasure-of-muslim-legacy/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/tamil-nadu/state-floats-tender-to-prepare-master-plan-for-a-global-city/article70062521.ece</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-date-extended-supreme-court-give-new-deadline-31st-january-2026-know-all/articleshow/123920003.cms</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3635550-metro-rail-lines-promise-to-ease-mumbais-traffic-woes</t>
+          <t>https://www.amarujala.com/india-news/vhp-s-hindu-only-diktat-for-garba-open-invitation-for-violence-ramdas-athawale-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/mumbai-news/mmrda-temporarily-suspends-monorail-services-in-mumbai/articleshow/124009977.cms</t>
+          <t>https://mandalnews.com/amravati/government-should-take-decision-with-a-common-perspective-regarding-tet-for-teachers/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-71735/</t>
+          <t>https://www.jansatta.com/national/prime-minister-narendra-modi-address-the-nation-live-today/4152510/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/maharashtra-ladki-bahin-yojana-ekyc-mandatory-beneficiaries-207500</t>
+          <t>https://maharashtratimes.com/career/career-news/mahatet-exam-2025-mandatory-exam-confusion-for-senior-teachers-application-process-begins-from-15-september/articleshow/123893618.cms</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/fir-filed-against-tejashwi-yadav-india-bloc-leaders-in-alleged-welfare-scheme-fraud-case-in-bihar-darbhanga-enn25091601745</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-government-will-announce-golden-data-bogus-beneficiaries-will-be-identified-what-is-golden-data-marathi-news-1385196</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/no-new-proposals-from-marathwada/</t>
+          <t>https://thebharatnow.in/national/ahmednagar-railway-station-renamed-now-it-will-be-known-as-ahilyanagar/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/mmrda-temporarily-suspends-monorail-services-in-mumbai/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/breaking-live-updates-22nd-september-marathi-news-maharashtra-weather-rain-alert-navratri-2025-ajit-pawar-devendra-fadnavis/liveblog/124035851.cms</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-makes-e-kyc-mandatory-for-ladki-bahin-scheme-beneficiaries-sets-2-month-deadline-23594786</t>
+          <t>https://hindi.latestly.com/india/education/latest-and-important-news-of-22nd-september-for-school-assembly-read-the-latest-updates-related-to-national-international-and-sports-2759750.html</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/ladki-behna-e-kyc-mandatory-maharashtra-mukhyamantri-meri-ladli-behen-scheme-19958911</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maha-govt-ensures-transparency-in-ladki-bahin-yojana-asks-beneficiaries-to-complete-e-kyc-process-in-two-months-3735616</t>
+          <t>https://timesofindia.indiatimes.com/india/tariffs-a-mistake-bolton-urges-india-us-talks-slams-donald-trumps-incoherent-approach/articleshow/123948590.cms</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/e-kyc-made-mandatory-for-beneficiaries-of-the-chief-ministers-majhi-laadki-behan-scheme-1360239.html</t>
+          <t>https://timesofindia.indiatimes.com/india/i-repeat-rahul-gandhis-weak-pm-jibe-after-trump-imposes-100000-fee-on-h-1b-visas-reshares-old-post/articleshow/124012869.cms</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-aditi-tatkare-important-explanation-about-ladki-bahin-yojana/articleshow/123977249.cms</t>
+          <t>https://timesofindia.indiatimes.com/sports/cricket/asia-cup/handshake-row-takes-ugly-turn-as-pakistan-threaten-to-withdraw-from-asia-cup-2025/articleshow/123900093.cms</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/business/mukhyamantri-ladki-bahin-yojana-ekyc-compulsory-for-all-check-how-complete-this-process-1385224</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/photos/ladki-bahin-yojana-ekyc-kashi-karaychi-rule-change-by-maharashtra-government-documents-application-process-deadline-ifnormation-every-details-you-need-to-know/940522</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-municipal-election-2025-mns-district-chief-raju-dindorle-will-join-bjp-mm76-rg93</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-cabinet-meeting-maharashtra-animation-vfx-gaming-policy-announced-maharashtra-government-has-taken-8-important-decisions-1384548</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/trial-run-held-for-metro-lines-4-and-4a-in-thane-project-to-cut-travel-time-significantly-101758530168095.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/eight-important-decisions-taken-in-cabinet-meeting-priority-given-to-industrial-sectors-in-the-state-new-momen.html</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-maja-top-10-headlines-16-september-2025-supreme-court-mahapalika-election-rain-mumbai-marathwada-1384618</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/state-news/thane-metro-begins-trial-run-after-20-year-wait-19966553</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/mumbai-metro-4-thane-metro-trial-run-between-gaimukh-to-cadbury-junction-today-22-september-station-list-9319633</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/nashik-zilla-parishad-to-send-students-from-first-batch-of-super-50-to-nasa-for-educational-trip/articleshow/124003718.cms</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/thane-thane-metro-stations-the-35-km-long-metro-will-make-the-journey-of-thane-residents-easier-thane-news-1385989</t>
+          <t>https://www.thehindu.com/news/national/tamil-nadu/state-floats-tender-to-prepare-master-plan-for-a-global-city/article70062521.ece</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/thane-gaimukh-to-wadala-metro-4-trial-today-read-its-route-and-other-details/articleshow/124037736.cms</t>
+          <t>https://travelbizmonitor.com/top-stories/pm-likely-to-inaugurate-navi-mumbai-international-airport-on-sept-30/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/hc-seeks-govt-s-stand-on-illegal-stay-on-demolition-by-dy-cm-101758137116362.html</t>
+          <t>https://sundayguardianlive.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-139969/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/press-release/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/2938489</t>
+          <t>https://m.economictimes.com/news/mumbai-news/mmrda-temporarily-suspends-monorail-services-in-mumbai/articleshow/124009977.cms</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/uttarakhand/uttarakhand-govt-to-buy-produce-from-apple-growers-in-disaster-hit-dharali/article70076273.ece</t>
+          <t>https://www.ptinews.com/press-release/naredco-maharashtra-announces-homethon-property-expo-2025-and-unveils-mr-homethon/2938489</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/revised-gr-will-reduce-farmers-compensation-by-40-say-activists/articleshow/124005535.cms</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/cm-devendra-fadnavis-dycm-ajit-pawar-to-inaugurate-beedahilyanagar-rail-line-on-marathwada-mukti-sangram-din</t>
+          <t>https://marathi.abplive.com/news/maharashtra/parashuram-economic-development-corporation-chairman-ministerial-status-to-ashish-damle-thane-news-1384578</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!politics/maharashtra-total-debt-of-rs-9-lakh-32-thousand-crores-ajit-pawars-clarification-mhs25091906423</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-government-makes-e-kyc-mandatory-for-ladki-bahin-beneficiaries-sets-two-month-deadline/article70068851.ece</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/world/us/charlie-kirk-assassination-did-tyler-robinson-confess-fbi-director-kash-patel-cites-dna-link-a-threatening-text/articleshow/123911719.cms</t>
+          <t>https://www.patrika.com/mumbai-news/ladki-behna-e-kyc-mandatory-maharashtra-mukhyamantri-meri-ladli-behen-scheme-19958911</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/sports/cricket/asia-cup/asia-cup-abhishek-sharma-haris-rauf-in-heated-face-off-during-ind-vs-pak-clash-watch/articleshow/124031346.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-aditi-tatkare-important-explanation-about-ladki-bahin-yojana/articleshow/123977249.cms</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/acharya-devvrat-appointed-as-new-governor-of-maharashtra-to-take-oath-on-monday-know-his-gujarat-connection/</t>
+          <t>https://marathi.abplive.com/business/mukhyamantri-ladki-bahin-yojana-ekyc-compulsory-for-all-check-how-complete-this-process-1385224</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
+          <t>https://www.tv9marathi.com/maharashtra/how-to-do-e-kyc-for-mazi-ladki-bahin-scheme-of-maharashtra-government-aditi-tatkare-given-information-1496902.html</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
+          <t>https://zeenews.india.com/marathi/photos/ladki-bahin-yojana-ekyc-kashi-karaychi-rule-change-by-maharashtra-government-documents-application-process-deadline-ifnormation-every-details-you-need-to-know/940522</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/breaking-live-updates-22nd-september-marathi-news-maharashtra-weather-rain-alert-navratri-2025-ajit-pawar-devendra-fadnavis/liveblog/124035851.cms</t>
+          <t>https://www.lokmat.com/maharashtra/majhi-ladki-bahin-yojana-beneficiary-women-do-e-kyc-compulsory-know-how-complete-this-step-by-step-process-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
+          <t>https://www.navarashtra.com/maharashtra/dont-worry-even-though-e-kyc-is-mandatory-follow-these-steps-and-get-your-ladki-bahin-yojana-kyc-done-995949.html</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/heavy-rains-in-marathwada-four-people-died-150-people-were-trapped-in-floods-in-dharashiv/924053/</t>
+          <t>https://prahaar.in/2025/09/20/women-who-steal-age-are-expelled-from-the-ladki-bahin-yojana/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bhubaneswar/odisha-sees-over-10-fold-increase-in-revenue-from-gutka-paan-masala-and-cigarette-sales/articleshow/124053527.cms</t>
+          <t>https://www.patrika.com/en/state-news/thane-metro-begins-trial-run-after-20-year-wait-19966553</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/elections/bihar-assembly/prashant-kishor-has-raised-hundreds-of-crores-of-rupees-through-shell-companies-alleges-bihar-bjp/article70075218.ece</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/journey-of-thanekars-will-be-comfortable-first-trial-run-of-thane-metro-line-4-will-be-held-96215</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/111-teachers-felicitated-with-krantijyoti-savitribai-phule-state-teacher-awards-101758565502417.html</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/thane-thane-metro-stations-the-35-km-long-metro-will-make-the-journey-of-thane-residents-easier-thane-news-1385989</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/acharya-devvrat-sworn-in-as-governor-of-maharashtra-reads-oath-in-sanskrit/</t>
+          <t>https://www.thehindu.com/news/national/uttarakhand/uttarakhand-govt-to-buy-produce-from-apple-growers-in-disaster-hit-dharali/article70076273.ece</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-assembly-election-2025-cm-nitish-eyes-the-lost-seats-of-paswan-and-kushwaha-2025-09-18</t>
+          <t>https://marathi.abplive.com/news/politics/sanjay-raut-on-maharashtra-debt-burden-slams-devendra-fadnavis-eknath-shinde-ajit-pawar-says-state-situation-is-similar-to-nepal-marathi-news-1384489</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/tejashwi-yadav-bihar-adhikar-yatra-tejashwi-yadav-afraid-of-rahul-gandhi-bihar-election-2025-2025-09-17</t>
+          <t>https://www.tv9marathi.com/videos/agriculture-minister-dattatray-bharne-big-announcement-government-to-compensate-farmers-before-diwali-2025-1498098.html</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/bihar-election-2025-rahul-gandhi-and-tejashwi-yadav-lalu-yadav-decide-on-seat-sharing-within-mahagathbandhan-2025-09-18</t>
+          <t>https://timesofindia.indiatimes.com/world/us/charlie-kirk-assassination-did-tyler-robinson-confess-fbi-director-kash-patel-cites-dna-link-a-threatening-text/articleshow/123911719.cms</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/chief-minister-bhagwant-mann-launched-mission-chadti-kala-for-flood-victims-in-punjab-made-this-appeal-to-t-2025-09-17</t>
+          <t>https://timesofindia.indiatimes.com/sports/cricket/asia-cup/asia-cup-abhishek-sharma-haris-rauf-in-heated-face-off-during-ind-vs-pak-clash-watch/articleshow/124031346.cms</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/disha-patni-house-firing-case-the-accused-of-firing-at-disha-patni-s-house-were-killed-adg-told-the-whole-st-2025-09-18</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-metro-4-4a-corridor-improves-transportation-reduce-congestion-on-gb-road-and-connectivity-in-thane-and-mumbai/articleshow/124029480.cms</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/acharya-devvrat-takes-oath-as-governor-of-maharashtra/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-fadnavis-flags-off-metro-4-trial-runs-in-thane-101758568924626.html</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/acharya-devvrat-is-the-new-governor-of-maharashtra-took-oath-in-the-presence-of-the-chief-minister.html</t>
+          <t>https://www.mypunepulse.com/acharya-devvrat-appointed-as-new-governor-of-maharashtra-to-take-oath-on-monday-know-his-gujarat-connection/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/bengali-navratra-2025-in-pune-artists-craft-goddess-idols-from-bengals-sacred-soil-maharashtra-news-mhs25092001990</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-updates-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-news-dcm-eknath-shinde-cm-devendra-fadnavis-deputy-dcm-ajit-pawar-shiv-sena-bjp-congress-ncp-n-4/921885/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/ministerial-status-to-the-chairman-of-parashuram-corporation/117448/</t>
+          <t>https://deshonnati.com/ahmednagar-railway-station-government-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/congress-doing-negative-politics-over-great-nicobar-project-environment-minister/article70067325.ece</t>
+          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/karnataka/bk-singh-to-head-sit-formed-to-probe-aland-voter-fraud-case/article70074360.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/bhubaneswar/odisha-sees-over-10-fold-increase-in-revenue-from-gutka-paan-masala-and-cigarette-sales/articleshow/124053527.cms</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/taken-nation-forward-in-last-11-years-eknath-shinde-extends-birthday-wishes-to-pm-modi20250917174418</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/world/australian-mp-tim-watts-meets-maharashtra-dy-cm-shinde-discusses-boosting-ties-in-agriculture-med-tech-education20250917002621-139969/</t>
+          <t>https://thenewsmill.com/2025/09/acharya-devvrat-sworn-in-as-governor-of-maharashtra-reads-oath-in-sanskrit/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3636158-metro-milestone-thane-moves-closer-to-seamless-connectivity</t>
+          <t>https://www.lokmatnews.in/spirituality/aaj-ka-panchang-17-sepember-2025-know-from-when-to-when-is-the-time-of-rahukaal-and-abhijeet-muhurta-today-b628/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://www.amarujala.com/video/india-news/bihar-assembly-election-2025-cm-nitish-eyes-the-lost-seats-of-paswan-and-kushwaha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/thane-metro-trial-run-hindi/</t>
+          <t>https://www.amarujala.com/video/india-news/tejashwi-yadav-bihar-adhikar-yatra-tejashwi-yadav-afraid-of-rahul-gandhi-bihar-election-2025-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/metro-line-connecting-thane-mumbai-be-operational-2026-end-says-cm-fadnavis-455400</t>
+          <t>https://www.amarujala.com/video/india-news/chief-minister-bhagwant-mann-launched-mission-chadti-kala-for-flood-victims-in-punjab-made-this-appeal-to-t-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/karnataka/congress-leaders-launch-campaign-alleging-vote-theft/article70080896.ece</t>
+          <t>https://www.amarujala.com/video/india-news/disha-patni-house-firing-case-the-accused-of-firing-at-disha-patni-s-house-were-killed-adg-told-the-whole-st-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-piyush-goyal-launches-swasth-nari-sashakt-parivar-campaign-in-mumbai/</t>
+          <t>https://dainikekmat.com/ministerial-status-to-the-chairman-of-parashuram-corporation/117448/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/business/india-business/ai-startup-krutrim-faces-reality-check/articleshow/123908669.cms</t>
+          <t>https://www.thehindu.com/news/national/congress-doing-negative-politics-over-great-nicobar-project-environment-minister/article70067325.ece</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/kumbh-mela-committee-accommodates-representatives-of-bjps-mahayuti-allies-ncp-shiv-sena/articleshow/124020480.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-shivaji-park-gymkhana-opens-its-doors-sachin-tendulkar-raj-thackeray-attend-inauguration-107467/6</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/opposition-targets-shiv-sena-over-mumbais-gb-hway-traffic-ahead-of-civic-polls/articleshow/124020437.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-markets-in-mumbai-jam-packed-as-shoppers-prepare-for-navratri-2025-107460/4</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-workers-burn-effigy-of-shiv-sena-ubt-mp-sanjay-raut-for-his-remark-about-anand-dighe/articleshow/123981706.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-mumbai-work-in-full-swing-at-jagannath-shankar-sheth-station-ahead-of-metro-line-3-launch-107456/6</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/paint-thrown-on-statue-of-meenatai-thackeray-at-mumbai-s-shivaji-park-101758093317894.html</t>
+          <t>https://dainikekmat.com/attorney-general-birendra-saraf-resigns/117476/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/replicas-diversity-mark-devi-durgeshwari-fest-in-thane</t>
+          <t>https://mumbaimirror.indiatimes.com/mumbai/hoarding-battle-betrays-a-deeper-rift-in-government/articleshow/123982977.html</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/current-mlas-get-rs-2-crore-and-i-get-rs-20-crore-big-claim-by-former-shiv-sena-mla-sada-sarvankar/4153263/</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/despite-not-being-an-mla-i-received-a-fund-of-rs-20-crore-shiv-sena-leader-sarwankar/871651/</t>
+          <t>https://metrorailtoday.com/news/mmrda-commences-trial-test-run-on-mumbai-metro-line-4</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/blog/india/bjp-shivsena-ncp-congress-local-body-elections-your-bow-and-arrow-but-target-is-ours-drawing-dividing-line-blog-amitabh-srivastava-b507/</t>
+          <t>https://thecsrjournal.in/thane-metro-trial-run-hindi/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/next-mumbai-mayor-will-be-from-maha-yuti-says-devendra-fadnavis-as-bjp-launches-campaign-for-bmc-polls-3730927</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pimpri-news-shiv-sena-ready-for-elections-avoid-factionalism-get-to-work-shrirang-barnes-instructions-to-office-bearers/</t>
+          <t>https://www.newsonair.gov.in/union-minister-piyush-goyal-launches-swasth-nari-sashakt-parivar-campaign-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/sudhir-mungantiwar_16.html</t>
+          <t>https://www.lokmattimes.com/mumbai/namo-yuva-yatra-milind-soman-flags-off-campaign-in-mumbai-says-theme-of-a-drug-free-india-is-very-important-watch-videos-a525/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/stocks/hudco-re-appoints-baldeo-purushartha-as-government-nominee-director/19487527</t>
+          <t>https://www.thehindu.com/news/national/karnataka/congress-leaders-launch-campaign-alleging-vote-theft/article70080896.ece</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/globe-nation/atlantic-journalist-claims-he-was-accidentally-sent-u-s-war-plans-trump-responds/11525/</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/kumbh-mela-committee-accommodates-representatives-of-bjps-mahayuti-allies-ncp-shiv-sena/articleshow/124020480.cms</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/cant-be-on-whims-delhi-hc-raps-centre-over-delay-in-kejriwal-house-allotment-calls-for-clear-policy/articleshow/123976159.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-workers-burn-effigy-of-shiv-sena-ubt-mp-sanjay-raut-for-his-remark-about-anand-dighe/articleshow/123981706.cms</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/thane-metro-line-4-train-run-conducted-successfully</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/opposition-targets-shiv-sena-over-mumbais-gb-hway-traffic-ahead-of-civic-polls/articleshow/124020437.cms</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/trial-run-of-metro-line-4-and-4a-conducted-in-thane/871907/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/iti-students-will-run-cleanliness-campaign-in-750-villages-special-campaign-by-minister-mangal-prabhat-lodha-on-pm-modis-birthday/articleshow/123915570.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-slams-sanjay-raut-and-gives-challenge-of-100-rupees/articleshow/123927800.cms</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/the-state-has-a-debt-of-rs-9-lakh-crores-development-of-the-state-is-stalled-deva-bhau-is-busy-in-advertising/</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/sudhir-mungantiwar_16.html</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
+          <t>https://scanx.trade/stock-market-news/stocks/hudco-re-appoints-baldeo-purushartha-as-government-nominee-director/19487527</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/arrangements-should-be-made-to-issue-all-relevant-permits-for-industries-in-a-single-application-chief-minister-fadnavis/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-devotees-gather-at-mount-mary-festival-to-honour-300-year-old-tradition-107376/3</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/jarange-plans-national-maratha-convention-in-delhi-hake-warns-of-obc-march-to-mumbai/articleshow/123952548.cms</t>
+          <t>https://timesofindia.indiatimes.com/india/cant-be-on-whims-delhi-hc-raps-centre-over-delay-in-kejriwal-house-allotment-calls-for-clear-policy/articleshow/123976159.cms</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maratha-quota-activist-manoj-jarange-patil-announce-chalo-delhi-program-after-mumbai-reservation-protest-know-all/articleshow/123982783.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/nashik-kumbh-mela-news-government-forms-committee-of-ministers-for-kumbh-mela-to-be-held-in-nashik-cm-devendra-fadnavis-girish-mahajan-dadabhuse-1385300</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/acharya-devvrat-oath-maharashtra-governor-10250775/</t>
+          <t>https://www.newsband.in/article_detail/thane-metro-line-4-train-run-conducted-successfully</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-news-live-updates-14-september-2025-asia-cup-cricket-hockey-pakistan-china-pm-modi-rain-alert-trump-israel-ukraine-russia-gaza-war-bjp-congress/liveblog/123877354.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/iti-students-will-run-cleanliness-campaign-in-750-villages-special-campaign-by-minister-mangal-prabhat-lodha-on-pm-modis-birthday/articleshow/123915570.cms</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/eknath-shinde-s-x-account-hacked-images-of-pakistan-turkiye-s-flags-posted-1801504</t>
+          <t>https://www.hindisaamana.com/the-state-has-a-debt-of-rs-9-lakh-crores-development-of-the-state-is-stalled-deva-bhau-is-busy-in-advertising/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/sport/cricket/former-delhi-captain-mithun-manhas-set-to-be-next-bcci-president/article70075244.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/jarange-plans-national-maratha-convention-in-delhi-hake-warns-of-obc-march-to-mumbai/articleshow/123952548.cms</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/transporters-cite-increased-costs-supply-disruptions-want-new-traffic-curbs-lifted/articleshow/124005110.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maratha-quota-activist-manoj-jarange-patil-announce-chalo-delhi-program-after-mumbai-reservation-protest-know-all/articleshow/123982783.cms</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/trial-runs-on-metro-4s-cadbury-junction-gaimukh-stretch-to-commence-monday-mumbai-metropolitan-region-development-authority-officials-say-corridor-on-track-for-year-end-operations/articleshow/124001171.cms</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/ncpap-hints-at-fighting-independently-in-the-upcoming-local-body-elections-in-maharashtra/article70073542.ece</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/sanjay-raut-statement-on-anand-dighe-thane-balasaheb-thackeray-photo-advertise-shivsena-maharashtra-marathi-news-1385015</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/transporters-cite-increased-costs-supply-disruptions-want-new-traffic-curbs-lifted/articleshow/124005110.cms</t>
         </is>
       </c>
     </row>
@@ -2861,13 +2861,6 @@
       <c r="A348" t="inlineStr">
         <is>
           <t>https://marathi.webdunia.com/article/regional-marathi-news/violence-escalates-in-maratha-obc-reservation-dispute-obc-leader-s-car-set-on-fire-in-jalna-125092300009_1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/thane-metro-4-4a-corridor-improves-transportation-reduce-congestion-on-gb-road-and-connectivity-in-thane-and-mumbai/articleshow/124029480.cms</t>
         </is>
       </c>
     </row>
